--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="513">
   <si>
     <t>MICROEMPRESA</t>
   </si>
@@ -1586,12 +1586,33 @@
   <si>
     <t>48+000</t>
   </si>
+  <si>
+    <t>7, 10, 3437, 3447, 3448, 3449, 3450, 3451, 3452, 3453, 3468, 3483, 3486, 3488, 3505, 3512, 3517, 3526, 3531, 3539, 3541, 3543, 3547, 3549, 3553, 3560, 3565, 3566, 3567, 3579, 3583, 3584, 3590, 3594, 3595, 3599, 3604, 3605, 3607, 3608, 3612, 3621, 3629, 3638, 3639, 3643, 3647, 3662, 3666</t>
+  </si>
+  <si>
+    <t>1746, 1790, 1799, 1810, 1816, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2045, 2054, 2059, 2133, 2166, 2193, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2359, 2364, 2372, 2382, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2649, 2671, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
+  </si>
+  <si>
+    <t>3, 4, 15, 304, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3912, 3914, 3915, 3916, 3917, 3918, 3920, 3922, 3923, 3924, 3925, 3926, 3928, 3929, 3931, 3932, 3933, 3934, 3936, 3937, 3938, 3939, 3940, 3943, 3944, 3945, 3946, 3947, 3948, 3951, 3952, 3953, 3954, 3958, 3961, 3962, 3963, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4013, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4201, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
+  </si>
+  <si>
+    <t>307, 3861, 3878, 3880, 3883, 3888, 3895, 3901, 3909, 3913, 3942, 3979, 3980, 3985, 3992, 4018, 4034, 4097, 4164, 4332</t>
+  </si>
+  <si>
+    <t>333, 335, 4238, 4240, 4269, 4272, 4274, 4289, 4295, 4302, 4303, 4311, 4312, 4316, 4327, 4330, 4336, 4345, 4350, 4353, 4370, 4375, 4387, 4393, 4394, 4395, 4400, 4406, 4421, 4422, 4433, 4435, 4436, 4437, 4440, 4443, 4444, 4449, 4454, 4456, 4458, 4459, 4460, 4464, 4466, 4467, 4471, 4474, 4478, 4481, 4484, 4487, 4491, 4492, 4498, 4508, 4510, 4522, 4524, 4531, 4533, 4536, 4540, 4544, 4545, 4548, 4549, 4552</t>
+  </si>
+  <si>
+    <t>288, 2173, 2181, 2206, 2276, 2281, 2288, 2305, 2317, 2332, 2354, 2361, 2367, 2368, 2385, 2389, 2395, 2408, 2428, 2445, 2452, 2468, 2469, 2475, 2484, 2495, 2577, 2590, 2597, 2605, 2617, 2628, 2636, 2640, 2647, 2651, 2653, 2654, 2657, 2661, 2665, 2677, 2692, 2701, 2714, 2733, 2751, 2753, 2755, 2759, 2766, 2771, 2772, 2780, 2784, 2791, 2798, 2806, 2811, 2819, 2835, 2838, 2846, 2850, 2852, 2857, 2861, 2866, 2872, 2876, 2880, 2883, 2887, 2889, 2890, 2894, 2898, 2916, 2941, 2951, 2966, 2972, 2993, 3031, 3035, 3044, 3064, 3081, 3097, 3104, 3108, 3112</t>
+  </si>
+  <si>
+    <t>67, 77, 78, 172, 174, 182, 186, 188, 189, 785, 790, 808, 825, 848, 850, 852, 853, 855, 856, 873, 875, 878, 884, 885, 889, 893, 897, 899, 900, 904, 912, 913, 922, 923, 925, 935, 942, 945, 947, 948, 950, 954, 955, 957, 958, 959, 962, 964, 966, 967, 968, 969, 971, 972, 974, 975, 977, 979, 981, 982, 984, 985, 986, 989, 991, 995, 997, 998, 1001, 1002, 1010, 1011, 1012, 1016, 1019, 1020, 1024, 1025, 1026, 1028, 1031, 1032, 1036, 1037, 1039, 1040, 1041, 1042, 1044, 1045, 1047, 1048, 1049, 1051, 1053, 1055, 1056, 1058, 1059, 1060, 1062, 1064, 1065, 1066, 1067, 1069</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1662,8 +1683,21 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1694,8 +1728,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1746,11 +1786,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1944,17 +1999,54 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="674">
+  <dxfs count="676">
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -9759,7 +9851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q283"/>
+  <dimension ref="A1:Q314"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="53.42578125" style="8" customWidth="1"/>
@@ -9768,7 +9860,7 @@
     <col min="4" max="4" width="53.85546875" style="8" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" style="8" customWidth="1"/>
     <col min="6" max="6" width="41.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="43.85546875" style="76" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" style="75" customWidth="1"/>
     <col min="8" max="8" width="27.7109375" style="9" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="75" style="9" customWidth="1"/>
     <col min="10" max="10" width="46.7109375" style="9" customWidth="1"/>
@@ -16498,7 +16590,7 @@
       <c r="G267" s="70"/>
       <c r="H267" s="52"/>
       <c r="I267" s="62"/>
-      <c r="J267" s="52"/>
+      <c r="J267" s="76"/>
       <c r="K267" s="52"/>
       <c r="L267" s="52"/>
       <c r="M267" s="52"/>
@@ -16517,7 +16609,7 @@
       <c r="G268" s="74"/>
       <c r="H268" s="67"/>
       <c r="I268" s="67"/>
-      <c r="J268" s="67"/>
+      <c r="J268" s="76"/>
       <c r="K268" s="67"/>
       <c r="L268" s="67"/>
       <c r="M268" s="67"/>
@@ -16541,7 +16633,9 @@
       <c r="G269" s="74"/>
       <c r="H269" s="67"/>
       <c r="I269" s="67"/>
-      <c r="J269" s="67"/>
+      <c r="J269" s="78" t="s">
+        <v>506</v>
+      </c>
       <c r="K269" s="67"/>
       <c r="L269" s="67"/>
       <c r="M269" s="67"/>
@@ -16567,7 +16661,7 @@
       </c>
       <c r="H270" s="67"/>
       <c r="I270" s="67"/>
-      <c r="J270" s="67"/>
+      <c r="J270" s="76"/>
       <c r="K270" s="67"/>
       <c r="L270" s="67"/>
       <c r="M270" s="67"/>
@@ -16589,7 +16683,9 @@
       <c r="G271" s="74"/>
       <c r="H271" s="67"/>
       <c r="I271" s="67"/>
-      <c r="J271" s="67"/>
+      <c r="J271" s="78" t="s">
+        <v>507</v>
+      </c>
       <c r="K271" s="67"/>
       <c r="L271" s="67"/>
       <c r="M271" s="67"/>
@@ -16613,7 +16709,9 @@
       </c>
       <c r="H272" s="67"/>
       <c r="I272" s="67"/>
-      <c r="J272" s="67"/>
+      <c r="J272" s="78" t="s">
+        <v>508</v>
+      </c>
       <c r="K272" s="67"/>
       <c r="L272" s="67"/>
       <c r="M272" s="67"/>
@@ -16639,7 +16737,9 @@
       </c>
       <c r="H273" s="67"/>
       <c r="I273" s="67"/>
-      <c r="J273" s="67"/>
+      <c r="J273" s="78" t="s">
+        <v>509</v>
+      </c>
       <c r="K273" s="67"/>
       <c r="L273" s="67"/>
       <c r="M273" s="67"/>
@@ -16665,7 +16765,9 @@
       </c>
       <c r="H274" s="67"/>
       <c r="I274" s="67"/>
-      <c r="J274" s="67"/>
+      <c r="J274" s="78" t="s">
+        <v>510</v>
+      </c>
       <c r="K274" s="67"/>
       <c r="L274" s="67"/>
       <c r="M274" s="67"/>
@@ -16687,7 +16789,7 @@
       </c>
       <c r="H275" s="67"/>
       <c r="I275" s="67"/>
-      <c r="J275" s="67"/>
+      <c r="J275" s="77"/>
       <c r="K275" s="67"/>
       <c r="L275" s="67"/>
       <c r="M275" s="67"/>
@@ -16709,7 +16811,7 @@
       <c r="G276" s="74"/>
       <c r="H276" s="67"/>
       <c r="I276" s="67"/>
-      <c r="J276" s="67"/>
+      <c r="J276" s="77"/>
       <c r="K276" s="67"/>
       <c r="L276" s="67"/>
       <c r="M276" s="67"/>
@@ -16731,7 +16833,7 @@
       <c r="G277" s="74"/>
       <c r="H277" s="67"/>
       <c r="I277" s="67"/>
-      <c r="J277" s="67"/>
+      <c r="J277" s="77"/>
       <c r="K277" s="67"/>
       <c r="L277" s="67"/>
       <c r="M277" s="67"/>
@@ -16751,7 +16853,9 @@
       <c r="G278" s="74"/>
       <c r="H278" s="67"/>
       <c r="I278" s="67"/>
-      <c r="J278" s="67"/>
+      <c r="J278" s="78" t="s">
+        <v>511</v>
+      </c>
       <c r="K278" s="67"/>
       <c r="L278" s="67"/>
       <c r="M278" s="67"/>
@@ -16777,7 +16881,7 @@
       </c>
       <c r="H279" s="67"/>
       <c r="I279" s="67"/>
-      <c r="J279" s="67"/>
+      <c r="J279" s="77"/>
       <c r="K279" s="67"/>
       <c r="L279" s="67"/>
       <c r="M279" s="67"/>
@@ -16797,7 +16901,9 @@
       <c r="G280" s="74"/>
       <c r="H280" s="67"/>
       <c r="I280" s="67"/>
-      <c r="J280" s="67"/>
+      <c r="J280" s="78" t="s">
+        <v>512</v>
+      </c>
       <c r="K280" s="67"/>
       <c r="L280" s="67"/>
       <c r="M280" s="67"/>
@@ -16823,7 +16929,7 @@
       </c>
       <c r="H281" s="67"/>
       <c r="I281" s="67"/>
-      <c r="J281" s="67"/>
+      <c r="J281" s="79"/>
       <c r="K281" s="67"/>
       <c r="L281" s="67"/>
       <c r="M281" s="67"/>
@@ -16836,7 +16942,7 @@
       <c r="D282" s="66"/>
       <c r="E282" s="66"/>
       <c r="F282" s="66"/>
-      <c r="G282" s="75"/>
+      <c r="G282" s="80"/>
       <c r="H282" s="66"/>
       <c r="I282" s="66"/>
       <c r="J282" s="66"/>
@@ -16852,7 +16958,7 @@
       <c r="D283" s="66"/>
       <c r="E283" s="66"/>
       <c r="F283" s="66"/>
-      <c r="G283" s="75"/>
+      <c r="G283" s="80"/>
       <c r="H283" s="66"/>
       <c r="I283" s="66"/>
       <c r="J283" s="66"/>
@@ -16861,6 +16967,99 @@
       <c r="M283" s="66"/>
       <c r="N283" s="66"/>
     </row>
+    <row r="284" spans="1:14">
+      <c r="G284" s="81"/>
+    </row>
+    <row r="285" spans="1:14">
+      <c r="G285" s="81"/>
+    </row>
+    <row r="286" spans="1:14">
+      <c r="G286" s="81"/>
+    </row>
+    <row r="287" spans="1:14">
+      <c r="G287" s="81"/>
+    </row>
+    <row r="288" spans="1:14">
+      <c r="G288" s="81"/>
+    </row>
+    <row r="289" spans="7:7">
+      <c r="G289" s="81"/>
+    </row>
+    <row r="290" spans="7:7">
+      <c r="G290" s="81"/>
+    </row>
+    <row r="291" spans="7:7">
+      <c r="G291" s="81"/>
+    </row>
+    <row r="292" spans="7:7">
+      <c r="G292" s="81"/>
+    </row>
+    <row r="293" spans="7:7">
+      <c r="G293" s="81"/>
+    </row>
+    <row r="294" spans="7:7">
+      <c r="G294" s="81"/>
+    </row>
+    <row r="295" spans="7:7">
+      <c r="G295" s="81"/>
+    </row>
+    <row r="296" spans="7:7">
+      <c r="G296" s="81"/>
+    </row>
+    <row r="297" spans="7:7">
+      <c r="G297" s="81"/>
+    </row>
+    <row r="298" spans="7:7">
+      <c r="G298" s="81"/>
+    </row>
+    <row r="299" spans="7:7">
+      <c r="G299" s="81"/>
+    </row>
+    <row r="300" spans="7:7">
+      <c r="G300" s="81"/>
+    </row>
+    <row r="301" spans="7:7">
+      <c r="G301" s="81"/>
+    </row>
+    <row r="302" spans="7:7">
+      <c r="G302" s="81"/>
+    </row>
+    <row r="303" spans="7:7">
+      <c r="G303" s="81"/>
+    </row>
+    <row r="304" spans="7:7">
+      <c r="G304" s="81"/>
+    </row>
+    <row r="305" spans="7:7">
+      <c r="G305" s="81"/>
+    </row>
+    <row r="306" spans="7:7">
+      <c r="G306" s="81"/>
+    </row>
+    <row r="307" spans="7:7">
+      <c r="G307" s="81"/>
+    </row>
+    <row r="308" spans="7:7">
+      <c r="G308" s="81"/>
+    </row>
+    <row r="309" spans="7:7">
+      <c r="G309" s="81"/>
+    </row>
+    <row r="310" spans="7:7">
+      <c r="G310" s="81"/>
+    </row>
+    <row r="311" spans="7:7">
+      <c r="G311" s="81"/>
+    </row>
+    <row r="312" spans="7:7">
+      <c r="G312" s="81"/>
+    </row>
+    <row r="313" spans="7:7">
+      <c r="G313" s="81"/>
+    </row>
+    <row r="314" spans="7:7">
+      <c r="G314" s="81"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
@@ -27360,7 +27559,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E254:F254 J260:M263 J259 J266:M267 C255:F261 C264:F264 C265:D265 J256:M258 J264:J265 M264:M265 C262:D263 F262 H254:H265</xm:sqref>
+          <xm:sqref>E254:F254 J260:M263 J259 J266:M266 C255:F261 C264:F264 C265:D265 J256:M258 J264:J265 M264:M265 C262:D263 F262 H254:H265 K267:M267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="267" operator="containsText" id="{112270DF-084F-4A25-8D8B-63F258F11816}">

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="513">
   <si>
     <t>MICROEMPRESA</t>
   </si>
@@ -9798,7 +9798,9 @@
       <c r="J269" s="63" t="s">
         <v>503</v>
       </c>
-      <c r="K269" s="74"/>
+      <c r="K269" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="L269" s="74"/>
       <c r="M269" s="74"/>
       <c r="N269" s="76"/>
@@ -9848,7 +9850,9 @@
       <c r="J271" s="63" t="s">
         <v>505</v>
       </c>
-      <c r="K271" s="74"/>
+      <c r="K271" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="L271" s="74"/>
       <c r="M271" s="74"/>
       <c r="N271" s="76"/>
@@ -9874,7 +9878,9 @@
       <c r="J272" s="63" t="s">
         <v>506</v>
       </c>
-      <c r="K272" s="74"/>
+      <c r="K272" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="L272" s="74"/>
       <c r="M272" s="74"/>
       <c r="N272" s="76"/>
@@ -9902,7 +9908,9 @@
       <c r="J273" s="63" t="s">
         <v>507</v>
       </c>
-      <c r="K273" s="74"/>
+      <c r="K273" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="L273" s="74"/>
       <c r="M273" s="74"/>
       <c r="N273" s="76"/>
@@ -9930,7 +9938,9 @@
       <c r="J274" s="63" t="s">
         <v>508</v>
       </c>
-      <c r="K274" s="74"/>
+      <c r="K274" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="L274" s="74"/>
       <c r="M274" s="74"/>
       <c r="N274" s="76"/>
@@ -10018,7 +10028,9 @@
       <c r="J278" s="63" t="s">
         <v>509</v>
       </c>
-      <c r="K278" s="74"/>
+      <c r="K278" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="L278" s="74"/>
       <c r="M278" s="74"/>
       <c r="N278" s="76"/>
@@ -10066,7 +10078,9 @@
       <c r="J280" s="63" t="s">
         <v>511</v>
       </c>
-      <c r="K280" s="74"/>
+      <c r="K280" s="18" t="s">
+        <v>302</v>
+      </c>
       <c r="L280" s="74"/>
       <c r="M280" s="74"/>
       <c r="N280" s="76"/>
@@ -10231,7 +10245,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="147" operator="containsText" id="{0569e4f6-82d8-4f46-860b-066af5f24945}">
+          <x14:cfRule type="containsText" priority="161" operator="containsText" id="{d7361c41-66cd-4aad-a770-b1922e4390a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G28)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10246,7 +10260,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="148" operator="containsText" id="{4b5512a9-b9d6-44b1-841d-86b761908f30}">
+          <x14:cfRule type="containsText" priority="162" operator="containsText" id="{506f6c8e-adcc-4d49-bf8c-e9be8bb01442}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G28)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10264,7 +10278,7 @@
           <xm:sqref>G28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="145" operator="containsText" id="{82708d07-2b30-44df-87ea-69e58477bd6e}">
+          <x14:cfRule type="containsText" priority="159" operator="containsText" id="{03c99a58-b262-4745-b8a9-e032f642495f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G42)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10279,7 +10293,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="146" operator="containsText" id="{01c70c01-2ac6-4c41-9203-91fa7bbf2566}">
+          <x14:cfRule type="containsText" priority="160" operator="containsText" id="{8ca92621-caec-4349-bb19-961d8521f78a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G42)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10297,7 +10311,7 @@
           <xm:sqref>G42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="143" operator="containsText" id="{9c607d83-1346-4725-83b2-3963b59d5d9d}">
+          <x14:cfRule type="containsText" priority="157" operator="containsText" id="{7430d174-7219-4979-bfbf-e0bfe09c9af7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G56)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10312,7 +10326,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="144" operator="containsText" id="{95bd912f-d936-40eb-ab4b-975c900417cd}">
+          <x14:cfRule type="containsText" priority="158" operator="containsText" id="{5c3740e5-9346-46be-bdc6-432d37285ce9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G56)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10330,7 +10344,7 @@
           <xm:sqref>G56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="141" operator="containsText" id="{a8f9b328-63aa-44c3-ad31-7d2cfaaf8b5e}">
+          <x14:cfRule type="containsText" priority="155" operator="containsText" id="{8403385a-5612-4920-bc01-c39968755356}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G70)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10345,7 +10359,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="142" operator="containsText" id="{93a4872e-dbb5-4583-8759-5f1e0b09c670}">
+          <x14:cfRule type="containsText" priority="156" operator="containsText" id="{4978b88a-0de5-4345-adfd-aa152f6d8793}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G70)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10363,7 +10377,7 @@
           <xm:sqref>G70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="817" operator="containsText" id="{5d816377-ba35-41be-9dc7-8875394fe1c5}">
+          <x14:cfRule type="containsText" priority="831" operator="containsText" id="{7104d32b-8e37-474f-aa25-ed7a336166dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K73)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10378,7 +10392,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="818" operator="containsText" id="{ee8fa719-5fc5-4abb-9c71-32a34b720220}">
+          <x14:cfRule type="containsText" priority="832" operator="containsText" id="{47d955d9-918a-4d15-a464-004c84dfa758}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K73)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10396,7 +10410,7 @@
           <xm:sqref>K73</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="815" operator="containsText" id="{658311b8-a078-4b5c-b3c6-546994100665}">
+          <x14:cfRule type="containsText" priority="829" operator="containsText" id="{9318f057-40c6-4e22-8e90-68ed86540f60}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K83)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10411,7 +10425,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="816" operator="containsText" id="{939c3f03-2eac-4d03-9421-d1095a220625}">
+          <x14:cfRule type="containsText" priority="830" operator="containsText" id="{fab03b92-d5d1-413c-bbb8-94abf8c5c0d4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K83)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10429,7 +10443,7 @@
           <xm:sqref>K83</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="813" operator="containsText" id="{dbda637e-7e43-43a7-83d8-3295cfdd0095}">
+          <x14:cfRule type="containsText" priority="827" operator="containsText" id="{0f90cabc-0772-4673-bf7e-9cea711a3692}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K84)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10444,7 +10458,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="814" operator="containsText" id="{f1e11d62-70be-4ea7-8113-22420adcae61}">
+          <x14:cfRule type="containsText" priority="828" operator="containsText" id="{1b27c2f8-3b5c-49b9-87ad-312f6ef52b18}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K84)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10462,7 +10476,7 @@
           <xm:sqref>K84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="841" operator="containsText" id="{80c7b64b-7e5d-4cdf-a09a-e27f57ff1502}">
+          <x14:cfRule type="containsText" priority="855" operator="containsText" id="{271c4faa-4ff1-4820-b4d7-0531aaa0b995}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L87)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10477,7 +10491,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="842" operator="containsText" id="{a828d622-5a17-4a4e-9d94-aa21b1f109e9}">
+          <x14:cfRule type="containsText" priority="856" operator="containsText" id="{ec550099-5dba-433b-a367-17f1b5b62223}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L87)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10495,7 +10509,7 @@
           <xm:sqref>L87</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="839" operator="containsText" id="{10f7827c-93d3-449e-99a2-3b795e89e68f}">
+          <x14:cfRule type="containsText" priority="853" operator="containsText" id="{04fec25c-57a1-423e-867b-59845ec0fdfe}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I92)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10510,7 +10524,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="840" operator="containsText" id="{65a6e73b-033e-4374-8daa-cc6c518338c5}">
+          <x14:cfRule type="containsText" priority="854" operator="containsText" id="{8f20cd18-dd09-4c12-964b-b1d5f58c8a2c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I92)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10528,7 +10542,7 @@
           <xm:sqref>I92</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="845" operator="containsText" id="{a9a5ae26-7071-4c4c-8985-71a68f095c2f}">
+          <x14:cfRule type="containsText" priority="859" operator="containsText" id="{89b0f6f3-8f78-43e6-9817-a4902698778b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I93)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10543,7 +10557,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="846" operator="containsText" id="{e7f5c328-e6af-4152-94fd-588ccd3b482c}">
+          <x14:cfRule type="containsText" priority="860" operator="containsText" id="{ed208ba5-896d-46ad-a702-c0358f4d26b4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I93)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10561,7 +10575,7 @@
           <xm:sqref>I93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="843" operator="containsText" id="{b43483a0-235f-4d83-b393-1ef433b4ab0b}">
+          <x14:cfRule type="containsText" priority="857" operator="containsText" id="{872d4676-5fa3-463a-b6e1-d51541f3c4cd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I96)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10576,7 +10590,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="844" operator="containsText" id="{ede28470-cf76-42bb-b6d4-63976ae59b4a}">
+          <x14:cfRule type="containsText" priority="858" operator="containsText" id="{e2a31c45-f94d-4ea4-879d-e2bc14554ddd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I96)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10594,7 +10608,7 @@
           <xm:sqref>I96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="811" operator="containsText" id="{8c3c5f1c-6c98-4cff-af6f-63021304705d}">
+          <x14:cfRule type="containsText" priority="825" operator="containsText" id="{11619816-be8c-4bc7-b70d-6508ccbeef39}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K96)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10609,7 +10623,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="812" operator="containsText" id="{d1ad0d41-81a3-4446-b7e6-a6771ffc87d0}">
+          <x14:cfRule type="containsText" priority="826" operator="containsText" id="{97697454-6b33-45e6-b2a3-27ae13dd5af3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K96)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10627,7 +10641,7 @@
           <xm:sqref>K96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="849" operator="containsText" id="{ddcef20d-8f70-47ea-8415-c11ad49bbdd8}">
+          <x14:cfRule type="containsText" priority="863" operator="containsText" id="{979a6492-f535-41ac-bebf-ac2df19ddb1a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10642,7 +10656,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="850" operator="containsText" id="{61d747b0-053d-4670-ae3d-8ca433a5022f}">
+          <x14:cfRule type="containsText" priority="864" operator="containsText" id="{17a84108-73f1-4ba1-a1cd-caf44b35d7bc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10660,7 +10674,7 @@
           <xm:sqref>I97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="809" operator="containsText" id="{d3a58106-5a31-4898-bb4e-177ec1d89412}">
+          <x14:cfRule type="containsText" priority="823" operator="containsText" id="{173c96c9-3b52-4a6b-9573-6d062e025272}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10675,7 +10689,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="810" operator="containsText" id="{8b784313-4025-4e33-8dd5-d2ddb2b2cc61}">
+          <x14:cfRule type="containsText" priority="824" operator="containsText" id="{618bbd2a-e94f-48af-90cc-e1f9adfd348e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10693,7 +10707,7 @@
           <xm:sqref>K97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="847" operator="containsText" id="{3d5541b1-c959-4151-bd3e-0e082acfebca}">
+          <x14:cfRule type="containsText" priority="861" operator="containsText" id="{631035e5-ffac-4bf6-b4bb-f9cefae5a1f9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10708,7 +10722,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="848" operator="containsText" id="{cc6bb4e5-8d23-48a0-95dd-27fc28cea056}">
+          <x14:cfRule type="containsText" priority="862" operator="containsText" id="{1d735228-d580-497f-ba7e-6732f7916513}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10726,7 +10740,7 @@
           <xm:sqref>L97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="137" operator="containsText" id="{3bfb439f-a080-4f2d-a313-1644934a5019}">
+          <x14:cfRule type="containsText" priority="151" operator="containsText" id="{c6c60acd-1b03-4c25-ae79-7a8405fa129b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G98)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10741,7 +10755,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="138" operator="containsText" id="{50f1c70c-369d-4c93-bc8c-1afe95201cad}">
+          <x14:cfRule type="containsText" priority="152" operator="containsText" id="{2606aa8d-a5d5-4f3f-9872-48eef3c8b2c7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G98)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10759,7 +10773,7 @@
           <xm:sqref>G98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="823" operator="containsText" id="{d39f90df-785e-4c95-90c3-ee8eec02a84a}">
+          <x14:cfRule type="containsText" priority="837" operator="containsText" id="{02fb5de7-5cfc-4f8f-9312-051aebf054b3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L101)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10774,7 +10788,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="824" operator="containsText" id="{8ccbf192-938b-49ea-aaf0-a248fea0c9d0}">
+          <x14:cfRule type="containsText" priority="838" operator="containsText" id="{25e7db51-f423-4e29-a789-63795f57fe78}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L101)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10792,7 +10806,7 @@
           <xm:sqref>L101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="795" operator="containsText" id="{5c985a1f-d429-4574-9940-c02afe18a46a}">
+          <x14:cfRule type="containsText" priority="809" operator="containsText" id="{df030340-685e-480c-b314-cadf9518b721}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I102)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10807,7 +10821,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="796" operator="containsText" id="{6e88e852-4b24-4d47-a931-22f5cf71c782}">
+          <x14:cfRule type="containsText" priority="810" operator="containsText" id="{f12a39b4-7222-4df6-a395-b570e6de0d4a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I102)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10825,7 +10839,7 @@
           <xm:sqref>I102</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="799" operator="containsText" id="{c9ce1388-9ef3-4e6b-9a10-83a03f15a162}">
+          <x14:cfRule type="containsText" priority="813" operator="containsText" id="{4b73c276-5908-4524-950e-ab7f27bf526c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I106)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10840,7 +10854,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="800" operator="containsText" id="{c1341c35-24de-46e4-989a-12886602a463}">
+          <x14:cfRule type="containsText" priority="814" operator="containsText" id="{d06b4801-aa5e-46f4-8cc0-dbb8f0fcfc1d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I106)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10858,7 +10872,7 @@
           <xm:sqref>I106</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="797" operator="containsText" id="{78b5d05a-2f19-4f46-ad48-f55f65f3a1d2}">
+          <x14:cfRule type="containsText" priority="811" operator="containsText" id="{8d74b9ed-7296-49a2-a4ae-998d4eb77600}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I107)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10873,7 +10887,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="798" operator="containsText" id="{a848a697-ed53-4037-9eb7-9376bf76fb33}">
+          <x14:cfRule type="containsText" priority="812" operator="containsText" id="{252ac65f-84c9-47da-9eb8-c5012bd9c4b1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I107)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10891,7 +10905,7 @@
           <xm:sqref>I107</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="801" operator="containsText" id="{45ae81f2-883f-4b15-87a8-02e58e866064}">
+          <x14:cfRule type="containsText" priority="815" operator="containsText" id="{e0c043c4-d5b7-47c9-923e-8e8e166a68bc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I110)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10906,7 +10920,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="802" operator="containsText" id="{24b17438-6a85-4c7e-bef5-03522e657206}">
+          <x14:cfRule type="containsText" priority="816" operator="containsText" id="{3a293053-1e7b-4e7e-bd14-a932a4f28ea4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I110)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10924,7 +10938,7 @@
           <xm:sqref>I110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="819" operator="containsText" id="{8884732e-5310-4f7a-a86c-8449ce662983}">
+          <x14:cfRule type="containsText" priority="833" operator="containsText" id="{f5f2993d-c58b-44ac-9557-0307cdeb04b8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10939,7 +10953,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="820" operator="containsText" id="{0a945b10-43ef-4926-b769-113609907b53}">
+          <x14:cfRule type="containsText" priority="834" operator="containsText" id="{d74a999f-e718-4edc-b02f-db9fc3c2219f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10957,7 +10971,7 @@
           <xm:sqref>I111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="807" operator="containsText" id="{f1ab05b9-a35c-4af7-8997-0a0b7b4c31e8}">
+          <x14:cfRule type="containsText" priority="821" operator="containsText" id="{bd9256c7-3ec8-4d7c-8bbb-ab8ab3e6a227}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10972,7 +10986,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="808" operator="containsText" id="{e15f9f44-21ad-4abd-aa4c-7dc9e1321bf6}">
+          <x14:cfRule type="containsText" priority="822" operator="containsText" id="{bd238ee3-a581-4401-a1b6-fba61541ab6c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10990,7 +11004,7 @@
           <xm:sqref>K111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="805" operator="containsText" id="{6ec55d43-0f56-4ec3-8c6f-30013ae3c30b}">
+          <x14:cfRule type="containsText" priority="819" operator="containsText" id="{36b036e0-1f98-4786-a326-964fde40820d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11005,7 +11019,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="806" operator="containsText" id="{c977232a-b737-4c64-b8a3-ca5447edb31a}">
+          <x14:cfRule type="containsText" priority="820" operator="containsText" id="{16e31694-3653-4628-b0f0-3b0fb052c9f5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11023,7 +11037,7 @@
           <xm:sqref>L111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="133" operator="containsText" id="{079f7021-98a8-4e41-a849-b75543f7346f}">
+          <x14:cfRule type="containsText" priority="147" operator="containsText" id="{8db5ae8e-60d2-46b2-bdab-5d2638a6fb28}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11038,7 +11052,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="134" operator="containsText" id="{d94f0f08-e852-43c2-800e-bc3a99724808}">
+          <x14:cfRule type="containsText" priority="148" operator="containsText" id="{80e09c66-a62e-4447-9715-b4189a1fbd24}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11056,7 +11070,7 @@
           <xm:sqref>G112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="803" operator="containsText" id="{9152e4f2-379b-4af8-915d-3e311c663e83}">
+          <x14:cfRule type="containsText" priority="817" operator="containsText" id="{01efd41a-d5a2-45ff-bd57-b96ee7dc9271}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11071,7 +11085,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="804" operator="containsText" id="{c941eaea-bb07-46c2-b627-4ed4099da64c}">
+          <x14:cfRule type="containsText" priority="818" operator="containsText" id="{868ef3bb-e80c-4074-bfe7-e08a8a1a7aa6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11089,7 +11103,7 @@
           <xm:sqref>I112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="769" operator="containsText" id="{4e75b115-5e4d-4575-930c-61ddd428b756}">
+          <x14:cfRule type="containsText" priority="783" operator="containsText" id="{7a719f9e-d085-47af-8c8d-8f2b8b140b93}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11104,7 +11118,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="770" operator="containsText" id="{92c37fc3-39b7-4a53-b3ef-7d1efe2a1ec5}">
+          <x14:cfRule type="containsText" priority="784" operator="containsText" id="{4341bebf-8474-4b26-87d1-8737e80641d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11122,7 +11136,7 @@
           <xm:sqref>I114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="787" operator="containsText" id="{18f93983-b540-4f0e-83da-4662eba993e4}">
+          <x14:cfRule type="containsText" priority="801" operator="containsText" id="{0de47f16-ded7-47d7-9b58-418df84e04c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L115)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11137,7 +11151,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="788" operator="containsText" id="{08915516-6eb6-4c27-a96f-dc129886383c}">
+          <x14:cfRule type="containsText" priority="802" operator="containsText" id="{61c723cc-ce9b-4172-a135-2ec086b3c0de}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L115)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11155,7 +11169,7 @@
           <xm:sqref>L115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="771" operator="containsText" id="{6415e2f8-b9d9-4873-bc38-17e147f4913f}">
+          <x14:cfRule type="containsText" priority="785" operator="containsText" id="{b738b375-22cb-4034-9c63-439ea90539a8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I116)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11170,7 +11184,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="772" operator="containsText" id="{6e418975-cfaf-459b-9fe1-fc745359e6a4}">
+          <x14:cfRule type="containsText" priority="786" operator="containsText" id="{3f414d88-29a1-4f39-9ea1-79f21fd07ce1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I116)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11188,7 +11202,7 @@
           <xm:sqref>I116</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="763" operator="containsText" id="{86aaaaa7-676a-4295-8c0e-d15962d95e56}">
+          <x14:cfRule type="containsText" priority="777" operator="containsText" id="{9f778628-0031-43ab-af9b-beaff27382ea}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I120)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11203,7 +11217,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="764" operator="containsText" id="{14d55cd0-2d77-4758-b013-7e1b6dde1993}">
+          <x14:cfRule type="containsText" priority="778" operator="containsText" id="{f8490bb9-ebca-454c-9230-f0bd274151fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I120)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11221,7 +11235,7 @@
           <xm:sqref>I120</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="759" operator="containsText" id="{1e24141e-0ea8-4d86-a7ac-bfbd44941776}">
+          <x14:cfRule type="containsText" priority="773" operator="containsText" id="{0c2d5a32-b2fc-4cb9-843e-1235c93ed249}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I121)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11236,7 +11250,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="760" operator="containsText" id="{f943875d-fa04-4eab-9d38-ed8138b950e3}">
+          <x14:cfRule type="containsText" priority="774" operator="containsText" id="{0c02a6f1-467b-4c59-8f7d-ed339d294533}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I121)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11254,7 +11268,7 @@
           <xm:sqref>I121</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="761" operator="containsText" id="{0ae6563b-0da4-4440-b640-f45019630c22}">
+          <x14:cfRule type="containsText" priority="775" operator="containsText" id="{55804aed-b2e3-4c80-abee-cf36e424b38f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I122)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11269,7 +11283,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="762" operator="containsText" id="{6752d9d3-8f18-42bc-8d6a-1bad2fef1119}">
+          <x14:cfRule type="containsText" priority="776" operator="containsText" id="{c66a704a-f722-450d-ab6e-5f49e4b335a6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I122)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11287,7 +11301,7 @@
           <xm:sqref>I122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="755" operator="containsText" id="{26be4b2c-2e73-4b0d-a9d5-84d0ead1ab5a}">
+          <x14:cfRule type="containsText" priority="769" operator="containsText" id="{1d12726f-3b87-4585-8bad-839e412558b4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I123)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11302,7 +11316,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="756" operator="containsText" id="{ff004254-c1f8-4093-b78e-b88afeb2c138}">
+          <x14:cfRule type="containsText" priority="770" operator="containsText" id="{7233f1d3-cf18-4169-a850-bc10fadbf745}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I123)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11320,7 +11334,7 @@
           <xm:sqref>I123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="777" operator="containsText" id="{87c31886-dca5-4956-9283-1dcc1857e1d7}">
+          <x14:cfRule type="containsText" priority="791" operator="containsText" id="{11042b86-445a-4aae-b01a-6f2ed572e9ab}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I124)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11335,7 +11349,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="778" operator="containsText" id="{3165e32b-35b9-4756-a10d-0a3d4a37b763}">
+          <x14:cfRule type="containsText" priority="792" operator="containsText" id="{e1613c33-5c79-4ef3-bc23-3aa86153b64c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I124)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11353,7 +11367,7 @@
           <xm:sqref>I124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="767" operator="containsText" id="{38089540-2d51-4c4a-994e-e1fd95bc5e47}">
+          <x14:cfRule type="containsText" priority="781" operator="containsText" id="{9b1684b0-bec1-4b57-8d7a-6f3e2640e1c4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11368,7 +11382,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="768" operator="containsText" id="{3a94edeb-6ad4-4c21-8af7-40132b7ca98f}">
+          <x14:cfRule type="containsText" priority="782" operator="containsText" id="{dd5e552b-c1dd-4c16-ad61-fdfe932493ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11386,7 +11400,7 @@
           <xm:sqref>I125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="783" operator="containsText" id="{5b2ed3e2-a070-4af1-b8ed-634780b9cb8d}">
+          <x14:cfRule type="containsText" priority="797" operator="containsText" id="{8629284f-5c78-45c8-b1a3-9c79ae4026e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11401,7 +11415,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="784" operator="containsText" id="{66b3291f-08dc-4334-98c3-4969d1639d09}">
+          <x14:cfRule type="containsText" priority="798" operator="containsText" id="{49103e19-7155-4f07-84e3-543a77e4d97a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11419,7 +11433,7 @@
           <xm:sqref>K125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="765" operator="containsText" id="{ffed492a-abe6-4175-91c6-dc2dee0319d2}">
+          <x14:cfRule type="containsText" priority="779" operator="containsText" id="{40b17e71-48d8-4c18-8f0b-558249e65971}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11434,7 +11448,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="766" operator="containsText" id="{d618fe46-d40c-4dad-8eb0-178cdaa95b15}">
+          <x14:cfRule type="containsText" priority="780" operator="containsText" id="{b66b4e01-a243-4d45-a419-618b173ba520}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11452,7 +11466,7 @@
           <xm:sqref>L125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="129" operator="containsText" id="{3cd7bf75-2955-41b7-8ace-52450d5f7cd7}">
+          <x14:cfRule type="containsText" priority="143" operator="containsText" id="{0220945b-efad-4f3a-ace1-13a51870a169}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11467,7 +11481,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="130" operator="containsText" id="{e8f6dc94-5588-4eaf-8ca2-f8d8603c9935}">
+          <x14:cfRule type="containsText" priority="144" operator="containsText" id="{2ee8aae2-165e-4c2a-b9f5-9242c677a2ef}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11485,7 +11499,7 @@
           <xm:sqref>G126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="757" operator="containsText" id="{34dbf873-6d8a-4040-8764-5289868cfd6a}">
+          <x14:cfRule type="containsText" priority="771" operator="containsText" id="{1e1d15f6-5a62-481c-88e6-74798364b434}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11500,7 +11514,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="758" operator="containsText" id="{417175e5-ce98-4c5e-aa9e-8c1c14faccf4}">
+          <x14:cfRule type="containsText" priority="772" operator="containsText" id="{b46703b3-c17f-4e4d-ae41-1801d4c2b9c4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11518,7 +11532,7 @@
           <xm:sqref>I126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="739" operator="containsText" id="{25e77204-0309-42ab-84bb-4878753b060c}">
+          <x14:cfRule type="containsText" priority="753" operator="containsText" id="{0d745440-6d10-4400-9474-3a1cab518abc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11533,7 +11547,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="740" operator="containsText" id="{37fb376f-3d54-46b9-b75b-7745fc8128b3}">
+          <x14:cfRule type="containsText" priority="754" operator="containsText" id="{93c63f98-4ba7-4aa9-80eb-e012ca2f530a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11551,7 +11565,7 @@
           <xm:sqref>I128</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="715" operator="containsText" id="{eeaf906a-8a4d-4d32-b8c3-1d132898fc06}">
+          <x14:cfRule type="containsText" priority="729" operator="containsText" id="{cca030f3-01fa-44c6-a5a5-06c60004202c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I129)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11566,7 +11580,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="716" operator="containsText" id="{eae149ba-5aee-4034-8e90-3ef030c0833f}">
+          <x14:cfRule type="containsText" priority="730" operator="containsText" id="{42b5ea14-63f0-4882-8f5d-5f8a0883e666}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I129)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11584,7 +11598,7 @@
           <xm:sqref>I129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="747" operator="containsText" id="{74e784c2-bd7e-4472-b0ef-3f2b8f7737a7}">
+          <x14:cfRule type="containsText" priority="761" operator="containsText" id="{f1bf220d-8615-4673-a243-86ce224ab71b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L129)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11599,7 +11613,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="748" operator="containsText" id="{6b28a688-5103-4801-80dd-d9982b636815}">
+          <x14:cfRule type="containsText" priority="762" operator="containsText" id="{e730f9d8-97d5-47a8-ae76-1fb7fa911e24}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L129)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11617,7 +11631,7 @@
           <xm:sqref>L129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="741" operator="containsText" id="{da526462-530c-4da8-8fca-101111def7d4}">
+          <x14:cfRule type="containsText" priority="755" operator="containsText" id="{0a6b24f6-5027-4fe0-b343-78ca34619ac7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I130)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11632,7 +11646,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="742" operator="containsText" id="{8095fd8f-5dee-4827-9c3d-a0dd35edda34}">
+          <x14:cfRule type="containsText" priority="756" operator="containsText" id="{ab5bc86d-9e43-4ba0-ad07-4f2646d8ed4e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I130)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11650,7 +11664,7 @@
           <xm:sqref>I130</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="719" operator="containsText" id="{9e505649-92a5-4896-b60f-27b2050334c1}">
+          <x14:cfRule type="containsText" priority="733" operator="containsText" id="{f97921e6-e3e7-43d5-b1ed-22a78f3a548a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11665,7 +11679,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="720" operator="containsText" id="{0b988f45-26e2-4f07-b04c-a0a9893909a1}">
+          <x14:cfRule type="containsText" priority="734" operator="containsText" id="{25cf34cb-7818-4d3a-9218-ba73d804b62e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11683,7 +11697,7 @@
           <xm:sqref>I133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="659" operator="containsText" id="{49f136e4-f4bf-42ac-9524-77400a505888}">
+          <x14:cfRule type="containsText" priority="673" operator="containsText" id="{e27d8696-8dcd-4e47-91f5-135c70e3c6a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11698,7 +11712,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="660" operator="containsText" id="{7d7e3db7-2828-4853-81c4-465300525bbf}">
+          <x14:cfRule type="containsText" priority="674" operator="containsText" id="{02e6a853-db23-4b96-a4b5-85ffca0a4da3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11716,7 +11730,7 @@
           <xm:sqref>K133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="717" operator="containsText" id="{42ab8dda-82cf-4852-9f9a-065ebb56fd4b}">
+          <x14:cfRule type="containsText" priority="731" operator="containsText" id="{0b8aba20-f470-4932-a3b6-f37f43f92c73}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11731,7 +11745,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="718" operator="containsText" id="{18e665d9-8801-4e79-a684-cab4d19c58b5}">
+          <x14:cfRule type="containsText" priority="732" operator="containsText" id="{284e584b-8157-471e-a3b5-f35c2fd2e8a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11749,7 +11763,7 @@
           <xm:sqref>L133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="711" operator="containsText" id="{dbc699c2-fca8-44e6-ab3d-321724642e53}">
+          <x14:cfRule type="containsText" priority="725" operator="containsText" id="{5bfd964f-83c4-416d-8faa-147977ad248a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I134)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11764,7 +11778,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="712" operator="containsText" id="{45ec7a63-2d9b-46fb-b067-0daa1bd74bef}">
+          <x14:cfRule type="containsText" priority="726" operator="containsText" id="{7918682e-ab0b-4ca1-877d-d090e0fbf808}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I134)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11782,7 +11796,7 @@
           <xm:sqref>I134</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="713" operator="containsText" id="{d9bea095-0830-4c09-893e-c441fa99de19}">
+          <x14:cfRule type="containsText" priority="727" operator="containsText" id="{cbb8e9d8-0468-497b-be8b-83d1c767265b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I135)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11797,7 +11811,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="714" operator="containsText" id="{60cbe418-7f3f-4307-a778-abcb8c36b940}">
+          <x14:cfRule type="containsText" priority="728" operator="containsText" id="{0fbae696-a564-475f-ad61-fc40ced2d374}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I135)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11815,7 +11829,7 @@
           <xm:sqref>I135</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="725" operator="containsText" id="{87d2c56e-ecbd-4cb0-93a6-851121daa4be}">
+          <x14:cfRule type="containsText" priority="739" operator="containsText" id="{6055d6b9-0c27-4871-a78e-148aa7f7665c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I137)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11830,7 +11844,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="726" operator="containsText" id="{16b3a798-2f20-45f5-8487-e09afe38ecda}">
+          <x14:cfRule type="containsText" priority="740" operator="containsText" id="{6ce6a22e-c5a8-4b9c-926a-37c4b5f2ae73}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I137)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11848,7 +11862,7 @@
           <xm:sqref>I137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="743" operator="containsText" id="{5edd0693-c53f-448d-9dc2-e55bd331caf0}">
+          <x14:cfRule type="containsText" priority="757" operator="containsText" id="{fbc8ee9b-722d-4c02-ab0b-5fb91e629a11}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I138)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11863,7 +11877,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="744" operator="containsText" id="{8d095eed-8e13-4a7d-8874-5cb13279e1d0}">
+          <x14:cfRule type="containsText" priority="758" operator="containsText" id="{1a65bafc-2803-4966-90af-eac79e43ab5a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I138)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11881,7 +11895,7 @@
           <xm:sqref>I138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="723" operator="containsText" id="{eaa9324e-8939-474c-b42b-45627a7a55af}">
+          <x14:cfRule type="containsText" priority="737" operator="containsText" id="{0862b2a5-b245-41c3-8fd5-ea14affeff86}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11896,7 +11910,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="724" operator="containsText" id="{4fca9f5e-3053-4c03-acbb-34d0bfeeb489}">
+          <x14:cfRule type="containsText" priority="738" operator="containsText" id="{e2c39b2f-2fc2-44cc-9112-2960a9307604}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11914,7 +11928,7 @@
           <xm:sqref>I139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="673" operator="containsText" id="{97acffd4-c3ba-4a0a-8445-accd9465cd33}">
+          <x14:cfRule type="containsText" priority="687" operator="containsText" id="{401451a6-3483-4e5e-910b-152f7fce9d96}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11929,7 +11943,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="674" operator="containsText" id="{1cd87d3e-c2cd-4e53-8c84-3f0863fd8497}">
+          <x14:cfRule type="containsText" priority="688" operator="containsText" id="{391ebf12-ad41-4b00-9871-92c5148bdb44}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11947,7 +11961,7 @@
           <xm:sqref>K139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="721" operator="containsText" id="{7b8e2d11-817d-4cf4-8543-767d8d11afbe}">
+          <x14:cfRule type="containsText" priority="735" operator="containsText" id="{4d060afc-3f75-43d5-b32e-d2a559145012}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11962,7 +11976,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="722" operator="containsText" id="{618cc30b-85e2-40b8-a231-e202ea493a15}">
+          <x14:cfRule type="containsText" priority="736" operator="containsText" id="{e7364bf3-edab-45f1-8467-ff5b211ac8ee}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11980,7 +11994,7 @@
           <xm:sqref>L139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="125" operator="containsText" id="{f97d5756-8d29-4e4b-8167-315213097c49}">
+          <x14:cfRule type="containsText" priority="139" operator="containsText" id="{900d1c2a-9215-4d41-8931-09b95896766f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11995,7 +12009,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="126" operator="containsText" id="{09ca41c0-6239-4c67-8189-060bf6ec7975}">
+          <x14:cfRule type="containsText" priority="140" operator="containsText" id="{b1a13e94-408e-4a43-b25f-ce1f83b03653}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12013,7 +12027,7 @@
           <xm:sqref>G140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="727" operator="containsText" id="{93922bb2-7480-46d4-9779-4102634129d1}">
+          <x14:cfRule type="containsText" priority="741" operator="containsText" id="{56f6e541-dda5-482f-8c17-40b064ef3cdf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12028,7 +12042,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="728" operator="containsText" id="{ad571404-c1e1-4dea-a392-00c07c96942f}">
+          <x14:cfRule type="containsText" priority="742" operator="containsText" id="{d41fe6b4-207a-4af2-a087-b436b4a761f7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12046,7 +12060,7 @@
           <xm:sqref>I140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="695" operator="containsText" id="{43c99943-16e2-477c-9bc7-9d2fd91981aa}">
+          <x14:cfRule type="containsText" priority="709" operator="containsText" id="{7895074a-10ce-4de9-8818-a39380804c19}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12061,7 +12075,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="696" operator="containsText" id="{1a3a8b5e-c194-49d1-8389-fa1e1770d9a3}">
+          <x14:cfRule type="containsText" priority="710" operator="containsText" id="{d0390427-2f8f-46d0-b705-a597fd6fb7f7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12079,7 +12093,7 @@
           <xm:sqref>I142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="675" operator="containsText" id="{121ab178-d248-4e7b-aa55-bed46ce1c815}">
+          <x14:cfRule type="containsText" priority="689" operator="containsText" id="{10a56bb6-7d1b-479c-99c6-dab5a9e403dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12094,7 +12108,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="676" operator="containsText" id="{9bcaae35-c5d4-4581-a996-dcf391798be2}">
+          <x14:cfRule type="containsText" priority="690" operator="containsText" id="{c9bc760f-44c2-4647-9806-07a6d4aff7e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12112,7 +12126,7 @@
           <xm:sqref>L142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="697" operator="containsText" id="{fa923e5e-ee68-41f5-bbc5-f81439e61b4b}">
+          <x14:cfRule type="containsText" priority="711" operator="containsText" id="{e9e359bb-b017-4697-a15f-ef5574b10a4d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I144)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12127,7 +12141,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="698" operator="containsText" id="{5da60e2b-0c6c-4cae-8041-55f304ee46c4}">
+          <x14:cfRule type="containsText" priority="712" operator="containsText" id="{40d53209-edd6-4daf-92d2-d9a0275bbfb3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I144)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12145,7 +12159,7 @@
           <xm:sqref>I144</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="663" operator="containsText" id="{4c56fbf3-90d1-4981-99de-be3ce54b632b}">
+          <x14:cfRule type="containsText" priority="677" operator="containsText" id="{ba5d1d81-89d1-4b80-9793-a4965b2f6e0a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I146)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12160,7 +12174,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="664" operator="containsText" id="{a5098aea-ac10-4bf9-95db-b336ff0cce93}">
+          <x14:cfRule type="containsText" priority="678" operator="containsText" id="{8a57e2f6-41a2-4f88-aadf-47147970527f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I146)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12178,7 +12192,7 @@
           <xm:sqref>I146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="661" operator="containsText" id="{bdd580c0-57f7-488b-bda6-33c709127a9d}">
+          <x14:cfRule type="containsText" priority="675" operator="containsText" id="{3d6e0cf0-8303-4930-ba13-964cbf07c5af}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I147)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12193,7 +12207,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="662" operator="containsText" id="{78cb7709-ead2-4628-8376-067293c761b9}">
+          <x14:cfRule type="containsText" priority="676" operator="containsText" id="{28f25874-2724-4e49-a19e-f92f86fc3607}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I147)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12211,7 +12225,7 @@
           <xm:sqref>I147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="667" operator="containsText" id="{bca24b1a-8804-4c27-9133-89e6d878fefd}">
+          <x14:cfRule type="containsText" priority="681" operator="containsText" id="{5570509e-c2dc-4cc5-b91c-394467869765}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L147)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12226,7 +12240,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="668" operator="containsText" id="{c704c56b-48a0-43fa-86f4-a60ce6171f95}">
+          <x14:cfRule type="containsText" priority="682" operator="containsText" id="{7f2af6eb-9d60-4442-8a5d-bf9f4f0588be}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L147)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12244,7 +12258,7 @@
           <xm:sqref>L147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="665" operator="containsText" id="{6b31d7d9-e508-4067-af93-b40251be2c0a}">
+          <x14:cfRule type="containsText" priority="679" operator="containsText" id="{f8adcabf-7670-47cc-abd1-629dd8ab9743}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I148)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12259,7 +12273,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="666" operator="containsText" id="{73cadd82-928b-4140-ba79-eaee6c587a5d}">
+          <x14:cfRule type="containsText" priority="680" operator="containsText" id="{e0f2805a-953e-439a-9862-9ad2f2100f6b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I148)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12277,7 +12291,7 @@
           <xm:sqref>I148</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="669" operator="containsText" id="{1f07a177-173b-41c5-99e0-0b364b141221}">
+          <x14:cfRule type="containsText" priority="683" operator="containsText" id="{e21e3ed2-dd9f-4678-855c-a7033ddfa461}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I149)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12292,7 +12306,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="670" operator="containsText" id="{660842e1-e953-485c-9535-a3a9a9133af8}">
+          <x14:cfRule type="containsText" priority="684" operator="containsText" id="{5d907d8e-356d-4533-9a46-8d4e974937b7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I149)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12310,7 +12324,7 @@
           <xm:sqref>I149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="691" operator="containsText" id="{df95cba5-7190-4e69-8f6c-8dbd2b5e9c25}">
+          <x14:cfRule type="containsText" priority="705" operator="containsText" id="{5c50ddba-0c8d-4b65-b6c6-1726db7d9dcb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I151)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12325,7 +12339,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="692" operator="containsText" id="{8ee7221b-e4b9-4d90-bac4-41386fa51542}">
+          <x14:cfRule type="containsText" priority="706" operator="containsText" id="{64d869fb-9952-403d-b2f8-6dd8a43619a0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I151)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12343,7 +12357,7 @@
           <xm:sqref>I151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="699" operator="containsText" id="{38afc81e-c6aa-4f11-95a7-58e1496349f5}">
+          <x14:cfRule type="containsText" priority="713" operator="containsText" id="{0d8446cd-9948-407c-8a44-4260343b840a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I152)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12358,7 +12372,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="700" operator="containsText" id="{8b30efeb-1ac3-4561-8afd-6841a24af429}">
+          <x14:cfRule type="containsText" priority="714" operator="containsText" id="{9884dc0b-e2b6-4ac2-a91e-213de9deb3fe}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I152)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12376,7 +12390,7 @@
           <xm:sqref>I152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="689" operator="containsText" id="{0e78a18b-7b66-4fc8-a3af-51ab7dc0f494}">
+          <x14:cfRule type="containsText" priority="703" operator="containsText" id="{07465d9e-7f52-4230-a9f7-5f92a2fd2b83}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12391,7 +12405,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="690" operator="containsText" id="{0b0af535-7718-433a-ae54-6ad318bbe6dd}">
+          <x14:cfRule type="containsText" priority="704" operator="containsText" id="{ac7e07e3-2ff6-4ef5-ac64-30ad1d832341}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12409,7 +12423,7 @@
           <xm:sqref>I153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="701" operator="containsText" id="{1045cb04-32e2-449c-a122-b284f498bda0}">
+          <x14:cfRule type="containsText" priority="715" operator="containsText" id="{3dd5b104-1d82-46e7-bd77-66b33edc60e9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12424,7 +12438,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="702" operator="containsText" id="{05289cdd-26fb-4d60-8381-a945bff708fa}">
+          <x14:cfRule type="containsText" priority="716" operator="containsText" id="{cd9f6be6-1821-4d63-ac6d-c66bbbe304ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12442,7 +12456,7 @@
           <xm:sqref>K153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="687" operator="containsText" id="{1620dda4-5b8b-46eb-8043-dcaf915aaab3}">
+          <x14:cfRule type="containsText" priority="701" operator="containsText" id="{adf41b25-d041-4627-9a89-fd77799f8f8a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12457,7 +12471,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="688" operator="containsText" id="{d7f1f607-5bbc-4000-89b5-a65babea973a}">
+          <x14:cfRule type="containsText" priority="702" operator="containsText" id="{12cd87ba-c3ae-41e3-be54-6d8b11ffbec5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12475,7 +12489,7 @@
           <xm:sqref>L153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="121" operator="containsText" id="{471cb06c-9557-4aff-8355-fc2fd562645a}">
+          <x14:cfRule type="containsText" priority="135" operator="containsText" id="{4c2885e8-cd01-4480-aa58-309a3fe47ff6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12490,7 +12504,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="122" operator="containsText" id="{ed6c1aaf-672f-4ff0-a3be-7e722ababe75}">
+          <x14:cfRule type="containsText" priority="136" operator="containsText" id="{77c1e18e-1279-431c-a128-c919f48aa017}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12508,7 +12522,7 @@
           <xm:sqref>G154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="693" operator="containsText" id="{cbaed65f-cb61-4519-86a3-77e698047c23}">
+          <x14:cfRule type="containsText" priority="707" operator="containsText" id="{ed8f9a9b-af4b-4c21-a36d-2933d697b6ee}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12523,7 +12537,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="694" operator="containsText" id="{9b74dd56-8a71-4e69-a15c-c8b17571cbf1}">
+          <x14:cfRule type="containsText" priority="708" operator="containsText" id="{e4939627-c5df-488c-ba68-e3f7f55acae2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12541,7 +12555,7 @@
           <xm:sqref>I154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="671" operator="containsText" id="{8a76ae06-6035-4093-bfda-5a7f3ef4f134}">
+          <x14:cfRule type="containsText" priority="685" operator="containsText" id="{9fdc58d4-54d2-40dc-8333-2f373761c3a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I155)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12556,7 +12570,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="672" operator="containsText" id="{a0455528-6c9e-4a89-b7d1-7e3a2c739546}">
+          <x14:cfRule type="containsText" priority="686" operator="containsText" id="{3c8a01d0-38b8-4f19-b0a4-282fc87639bd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I155)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12574,7 +12588,7 @@
           <xm:sqref>I155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="643" operator="containsText" id="{8a57d4f9-342d-40b8-ba0e-06d3cf67bb1a}">
+          <x14:cfRule type="containsText" priority="657" operator="containsText" id="{2e184a62-c5e5-426f-8034-20c34dfbe3f8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12589,7 +12603,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="644" operator="containsText" id="{1ee9ee15-2021-403c-827b-2c1bd6f43d25}">
+          <x14:cfRule type="containsText" priority="658" operator="containsText" id="{25c3c7ba-e758-4576-8cf7-a64c1f0e5faf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12607,7 +12621,7 @@
           <xm:sqref>I156</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="633" operator="containsText" id="{80c186b4-26d6-4434-8c81-b0c50c899fbd}">
+          <x14:cfRule type="containsText" priority="647" operator="containsText" id="{e2deebf3-77d0-4933-89cf-bc594e559034}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12622,7 +12636,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="634" operator="containsText" id="{865f0fd4-feb8-4f92-b4be-93c509138fe5}">
+          <x14:cfRule type="containsText" priority="648" operator="containsText" id="{833fc81c-d685-4737-ab09-ec263c027d61}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12640,7 +12654,7 @@
           <xm:sqref>L156</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="645" operator="containsText" id="{562b4e81-3cab-40d8-b3b0-1ed9f9748b49}">
+          <x14:cfRule type="containsText" priority="659" operator="containsText" id="{e0ee5092-56cb-46ce-9ab8-ab4fa8ad0fb8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I158)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12655,7 +12669,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="646" operator="containsText" id="{41a749fe-932f-444b-9fd4-12c46134a7d9}">
+          <x14:cfRule type="containsText" priority="660" operator="containsText" id="{ef6be51b-ac2a-4702-91e3-88654eebe861}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I158)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12673,7 +12687,7 @@
           <xm:sqref>I158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="623" operator="containsText" id="{943a1837-e467-462c-bfc0-1489073d272e}">
+          <x14:cfRule type="containsText" priority="637" operator="containsText" id="{8cc8c399-1f9c-4d46-bdf7-73b310955c40}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I160)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12688,7 +12702,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="624" operator="containsText" id="{08169eb9-4463-4c62-9e19-5e3f4df6c7e8}">
+          <x14:cfRule type="containsText" priority="638" operator="containsText" id="{596c09c4-39e2-4ccf-b07c-c6ed369dd87a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I160)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12706,7 +12720,7 @@
           <xm:sqref>I160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="621" operator="containsText" id="{c3bb65b1-7faa-4623-aad9-a316f7853230}">
+          <x14:cfRule type="containsText" priority="635" operator="containsText" id="{fe760126-4feb-4268-a2a6-1bb441328c81}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I161)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12721,7 +12735,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="622" operator="containsText" id="{68f612db-e8e3-4947-88db-92f0b6c9cd3d}">
+          <x14:cfRule type="containsText" priority="636" operator="containsText" id="{ae15a286-1192-46a3-ad8d-e7348a2844ec}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I161)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12739,7 +12753,7 @@
           <xm:sqref>I161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="627" operator="containsText" id="{be4365b4-e40e-4e6b-a8dd-9a7c4d8c6390}">
+          <x14:cfRule type="containsText" priority="641" operator="containsText" id="{786433a3-a5bd-425d-8b2e-ccf185fc39f7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L161)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12754,7 +12768,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="628" operator="containsText" id="{8183024a-2591-44e5-8c89-ce3361dc355b}">
+          <x14:cfRule type="containsText" priority="642" operator="containsText" id="{307ef040-5f01-408b-a137-55dd285a8b4f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L161)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12772,7 +12786,7 @@
           <xm:sqref>L161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="613" operator="containsText" id="{719c16b8-3ca4-4cde-9909-f77746a1b570}">
+          <x14:cfRule type="containsText" priority="627" operator="containsText" id="{733a6ce1-7929-4e3a-ba76-e3502bf1ba93}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I162)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12787,7 +12801,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="614" operator="containsText" id="{f2d0f446-b70d-4724-bf9c-21d551a8ca67}">
+          <x14:cfRule type="containsText" priority="628" operator="containsText" id="{f16a2935-d164-4b31-859e-b1bfd7681157}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I162)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12805,7 +12819,7 @@
           <xm:sqref>I162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="615" operator="containsText" id="{bdd03a63-da02-4f94-a375-7ec7e63f4abd}">
+          <x14:cfRule type="containsText" priority="629" operator="containsText" id="{dd72c717-332a-45fb-9bbc-d229bf47464b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I163)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12820,7 +12834,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="616" operator="containsText" id="{1224c913-2d6d-4a48-806b-e0debdf0b998}">
+          <x14:cfRule type="containsText" priority="630" operator="containsText" id="{3fcba348-33c1-4b60-9aba-1a277fd788c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I163)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12838,7 +12852,7 @@
           <xm:sqref>I163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="639" operator="containsText" id="{373f51d3-23ea-4b1b-87ed-fc23d21de4fe}">
+          <x14:cfRule type="containsText" priority="653" operator="containsText" id="{a0373c03-91cd-45fb-a1c0-b35fbdf8831d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I165)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12853,7 +12867,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="640" operator="containsText" id="{c83a4fc8-8287-4b10-aa8d-6fd910b4c0ba}">
+          <x14:cfRule type="containsText" priority="654" operator="containsText" id="{dc385d89-bb2b-4e63-b77e-0cb647c9a784}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I165)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12871,7 +12885,7 @@
           <xm:sqref>I165</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="647" operator="containsText" id="{7cddbca6-915d-4a3d-8eb5-353e58521824}">
+          <x14:cfRule type="containsText" priority="661" operator="containsText" id="{334d53d8-b756-4fa6-a4e3-938cdaef5c38}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I166)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12886,7 +12900,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="648" operator="containsText" id="{7a5a3f55-d294-44e5-9ab7-6f473faa5fbd}">
+          <x14:cfRule type="containsText" priority="662" operator="containsText" id="{7dd1900f-df4b-4d55-90a5-264463897d60}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I166)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12904,7 +12918,7 @@
           <xm:sqref>I166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="619" operator="containsText" id="{f2bd2f4c-231f-4b22-8f28-b93ebb3f9b1c}">
+          <x14:cfRule type="containsText" priority="633" operator="containsText" id="{036b6362-d72f-47ed-aebc-390ad7ba049b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12919,7 +12933,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="620" operator="containsText" id="{06911c20-8148-417a-839f-d6a2cf230f8e}">
+          <x14:cfRule type="containsText" priority="634" operator="containsText" id="{1dbeee1c-706d-452a-bf10-2cb5ef61f81f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12937,7 +12951,7 @@
           <xm:sqref>I167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="649" operator="containsText" id="{f7ab0cdd-05e1-4a5e-9288-8ccc0b57c1de}">
+          <x14:cfRule type="containsText" priority="663" operator="containsText" id="{c970fb9f-5c3a-4255-911c-ae8ca72b5704}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12952,7 +12966,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="650" operator="containsText" id="{e45e8774-a10f-4f7e-aa61-e541daa64e16}">
+          <x14:cfRule type="containsText" priority="664" operator="containsText" id="{d76988d0-d97a-46a8-988f-9984469358e0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12970,7 +12984,7 @@
           <xm:sqref>K167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="617" operator="containsText" id="{f9c450b5-853f-41b0-9bc6-10d737c27d63}">
+          <x14:cfRule type="containsText" priority="631" operator="containsText" id="{887cca1e-e6d6-494a-b068-cf0f4dac6036}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12985,7 +12999,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="618" operator="containsText" id="{19630a11-a925-4e99-b49e-fef8e83f357c}">
+          <x14:cfRule type="containsText" priority="632" operator="containsText" id="{13e83e0c-05a6-4397-8ff2-952fbf751c88}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13003,7 +13017,7 @@
           <xm:sqref>L167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="117" operator="containsText" id="{aa2f46bd-20b1-4632-89fb-73311d99d773}">
+          <x14:cfRule type="containsText" priority="131" operator="containsText" id="{2a8609a4-9a8b-4471-ad37-a1b740a74bec}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13018,7 +13032,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="118" operator="containsText" id="{3ffa42df-5359-4f16-a356-cb750880778b}">
+          <x14:cfRule type="containsText" priority="132" operator="containsText" id="{80c26520-3e54-4f88-9bbd-5d89a60d9248}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13036,7 +13050,7 @@
           <xm:sqref>G168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="641" operator="containsText" id="{18b17b6d-e5c6-40c8-9293-345fdeb45865}">
+          <x14:cfRule type="containsText" priority="655" operator="containsText" id="{17361b83-fa71-4bce-beb5-10f220484f5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13051,7 +13065,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="642" operator="containsText" id="{c4201a88-2f75-4b26-a8f1-d7bffb28991e}">
+          <x14:cfRule type="containsText" priority="656" operator="containsText" id="{09960ae4-439d-449a-9e3b-ba69a759da14}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13069,7 +13083,7 @@
           <xm:sqref>I168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="631" operator="containsText" id="{9ba421f9-8914-4ca1-b3ed-ba0432ecf144}">
+          <x14:cfRule type="containsText" priority="645" operator="containsText" id="{40c2152d-3ffc-493d-a115-4923e2eb2219}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I169)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13084,7 +13098,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="632" operator="containsText" id="{6d00d0ec-c8cf-4eb6-bb5b-9d2b971a9e82}">
+          <x14:cfRule type="containsText" priority="646" operator="containsText" id="{0b79345a-7c21-4273-a3c3-88a9a2bce695}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I169)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13102,7 +13116,7 @@
           <xm:sqref>I169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="597" operator="containsText" id="{adedd573-5d96-48ec-a7db-204a9c8b5fcd}">
+          <x14:cfRule type="containsText" priority="611" operator="containsText" id="{331f8097-062f-4228-b487-33a69937b276}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13117,7 +13131,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="598" operator="containsText" id="{682034c5-b582-460f-9d01-cecb319d8327}">
+          <x14:cfRule type="containsText" priority="612" operator="containsText" id="{063f9535-1bdb-4889-abbf-e989c90c10cd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13135,7 +13149,7 @@
           <xm:sqref>I170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="591" operator="containsText" id="{51d10a12-c82d-4ee7-99f4-531036991516}">
+          <x14:cfRule type="containsText" priority="605" operator="containsText" id="{cb5a924b-3cb4-4e95-ae50-48b7334c1c54}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13150,7 +13164,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="592" operator="containsText" id="{3893d51c-56a0-4277-bde4-0af0154dea21}">
+          <x14:cfRule type="containsText" priority="606" operator="containsText" id="{0c92598c-ae11-4be6-8fa6-e9eb67698a2c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13168,7 +13182,7 @@
           <xm:sqref>L170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="567" operator="containsText" id="{c9c52a7f-0a2d-4a03-9645-9f8da8832358}">
+          <x14:cfRule type="containsText" priority="581" operator="containsText" id="{3e8bfe0e-b517-4f3b-8c22-9a1e84f2ebbf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13183,7 +13197,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="568" operator="containsText" id="{5a27d960-3468-4820-a330-cf4875e9be58}">
+          <x14:cfRule type="containsText" priority="582" operator="containsText" id="{09afa2ae-97fc-4e4d-84b2-2fa815edccb9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13201,7 +13215,7 @@
           <xm:sqref>I171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="151" operator="containsText" id="{e91c45a6-7efe-499b-b134-755e497d8592}">
+          <x14:cfRule type="containsText" priority="165" operator="containsText" id="{0bbb4e4d-bf5b-463d-8126-8599052ddad6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13216,7 +13230,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="152" operator="containsText" id="{05ef9f5d-d8ec-4c5e-a13e-cba87ba55977}">
+          <x14:cfRule type="containsText" priority="166" operator="containsText" id="{bb6cae24-8454-4678-b2a8-2179e38ae56c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13234,7 +13248,7 @@
           <xm:sqref>K171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="565" operator="containsText" id="{1ed4c0dc-dd3b-4431-8f55-84f087ec8e4f}">
+          <x14:cfRule type="containsText" priority="579" operator="containsText" id="{99723954-3d42-41c2-b471-27a34fbd1c9d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13249,7 +13263,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="566" operator="containsText" id="{6a1c3824-e8f1-417a-85da-52836dcaeca0}">
+          <x14:cfRule type="containsText" priority="580" operator="containsText" id="{a946dd41-f0a9-4d0f-8b98-2ca314235291}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13267,7 +13281,7 @@
           <xm:sqref>L171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="599" operator="containsText" id="{7b9363a1-4726-49b7-a6c9-2730d84725d9}">
+          <x14:cfRule type="containsText" priority="613" operator="containsText" id="{aac3dc52-196b-4c50-b05e-2aa4efc6db13}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I172)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13282,7 +13296,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="600" operator="containsText" id="{948910c0-0a22-441a-b9db-97452d697e22}">
+          <x14:cfRule type="containsText" priority="614" operator="containsText" id="{8b4c549b-281d-4c8d-9a48-11eb1069806d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I172)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13300,7 +13314,7 @@
           <xm:sqref>I172</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="585" operator="containsText" id="{bdd7b84c-602e-4493-ae9b-81b5d29dd118}">
+          <x14:cfRule type="containsText" priority="599" operator="containsText" id="{3dedca25-f44b-4bfb-ac28-6b2958ec04be}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I174)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13315,7 +13329,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="586" operator="containsText" id="{b972cb7e-6ba6-4366-a223-5f47410ac0d6}">
+          <x14:cfRule type="containsText" priority="600" operator="containsText" id="{82ea49df-0f0f-46d3-891b-0d4887c49f12}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I174)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13333,7 +13347,7 @@
           <xm:sqref>I174</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="583" operator="containsText" id="{c77c8a20-11b1-4701-b721-680773317137}">
+          <x14:cfRule type="containsText" priority="597" operator="containsText" id="{95d081c8-bf2e-4d8a-915a-83214b6c557f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13348,7 +13362,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="584" operator="containsText" id="{8a1909b0-ac7d-49dc-8a6e-a5ce4740cb74}">
+          <x14:cfRule type="containsText" priority="598" operator="containsText" id="{6d30a0be-e5af-4485-9f99-755888472d62}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13366,7 +13380,7 @@
           <xm:sqref>I175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="507" operator="containsText" id="{33a4577e-be01-4e22-bcc2-6588776713a3}">
+          <x14:cfRule type="containsText" priority="521" operator="containsText" id="{9f00a1b8-237c-4060-8d98-22a8a110f310}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13381,7 +13395,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="508" operator="containsText" id="{1d31d150-64f0-4372-bc22-a19d8c793281}">
+          <x14:cfRule type="containsText" priority="522" operator="containsText" id="{5e93d152-68ce-42d5-be83-1094c585048d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13399,7 +13413,7 @@
           <xm:sqref>K175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="559" operator="containsText" id="{f8eb9a17-7855-49e4-ab9c-5cdde694d8ff}">
+          <x14:cfRule type="containsText" priority="573" operator="containsText" id="{c1dc8280-8884-4e21-bcf8-40d5cc8e44cd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13414,7 +13428,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="560" operator="containsText" id="{d349af19-e161-4b9a-91c9-5e3258ce43dc}">
+          <x14:cfRule type="containsText" priority="574" operator="containsText" id="{5c41f620-6e83-4fd3-bee0-7a8edf9d8f37}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13432,7 +13446,7 @@
           <xm:sqref>L175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="561" operator="containsText" id="{49f03238-d8f7-45c3-82f7-d23ba402d263}">
+          <x14:cfRule type="containsText" priority="575" operator="containsText" id="{ea92af7b-e2be-4eef-9db9-cb23cef618a6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I176)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13447,7 +13461,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="562" operator="containsText" id="{4ee2263f-053f-476e-b22b-4e87cf576d22}">
+          <x14:cfRule type="containsText" priority="576" operator="containsText" id="{d478c69a-229a-48b0-b5fa-f8bc74dcece4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I176)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13465,7 +13479,7 @@
           <xm:sqref>I176</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="563" operator="containsText" id="{4aa5086c-f538-46a8-818a-bfff539b600c}">
+          <x14:cfRule type="containsText" priority="577" operator="containsText" id="{4353586d-2e77-40e7-9f3d-3d73e1aec4fe}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I177)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13480,7 +13494,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="564" operator="containsText" id="{6fd48abe-e3b3-4ad0-b599-5b218f6af79f}">
+          <x14:cfRule type="containsText" priority="578" operator="containsText" id="{0b4c1621-bac0-4617-bcf5-770a10190e4f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I177)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13498,7 +13512,7 @@
           <xm:sqref>I177</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="593" operator="containsText" id="{1b86ee6d-c12a-4748-9fa8-132529c95b2e}">
+          <x14:cfRule type="containsText" priority="607" operator="containsText" id="{1ea34bd4-784a-43a0-b4bd-046734b9cc64}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I179)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13513,7 +13527,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="594" operator="containsText" id="{cb940a2d-07a3-4521-9c53-f57eb29f08b8}">
+          <x14:cfRule type="containsText" priority="608" operator="containsText" id="{7fe98c22-ac88-4016-b8cf-0def530ac0a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I179)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13531,7 +13545,7 @@
           <xm:sqref>I179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="601" operator="containsText" id="{f1644536-7c7a-4033-b07f-b7fb89bf6c82}">
+          <x14:cfRule type="containsText" priority="615" operator="containsText" id="{2532e5ba-99ef-4ff6-b780-96659525490a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I180)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13546,7 +13560,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="602" operator="containsText" id="{69506c1f-dfa6-4fe7-baf8-f5ea9d908864}">
+          <x14:cfRule type="containsText" priority="616" operator="containsText" id="{26d9330d-f8f4-4ba8-a103-4593a31f8715}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I180)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13564,7 +13578,7 @@
           <xm:sqref>I180</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="571" operator="containsText" id="{0695d96c-7cd6-4851-ae42-672edb06f62b}">
+          <x14:cfRule type="containsText" priority="585" operator="containsText" id="{a4c52e70-0af8-4de8-8243-70ecf6e46213}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13579,7 +13593,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="572" operator="containsText" id="{87055f02-2c35-4faa-9fef-8a15c140a742}">
+          <x14:cfRule type="containsText" priority="586" operator="containsText" id="{daeef6d9-f370-4bcd-9664-c975409b4f2e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13597,7 +13611,7 @@
           <xm:sqref>I181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="603" operator="containsText" id="{a0b4efa4-6003-417a-8175-e0fe6d6a77c6}">
+          <x14:cfRule type="containsText" priority="617" operator="containsText" id="{85e2b841-2290-4551-9b35-bb08cc98fb1c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13612,7 +13626,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="604" operator="containsText" id="{2c35268b-3aaf-45c0-8704-05961f2f4398}">
+          <x14:cfRule type="containsText" priority="618" operator="containsText" id="{2d16477a-0562-44e0-a16a-d338a23dc313}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13630,7 +13644,7 @@
           <xm:sqref>K181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="569" operator="containsText" id="{7022f227-44d2-4916-b8b5-d2d39b07e8a7}">
+          <x14:cfRule type="containsText" priority="583" operator="containsText" id="{e8017c2a-b558-401e-84ad-59b0b08df8a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13645,7 +13659,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="570" operator="containsText" id="{1933746f-c0ed-4dee-a676-804525b6b8f5}">
+          <x14:cfRule type="containsText" priority="584" operator="containsText" id="{0fb48f1b-c6f7-4afd-bbf9-b0aa87e8876b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13663,7 +13677,7 @@
           <xm:sqref>L181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="113" operator="containsText" id="{fe46f071-66ed-4ed2-8803-aa027973d377}">
+          <x14:cfRule type="containsText" priority="127" operator="containsText" id="{4a666582-e966-4808-81b7-70379cae7221}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13678,7 +13692,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="114" operator="containsText" id="{21f026b0-6dc0-403d-9bfd-90c471bbcb53}">
+          <x14:cfRule type="containsText" priority="128" operator="containsText" id="{bbe55f48-d41d-47da-8503-b2bd8933acec}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13696,7 +13710,7 @@
           <xm:sqref>G182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="595" operator="containsText" id="{bfbf19e8-8924-4ff9-9848-9a34a3ac643d}">
+          <x14:cfRule type="containsText" priority="609" operator="containsText" id="{acfee822-9b07-4f52-927e-2514c678e270}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13711,7 +13725,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="596" operator="containsText" id="{4cef4123-8af2-4aaa-bec5-a8fd20dd4f8d}">
+          <x14:cfRule type="containsText" priority="610" operator="containsText" id="{25c7007c-b64b-4358-bc06-6721337512e1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13729,7 +13743,7 @@
           <xm:sqref>I182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="573" operator="containsText" id="{ccf5956a-9f5a-4406-af32-66a6e3434f1f}">
+          <x14:cfRule type="containsText" priority="587" operator="containsText" id="{a40c1c17-50ae-4da1-9648-b01e89e32bf8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I183)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13744,7 +13758,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="574" operator="containsText" id="{88459d76-ec84-4de3-ba99-db57f8adb47b}">
+          <x14:cfRule type="containsText" priority="588" operator="containsText" id="{487b7d5c-63df-4947-9df3-23069ef240b1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I183)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13762,7 +13776,7 @@
           <xm:sqref>I183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="543" operator="containsText" id="{7e677287-0299-409a-8680-48f644112427}">
+          <x14:cfRule type="containsText" priority="557" operator="containsText" id="{37f82c7b-ab74-4479-87e0-843be5a7aaa7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13777,7 +13791,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="544" operator="containsText" id="{adfa6653-106e-4fa1-a5fd-e2e1627473b2}">
+          <x14:cfRule type="containsText" priority="558" operator="containsText" id="{136159fd-21cf-4b9f-9c61-f6dd57686092}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13795,7 +13809,7 @@
           <xm:sqref>I184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="537" operator="containsText" id="{442fadf3-6006-4705-97ab-aebf75a5615f}">
+          <x14:cfRule type="containsText" priority="551" operator="containsText" id="{bb3dfea8-7107-4011-8eb4-475d69ed426b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13810,7 +13824,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="538" operator="containsText" id="{ee3de7c2-33d0-4211-9904-091154706663}">
+          <x14:cfRule type="containsText" priority="552" operator="containsText" id="{810d5213-e1a8-40d9-99ab-aab5b822c7b7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13828,7 +13842,7 @@
           <xm:sqref>L184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="525" operator="containsText" id="{1329b7b8-72a0-4d7c-b748-38ca180f90ad}">
+          <x14:cfRule type="containsText" priority="539" operator="containsText" id="{35f4a93f-25c0-4810-8b94-45263e76bba2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I185)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13843,7 +13857,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="526" operator="containsText" id="{67e1022e-f7a7-435a-8eb7-f08e53b1cefa}">
+          <x14:cfRule type="containsText" priority="540" operator="containsText" id="{40c82d32-8695-4ae3-a667-be82538aac89}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I185)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13861,7 +13875,7 @@
           <xm:sqref>I185</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="523" operator="containsText" id="{f2ae3986-5ec7-4757-924a-fc568aae4b6c}">
+          <x14:cfRule type="containsText" priority="537" operator="containsText" id="{8998f1d0-ab0f-40b0-b127-f7fb2d036c35}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L185)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13876,7 +13890,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="524" operator="containsText" id="{32b9637b-7c11-470e-a630-45bec76a5bf0}">
+          <x14:cfRule type="containsText" priority="538" operator="containsText" id="{6b97790e-ffb1-4096-88fd-94c63511ecaa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L185)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13894,7 +13908,7 @@
           <xm:sqref>L185</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="545" operator="containsText" id="{7e8254ac-e47e-4b18-84a0-df077386ffaf}">
+          <x14:cfRule type="containsText" priority="559" operator="containsText" id="{a0110a72-bd5c-4f8a-b943-d0774cd90ab1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I186)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13909,7 +13923,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="546" operator="containsText" id="{803346ae-0d10-4c83-b321-ad1b80805c76}">
+          <x14:cfRule type="containsText" priority="560" operator="containsText" id="{e7128929-e085-4c24-9a75-9678b2d5b964}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I186)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13927,7 +13941,7 @@
           <xm:sqref>I186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="535" operator="containsText" id="{f7737256-2920-4591-804f-be01c6222c8b}">
+          <x14:cfRule type="containsText" priority="549" operator="containsText" id="{80dc9921-1d6d-4f53-8495-a3cc01e81acc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I188)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13942,7 +13956,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="536" operator="containsText" id="{c6d115d9-d45e-48a9-91d8-07d6165e66bf}">
+          <x14:cfRule type="containsText" priority="550" operator="containsText" id="{ae449a50-30f0-4462-88e2-4d7b103b2aed}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I188)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13960,7 +13974,7 @@
           <xm:sqref>I188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="533" operator="containsText" id="{47607060-b29f-4d71-ba9b-92e28edecbf6}">
+          <x14:cfRule type="containsText" priority="547" operator="containsText" id="{90fb81e9-0731-469c-9df1-d1ba452a4768}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13975,7 +13989,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="534" operator="containsText" id="{69c2a759-5946-49dd-9991-e36da50c0bca}">
+          <x14:cfRule type="containsText" priority="548" operator="containsText" id="{40ce091f-541c-49a3-830e-b7d985947665}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13993,7 +14007,7 @@
           <xm:sqref>I189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="179" operator="containsText" id="{2c526d7e-7100-4f82-8b66-7b6c890f8ae0}">
+          <x14:cfRule type="containsText" priority="193" operator="containsText" id="{10089050-028b-497b-9915-5dc6b3ac761f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14008,7 +14022,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="180" operator="containsText" id="{99343cb3-0b81-47ab-8d88-c412244dd360}">
+          <x14:cfRule type="containsText" priority="194" operator="containsText" id="{70c66176-4989-468b-903a-4ffa81185293}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14026,7 +14040,7 @@
           <xm:sqref>K189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="511" operator="containsText" id="{4b71749c-622a-4e87-91e4-410e88fea46e}">
+          <x14:cfRule type="containsText" priority="525" operator="containsText" id="{4dc5f4ee-a14c-47ba-84e7-896df17105ea}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14041,7 +14055,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="512" operator="containsText" id="{299eb9f1-4edb-4a92-bcce-a37ea6363daf}">
+          <x14:cfRule type="containsText" priority="526" operator="containsText" id="{05d46f54-1056-4865-ac0a-3c2a37f6d516}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14059,7 +14073,7 @@
           <xm:sqref>L189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="509" operator="containsText" id="{5845cc18-53ca-4e7e-b93a-62d92b155455}">
+          <x14:cfRule type="containsText" priority="523" operator="containsText" id="{217e6c45-8544-47d5-920d-3906766e94d4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I190)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14074,7 +14088,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="510" operator="containsText" id="{46d75862-7202-4824-9dad-8d2e0f3cebdb}">
+          <x14:cfRule type="containsText" priority="524" operator="containsText" id="{64123ebf-93ac-4a7f-bce9-4fa237eab3ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I190)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14092,7 +14106,7 @@
           <xm:sqref>I190</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="521" operator="containsText" id="{e1510c6f-dc22-4e6c-af26-a649cb4a6bad}">
+          <x14:cfRule type="containsText" priority="535" operator="containsText" id="{7284a0e7-1ddf-48f4-ae22-555c78fb9b91}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I191)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14107,7 +14121,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="522" operator="containsText" id="{09c9a136-be68-4fef-9fe3-21eb004ce607}">
+          <x14:cfRule type="containsText" priority="536" operator="containsText" id="{6bff71fb-6f23-4e0a-815b-990559cbcab0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I191)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14125,7 +14139,7 @@
           <xm:sqref>I191</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="539" operator="containsText" id="{ea6b804b-49c8-4239-8ce9-1f96c95fd59f}">
+          <x14:cfRule type="containsText" priority="553" operator="containsText" id="{900a8205-5512-4b01-9f74-f3d83a68a936}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I193)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14140,7 +14154,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="540" operator="containsText" id="{dd387301-8404-496b-8a0d-dbde76d1145e}">
+          <x14:cfRule type="containsText" priority="554" operator="containsText" id="{d05e7c8a-376c-40eb-abbf-9e30c433729b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I193)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14158,7 +14172,7 @@
           <xm:sqref>I193</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="547" operator="containsText" id="{eda71cb8-0312-4811-8b0d-6ec9f251943d}">
+          <x14:cfRule type="containsText" priority="561" operator="containsText" id="{f2faddf2-b764-419b-9976-f60f50748c43}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I194)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14173,7 +14187,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="548" operator="containsText" id="{8a81c288-6fbd-4e0b-a143-afe0d065b74b}">
+          <x14:cfRule type="containsText" priority="562" operator="containsText" id="{9f5c82ca-dcbb-4e74-8f43-20e576c89a6f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I194)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14191,7 +14205,7 @@
           <xm:sqref>I194</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="515" operator="containsText" id="{7c6722de-e9ed-4fd3-9e23-1797f39e61b8}">
+          <x14:cfRule type="containsText" priority="529" operator="containsText" id="{4d9d0a40-5586-4bdb-9d25-4b88ac61967d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14206,7 +14220,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="516" operator="containsText" id="{dc9a28ce-6f64-4fae-9242-631e950d4f6c}">
+          <x14:cfRule type="containsText" priority="530" operator="containsText" id="{1920d865-b743-4a93-a797-8f9ed6deab0a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14224,7 +14238,7 @@
           <xm:sqref>I195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="177" operator="containsText" id="{4e2d45a0-bb48-4787-831a-b5b82b656ac3}">
+          <x14:cfRule type="containsText" priority="191" operator="containsText" id="{fa2dcf7b-708d-4cae-a0d5-172264b14d64}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14239,7 +14253,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="178" operator="containsText" id="{42b357ef-da92-404a-8496-2f52e98e598d}">
+          <x14:cfRule type="containsText" priority="192" operator="containsText" id="{c01f52d2-4c65-42d7-b49c-03642a7e73dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14257,7 +14271,7 @@
           <xm:sqref>K195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="513" operator="containsText" id="{58be00ab-a292-4119-80a2-f0725484eb06}">
+          <x14:cfRule type="containsText" priority="527" operator="containsText" id="{b25fa30e-6500-445c-95e0-3cb5a9617b97}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14272,7 +14286,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="514" operator="containsText" id="{2b9e46d0-3df9-4611-8f40-225a0d069551}">
+          <x14:cfRule type="containsText" priority="528" operator="containsText" id="{2aa38cbd-4561-4dd1-8dea-50e7a5768c32}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14290,7 +14304,7 @@
           <xm:sqref>L195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{80afd11a-b3ec-4155-a9da-4b8d18d717d7}">
+          <x14:cfRule type="containsText" priority="123" operator="containsText" id="{3ccc2766-5601-4e9b-acc3-f683f931fe48}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14305,7 +14319,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{63c8ab32-22d2-4d2a-9faf-5d9c47f6c3f3}">
+          <x14:cfRule type="containsText" priority="124" operator="containsText" id="{d758a2ed-cae7-4901-a75c-3ed062e63712}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14323,7 +14337,7 @@
           <xm:sqref>G196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="541" operator="containsText" id="{a6e720d6-eed6-4ab7-a6dd-4ff70537366c}">
+          <x14:cfRule type="containsText" priority="555" operator="containsText" id="{87506e95-9ee9-412c-8cb0-f0616f75346d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14338,7 +14352,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="542" operator="containsText" id="{9a201054-a807-4db4-becc-311ef88522c2}">
+          <x14:cfRule type="containsText" priority="556" operator="containsText" id="{6ed72d66-36e3-45e4-a919-49a7c7261607}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14356,7 +14370,7 @@
           <xm:sqref>I196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="531" operator="containsText" id="{f69778ec-65bb-49ee-968a-30962c6b8414}">
+          <x14:cfRule type="containsText" priority="545" operator="containsText" id="{e1a75d30-781c-439a-b995-93d0fe5a48ba}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I197)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14371,7 +14385,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="532" operator="containsText" id="{e7a0b849-81a1-40b5-91fe-642d0c23da9f}">
+          <x14:cfRule type="containsText" priority="546" operator="containsText" id="{5b68a163-a143-4e50-b736-647366f0a12c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I197)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14389,7 +14403,7 @@
           <xm:sqref>I197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="489" operator="containsText" id="{4279e510-a56e-4ba6-a7e1-659e8cdf5401}">
+          <x14:cfRule type="containsText" priority="503" operator="containsText" id="{95a58a4d-89fb-4a82-9efd-91c780b7eaca}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14404,7 +14418,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="490" operator="containsText" id="{5d6dd710-bf64-4555-8d31-6c1a48cdc3bb}">
+          <x14:cfRule type="containsText" priority="504" operator="containsText" id="{d92ee231-1c15-4589-a6d9-b129c38aa916}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14422,7 +14436,7 @@
           <xm:sqref>I198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="483" operator="containsText" id="{447ca5f8-4d07-4633-a0a3-2eb05a5806ed}">
+          <x14:cfRule type="containsText" priority="497" operator="containsText" id="{f79f1166-f5b2-451b-93bd-504f57c3c123}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14437,7 +14451,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="484" operator="containsText" id="{069d5524-2419-486e-b87c-26878fbf48ab}">
+          <x14:cfRule type="containsText" priority="498" operator="containsText" id="{9b2486ff-478c-4440-937f-25e63757b896}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14455,7 +14469,7 @@
           <xm:sqref>L198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="475" operator="containsText" id="{9d59d39b-d00d-44ad-8063-1faae3aa9fcb}">
+          <x14:cfRule type="containsText" priority="489" operator="containsText" id="{f3a1641c-4b34-4698-aed7-4be89dc242ed}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14470,7 +14484,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="476" operator="containsText" id="{d548b9cf-9948-4648-8e73-a0babfce2993}">
+          <x14:cfRule type="containsText" priority="490" operator="containsText" id="{25dd3072-f53a-4e98-b0fa-7ed76a8c38af}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14488,7 +14502,7 @@
           <xm:sqref>I199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="175" operator="containsText" id="{bc09c8a0-28ec-41b7-ba1b-2c9c125da5a1}">
+          <x14:cfRule type="containsText" priority="189" operator="containsText" id="{2d7c0730-1b39-420a-ae5e-65c95cbde4da}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14503,7 +14517,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="176" operator="containsText" id="{fbe11d3e-0acb-451f-8677-814ee9463d45}">
+          <x14:cfRule type="containsText" priority="190" operator="containsText" id="{63cb1674-6ac4-403c-a4c6-f1c74d1538dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14521,7 +14535,7 @@
           <xm:sqref>K199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="455" operator="containsText" id="{ae7c79d7-8947-480a-9ce3-c0c07771db59}">
+          <x14:cfRule type="containsText" priority="469" operator="containsText" id="{69211355-4440-43da-9fea-9ddef4e647b0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14536,7 +14550,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="456" operator="containsText" id="{843efc0f-6618-476b-bc9d-67c6d0b70a1d}">
+          <x14:cfRule type="containsText" priority="470" operator="containsText" id="{6f82b4ff-2927-421c-83dd-7ed647e84b33}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14554,7 +14568,7 @@
           <xm:sqref>L199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="491" operator="containsText" id="{ebd59229-5138-4092-8466-4aee6097e6a5}">
+          <x14:cfRule type="containsText" priority="505" operator="containsText" id="{d6641c87-f03c-4341-ad9e-eab22f277dfe}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I200)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14569,7 +14583,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="492" operator="containsText" id="{620cd1a8-8048-4e28-a954-24419c47975e}">
+          <x14:cfRule type="containsText" priority="506" operator="containsText" id="{93061a71-cb60-49e5-8312-294acf811ca7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I200)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14587,7 +14601,7 @@
           <xm:sqref>I200</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="481" operator="containsText" id="{596c465e-6e69-4062-a2bb-3a886b12f291}">
+          <x14:cfRule type="containsText" priority="495" operator="containsText" id="{27572ea5-4d8e-4dc0-acf1-e45cfe4fc931}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I202)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14602,7 +14616,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="482" operator="containsText" id="{49981752-7755-4ba4-8606-2f5ca3365985}">
+          <x14:cfRule type="containsText" priority="496" operator="containsText" id="{62fced1f-4ca1-4eb8-b517-2077e1bfd99a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I202)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14620,7 +14634,7 @@
           <xm:sqref>I202</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="479" operator="containsText" id="{4f2aad3d-98d4-4c88-831e-1c9f71f18d9a}">
+          <x14:cfRule type="containsText" priority="493" operator="containsText" id="{298e1fc3-abec-4fb0-b19b-969ef0b2b42d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14635,7 +14649,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="480" operator="containsText" id="{8ec37b61-a789-4c5f-93e3-1f62b3254ae3}">
+          <x14:cfRule type="containsText" priority="494" operator="containsText" id="{1faa4cdc-9c88-4a3a-9e8d-b1b4ee85773e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14653,7 +14667,7 @@
           <xm:sqref>I203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="173" operator="containsText" id="{bc6adbe8-a045-4e7d-8950-cd342604cadd}">
+          <x14:cfRule type="containsText" priority="187" operator="containsText" id="{6d5af6b9-4b26-4829-b672-70c44fb96d9f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14668,7 +14682,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="174" operator="containsText" id="{4ac47483-f18b-4f0b-9af9-902609778554}">
+          <x14:cfRule type="containsText" priority="188" operator="containsText" id="{ede6fe3a-46bd-4d0f-932b-9a0c90c3e62b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14686,7 +14700,7 @@
           <xm:sqref>K203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="461" operator="containsText" id="{2ba42c1f-c892-40a7-9060-df9b11e37bd8}">
+          <x14:cfRule type="containsText" priority="475" operator="containsText" id="{d79b8c52-ace2-454a-aeb1-daf9a9628794}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14701,7 +14715,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="462" operator="containsText" id="{dd4e68a3-bd99-478d-97a1-9587f427185c}">
+          <x14:cfRule type="containsText" priority="476" operator="containsText" id="{907293c3-0bd5-401b-a495-ef7f31ef54e8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14719,7 +14733,7 @@
           <xm:sqref>L203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="463" operator="containsText" id="{48c3c090-516e-4ad4-b23f-84174e5ed7cd}">
+          <x14:cfRule type="containsText" priority="477" operator="containsText" id="{a28151aa-c6b1-40e3-b67f-4bf44215a7af}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I204)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14734,7 +14748,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="464" operator="containsText" id="{a67531bb-c59e-4948-9480-570e9134d484}">
+          <x14:cfRule type="containsText" priority="478" operator="containsText" id="{14ee1177-93a9-477d-b163-b09249e85263}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I204)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14752,7 +14766,7 @@
           <xm:sqref>I204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="453" operator="containsText" id="{78a1c320-5cf5-4eb4-9927-c57b173b3c94}">
+          <x14:cfRule type="containsText" priority="467" operator="containsText" id="{43e61c65-74d7-4d0a-85f0-4ed5724de909}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I205)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14767,7 +14781,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="454" operator="containsText" id="{b23f8342-0f8f-4167-af4b-ec0cf47ca542}">
+          <x14:cfRule type="containsText" priority="468" operator="containsText" id="{c843d041-0847-48ef-b14a-b252f1693a97}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I205)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14785,7 +14799,7 @@
           <xm:sqref>I205</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="485" operator="containsText" id="{cbb5b174-8688-483f-a1c7-d512cbe8387a}">
+          <x14:cfRule type="containsText" priority="499" operator="containsText" id="{535f66b5-e6df-4c3d-985a-7e60de50b9d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I207)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14800,7 +14814,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="486" operator="containsText" id="{6fb53faf-c72d-4236-9504-00b5d5611d4b}">
+          <x14:cfRule type="containsText" priority="500" operator="containsText" id="{bc71cc37-325f-4608-828a-c3ff4693dafd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I207)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14818,7 +14832,7 @@
           <xm:sqref>I207</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="493" operator="containsText" id="{79e5f102-8055-497e-914c-f475c22f5153}">
+          <x14:cfRule type="containsText" priority="507" operator="containsText" id="{9b00b42b-4732-4f04-88c1-33c7970481e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I208)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14833,7 +14847,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="494" operator="containsText" id="{d3927a03-5f3b-4446-9667-acec146b18f5}">
+          <x14:cfRule type="containsText" priority="508" operator="containsText" id="{e719f814-036f-4637-9f2b-7a2814389646}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I208)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14851,7 +14865,7 @@
           <xm:sqref>I208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="459" operator="containsText" id="{080b03c3-6956-4c1f-a743-a52ed7866f4a}">
+          <x14:cfRule type="containsText" priority="473" operator="containsText" id="{375d48ad-2f08-4d2c-ade4-219b163228a4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14866,7 +14880,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="460" operator="containsText" id="{2238fd0e-52cc-41f0-92d3-dba0c657a39d}">
+          <x14:cfRule type="containsText" priority="474" operator="containsText" id="{ebac8721-84f1-4211-9ca0-a4f3519c58cc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14884,7 +14898,7 @@
           <xm:sqref>I209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="171" operator="containsText" id="{86eceb73-7900-4fa3-822f-07063c8102c1}">
+          <x14:cfRule type="containsText" priority="185" operator="containsText" id="{44e7e77c-0353-4a33-8fa7-739e21528547}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14899,7 +14913,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="172" operator="containsText" id="{fff07e3a-568e-40b0-9e94-55ebadfdd94b}">
+          <x14:cfRule type="containsText" priority="186" operator="containsText" id="{2417fdb7-d4b2-48c1-86fe-33fbd8351f34}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14917,7 +14931,7 @@
           <xm:sqref>K209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="457" operator="containsText" id="{460155ff-e466-4c08-aa96-19e40fd8ac00}">
+          <x14:cfRule type="containsText" priority="471" operator="containsText" id="{638ad71f-f8b6-4bac-a07f-60419821da2a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14932,7 +14946,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="458" operator="containsText" id="{2a62ec65-3ba6-4a4a-bd3a-b4a75128b11c}">
+          <x14:cfRule type="containsText" priority="472" operator="containsText" id="{826f7258-a536-4fcf-91f6-3decb5a570fb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14950,7 +14964,7 @@
           <xm:sqref>L209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="103" operator="containsText" id="{70b88dcb-f3cc-45f0-9c7b-aae1a803d401}">
+          <x14:cfRule type="containsText" priority="117" operator="containsText" id="{1935dc98-4f1b-4f51-91e2-557616d34217}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14965,7 +14979,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="104" operator="containsText" id="{b28a08e7-afbb-445d-a900-4f21a3447b2d}">
+          <x14:cfRule type="containsText" priority="118" operator="containsText" id="{1bc0bf0c-7a27-4067-868f-ef330015989f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14983,7 +14997,7 @@
           <xm:sqref>G210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="487" operator="containsText" id="{7c936ea9-f775-4e55-9f2b-51d980408e17}">
+          <x14:cfRule type="containsText" priority="501" operator="containsText" id="{23cbcad8-1bb1-413f-a37c-44f5c98e0d97}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14998,7 +15012,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="488" operator="containsText" id="{5e229e8e-33e7-4840-aed7-61164eaaf997}">
+          <x14:cfRule type="containsText" priority="502" operator="containsText" id="{e692bbf2-5ff7-4a98-8961-48a8bcd0a265}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15016,7 +15030,7 @@
           <xm:sqref>I210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="107" operator="containsText" id="{1c17647e-54ef-4d13-bf38-e821ca81d8cf}">
+          <x14:cfRule type="containsText" priority="121" operator="containsText" id="{556e077f-18f3-486d-9891-63338eee92da}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15031,7 +15045,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{bf05142c-cc8c-4725-8961-95f0476b33ae}">
+          <x14:cfRule type="containsText" priority="122" operator="containsText" id="{16d04f4b-1d5a-45f3-a3a0-1fb4cb928d59}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15049,7 +15063,7 @@
           <xm:sqref>G211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="477" operator="containsText" id="{510c9f51-a139-4240-bb8b-aea8bd092a70}">
+          <x14:cfRule type="containsText" priority="491" operator="containsText" id="{d0958fa5-bccd-4f3b-a998-9ad46c0c3b6e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15064,7 +15078,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="478" operator="containsText" id="{8b0314c7-8dac-4ccf-a6a4-54dee81c3a69}">
+          <x14:cfRule type="containsText" priority="492" operator="containsText" id="{e75891c1-6937-475e-aa44-775a660b2fee}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15082,7 +15096,7 @@
           <xm:sqref>I211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="435" operator="containsText" id="{9376287c-d0e4-42bf-acb4-4611151f0fc5}">
+          <x14:cfRule type="containsText" priority="449" operator="containsText" id="{5bc18c21-79da-4f3e-95e4-cafbea38690b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15097,7 +15111,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="436" operator="containsText" id="{44a90cad-c384-4c61-a595-ae0daa052760}">
+          <x14:cfRule type="containsText" priority="450" operator="containsText" id="{7a542e25-5c25-4dbd-a875-a890a51a162a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15115,7 +15129,7 @@
           <xm:sqref>I212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="429" operator="containsText" id="{1d4ba4a7-9c1c-4df2-8b5a-56d5cbf5504c}">
+          <x14:cfRule type="containsText" priority="443" operator="containsText" id="{f879cd7f-d3b4-4d1d-a909-24e2d3078e18}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15130,7 +15144,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="430" operator="containsText" id="{93b56f4d-a0c9-4d25-8b0f-a1766f47ecc5}">
+          <x14:cfRule type="containsText" priority="444" operator="containsText" id="{3c6b4ab0-cccf-40a9-9ce7-f6ec103c05e8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15148,7 +15162,7 @@
           <xm:sqref>L212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="421" operator="containsText" id="{6b0de869-9bf5-4ef1-9abf-0b6abbccbaeb}">
+          <x14:cfRule type="containsText" priority="435" operator="containsText" id="{deb5fb58-fb97-46ae-8bd1-6f8b360c4a44}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I213)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15163,7 +15177,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="422" operator="containsText" id="{66fc8c3c-094d-4329-921a-83172d342d6f}">
+          <x14:cfRule type="containsText" priority="436" operator="containsText" id="{2c68d4f3-3f4b-4552-a7f0-87b09bd0631d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I213)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15181,7 +15195,7 @@
           <xm:sqref>I213</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="411" operator="containsText" id="{169d4cca-6785-4c2b-b6c4-4c46635920bc}">
+          <x14:cfRule type="containsText" priority="425" operator="containsText" id="{6c74c31e-8fd9-40a9-9806-12a1b1e549e2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L213)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15196,7 +15210,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="412" operator="containsText" id="{0265b61c-0832-435c-b997-2f7994d7746f}">
+          <x14:cfRule type="containsText" priority="426" operator="containsText" id="{aec73ef0-34b4-4b7c-ac8d-1b10eb88e6d9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L213)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15214,7 +15228,7 @@
           <xm:sqref>L213</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="437" operator="containsText" id="{f36be66e-be44-4ab7-8064-7beb88a2482e}">
+          <x14:cfRule type="containsText" priority="451" operator="containsText" id="{a6623a6c-a76f-4fe0-a267-e5d7a8c0baf7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I214)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15229,7 +15243,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="438" operator="containsText" id="{dd678ffb-94d6-4aef-a7d2-e2a794f610c5}">
+          <x14:cfRule type="containsText" priority="452" operator="containsText" id="{05bc97ce-f87d-46ef-97a6-a59873642324}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I214)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15247,7 +15261,7 @@
           <xm:sqref>I214</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="427" operator="containsText" id="{d35c7225-b190-4190-b5a4-0ec66804d205}">
+          <x14:cfRule type="containsText" priority="441" operator="containsText" id="{5b494129-d01f-45ed-a72a-e71da6bfbf92}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I216)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15262,7 +15276,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="428" operator="containsText" id="{e613d54f-e993-46a0-bab8-6525b71abba3}">
+          <x14:cfRule type="containsText" priority="442" operator="containsText" id="{b6c785c1-f463-4fcb-902f-cc0bf2aba18c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I216)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15280,7 +15294,7 @@
           <xm:sqref>I216</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="401" operator="containsText" id="{d8ef770e-7f75-4885-a3e5-3b724b9e8633}">
+          <x14:cfRule type="containsText" priority="415" operator="containsText" id="{fecdd2a3-11a9-45b0-ad2e-ee40a4f54cbd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15295,7 +15309,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="402" operator="containsText" id="{2de26de3-e3fc-44f9-8a82-e252583c14c5}">
+          <x14:cfRule type="containsText" priority="416" operator="containsText" id="{98c0e238-aef6-4376-a730-1fed023a75db}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15313,7 +15327,7 @@
           <xm:sqref>I217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="169" operator="containsText" id="{572543bb-09f4-4527-9b60-12cf846f7d93}">
+          <x14:cfRule type="containsText" priority="183" operator="containsText" id="{9c0d3370-8878-43fa-a1d9-97bf1e47c564}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15328,7 +15342,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="170" operator="containsText" id="{ebbb6164-8136-4278-9b33-a75791769a61}">
+          <x14:cfRule type="containsText" priority="184" operator="containsText" id="{57ff0752-292f-461e-9769-ec68ae587840}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15346,7 +15360,7 @@
           <xm:sqref>K217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="403" operator="containsText" id="{f5c6e01e-6492-4281-9995-c5db4f0786c7}">
+          <x14:cfRule type="containsText" priority="417" operator="containsText" id="{ac3d7898-58be-46cd-844d-6d2d25442b6c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15361,7 +15375,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="404" operator="containsText" id="{067964b4-7ce2-4647-bb5d-edd1c9a61627}">
+          <x14:cfRule type="containsText" priority="418" operator="containsText" id="{ad558f1b-2961-4998-aab7-5a92599e0956}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15379,7 +15393,7 @@
           <xm:sqref>L217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="419" operator="containsText" id="{7fe8eeb5-0b2f-4557-aba3-38557064c823}">
+          <x14:cfRule type="containsText" priority="433" operator="containsText" id="{0fdb71d2-7326-4e9f-aec5-b511788b21d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I218)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15394,7 +15408,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="420" operator="containsText" id="{286470f0-a324-4a9b-be17-e7e06a480b57}">
+          <x14:cfRule type="containsText" priority="434" operator="containsText" id="{8641dbc5-d39d-40d0-99eb-294c903806db}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I218)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15412,7 +15426,7 @@
           <xm:sqref>I218</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="355" operator="containsText" id="{d1949806-c05c-4721-8141-0e030a99c121}">
+          <x14:cfRule type="containsText" priority="369" operator="containsText" id="{a412cc88-cbf2-4f27-b863-4724422a838f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I219)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15427,7 +15441,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="356" operator="containsText" id="{939fb040-2055-4049-96f2-ff1335203180}">
+          <x14:cfRule type="containsText" priority="370" operator="containsText" id="{11bb3ee1-e1a3-49b1-a29f-e083314a6b8e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I219)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15445,7 +15459,7 @@
           <xm:sqref>I219</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="431" operator="containsText" id="{9f3db688-8e48-4f3b-9880-37143eaf7a4e}">
+          <x14:cfRule type="containsText" priority="445" operator="containsText" id="{809ebf46-38a1-4cdb-8806-61851326633a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I221)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15460,7 +15474,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="432" operator="containsText" id="{c9603be6-1af0-4682-a6f7-85cca5cd2cb0}">
+          <x14:cfRule type="containsText" priority="446" operator="containsText" id="{8d0d1e6a-35bb-4772-b895-d3ce61a04f6a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I221)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15478,7 +15492,7 @@
           <xm:sqref>I221</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="439" operator="containsText" id="{ae09f02a-6cbf-4503-8f87-79468da06525}">
+          <x14:cfRule type="containsText" priority="453" operator="containsText" id="{e1a1ab4a-fe8e-4bff-832b-9a246b0fac2e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I222)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15493,7 +15507,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="440" operator="containsText" id="{a55a6b6a-c81d-4879-af15-cb343309d4e4}">
+          <x14:cfRule type="containsText" priority="454" operator="containsText" id="{25c39c22-2a80-4366-89a8-9c6c94af5894}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I222)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15511,7 +15525,7 @@
           <xm:sqref>I222</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="407" operator="containsText" id="{b34ed961-e5ab-405b-9460-ac8b9b971877}">
+          <x14:cfRule type="containsText" priority="421" operator="containsText" id="{02d8b942-c8cf-4067-b509-1560574975e3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15526,7 +15540,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="408" operator="containsText" id="{248c4f77-32db-4e9c-9829-4e543b766cd5}">
+          <x14:cfRule type="containsText" priority="422" operator="containsText" id="{ed6ade6e-4dbc-4a05-951e-8ddc17aba9d8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15544,7 +15558,7 @@
           <xm:sqref>I223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="167" operator="containsText" id="{c3ceb28e-d1c7-408c-ab32-7725275766ec}">
+          <x14:cfRule type="containsText" priority="181" operator="containsText" id="{1e94d9f9-7ec8-46ff-8c06-7e3d98253c3a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15559,7 +15573,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="168" operator="containsText" id="{be563792-e752-4b72-93d5-888649c58742}">
+          <x14:cfRule type="containsText" priority="182" operator="containsText" id="{e81434cf-f481-484d-8c12-e10ce3577630}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15577,7 +15591,7 @@
           <xm:sqref>K223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="405" operator="containsText" id="{98007ff3-a2e9-46ae-a822-ef535f8dd575}">
+          <x14:cfRule type="containsText" priority="419" operator="containsText" id="{1e0ffb28-bd9f-42ce-84f4-32ccfd32f7a9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15592,7 +15606,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="406" operator="containsText" id="{2568ce8a-0516-4f2f-8167-c0dbae8ff4bf}">
+          <x14:cfRule type="containsText" priority="420" operator="containsText" id="{b7f448dd-5f38-441f-9bd0-2105663fe936}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15610,7 +15624,7 @@
           <xm:sqref>L223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="97" operator="containsText" id="{11b6fe7f-cca2-43a7-bded-48e61034361d}">
+          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{3a9d3f4f-4329-4240-b06c-5129f1d42362}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15625,7 +15639,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="98" operator="containsText" id="{74ef3b00-9e66-4faf-bd04-65761cc17edf}">
+          <x14:cfRule type="containsText" priority="112" operator="containsText" id="{edcd0ffd-5508-4975-8cb8-21d5be7e67ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15643,7 +15657,7 @@
           <xm:sqref>G224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="433" operator="containsText" id="{f1aa9072-772a-4fcf-a0ae-ecf801cfe2a1}">
+          <x14:cfRule type="containsText" priority="447" operator="containsText" id="{9ee1ff17-5799-479e-83d4-1b744ae19a16}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15658,7 +15672,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="434" operator="containsText" id="{66286693-4315-4d76-ac1b-69969815b01d}">
+          <x14:cfRule type="containsText" priority="448" operator="containsText" id="{1871e5ef-f530-46cc-b93c-2bd37a7a89d0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15676,7 +15690,7 @@
           <xm:sqref>I224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="101" operator="containsText" id="{67383838-bf74-406a-8982-91e0bab7bb08}">
+          <x14:cfRule type="containsText" priority="115" operator="containsText" id="{3491a1a9-ec5e-4333-9ac8-9adec9cc0268}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15691,7 +15705,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="102" operator="containsText" id="{dfcddba4-b368-4ccc-a280-1e1cd9c1179b}">
+          <x14:cfRule type="containsText" priority="116" operator="containsText" id="{7f70301e-525a-4662-9635-77e4e3c04665}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15709,7 +15723,7 @@
           <xm:sqref>G225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="423" operator="containsText" id="{cb4fc367-81af-4dd9-9b80-9c2c857993a4}">
+          <x14:cfRule type="containsText" priority="437" operator="containsText" id="{e45ec254-090c-4945-9897-f2c49c8db8a6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15724,7 +15738,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="424" operator="containsText" id="{ae96a80e-f66e-463e-bae5-dd4c5ae684b2}">
+          <x14:cfRule type="containsText" priority="438" operator="containsText" id="{17dfa2d8-87e7-423b-b45e-573884f721bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15742,7 +15756,7 @@
           <xm:sqref>I225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="377" operator="containsText" id="{f3aac7b0-e44f-413a-8fba-248396e4c8c2}">
+          <x14:cfRule type="containsText" priority="391" operator="containsText" id="{7be726b8-5811-412a-9f55-59dbd000cb8b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15757,7 +15771,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="378" operator="containsText" id="{faceaa4c-ab7d-4a59-99bb-564e1412b2ed}">
+          <x14:cfRule type="containsText" priority="392" operator="containsText" id="{6d489123-7fcf-486f-afc6-dd7f89c36f44}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15775,7 +15789,7 @@
           <xm:sqref>L226</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="371" operator="containsText" id="{1716d2fd-0008-42f6-a78c-ec14efa274d8}">
+          <x14:cfRule type="containsText" priority="385" operator="containsText" id="{50acb5f5-1c34-4a6b-946a-f8fb6176b80e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I227)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15790,7 +15804,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="372" operator="containsText" id="{e272014f-2490-4d10-99cc-e1c1e37d53a1}">
+          <x14:cfRule type="containsText" priority="386" operator="containsText" id="{99e6755a-ae74-4f8f-86f2-3d393e413102}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I227)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15808,7 +15822,7 @@
           <xm:sqref>I227</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="367" operator="containsText" id="{f23bfef0-1f46-498d-8056-0fdc98d33137}">
+          <x14:cfRule type="containsText" priority="381" operator="containsText" id="{eab2a2a8-dc11-4929-a495-e47409479e1e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L227)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15823,7 +15837,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="368" operator="containsText" id="{7a059c41-6770-41ce-a274-ae71d9f78164}">
+          <x14:cfRule type="containsText" priority="382" operator="containsText" id="{7f7ffc6e-0b1c-4c93-aabd-7e74405f6709}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L227)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15841,7 +15855,7 @@
           <xm:sqref>L227</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="385" operator="containsText" id="{a1e9427a-90b1-4fd1-abc4-56519b90a503}">
+          <x14:cfRule type="containsText" priority="399" operator="containsText" id="{0242f718-9e25-4e3a-a8dc-0e18b7800ad5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I228)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15856,7 +15870,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="386" operator="containsText" id="{5a73710e-e1cb-4f60-a8e7-b94392a9a0d0}">
+          <x14:cfRule type="containsText" priority="400" operator="containsText" id="{645051da-ef3b-499b-8344-376eeb3704c7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I228)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15874,7 +15888,7 @@
           <xm:sqref>I228</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="349" operator="containsText" id="{3a6c55ea-ac8d-4d2a-b7c9-0d97cda09dd5}">
+          <x14:cfRule type="containsText" priority="363" operator="containsText" id="{fededb8a-4918-4d27-8b20-3de88a73827a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I229)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15889,7 +15903,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="350" operator="containsText" id="{0d2c74ab-96b8-4b9c-b288-61f1ed8a8920}">
+          <x14:cfRule type="containsText" priority="364" operator="containsText" id="{04126213-209e-4c17-ac2c-363581e26067}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I229)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15907,7 +15921,7 @@
           <xm:sqref>I229</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="375" operator="containsText" id="{b511cd4c-fddf-42f6-aa6a-15d3226b3213}">
+          <x14:cfRule type="containsText" priority="389" operator="containsText" id="{862afbfd-0168-4307-b266-4e1326f2d86c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I230)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15922,7 +15936,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="376" operator="containsText" id="{6db5d37f-af75-4c96-a50d-b0ef707d0c9d}">
+          <x14:cfRule type="containsText" priority="390" operator="containsText" id="{491d0493-d38a-4f49-ab62-520f0af1ef6e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I230)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15940,7 +15954,7 @@
           <xm:sqref>I230</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="357" operator="containsText" id="{003e8f60-dd5c-426e-846e-0c68cc9b223e}">
+          <x14:cfRule type="containsText" priority="371" operator="containsText" id="{1468980c-391a-4190-bf71-06e46d929e5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15955,7 +15969,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="358" operator="containsText" id="{1bde0c2d-517c-43b5-8fae-ee2c3f907895}">
+          <x14:cfRule type="containsText" priority="372" operator="containsText" id="{68e7a192-2b77-4520-9259-47d09c733801}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15973,7 +15987,7 @@
           <xm:sqref>I231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="165" operator="containsText" id="{324ecaa0-2ebf-4e29-8e5f-29238bc9b749}">
+          <x14:cfRule type="containsText" priority="179" operator="containsText" id="{63d52e7b-45f2-458d-90c5-fdc4614dde7c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15988,7 +16002,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="166" operator="containsText" id="{f0ba05b7-4ecf-45a2-91de-b7598071e129}">
+          <x14:cfRule type="containsText" priority="180" operator="containsText" id="{3e7dbaa5-061d-4874-8989-6ba5c4c168c1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16006,7 +16020,7 @@
           <xm:sqref>K231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="347" operator="containsText" id="{3e9ae98f-5ce6-4b37-834a-865d38546ea4}">
+          <x14:cfRule type="containsText" priority="361" operator="containsText" id="{cdb640e7-8fe4-48e3-8c92-81b2112aae21}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16021,7 +16035,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="348" operator="containsText" id="{7e800423-7943-47b2-91fa-c5e8e4dd9a2a}">
+          <x14:cfRule type="containsText" priority="362" operator="containsText" id="{30a161e2-49c0-46ce-b537-31d8b5519848}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16039,7 +16053,7 @@
           <xm:sqref>L231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="369" operator="containsText" id="{b58f27d5-775b-4b9c-af22-8303a68bb1cf}">
+          <x14:cfRule type="containsText" priority="383" operator="containsText" id="{d0295702-9577-4161-93a7-a62be5f8cb23}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I232)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16054,7 +16068,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="370" operator="containsText" id="{edf5efb4-79db-49d6-b552-53fc65115dfa}">
+          <x14:cfRule type="containsText" priority="384" operator="containsText" id="{46c01395-ba8d-46a3-8706-ab12d560f3bc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I232)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16072,7 +16086,7 @@
           <xm:sqref>I232</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="345" operator="containsText" id="{7f7bf925-7573-4ac9-a47c-c510c3b3bf1a}">
+          <x14:cfRule type="containsText" priority="359" operator="containsText" id="{318d5280-6bd6-4a7e-911d-5934df08832b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I233)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16087,7 +16101,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="346" operator="containsText" id="{ad68887d-b9d7-428c-9012-5d7a226fc670}">
+          <x14:cfRule type="containsText" priority="360" operator="containsText" id="{6f0e2a9f-3ccb-44e8-bd13-0514afbc5515}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I233)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16105,7 +16119,7 @@
           <xm:sqref>I233</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="379" operator="containsText" id="{256d269b-e9b1-442f-83e6-26e2a34f449a}">
+          <x14:cfRule type="containsText" priority="393" operator="containsText" id="{ef7fd9c9-76b9-48f7-81d3-7a82ab557c90}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I235)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16120,7 +16134,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="380" operator="containsText" id="{6e57926a-5131-4cd3-916f-0f8273b5913b}">
+          <x14:cfRule type="containsText" priority="394" operator="containsText" id="{9d4ef230-6176-4e45-9dc9-06bfc25c4d14}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I235)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16138,7 +16152,7 @@
           <xm:sqref>I235</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="387" operator="containsText" id="{a76909de-31e9-42c3-88c7-78e6e21cad75}">
+          <x14:cfRule type="containsText" priority="401" operator="containsText" id="{a9e45c4d-0956-485d-85c9-2cb96b8dcffc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I236)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16153,7 +16167,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="388" operator="containsText" id="{1adce7c8-a308-4df6-89ac-b34c0b6d32cb}">
+          <x14:cfRule type="containsText" priority="402" operator="containsText" id="{c89655e1-f155-4679-b634-fc923c988294}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I236)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16171,7 +16185,7 @@
           <xm:sqref>I236</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="353" operator="containsText" id="{e10bd167-e9a1-4312-9a7c-9c19db28d656}">
+          <x14:cfRule type="containsText" priority="367" operator="containsText" id="{b6fa6c84-654e-4661-86d1-b77b4c8071e0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16186,7 +16200,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="354" operator="containsText" id="{5ecbe5b6-c7df-4646-acd6-fd0b78e33f4d}">
+          <x14:cfRule type="containsText" priority="368" operator="containsText" id="{9195f9da-38f3-433c-9385-8e41afa0175e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16204,7 +16218,7 @@
           <xm:sqref>I237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="163" operator="containsText" id="{9e32f7f5-70d4-4475-a87b-4618736a7375}">
+          <x14:cfRule type="containsText" priority="177" operator="containsText" id="{3054beb4-650d-44c3-a021-db2927f3b7a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16219,7 +16233,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="164" operator="containsText" id="{b3c1f6c2-0cf6-4234-8588-fb21f24c8ccd}">
+          <x14:cfRule type="containsText" priority="178" operator="containsText" id="{1d66fdce-e1ce-4474-bb56-b93cfe51383f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16237,7 +16251,7 @@
           <xm:sqref>K237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="351" operator="containsText" id="{2df1294d-1124-4a57-a7c2-55b03c6baf99}">
+          <x14:cfRule type="containsText" priority="365" operator="containsText" id="{7cafa801-058f-43c8-8d37-fbd16b6bda42}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16252,7 +16266,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="352" operator="containsText" id="{3b9ec54a-d144-44db-b37b-e746ca820e2c}">
+          <x14:cfRule type="containsText" priority="366" operator="containsText" id="{cbd9085f-edd9-4d62-a232-3b5b1cbd5db4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16270,7 +16284,7 @@
           <xm:sqref>L237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="91" operator="containsText" id="{88ead266-78b8-4522-b6d1-6aecb15bbf6e}">
+          <x14:cfRule type="containsText" priority="105" operator="containsText" id="{08b176fe-ac4c-457d-af9d-6ca1d7a7dc1b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16285,7 +16299,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="92" operator="containsText" id="{5bace867-5bc1-4b49-a3c7-f6ee66994733}">
+          <x14:cfRule type="containsText" priority="106" operator="containsText" id="{57e350b7-ed3c-4690-9dc7-1fa605fe870c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16303,7 +16317,7 @@
           <xm:sqref>G238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="343" operator="containsText" id="{937901a5-1d7e-453c-82c6-02127e0a8f3b}">
+          <x14:cfRule type="containsText" priority="357" operator="containsText" id="{caa7530b-da37-4fad-9774-ebf10e67a361}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16318,7 +16332,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="344" operator="containsText" id="{244fa836-2bc5-4444-b109-a1e8e5c4b25d}">
+          <x14:cfRule type="containsText" priority="358" operator="containsText" id="{bd42e112-c2a1-46eb-9d08-b12eeb8c2a42}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16336,7 +16350,7 @@
           <xm:sqref>I238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="95" operator="containsText" id="{63b67499-8298-48fb-b15b-1cfeb7b44a9e}">
+          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{c0092698-cb38-4b12-8ee8-7a755ac83a28}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16351,7 +16365,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="96" operator="containsText" id="{dbfd0491-c4de-4025-a949-a75da9de30aa}">
+          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{42209790-13fa-4878-b281-2290677de5cd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16369,7 +16383,7 @@
           <xm:sqref>G239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="373" operator="containsText" id="{cbdbff48-2e21-446d-97bd-db0ee4860cd8}">
+          <x14:cfRule type="containsText" priority="387" operator="containsText" id="{7a32c69d-6f52-452b-8084-230d2c9c268e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16384,7 +16398,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="374" operator="containsText" id="{2db2f16f-6532-46c0-b4c4-dabb17834cc0}">
+          <x14:cfRule type="containsText" priority="388" operator="containsText" id="{62d88822-0d90-4ac5-ae86-8901ec2ce6e1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16402,7 +16416,7 @@
           <xm:sqref>I239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="293" operator="containsText" id="{dcb62b92-e095-480d-a2ab-e5997de80186}">
+          <x14:cfRule type="containsText" priority="307" operator="containsText" id="{2c98adcd-7a73-4b56-9aaa-62a6fa25d5a6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16417,7 +16431,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="294" operator="containsText" id="{a568b418-a4f5-42fe-aba2-ccd3286f915e}">
+          <x14:cfRule type="containsText" priority="308" operator="containsText" id="{6e03261e-6a22-4376-a0ca-d71adf4849af}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16435,7 +16449,7 @@
           <xm:sqref>I240</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="323" operator="containsText" id="{3b0a332d-06f8-4511-a1b8-fa287b690fbb}">
+          <x14:cfRule type="containsText" priority="337" operator="containsText" id="{0a38c1c2-98b7-462b-a704-b90385a87ede}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16450,7 +16464,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="324" operator="containsText" id="{ac1a0950-a2fc-493a-bae2-14e6f7647a21}">
+          <x14:cfRule type="containsText" priority="338" operator="containsText" id="{f7570955-1ff2-4c53-8a60-654f00bbe2f9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16468,7 +16482,7 @@
           <xm:sqref>L240</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="317" operator="containsText" id="{8ce0dda9-f376-4bc1-8ec0-08c6dbdf22df}">
+          <x14:cfRule type="containsText" priority="331" operator="containsText" id="{af516d02-6122-4b51-91f4-25909391008d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16483,7 +16497,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="318" operator="containsText" id="{49b4fd05-3a60-4d74-b2c9-5de006e84b63}">
+          <x14:cfRule type="containsText" priority="332" operator="containsText" id="{40fc5170-a24d-478e-bb70-abcbd87f35d2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16501,7 +16515,7 @@
           <xm:sqref>I241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="161" operator="containsText" id="{42bd8c0d-5106-4877-ae0f-8ed543e2defd}">
+          <x14:cfRule type="containsText" priority="175" operator="containsText" id="{7f0f4b77-945e-4120-9878-f82a7d53a68d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16516,7 +16530,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="162" operator="containsText" id="{e7574754-c331-4a2b-802e-a1d10f3773d1}">
+          <x14:cfRule type="containsText" priority="176" operator="containsText" id="{539638f8-f245-4622-81cf-0ecc570dae47}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16534,7 +16548,7 @@
           <xm:sqref>K241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="291" operator="containsText" id="{67564b6f-966c-412a-b07b-637e55fd51c8}">
+          <x14:cfRule type="containsText" priority="305" operator="containsText" id="{28410347-8392-433a-841d-d49b25426fab}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16549,7 +16563,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="292" operator="containsText" id="{1a289c26-14c1-460d-b42a-3fe07a6b49e5}">
+          <x14:cfRule type="containsText" priority="306" operator="containsText" id="{91bf4655-2328-4c91-b156-48756ab2be7c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16567,7 +16581,7 @@
           <xm:sqref>L241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="287" operator="containsText" id="{e34a06ce-f3eb-45f4-8642-55abc3056e8d}">
+          <x14:cfRule type="containsText" priority="301" operator="containsText" id="{e621302b-be36-45b1-8b23-72e443e970b8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I242)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16582,7 +16596,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="288" operator="containsText" id="{6c3e5074-1d78-4cfc-a9c3-7d2de2672043}">
+          <x14:cfRule type="containsText" priority="302" operator="containsText" id="{c8c942b6-e414-484b-ac08-eb2d38ec8378}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I242)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16600,7 +16614,7 @@
           <xm:sqref>I242</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="305" operator="containsText" id="{8388ab4b-9875-4ae0-95fc-2bf61bb0b674}">
+          <x14:cfRule type="containsText" priority="319" operator="containsText" id="{ffd00efd-ae3f-4a2d-a2cf-a3569405a6d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I243)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16615,7 +16629,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="306" operator="containsText" id="{e0a16b31-73ab-4716-91b5-9a144da211d9}">
+          <x14:cfRule type="containsText" priority="320" operator="containsText" id="{f2f957e5-c636-4d2f-a2a3-71829dfc9e23}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I243)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16633,7 +16647,7 @@
           <xm:sqref>I243</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="321" operator="containsText" id="{984fd337-91ef-4fbc-8f88-2ff991f76e72}">
+          <x14:cfRule type="containsText" priority="335" operator="containsText" id="{90355884-afed-4bd7-b88e-7f81fb8f62bc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I244)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16648,7 +16662,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="322" operator="containsText" id="{3ccd95ad-b04a-4cb7-a7e9-4e5fbf0bff4d}">
+          <x14:cfRule type="containsText" priority="336" operator="containsText" id="{c56a5116-e2b2-4802-a748-301a4f9a3690}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I244)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16666,7 +16680,7 @@
           <xm:sqref>I244</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="311" operator="containsText" id="{7d382e12-135a-440b-9dbd-311ca818d929}">
+          <x14:cfRule type="containsText" priority="325" operator="containsText" id="{0be25444-faf5-4c57-b1c3-d12fb340416a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I245)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16681,7 +16695,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="312" operator="containsText" id="{41412853-10b4-4933-b42e-fdce0d0387a6}">
+          <x14:cfRule type="containsText" priority="326" operator="containsText" id="{a8565f9e-911d-4f10-9502-5dc3948f01dc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I245)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16699,7 +16713,7 @@
           <xm:sqref>I245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="303" operator="containsText" id="{f0c7d629-66ee-467c-a8fa-4987bc606782}">
+          <x14:cfRule type="containsText" priority="317" operator="containsText" id="{cdff7e26-4ab6-4204-b67e-a677d9b20d0c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L245)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16714,7 +16728,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="304" operator="containsText" id="{05cdc3b5-615e-4561-9f52-95a21f79ff3d}">
+          <x14:cfRule type="containsText" priority="318" operator="containsText" id="{af86ddb5-4b3f-4c42-9a93-6a075975d489}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L245)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16732,7 +16746,7 @@
           <xm:sqref>L245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="315" operator="containsText" id="{43ed455c-109a-4c87-8918-c7417dbbb4a4}">
+          <x14:cfRule type="containsText" priority="329" operator="containsText" id="{d1c4aa3f-24b7-48cf-aced-9b499a40c314}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I246)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16747,7 +16761,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="316" operator="containsText" id="{0096b937-9d38-448b-b8f5-294e506170d9}">
+          <x14:cfRule type="containsText" priority="330" operator="containsText" id="{f8641717-ea22-453b-90c7-d38a71c373de}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I246)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16765,7 +16779,7 @@
           <xm:sqref>I246</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="289" operator="containsText" id="{08f97b49-6933-4545-9c12-2d10df9a293e}">
+          <x14:cfRule type="containsText" priority="303" operator="containsText" id="{b3d38508-1391-42d8-9b9b-4a825666731a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I247)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16780,7 +16794,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="290" operator="containsText" id="{8f0837e9-c55b-4ba3-98fb-c40b5c3f94f0}">
+          <x14:cfRule type="containsText" priority="304" operator="containsText" id="{2a06694c-9885-4adb-b279-a2f76b091f4e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I247)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16798,7 +16812,7 @@
           <xm:sqref>I247</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="325" operator="containsText" id="{24b8afdb-166d-4106-bf03-56f68f8952cb}">
+          <x14:cfRule type="containsText" priority="339" operator="containsText" id="{6a02ccad-8e35-41af-863b-2971a922a43d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I249)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16813,7 +16827,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="326" operator="containsText" id="{850fdcc1-359c-4507-8c9d-32936067d9a0}">
+          <x14:cfRule type="containsText" priority="340" operator="containsText" id="{f9861040-e687-44d7-9275-37591db7ac4e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I249)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16831,7 +16845,7 @@
           <xm:sqref>I249</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="285" operator="containsText" id="{5bdbdc67-38a1-41f8-a12a-4e5350d129f0}">
+          <x14:cfRule type="containsText" priority="299" operator="containsText" id="{d5614883-0e3b-4c83-bebc-5a3a747074ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I250)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16846,7 +16860,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="286" operator="containsText" id="{6be23ffd-3a9d-4efe-92ad-7483ba7b022e}">
+          <x14:cfRule type="containsText" priority="300" operator="containsText" id="{a813e204-2bca-48e2-8ae6-c38df0584582}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I250)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16864,7 +16878,7 @@
           <xm:sqref>I250</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="297" operator="containsText" id="{ee19589b-5ff4-4e7a-b995-d41daa298689}">
+          <x14:cfRule type="containsText" priority="311" operator="containsText" id="{d138f2d5-59b5-4c6c-b840-c3a633d0bc38}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16879,7 +16893,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="298" operator="containsText" id="{30f3d1e7-5875-4c0f-bb42-42637bba0879}">
+          <x14:cfRule type="containsText" priority="312" operator="containsText" id="{1db05c80-806f-4625-8b0d-c2c981886ccb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16897,7 +16911,7 @@
           <xm:sqref>I251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="159" operator="containsText" id="{9a2bf28a-0768-41e2-b6d5-1f938a634400}">
+          <x14:cfRule type="containsText" priority="173" operator="containsText" id="{8935f3b8-449d-4bec-8ae7-e222eb478012}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16912,7 +16926,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="160" operator="containsText" id="{4f793669-c805-4b28-a5e5-6e2d05ba71af}">
+          <x14:cfRule type="containsText" priority="174" operator="containsText" id="{455ed126-ddd6-4cf7-9252-a10d94e7bd5a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16930,7 +16944,7 @@
           <xm:sqref>K251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="295" operator="containsText" id="{8b8d4dfa-3cf0-4e8a-ba74-380ff83b93eb}">
+          <x14:cfRule type="containsText" priority="309" operator="containsText" id="{db05dfd2-0dd6-409a-afb5-a05fc4fa7a72}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16945,7 +16959,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="296" operator="containsText" id="{82a17e53-bb3b-4389-924e-49cda00b65f2}">
+          <x14:cfRule type="containsText" priority="310" operator="containsText" id="{5371f6d4-82f8-4e99-bda2-66812b5b9c82}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16963,7 +16977,7 @@
           <xm:sqref>L251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="85" operator="containsText" id="{ec648539-d2de-4197-b2b6-c9310bf9064a}">
+          <x14:cfRule type="containsText" priority="99" operator="containsText" id="{94a757b4-772f-4700-95f6-e8c74c968281}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16978,7 +16992,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="86" operator="containsText" id="{e4616080-8a42-44b3-908c-4ead274e877c}">
+          <x14:cfRule type="containsText" priority="100" operator="containsText" id="{f1f74c22-74a6-47e1-afe3-bf39ed8ba43e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16996,7 +17010,7 @@
           <xm:sqref>G252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="193" operator="containsText" id="{cd523013-6e88-495a-afa4-06d5cb9d47b4}">
+          <x14:cfRule type="containsText" priority="207" operator="containsText" id="{9661c0b9-dc31-473b-b2dc-2138a5cc6cf8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17011,7 +17025,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="194" operator="containsText" id="{c76ddcf6-b7df-420c-a57a-c8d67bab59a7}">
+          <x14:cfRule type="containsText" priority="208" operator="containsText" id="{b82f6500-8196-44ba-97bf-fcc001b389f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17029,7 +17043,7 @@
           <xm:sqref>I252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="89" operator="containsText" id="{4e0f8ad7-1662-4610-a5d2-ad56393fcd92}">
+          <x14:cfRule type="containsText" priority="103" operator="containsText" id="{d652e579-a416-4e05-8cd2-a12f6e7dec00}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17044,7 +17058,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="90" operator="containsText" id="{449f8937-cdac-442f-acbd-254d433c87dd}">
+          <x14:cfRule type="containsText" priority="104" operator="containsText" id="{9c252ac5-6f6c-426e-bf74-671fec46d75f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17062,7 +17076,7 @@
           <xm:sqref>G253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="319" operator="containsText" id="{dbb10f1d-7d84-4058-9ed1-23c4a67adc32}">
+          <x14:cfRule type="containsText" priority="333" operator="containsText" id="{f2de0a61-8ae2-47f0-aca4-e3355b73226a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17077,7 +17091,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="320" operator="containsText" id="{d0453ab4-e054-4675-afba-56fcf3dbc4d1}">
+          <x14:cfRule type="containsText" priority="334" operator="containsText" id="{5a71d604-afb1-44a3-ad44-34b5c694b23f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17095,7 +17109,7 @@
           <xm:sqref>I253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="185" operator="containsText" id="{94262e57-5147-43d9-8ec9-052aa8b3972a}">
+          <x14:cfRule type="containsText" priority="199" operator="containsText" id="{d6cdd0d7-fff2-4103-994a-0bc6c0e36ac0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17110,7 +17124,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="186" operator="containsText" id="{cea3343a-4943-40c8-80b0-ab01dd5810f2}">
+          <x14:cfRule type="containsText" priority="200" operator="containsText" id="{adee85b6-2641-4e90-bfcf-7c2e77f66d74}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17128,7 +17142,7 @@
           <xm:sqref>I254</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="265" operator="containsText" id="{8e913289-ef20-47a7-972c-b91d7ab5a78d}">
+          <x14:cfRule type="containsText" priority="279" operator="containsText" id="{e7f99cb9-e28b-4659-ba16-dfc1c01e4fc2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17143,7 +17157,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="266" operator="containsText" id="{6aab977d-7b38-4f7f-95ad-69902583526d}">
+          <x14:cfRule type="containsText" priority="280" operator="containsText" id="{2cdeb04a-760b-4772-9fb9-e6940536b6ad}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17161,7 +17175,7 @@
           <xm:sqref>L254</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="259" operator="containsText" id="{e8385b95-4d33-4e2f-9774-695573163dd6}">
+          <x14:cfRule type="containsText" priority="273" operator="containsText" id="{93957009-0cc4-46cd-ae5d-a8b25d940af3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17176,7 +17190,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="260" operator="containsText" id="{1feb9838-e088-48d0-a9d7-eb484f633b34}">
+          <x14:cfRule type="containsText" priority="274" operator="containsText" id="{addbf204-1e70-4573-9a08-f8fb373624be}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17194,7 +17208,7 @@
           <xm:sqref>I255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="157" operator="containsText" id="{21930481-cc6f-4e81-860c-85e1883dfe28}">
+          <x14:cfRule type="containsText" priority="171" operator="containsText" id="{62da8f75-2cfd-4bb1-886b-b3d03f97aa31}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17209,7 +17223,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="158" operator="containsText" id="{e940f395-feec-4287-adf3-6f91e3aafb37}">
+          <x14:cfRule type="containsText" priority="172" operator="containsText" id="{d6368bf6-e1ee-4778-a1b6-70b842234d54}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17227,7 +17241,7 @@
           <xm:sqref>K255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="183" operator="containsText" id="{dd035121-c4dc-4c6d-99c2-65e752c773af}">
+          <x14:cfRule type="containsText" priority="197" operator="containsText" id="{e9f081d0-3a5c-484d-8c26-5624a7c3f645}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17242,7 +17256,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="184" operator="containsText" id="{c7b6d1d7-afaf-4bb5-a148-513c55287de7}">
+          <x14:cfRule type="containsText" priority="198" operator="containsText" id="{ef8e01b4-459a-49db-b01e-154d3ebb3258}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17260,7 +17274,7 @@
           <xm:sqref>L255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="269" operator="containsText" id="{310325c5-f119-4472-8be2-f15e5263572e}">
+          <x14:cfRule type="containsText" priority="283" operator="containsText" id="{8fc07325-d7b2-43c0-ae41-2bc2932d5763}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I256)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17275,7 +17289,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="270" operator="containsText" id="{88d7941c-4dba-4c52-96ea-3d6602001d0b}">
+          <x14:cfRule type="containsText" priority="284" operator="containsText" id="{1dfa204c-5e70-4438-9e9d-1f851e1b4e37}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I256)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17293,7 +17307,7 @@
           <xm:sqref>I256</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="247" operator="containsText" id="{752d792e-49fe-493a-bf85-c33f2e9c3371}">
+          <x14:cfRule type="containsText" priority="261" operator="containsText" id="{fca7086c-6f02-4e1e-9582-6125074053cb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I257)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17308,7 +17322,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="248" operator="containsText" id="{95668d7e-eb65-4678-b808-2c8b98cc8cea}">
+          <x14:cfRule type="containsText" priority="262" operator="containsText" id="{637b6749-d0cf-4017-8120-0c38f716c827}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I257)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17326,7 +17340,7 @@
           <xm:sqref>I257</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="263" operator="containsText" id="{8ad3fba3-413c-4397-972a-94b9a95675c7}">
+          <x14:cfRule type="containsText" priority="277" operator="containsText" id="{1049684a-dda1-4bc9-98dc-c24109d1783a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I258)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17341,7 +17355,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="264" operator="containsText" id="{ce2107c5-3682-4daf-bb4c-118d1a61a5e4}">
+          <x14:cfRule type="containsText" priority="278" operator="containsText" id="{5fde2806-f0b4-4328-9ee7-95c47ea95347}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I258)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17359,7 +17373,7 @@
           <xm:sqref>I258</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="253" operator="containsText" id="{1289281f-049d-41c5-87a7-e0c02314c6bd}">
+          <x14:cfRule type="containsText" priority="267" operator="containsText" id="{44834094-fdec-41c9-b725-7cd156c030b8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I259)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17374,7 +17388,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="254" operator="containsText" id="{42da038c-6bfa-48eb-b887-462b8475bf5a}">
+          <x14:cfRule type="containsText" priority="268" operator="containsText" id="{11bd1363-e0fc-4f06-8089-4560b3c7f9a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I259)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17392,7 +17406,7 @@
           <xm:sqref>I259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="245" operator="containsText" id="{feef87e8-c8d1-49d5-b777-0a148d26b236}">
+          <x14:cfRule type="containsText" priority="259" operator="containsText" id="{5498b87f-7ca0-4cda-aab2-facd3aa61096}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L259)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17407,7 +17421,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="246" operator="containsText" id="{6e6d9441-17ed-4c09-94f1-642b9d0f5509}">
+          <x14:cfRule type="containsText" priority="260" operator="containsText" id="{907a1ec1-3e64-4a05-8794-4ea812e29639}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L259)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17425,7 +17439,7 @@
           <xm:sqref>L259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="257" operator="containsText" id="{c95470cd-7015-4762-83a0-5c2200680e49}">
+          <x14:cfRule type="containsText" priority="271" operator="containsText" id="{8efbccc0-c57b-4bbf-8a10-d9b5ecfafff2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I260)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17440,7 +17454,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="258" operator="containsText" id="{a527dc67-ed0f-4b5a-a5ee-10e73ec20173}">
+          <x14:cfRule type="containsText" priority="272" operator="containsText" id="{68aa9423-63b4-4e40-8d81-b9e64b98aca2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I260)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17458,7 +17472,7 @@
           <xm:sqref>I260</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="243" operator="containsText" id="{4c42470d-aad4-4149-b505-211bccd275f3}">
+          <x14:cfRule type="containsText" priority="257" operator="containsText" id="{30eedf47-be75-4371-8595-21ce78bf59b9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I261)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17473,7 +17487,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="244" operator="containsText" id="{ae1d7352-a82f-4a54-a635-7cd6e3215a45}">
+          <x14:cfRule type="containsText" priority="258" operator="containsText" id="{c9854ff0-906d-489a-90f4-df006996488c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I261)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17491,7 +17505,7 @@
           <xm:sqref>I261</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="181" operator="containsText" id="{17f1e60e-803a-4e5c-b215-68311f713193}">
+          <x14:cfRule type="containsText" priority="195" operator="containsText" id="{af6adac5-00c8-4846-aa32-a0aaa8bef72e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I263)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17506,7 +17520,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="182" operator="containsText" id="{8883e01c-5289-4e10-b10f-bf959a7a0c00}">
+          <x14:cfRule type="containsText" priority="196" operator="containsText" id="{3f252157-ddae-48ab-a289-8b2286b35582}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I263)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17524,7 +17538,7 @@
           <xm:sqref>I263</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="271" operator="containsText" id="{84cf1af1-68dd-4186-b170-15670b757374}">
+          <x14:cfRule type="containsText" priority="285" operator="containsText" id="{15520379-6256-4067-bdab-2638b27f6753}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17539,7 +17553,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="272" operator="containsText" id="{76d89e7f-5f9e-4c43-a441-25cd61663a44}">
+          <x14:cfRule type="containsText" priority="286" operator="containsText" id="{65088df1-3a55-4e58-ad2a-22a33bab5a57}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17557,7 +17571,7 @@
           <xm:sqref>I264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="155" operator="containsText" id="{34a9afdc-9c8a-4b1b-8bee-1ef926654cbe}">
+          <x14:cfRule type="containsText" priority="169" operator="containsText" id="{c011e593-d6ad-4dd8-8a9b-30e83a1758f4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17572,7 +17586,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="156" operator="containsText" id="{3a414e91-89ad-4b74-8d7f-554e34631dce}">
+          <x14:cfRule type="containsText" priority="170" operator="containsText" id="{b1392c31-6da4-4bb1-8007-9e344630484a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17590,7 +17604,7 @@
           <xm:sqref>K264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="187" operator="containsText" id="{320e5a30-e4d6-478c-9a3f-cc095f95cfd2}">
+          <x14:cfRule type="containsText" priority="201" operator="containsText" id="{9bbeb365-63d6-47cf-92e1-4fc059d2834a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17605,7 +17619,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="188" operator="containsText" id="{fa4e5dc5-ca63-43e5-b432-f1e480a8b355}">
+          <x14:cfRule type="containsText" priority="202" operator="containsText" id="{e37835bc-2499-4ab5-bec1-1307eaf0756f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17623,7 +17637,7 @@
           <xm:sqref>L264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="191" operator="containsText" id="{3c0bf53e-6378-4d00-b490-3960e98454f0}">
+          <x14:cfRule type="containsText" priority="205" operator="containsText" id="{ba0930de-9e61-4e82-bb68-0dc85073b63a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17638,7 +17652,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="192" operator="containsText" id="{ed3e1d7b-faec-4350-ad26-d66cc83ba155}">
+          <x14:cfRule type="containsText" priority="206" operator="containsText" id="{960f89eb-222c-47c8-8d54-ffe58aa6390d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17656,7 +17670,7 @@
           <xm:sqref>I265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="153" operator="containsText" id="{07cc612f-a1fc-4af3-970b-bf2b3ae91602}">
+          <x14:cfRule type="containsText" priority="167" operator="containsText" id="{96bc4a71-70d8-47e4-b108-04f07f0fbf52}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17671,7 +17685,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="154" operator="containsText" id="{b647c090-0eee-40c2-ad48-11b8c1540283}">
+          <x14:cfRule type="containsText" priority="168" operator="containsText" id="{6f43965a-1c48-4889-a744-6f09b366e89a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17689,7 +17703,7 @@
           <xm:sqref>K265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="189" operator="containsText" id="{567ee8a8-7d4e-4222-8c43-72a284abf848}">
+          <x14:cfRule type="containsText" priority="203" operator="containsText" id="{32fc610b-8a52-4f84-ab21-3580e6553e93}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17704,7 +17718,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="190" operator="containsText" id="{405728db-a2c4-4e30-9e9c-17e10ccac30b}">
+          <x14:cfRule type="containsText" priority="204" operator="containsText" id="{76ae1d49-ec8d-4bf0-b070-7b37b69aec06}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17722,7 +17736,7 @@
           <xm:sqref>L265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="79" operator="containsText" id="{96f603db-ae9a-40ab-8fd3-a76b36b72455}">
+          <x14:cfRule type="containsText" priority="93" operator="containsText" id="{8e7da397-6c86-4f8c-ac27-80e588f2a2ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17737,7 +17751,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="80" operator="containsText" id="{25268049-5329-4944-a586-533cb34deb20}">
+          <x14:cfRule type="containsText" priority="94" operator="containsText" id="{25177b16-60c5-47ac-801d-e97735af5d72}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17755,7 +17769,7 @@
           <xm:sqref>G266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="241" operator="containsText" id="{c6ca18a6-be2e-45eb-84ae-fec6f2e7d667}">
+          <x14:cfRule type="containsText" priority="255" operator="containsText" id="{1da31595-8336-448b-904a-5c1767105948}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17770,7 +17784,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="242" operator="containsText" id="{9bec1655-71a7-41b8-8d8b-d7c2421ab448}">
+          <x14:cfRule type="containsText" priority="256" operator="containsText" id="{a96688f1-ec71-4b2b-9b4e-9b51b09b6a0f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17788,7 +17802,7 @@
           <xm:sqref>I266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="83" operator="containsText" id="{cfcc3e1d-8fe2-4c29-a461-53501b8e67ff}">
+          <x14:cfRule type="containsText" priority="97" operator="containsText" id="{baeb15de-00f2-41b6-827d-5738b66352d7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17803,7 +17817,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="84" operator="containsText" id="{44b281f0-e221-42d6-8304-0ca98c45f5de}">
+          <x14:cfRule type="containsText" priority="98" operator="containsText" id="{27d252ab-9a0e-44ee-8fbf-cf17a9c34d18}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17821,7 +17835,7 @@
           <xm:sqref>G267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="261" operator="containsText" id="{77902f84-8428-40a9-9f90-6354ddf5672e}">
+          <x14:cfRule type="containsText" priority="275" operator="containsText" id="{92db74cd-750e-4916-8268-5e147f43d5bf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17836,7 +17850,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="262" operator="containsText" id="{aca21f59-3bd0-47f6-8ebe-572bcfee1f8c}">
+          <x14:cfRule type="containsText" priority="276" operator="containsText" id="{ec762528-f540-4efa-9e2c-62748cdd3f1e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17854,7 +17868,7 @@
           <xm:sqref>I267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{d55e5f4f-708a-494e-9a6d-e5c5988dbf93}">
+          <x14:cfRule type="containsText" priority="51" operator="containsText" id="{52af84d6-7e6e-461c-8aea-79a991c06263}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17869,7 +17883,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{45a05738-bbc7-45b2-84a3-01a24b991420}">
+          <x14:cfRule type="containsText" priority="52" operator="containsText" id="{23123c76-8f37-40a3-a06b-a3abf258a780}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17887,7 +17901,7 @@
           <xm:sqref>F269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{e1def282-1d04-4313-91c6-c54d09ef7db9}">
+          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{4231638a-c568-49f3-a32c-6b180095af7c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17902,7 +17916,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{bd9ec81b-1ce8-46e8-b700-a774756be1b3}">
+          <x14:cfRule type="containsText" priority="27" operator="containsText" id="{3d1b752d-0b8b-449e-b0c5-8d6606073357}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17920,7 +17934,40 @@
           <xm:sqref>J269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{dc6917eb-a9e7-4937-a176-be8b1f959d61}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{daf34ebf-b67a-445f-bdff-84efde50f4f0}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,K269)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{ced1919b-9656-42fc-8aee-2348d94fc33d}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,K269)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K269</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{c79823de-89ca-47fc-9349-524d8bb9f108}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F270)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17935,7 +17982,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="36" operator="containsText" id="{16c31a07-2bdf-4ead-909c-450b4f9fc035}">
+          <x14:cfRule type="containsText" priority="50" operator="containsText" id="{0a405e0e-8649-4ef7-9443-c0c4e3d2a722}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F270)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17953,7 +18000,7 @@
           <xm:sqref>F270</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{58ae86fa-20cc-489f-a8cb-37ee2e9acb47}">
+          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{3822ee71-e674-45cd-9b83-b0c61554b258}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G270)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17968,7 +18015,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{02b90d9b-d77c-4f3c-bea1-b79aa9a8b73d}">
+          <x14:cfRule type="containsText" priority="48" operator="containsText" id="{6a6f8648-aa50-4250-8a13-80cf72d91cf9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G270)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17986,7 +18033,7 @@
           <xm:sqref>G270</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{82c9b131-d984-4b2e-9cee-027193fe369b}">
+          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{2d024aa3-7d61-4a49-84e0-1f41dec9a173}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J271)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18001,7 +18048,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{f6b595bb-2362-4896-8838-69bc7d2e9b6c}">
+          <x14:cfRule type="containsText" priority="25" operator="containsText" id="{bab02b73-a542-415c-9bed-c8732f0843a2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J271)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18019,7 +18066,40 @@
           <xm:sqref>J271</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="31" operator="containsText" id="{68b3b8b1-1321-4067-b0ce-adb7a724e416}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{1bce861b-3785-4574-99a9-dcd424ee8641}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,K271)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{e2ff7c88-e486-4ef7-83d8-126ae503a67d}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,K271)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K271</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="45" operator="containsText" id="{1b301783-1366-4b6e-a6c1-6b0838041771}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18034,7 +18114,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{f19a7ad9-7239-462c-adb9-9656b5ec1c9b}">
+          <x14:cfRule type="containsText" priority="46" operator="containsText" id="{1b46eb7d-b1c4-42b8-b15c-848c306ce915}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18052,7 +18132,7 @@
           <xm:sqref>G272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{d67c27b4-48b7-4dcd-9cd0-40b74aefdc9d}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{59bd8c0c-0476-4282-8ba8-6d0f5ff8d7d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18067,7 +18147,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{92d9ec0b-3652-4593-b460-a6714dafefe8}">
+          <x14:cfRule type="containsText" priority="23" operator="containsText" id="{7dbaf0f0-147c-4da6-bc4f-5921830ebd7a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18085,7 +18165,40 @@
           <xm:sqref>J272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="27" operator="containsText" id="{32bc681a-fd51-4535-a8a9-49538642083f}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{f3188d51-027d-43c3-95d2-f5260b9ddb9b}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,K272)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{f7dca86e-09e6-493a-8450-427a88b1bc9a}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,K272)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K272</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{5370b4d1-6d86-405f-b797-c5c4bad25aa0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18100,7 +18213,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{d4d9ae35-9a08-46dd-b4b6-5b724d876a70}">
+          <x14:cfRule type="containsText" priority="42" operator="containsText" id="{7585785f-939b-42ab-896a-f9aa4b286e5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18118,7 +18231,7 @@
           <xm:sqref>F273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{917f2ddb-25c4-4b94-a503-5d797090f90a}">
+          <x14:cfRule type="containsText" priority="43" operator="containsText" id="{bf49dfb5-65d2-484b-9584-c1c0da7c7a6a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18133,7 +18246,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="30" operator="containsText" id="{256b1b4a-3fb2-43b1-b5d4-3868132989ea}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{f6ffffe3-2528-4a4a-bf18-2f4a8c13b2d3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18151,7 +18264,7 @@
           <xm:sqref>G273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{6781a70b-541b-475c-9f2e-ee2b5518266a}">
+          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{3599da34-0d1e-47fb-80ae-4a3709806270}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18166,7 +18279,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{513cda1a-5b9a-4715-8bf3-9f75583ba21a}">
+          <x14:cfRule type="containsText" priority="21" operator="containsText" id="{6d18472f-2b83-4588-931e-670818234252}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18184,7 +18297,40 @@
           <xm:sqref>J273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="23" operator="containsText" id="{c2a9d4ef-a0e6-4739-ac45-3acc71ecd109}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{4ad7ca19-c35f-4bbc-ad04-f4edc39cb113}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,K273)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{72125e8c-061f-429c-864b-ba4a06d7478c}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,K273)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K273</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{45215737-8215-4d0b-b5aa-b1663815ada9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18199,7 +18345,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{cdd03a57-48b9-4229-8fee-2752205a71c1}">
+          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{6f785cba-c7c9-4524-91f8-52da7f818849}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18217,7 +18363,7 @@
           <xm:sqref>F274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="25" operator="containsText" id="{043f6615-f79c-4728-82a0-69823142b246}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{21760718-6b02-4fb6-a79f-24c3674b39fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18232,7 +18378,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{34c57e95-5fd0-4d62-b6bf-61d7779db849}">
+          <x14:cfRule type="containsText" priority="40" operator="containsText" id="{8e9b4b42-1565-48f0-a311-a1619a159d9d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18250,7 +18396,7 @@
           <xm:sqref>G274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{542f4a6b-85ae-45cd-9e7d-8f0606f4c587}">
+          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{4b36f18b-15b0-49cf-93fd-eef59fd13a00}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18265,7 +18411,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{005357e1-8c9c-4275-a528-36ecd307a2fa}">
+          <x14:cfRule type="containsText" priority="19" operator="containsText" id="{474a6d20-5c6f-421b-9b03-7c8ecd734af3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18283,7 +18429,40 @@
           <xm:sqref>J274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="21" operator="containsText" id="{b8b0fb05-b137-4012-afa5-b16ff1b0b824}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{dc9e1e87-848a-4252-9950-9b42e123d4bf}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,K274)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{a5f22981-2f0a-4794-8a29-647243fd36cb}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,K274)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K274</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{4bd32787-a0b3-4924-855e-4c1f009a7d25}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G275)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18298,7 +18477,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{cd60a251-871d-49ab-84c6-b65ddad9ef11}">
+          <x14:cfRule type="containsText" priority="36" operator="containsText" id="{df3e937f-ed21-42bd-bf62-cb9304ffb481}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G275)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18316,7 +18495,7 @@
           <xm:sqref>G275</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{434baa0d-e933-4afe-bc29-22f11cacf9d8}">
+          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{ee25c8b3-66ef-4f84-ae96-1b790c08aa24}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J278)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18331,7 +18510,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{a8553a9d-cdbd-434e-9772-dd1bf3148153}">
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{808e3517-0d51-495b-afe4-2d9a99f65158}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J278)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18349,7 +18528,40 @@
           <xm:sqref>J278</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{5bacebac-08d7-4b20-ab46-8d27cb5a20ad}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{196b96bf-43b6-45d9-874b-152c326d884d}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,K278)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{188b1ce6-3086-474a-b489-3e5a992abf87}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,K278)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K278</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="31" operator="containsText" id="{90763926-a7da-42af-baf6-47cc8afced8d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F279)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18364,7 +18576,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{614bca51-c050-4a19-bc4c-8d8de8a9c5d7}">
+          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{36dc35c0-bbb8-4fce-bd1d-b1733402ee82}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F279)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18382,7 +18594,7 @@
           <xm:sqref>F279</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="19" operator="containsText" id="{a9ebada7-d37f-4750-89e9-08c87e060835}">
+          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{2c99be84-ad30-41c0-8f2b-8275a7624082}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G279)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18397,7 +18609,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{05f0e1d4-140f-4aa5-a2cc-5dafb2e47ed1}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{475d7e65-338a-43be-93c4-322180adb284}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G279)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18415,7 +18627,7 @@
           <xm:sqref>G279</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="46" operator="containsText" id="{005f8992-9354-4806-9438-29658b9abc26}">
+          <x14:cfRule type="containsText" priority="60" operator="containsText" id="{03bde81d-5c0f-4328-af05-68c29a5059b1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18430,7 +18642,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="45" operator="containsText" id="{73382758-8626-42fc-b303-4c37c5a8ceea}">
+          <x14:cfRule type="containsText" priority="59" operator="containsText" id="{2315e527-4cf6-4126-bde4-759d77b8a8af}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18448,7 +18660,7 @@
           <xm:sqref>A280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{9700aaa0-7f8b-42c9-8a5a-9e8a9c2b0818}">
+          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{0e28734a-a709-420c-b7cd-570c3743249a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18463,7 +18675,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="40" operator="containsText" id="{fc766fae-9bea-4d8e-84a4-b8a58fc745c8}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{ae5189ef-5430-47ae-a67a-238473829dee}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18481,7 +18693,7 @@
           <xm:sqref>E280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{f3ff7666-ccd4-40c4-88b8-0171e9217168}">
+          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{2852349a-4ac0-453e-9e8f-a6ec2be6ccef}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18496,7 +18708,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{074688ec-c504-4eb0-accb-57141d51c13a}">
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{a3016d1e-587e-470a-b9ac-f1adb1bda59b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18514,7 +18726,40 @@
           <xm:sqref>J280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="43" operator="containsText" id="{a8489e45-8c24-4693-837f-9a6aae7f44a3}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{5b8d921b-04a0-4555-a2fd-78a23993d3c0}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,K280)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{f96ef0ab-00f8-42a7-b08a-fc7e2dd182fb}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,K280)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K280</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="57" operator="containsText" id="{fd5e4f53-5b4e-4f1d-9c1c-d3a3be9eb0da}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E281)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18529,7 +18774,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{9a61e1be-2f2b-4884-894f-8681f168f6a8}">
+          <x14:cfRule type="containsText" priority="58" operator="containsText" id="{617545fa-08f7-4045-b662-eaa52935e684}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E281)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18547,7 +18792,7 @@
           <xm:sqref>E281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{b1c322e1-401a-4622-b8d2-d554ec6710d1}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{99b40acb-d2e1-4858-bedc-fd14ebb787db}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G281)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18562,7 +18807,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{a351fd16-d574-410a-98a6-8be1ee20d771}">
+          <x14:cfRule type="containsText" priority="30" operator="containsText" id="{02cd9e6a-d9eb-41c7-9c31-f4420f409425}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G281)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18580,7 +18825,7 @@
           <xm:sqref>G281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="75" operator="containsText" id="{920b7600-1773-4c19-8e26-3d0e86dd3ac1}">
+          <x14:cfRule type="containsText" priority="89" operator="containsText" id="{b726cca5-6b58-4ea9-ae3e-3c0a0df335fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18595,7 +18840,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="76" operator="containsText" id="{c7e85a00-fe1d-4adb-9fee-49866f03c6fd}">
+          <x14:cfRule type="containsText" priority="90" operator="containsText" id="{6d0d5ada-00bf-4ad1-a58e-5ce7f36d5d91}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18613,7 +18858,7 @@
           <xm:sqref>B86:B99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="73" operator="containsText" id="{59318c52-a3eb-4791-bb94-87f73b1bcc3b}">
+          <x14:cfRule type="containsText" priority="87" operator="containsText" id="{a89461ec-9af0-40f1-a46d-016bcb273707}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18628,7 +18873,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="74" operator="containsText" id="{150cf5c3-4a46-4dc3-84c7-a825dbbc3951}">
+          <x14:cfRule type="containsText" priority="88" operator="containsText" id="{fa24e666-2f4d-42bc-a552-82a1570299c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18646,7 +18891,7 @@
           <xm:sqref>B100:B113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="71" operator="containsText" id="{613295f7-9884-45e7-9862-89e890092433}">
+          <x14:cfRule type="containsText" priority="85" operator="containsText" id="{d2c2b9ec-4f8f-4db6-8b06-285bcab17c87}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18661,7 +18906,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="72" operator="containsText" id="{b119ca71-053a-42d6-83ba-f1310f24e03f}">
+          <x14:cfRule type="containsText" priority="86" operator="containsText" id="{3a334b78-88da-40f6-b488-d559e550baff}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18679,7 +18924,7 @@
           <xm:sqref>B114:B127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="69" operator="containsText" id="{636d19c5-af43-485b-b6c5-5d14a62eddfa}">
+          <x14:cfRule type="containsText" priority="83" operator="containsText" id="{7f4a27c2-70f4-441e-88ef-aa48fbce049d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18694,7 +18939,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="70" operator="containsText" id="{de53052c-0f41-4b0a-8365-4941aa6034b3}">
+          <x14:cfRule type="containsText" priority="84" operator="containsText" id="{1916e1fd-d367-4534-acc2-9364e6d10d03}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18712,7 +18957,7 @@
           <xm:sqref>B128:B141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="67" operator="containsText" id="{1ef68349-af33-431c-8e9f-2a1f0d041647}">
+          <x14:cfRule type="containsText" priority="81" operator="containsText" id="{36420917-10cf-4e74-85b1-1f22ca2bd052}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18727,7 +18972,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="68" operator="containsText" id="{985357eb-35ee-4398-a491-656641898eed}">
+          <x14:cfRule type="containsText" priority="82" operator="containsText" id="{6b8dbd9f-973e-4871-a646-93e576b75672}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18745,7 +18990,7 @@
           <xm:sqref>B142:B155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="65" operator="containsText" id="{72487ed5-1979-40f3-8412-36c97d3a1fc5}">
+          <x14:cfRule type="containsText" priority="79" operator="containsText" id="{ea8e470b-f5aa-4a5a-a232-978893856e81}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18760,7 +19005,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="66" operator="containsText" id="{1d1ddda2-657e-4d80-adb1-de669ffe8335}">
+          <x14:cfRule type="containsText" priority="80" operator="containsText" id="{cddacec6-2d88-43d1-babe-d30afc81deb8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18778,7 +19023,7 @@
           <xm:sqref>B156:B169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="63" operator="containsText" id="{619f29f8-be99-406a-884b-3cea81fe9fab}">
+          <x14:cfRule type="containsText" priority="77" operator="containsText" id="{e9c89131-0c3c-4802-93fe-ba03f0763d91}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18793,7 +19038,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="64" operator="containsText" id="{0e2e17eb-17b8-452a-8959-7923b64b45b8}">
+          <x14:cfRule type="containsText" priority="78" operator="containsText" id="{9b6f080e-ff2e-4b9d-874c-9217c1208a2b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18811,7 +19056,7 @@
           <xm:sqref>B170:B183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="61" operator="containsText" id="{62158c10-d00a-40be-b0af-fcb7085206ab}">
+          <x14:cfRule type="containsText" priority="75" operator="containsText" id="{a33ece6e-19d5-4e40-bbbc-c1e3c8c5e922}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18826,7 +19071,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="62" operator="containsText" id="{e0b000e9-5892-4b74-bc1f-a6215a1b5b03}">
+          <x14:cfRule type="containsText" priority="76" operator="containsText" id="{a244db49-5840-4d8e-9f7d-9f7707fbcb5f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18844,7 +19089,7 @@
           <xm:sqref>B184:B197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="59" operator="containsText" id="{8bca9c02-f75a-45d0-9b9a-c76de06ad38a}">
+          <x14:cfRule type="containsText" priority="73" operator="containsText" id="{2d32bb2a-8a1f-4445-a840-cd34f8073d6f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18859,7 +19104,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="60" operator="containsText" id="{7dbad81e-356f-42fa-bf6b-a473ea965a2d}">
+          <x14:cfRule type="containsText" priority="74" operator="containsText" id="{72897fcd-8a07-4aeb-99bc-4019cd2a5e1f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18877,7 +19122,7 @@
           <xm:sqref>B198:B211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="57" operator="containsText" id="{48d3c460-1ff4-42fd-9506-6b621af83764}">
+          <x14:cfRule type="containsText" priority="71" operator="containsText" id="{d524492b-6124-4d98-82d1-e40aa32cec03}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18892,7 +19137,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="58" operator="containsText" id="{e2bbe827-af9b-4165-a3e1-d123708eaf18}">
+          <x14:cfRule type="containsText" priority="72" operator="containsText" id="{05030b9b-cc4a-4f9a-b52a-e01d5a2f6a4f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18910,7 +19155,7 @@
           <xm:sqref>B212:B225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="55" operator="containsText" id="{a558c54e-7613-43ff-8ac3-38234e97728a}">
+          <x14:cfRule type="containsText" priority="69" operator="containsText" id="{ea868fb7-4f2c-49f3-b7c6-2b0ada061556}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18925,7 +19170,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="56" operator="containsText" id="{7c5af402-d0d7-46e0-880c-e7638aff085e}">
+          <x14:cfRule type="containsText" priority="70" operator="containsText" id="{ef9726b7-409f-41dc-afb8-a79342ad6cb7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18943,7 +19188,7 @@
           <xm:sqref>B226:B239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{372c6139-9b3a-41dc-b26c-a4c30686bf75}">
+          <x14:cfRule type="containsText" priority="67" operator="containsText" id="{c39bdf49-850d-47b7-8422-c1487424109a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18958,7 +19203,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{704a1b65-7889-48b7-8ae4-92f4a58ec550}">
+          <x14:cfRule type="containsText" priority="68" operator="containsText" id="{4e2c5993-a999-4dbb-b972-bed807f6983a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18976,7 +19221,7 @@
           <xm:sqref>B240:B253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="51" operator="containsText" id="{384099b5-1014-4e88-b3e7-2f1ee5847c1f}">
+          <x14:cfRule type="containsText" priority="65" operator="containsText" id="{f0f17d5d-a703-4b16-b468-a07ed5698f41}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18991,7 +19236,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="52" operator="containsText" id="{5604cbbd-8b8f-454b-b05a-d44b137aa9f3}">
+          <x14:cfRule type="containsText" priority="66" operator="containsText" id="{fac2735e-f172-4234-a2f9-bcf8f668b5f1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19009,7 +19254,7 @@
           <xm:sqref>B254:B267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{e18a1a09-18cc-492e-80a3-89dc1bff1c06}">
+          <x14:cfRule type="containsText" priority="125" operator="containsText" id="{c00320f2-f883-495b-8565-3c7a42fdfbf0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19024,7 +19269,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="112" operator="containsText" id="{a7e9e0ff-cd8c-4927-8090-c7a37959724c}">
+          <x14:cfRule type="containsText" priority="126" operator="containsText" id="{ac0fd951-9f70-4385-986e-2326e8860c0b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19042,7 +19287,7 @@
           <xm:sqref>G184:G195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="105" operator="containsText" id="{2b91d1c2-64cd-4604-926a-e8fbdb8a1156}">
+          <x14:cfRule type="containsText" priority="119" operator="containsText" id="{2378a12e-3a57-4607-b60c-208097ac257d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19057,7 +19302,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="106" operator="containsText" id="{ae4827dc-ca80-4b72-9ea2-c4dc745ba853}">
+          <x14:cfRule type="containsText" priority="120" operator="containsText" id="{601c59fb-5b6e-4d81-b66a-aed1009ad8cc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19075,7 +19320,7 @@
           <xm:sqref>G198:G209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="99" operator="containsText" id="{781cf636-3fdb-4f96-a9bb-54c315bd9a47}">
+          <x14:cfRule type="containsText" priority="113" operator="containsText" id="{491419b4-112b-41b6-aef6-62a789f73d93}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19090,7 +19335,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="100" operator="containsText" id="{196c7402-b8c0-4a2d-9fcc-a6346b95e37f}">
+          <x14:cfRule type="containsText" priority="114" operator="containsText" id="{b2607817-8bbd-4223-ab22-1229b8f15f93}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19108,7 +19353,7 @@
           <xm:sqref>G212:G223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="93" operator="containsText" id="{c6cb0992-00b1-4e2f-9ea3-ead24e987659}">
+          <x14:cfRule type="containsText" priority="107" operator="containsText" id="{6d36f92b-7a9f-41fe-97bb-3a1bba2e81de}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19123,7 +19368,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="94" operator="containsText" id="{f6fe4558-c40e-4170-97ec-204704ecad87}">
+          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{4cf6b033-67d5-43dc-9cdb-dd2d3c633922}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19141,7 +19386,7 @@
           <xm:sqref>G226:G237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="87" operator="containsText" id="{0f7d5adb-69ec-48ec-921f-0ab4d439b3f1}">
+          <x14:cfRule type="containsText" priority="101" operator="containsText" id="{1c122cf8-a740-4684-9c5d-78dc39f72b8f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19156,7 +19401,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="88" operator="containsText" id="{a285abeb-cfef-4d6a-9603-9004e318e947}">
+          <x14:cfRule type="containsText" priority="102" operator="containsText" id="{cb4dfe7d-4878-4690-b38c-7ade412d17c0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19174,7 +19419,7 @@
           <xm:sqref>G240:G251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="81" operator="containsText" id="{aeb38a40-8cc1-49cb-bdd3-54e2bbfaed5d}">
+          <x14:cfRule type="containsText" priority="95" operator="containsText" id="{728f4970-22f3-46b5-aa6b-fe96c595a3b6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19189,7 +19434,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="82" operator="containsText" id="{28c73dfd-1c09-4c57-87a5-f5e95f0f9ba4}">
+          <x14:cfRule type="containsText" priority="96" operator="containsText" id="{225bbed2-3690-4be6-8523-860c89af40dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19207,7 +19452,7 @@
           <xm:sqref>G254:G265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="869" operator="containsText" id="{670e5db0-4a09-46ec-84e6-849d58afac22}">
+          <x14:cfRule type="containsText" priority="883" operator="containsText" id="{abe5ddfb-2f80-4971-a5df-a7a0b242db3d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K69)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19222,7 +19467,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="870" operator="containsText" id="{f0296cfa-76d6-4544-b11b-cc981e5741c7}">
+          <x14:cfRule type="containsText" priority="884" operator="containsText" id="{da73e6ae-8e4b-4fa0-82b2-7212d4874eb5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K69)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19240,7 +19485,7 @@
           <xm:sqref>K69:K70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="871" operator="containsText" id="{8ecc07c2-006a-41d2-aec1-d7832320a927}">
+          <x14:cfRule type="containsText" priority="885" operator="containsText" id="{a2a29c8e-913b-4491-9a5e-23d44a56b36c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19255,7 +19500,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="876" operator="containsText" id="{7037265a-e19a-43e4-9fec-e62fb4ab5305}">
+          <x14:cfRule type="containsText" priority="890" operator="containsText" id="{f255745c-a3a1-40bd-86e2-d54ffc61c731}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19273,7 +19518,7 @@
           <xm:sqref>L22:M22 M36 J38:M38 K21:M21 J31:M32 A29:A41 L58:M58 L67:M67 A71 L69:M70 A1:A27 E72:F72 J28:M28 A43:A55 J42:M42 A57:A69 J56:M56 J70 C85:F85 L73:M73 C73:F83 L83:M84 J84 L96:M96 J96:J97 M142 M147 C134:F134 J142:K142 K147 A284:F1048576 C197:D197 F197 E195 H197 H284:M1048576 H83:J83 H73:J73 H74:M82 H85:M85 H57:M57 H43:M55 H69:J69 H71:M72 H68:M68 H67:J67 H59:M66 H58:J58 H39:M41 H33:M35 H38 H37:M37 H36:K36 H21 H23:M27 H22:J22 H29:M29 H31:H32 H1:M20 C57:F69 C43:F55 C71:F71 C31:F41 C29:F29 C1:F27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="77" operator="containsText" id="{4197752c-b9fb-42d3-8dad-fde977200ec8}">
+          <x14:cfRule type="containsText" priority="91" operator="containsText" id="{01aaa7a5-cfc0-4769-90d6-b12c523a39aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19288,7 +19533,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="78" operator="containsText" id="{0169c74f-0db3-4293-81a6-c180ad1dd48f}">
+          <x14:cfRule type="containsText" priority="92" operator="containsText" id="{827d88a2-fd19-4a5d-9fc4-ce4d3cea173f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19306,7 +19551,7 @@
           <xm:sqref>B1:B2 B4 B6 B8 B10 B12 B14 B16:B85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="149" operator="containsText" id="{caf75177-868c-4979-bbc1-7eb7678feae4}">
+          <x14:cfRule type="containsText" priority="163" operator="containsText" id="{081ca0ed-630c-44d4-a8bd-e6d3e7e7442e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19321,7 +19566,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="150" operator="containsText" id="{8bddf82a-22bf-4045-bf7b-9ca5ecb0d767}">
+          <x14:cfRule type="containsText" priority="164" operator="containsText" id="{1f3df622-5784-4a9b-a9f5-b772a88f3c9a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19339,7 +19584,7 @@
           <xm:sqref>G31 G29 G33:G41 G1:G27 G57:G69 G71:G85 G96:G97 G284:G1048576 G197 G43:G55</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{feb109e0-f0ec-4b0d-b25d-434daded6e42}">
+          <x14:cfRule type="containsText" priority="63" operator="containsText" id="{f92a1f6f-f6d5-4269-8a7a-a84cf7d362b2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B3)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19354,7 +19599,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="50" operator="containsText" id="{b7551ef3-1f71-472d-8496-3eb25962ca5d}">
+          <x14:cfRule type="containsText" priority="64" operator="containsText" id="{f2eabd7a-6a0d-47bc-ac63-b823070c4c13}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B3)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19372,7 +19617,7 @@
           <xm:sqref>B3 B5 B7 B9 B11 B13 B15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="865" operator="containsText" id="{4a669671-b41a-4715-a70b-182e6046983e}">
+          <x14:cfRule type="containsText" priority="879" operator="containsText" id="{11cffe54-cba5-4542-b76c-c95fd990369c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A28)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19387,7 +19632,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="866" operator="containsText" id="{2d13c43b-0350-4589-a35f-bc26eaf0cc07}">
+          <x14:cfRule type="containsText" priority="880" operator="containsText" id="{b3d55d08-9884-4f14-b922-7b2be295430b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A28)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19405,7 +19650,7 @@
           <xm:sqref>A28 H28:I28 C28:F28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="863" operator="containsText" id="{759c5a71-3acb-4303-9981-0f4e1bb59327}">
+          <x14:cfRule type="containsText" priority="877" operator="containsText" id="{5a9cf33b-3e37-4dc3-bdf2-d9dab26281f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A42)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19420,7 +19665,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="864" operator="containsText" id="{3e26fb4a-0df2-4108-8dd4-137331fd567e}">
+          <x14:cfRule type="containsText" priority="878" operator="containsText" id="{ca71692b-fc30-42d1-87f5-ff38fd07b559}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A42)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19438,7 +19683,7 @@
           <xm:sqref>A42 H42:I42 C42:F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="861" operator="containsText" id="{b1b5ad1f-ec97-4d75-97f6-b3242d80a06f}">
+          <x14:cfRule type="containsText" priority="875" operator="containsText" id="{8b22d3f4-b926-455f-9154-6e73891f0cf5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A56)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19453,7 +19698,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="862" operator="containsText" id="{dcef013c-80d1-4251-8db1-01460cf03ea2}">
+          <x14:cfRule type="containsText" priority="876" operator="containsText" id="{4a2d3ed3-0403-4d33-8f38-bef98a571ceb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A56)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19471,7 +19716,7 @@
           <xm:sqref>A56 H56:I56 C56:F56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="859" operator="containsText" id="{8f956dbc-07ae-4247-9ad7-5e517d40764a}">
+          <x14:cfRule type="containsText" priority="873" operator="containsText" id="{ff0f3784-76fe-443f-8b09-b0248e016452}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A70)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19486,7 +19731,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="860" operator="containsText" id="{3a1844bb-e121-4fd0-80d5-fb712e35da99}">
+          <x14:cfRule type="containsText" priority="874" operator="containsText" id="{f43132e9-ff1e-44d7-a5e4-4b5ff823e758}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A70)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19504,7 +19749,7 @@
           <xm:sqref>A70 H70:I70 C70:F70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="867" operator="containsText" id="{c6e42086-4f49-4a56-97ac-40a436ec413d}">
+          <x14:cfRule type="containsText" priority="881" operator="containsText" id="{9fdd5f86-e7e0-4edc-accf-f429a468db1c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A72)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19519,7 +19764,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="868" operator="containsText" id="{95834db3-4eeb-4f13-b11f-96e5bf719368}">
+          <x14:cfRule type="containsText" priority="882" operator="containsText" id="{331499a1-953f-4a3b-87d5-0291806682c0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A72)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19537,7 +19782,7 @@
           <xm:sqref>A72:A83 A85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="857" operator="containsText" id="{31c0d67b-d6a1-4382-8439-4c35c6f85aa5}">
+          <x14:cfRule type="containsText" priority="871" operator="containsText" id="{142faf76-5000-45e3-8eb6-9a01da79b0d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A84)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19552,7 +19797,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="858" operator="containsText" id="{63e78237-2b85-499e-9d93-5ffa21a778c8}">
+          <x14:cfRule type="containsText" priority="872" operator="containsText" id="{c00719c0-4be2-4ed9-81e0-bc24178f8092}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A84)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19570,7 +19815,7 @@
           <xm:sqref>A84 H84:I84 C84:F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="853" operator="containsText" id="{2ec497e4-6a8c-486d-ae8e-863013f1fb1a}">
+          <x14:cfRule type="containsText" priority="867" operator="containsText" id="{c99a6a9e-c597-4e1b-bb45-b28b537a6855}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19585,7 +19830,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="854" operator="containsText" id="{5909999e-47f4-43b0-a86e-496063b5ae1e}">
+          <x14:cfRule type="containsText" priority="868" operator="containsText" id="{0a8fa5e0-7de3-4d55-9261-018c5d4124b1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19603,7 +19848,7 @@
           <xm:sqref>A86:A97 A99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="855" operator="containsText" id="{c57ae58b-26a6-4b9c-afb0-166bd66868db}">
+          <x14:cfRule type="containsText" priority="869" operator="containsText" id="{fb2e427b-8fb0-49cb-ade7-471840689f54}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19618,7 +19863,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="856" operator="containsText" id="{d632630e-87d5-4348-8e13-061dbdcfcf46}">
+          <x14:cfRule type="containsText" priority="870" operator="containsText" id="{77b427eb-0284-406c-9ef8-9ddb058b6ba2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19636,7 +19881,7 @@
           <xm:sqref>E86:F86 C99:F99 J98:M98 M97 M87 J92:M93 C87:F97 H96:H97 H92:H93 H87:K87 H88:M91 H94:M95 H99:M99 H86:M86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="139" operator="containsText" id="{ec20d65f-9da0-49d3-b50c-284eb356f161}">
+          <x14:cfRule type="containsText" priority="153" operator="containsText" id="{2a958c11-d99a-461c-b0d5-668ca85c8a89}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19651,7 +19896,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="140" operator="containsText" id="{6bee4bcb-6061-4ef2-982e-8b9a3135af4c}">
+          <x14:cfRule type="containsText" priority="154" operator="containsText" id="{8c70d476-53ad-487d-b5e4-bd3ddab013c0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19669,7 +19914,7 @@
           <xm:sqref>G99 G86:G95</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="851" operator="containsText" id="{8ccb0376-c554-406e-bb42-d885cc11c7b5}">
+          <x14:cfRule type="containsText" priority="865" operator="containsText" id="{17250323-4c3d-4852-91de-ff3f480fa09e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A98)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19684,7 +19929,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="852" operator="containsText" id="{b4ffe284-b3b7-4fb6-b85d-5907beeffb65}">
+          <x14:cfRule type="containsText" priority="866" operator="containsText" id="{e51337ff-d5fd-49ea-b63e-674f7cf01fa0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A98)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19702,7 +19947,7 @@
           <xm:sqref>A98 H98:I98 C98:F98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="835" operator="containsText" id="{74dd199a-ae31-4834-85eb-a2b0fc7c2336}">
+          <x14:cfRule type="containsText" priority="849" operator="containsText" id="{f2cfddfb-344e-4cc4-8f6b-9aa229a9c61b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19717,7 +19962,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="836" operator="containsText" id="{27035157-63fa-42a9-ac6d-003940c0eacb}">
+          <x14:cfRule type="containsText" priority="850" operator="containsText" id="{791ae424-2874-4e27-8b94-f67fce63604c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19735,7 +19980,7 @@
           <xm:sqref>A100:A111 A113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="837" operator="containsText" id="{164f2162-e89f-43cb-9fc6-c22e719d686f}">
+          <x14:cfRule type="containsText" priority="851" operator="containsText" id="{d2ace58f-1bd4-4106-b836-90dd6a5180c1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19750,7 +19995,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="838" operator="containsText" id="{bb372f4c-e9bc-4357-ac13-78cd80eb1d3e}">
+          <x14:cfRule type="containsText" priority="852" operator="containsText" id="{a1055a4f-5c7d-4303-b1c3-9b513e474898}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19768,7 +20013,7 @@
           <xm:sqref>E100:F100 C113:F113 J112:M112 J111 M111 J110:M110 M101 J106:M107 C101:F111 J102:M102 H102 H106:H107 H101:K101 H103:M105 H110:H111 H108:M109 H113:M113 H100:M100</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="135" operator="containsText" id="{3fd7f295-6094-465b-977d-2d77c8bdbd82}">
+          <x14:cfRule type="containsText" priority="149" operator="containsText" id="{8b1bb975-f8ae-430e-8306-d7e35d3663a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19783,7 +20028,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="136" operator="containsText" id="{7fec4f08-6a59-41f1-ba97-1d7774468f9e}">
+          <x14:cfRule type="containsText" priority="150" operator="containsText" id="{3b23a2b9-930f-4cf3-9744-896e05fde356}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19801,7 +20046,7 @@
           <xm:sqref>G113 G100:G111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="833" operator="containsText" id="{ebac5b3f-1b19-45e6-8ec1-f8b0ea0816a0}">
+          <x14:cfRule type="containsText" priority="847" operator="containsText" id="{53c3bf43-bcb7-4af0-8c7d-d596b1ac863e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19816,7 +20061,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="834" operator="containsText" id="{a5aed20d-04c6-4b76-b6f8-d6d739564825}">
+          <x14:cfRule type="containsText" priority="848" operator="containsText" id="{a9ce62c8-5042-4266-b568-33fe68c647ee}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19834,7 +20079,7 @@
           <xm:sqref>A112 H112 C112:F112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="791" operator="containsText" id="{4516c35f-fd6e-4e9e-a841-ca8d637fb6bf}">
+          <x14:cfRule type="containsText" priority="805" operator="containsText" id="{38751885-d358-481b-a2b7-72d676e5ff7a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19849,7 +20094,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="792" operator="containsText" id="{c0a8cdbf-aae5-4f19-9269-9277e937339d}">
+          <x14:cfRule type="containsText" priority="806" operator="containsText" id="{f94a795c-3f29-4ffd-9f62-e7fa221d87a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19867,7 +20112,7 @@
           <xm:sqref>A114:A125 A127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="793" operator="containsText" id="{7e3fad29-725e-4d3e-803d-53e816f73210}">
+          <x14:cfRule type="containsText" priority="807" operator="containsText" id="{4c391ea1-0f2f-4586-9797-a23ce9c1db82}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19882,7 +20127,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="794" operator="containsText" id="{52ae53d9-758f-452d-a208-2c3963838dee}">
+          <x14:cfRule type="containsText" priority="808" operator="containsText" id="{4125f3c6-c118-4db4-b2f5-5a448c35a150}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19900,7 +20145,7 @@
           <xm:sqref>E114:F114 C127:F127 J126:M126 J125 M125 M115 J116:M116 J114:M114 C115:F125 J120:M124 H120:H125 H116 H115:K115 H117:M119 H127:M127 H114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="131" operator="containsText" id="{83ae05be-49da-4df0-a32b-a59da2700191}">
+          <x14:cfRule type="containsText" priority="145" operator="containsText" id="{a8296a6d-19ad-4f93-9de5-5e85f45defde}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19915,7 +20160,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="132" operator="containsText" id="{d00f44c5-1a46-4770-a96f-81b5152f6d5b}">
+          <x14:cfRule type="containsText" priority="146" operator="containsText" id="{c23344a6-26e1-4e82-b3f6-470505f1b1f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19933,7 +20178,7 @@
           <xm:sqref>G127 G114:G125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="789" operator="containsText" id="{f2c4f849-6f8b-45aa-ab78-e935c98ddf7a}">
+          <x14:cfRule type="containsText" priority="803" operator="containsText" id="{20f9b80e-0fd2-4ef4-9a70-608c244446aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19948,7 +20193,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="790" operator="containsText" id="{26542266-c323-4572-a4b1-234e029e905b}">
+          <x14:cfRule type="containsText" priority="804" operator="containsText" id="{2dc4853e-b589-40c3-8089-0fc32678987c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19966,7 +20211,7 @@
           <xm:sqref>A126 H126 C126:F126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="751" operator="containsText" id="{b2053166-2ff1-4063-807b-daf6ed53d4ed}">
+          <x14:cfRule type="containsText" priority="765" operator="containsText" id="{a76cdb54-cb5f-4d65-aac4-e0b33de76344}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19981,7 +20226,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="752" operator="containsText" id="{84547f13-2503-4ce1-9f93-d4888110cfd4}">
+          <x14:cfRule type="containsText" priority="766" operator="containsText" id="{0b39c10d-b08d-404d-acbd-1ccc2ec176f1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19999,7 +20244,7 @@
           <xm:sqref>A128:A139 A141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="753" operator="containsText" id="{946e8304-06bd-48f4-b184-6da264de241d}">
+          <x14:cfRule type="containsText" priority="767" operator="containsText" id="{e1cd72bb-06dc-46a2-8224-24b660a744e0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20014,7 +20259,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="754" operator="containsText" id="{22913be4-beaf-4067-b66d-fb3cb68928c4}">
+          <x14:cfRule type="containsText" priority="768" operator="containsText" id="{bd06be69-dbc1-41bd-b6f0-572d1ee34254}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20032,7 +20277,7 @@
           <xm:sqref>E128:F128 C141:F141 J140:M140 J139 M139 M129 J130:M130 J128:M128 C129:F133 J134:M138 J133 M133 J129:K129 C135:F139 H133:H139 H131:M132 H141:M141 H128:H130</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="127" operator="containsText" id="{e6626918-c268-48f0-87b0-21b9e9d6b786}">
+          <x14:cfRule type="containsText" priority="141" operator="containsText" id="{a4bfdb1c-32fd-400c-8d22-7077b9a9e1ed}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20047,7 +20292,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="128" operator="containsText" id="{2e07b293-4f03-4bc5-8131-4e9f4b6edbe0}">
+          <x14:cfRule type="containsText" priority="142" operator="containsText" id="{653aea61-830a-430c-8264-956f74f57c83}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20065,7 +20310,7 @@
           <xm:sqref>G141 G128:G139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="749" operator="containsText" id="{34b13b2d-ebe4-481b-b174-9c9cb5df1338}">
+          <x14:cfRule type="containsText" priority="763" operator="containsText" id="{adc548e3-b34b-4229-8ecf-cdf5088f7624}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20080,7 +20325,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="750" operator="containsText" id="{293f68c2-c5c0-4fe6-9b97-62bd5b134704}">
+          <x14:cfRule type="containsText" priority="764" operator="containsText" id="{e6dea337-2735-4a6a-854c-99e247813def}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20098,7 +20343,7 @@
           <xm:sqref>A140 H140 C140:F140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="707" operator="containsText" id="{0e1633ad-ef06-42f8-ab95-8ab13d75a5e4}">
+          <x14:cfRule type="containsText" priority="721" operator="containsText" id="{65bbae35-993b-49ff-b010-2be3159faca7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20113,7 +20358,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="708" operator="containsText" id="{ba570e9d-0c3a-4de9-97c2-0e77febdc3ef}">
+          <x14:cfRule type="containsText" priority="722" operator="containsText" id="{72bf49ac-36b0-4717-baa9-45829a25ef05}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20131,7 +20376,7 @@
           <xm:sqref>A142:A153 A155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="709" operator="containsText" id="{127e44c6-8f12-4134-9fe8-f9e93a32b91c}">
+          <x14:cfRule type="containsText" priority="723" operator="containsText" id="{f10cceea-910b-49fd-b9b2-2c4bf7206473}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20146,7 +20391,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="710" operator="containsText" id="{f5aae66c-d769-4a27-b164-e85bcc9cd223}">
+          <x14:cfRule type="containsText" priority="724" operator="containsText" id="{50eaf9bf-5ed3-4412-99e9-dcc1db7c4948}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20164,7 +20409,7 @@
           <xm:sqref>E142:F142 C155:F155 J153 M153 J144:M144 J148:M152 J147 J154:M155 C143:F153 J146:M146 H146:H153 H145:M145 H155 H142:H144</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="123" operator="containsText" id="{40445dde-1aaf-423b-b8f2-632398ca3a65}">
+          <x14:cfRule type="containsText" priority="137" operator="containsText" id="{73a2d580-7c3f-4921-a640-8cd1e42274bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20179,7 +20424,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="124" operator="containsText" id="{541187b7-9547-491b-9b1a-e0d394177fe6}">
+          <x14:cfRule type="containsText" priority="138" operator="containsText" id="{4380dc50-ffd1-449d-a7a7-3653148c108d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20197,7 +20442,7 @@
           <xm:sqref>G155 G142:G153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="705" operator="containsText" id="{13c585a2-ed46-4e68-974e-7d56c7eedaa9}">
+          <x14:cfRule type="containsText" priority="719" operator="containsText" id="{cd3f81b4-ff85-427d-9d86-163f9af9fd1e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20212,7 +20457,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="706" operator="containsText" id="{64ccbc07-47a1-48e5-9e63-0c2228f5a42d}">
+          <x14:cfRule type="containsText" priority="720" operator="containsText" id="{471dd8d7-163c-4de6-a015-88b1213a3603}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20230,7 +20475,7 @@
           <xm:sqref>A154 H154 C154:F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="653" operator="containsText" id="{007969df-3089-453b-9e72-0409ecd04c1d}">
+          <x14:cfRule type="containsText" priority="667" operator="containsText" id="{18976a92-c7c8-47f3-8205-e7f94e065721}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20245,7 +20490,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="654" operator="containsText" id="{098ad2c4-5d61-47d0-9c29-b90abb2d38da}">
+          <x14:cfRule type="containsText" priority="668" operator="containsText" id="{01b49977-511d-4797-bcd5-3a99537ed891}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20263,7 +20508,7 @@
           <xm:sqref>A156:A167 A169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="655" operator="containsText" id="{dc5601b7-b3a1-43bb-92d7-4a940817a3fd}">
+          <x14:cfRule type="containsText" priority="669" operator="containsText" id="{cf502fd3-06af-4792-a0f1-51d2008916d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20278,7 +20523,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="656" operator="containsText" id="{6a334525-9233-46c2-8ab6-de71152106ee}">
+          <x14:cfRule type="containsText" priority="670" operator="containsText" id="{4b05c711-4997-475d-939c-47d2b63c8df4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20296,7 +20541,7 @@
           <xm:sqref>E156:F156 C169:F169 J167 M167 J158:M158 J162:M166 J161 J168:M169 C157:F167 J160:M160 H160:H167 H159:M159 H169 H156:H158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="119" operator="containsText" id="{fecae2d6-e20c-4ca0-ac1a-8dfa07db7292}">
+          <x14:cfRule type="containsText" priority="133" operator="containsText" id="{9f72062d-0467-4bf7-b46f-4885165b266b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20311,7 +20556,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="120" operator="containsText" id="{9a02b57c-1151-4c0a-b86c-e9205770b8c9}">
+          <x14:cfRule type="containsText" priority="134" operator="containsText" id="{f8f2d644-c316-4260-b5db-81c1806160ec}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20329,7 +20574,7 @@
           <xm:sqref>G169 G156:G167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="657" operator="containsText" id="{ff068189-f5ff-4dcc-be68-e8fa33afddf6}">
+          <x14:cfRule type="containsText" priority="671" operator="containsText" id="{c7ba9455-74e9-4ecc-9834-9c999a593372}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20344,7 +20589,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="658" operator="containsText" id="{50026f95-c79f-40ac-8bfe-1430afcbeed5}">
+          <x14:cfRule type="containsText" priority="672" operator="containsText" id="{7e6c884d-3b29-4c62-8ba2-a1e82695d295}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20362,7 +20607,7 @@
           <xm:sqref>M156 M161 J156:K156 K161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="651" operator="containsText" id="{4b98c722-4dae-491d-ada5-a6089c0822b8}">
+          <x14:cfRule type="containsText" priority="665" operator="containsText" id="{2588aef0-49e4-4bd3-bef1-9e46eac43564}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20377,7 +20622,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="652" operator="containsText" id="{e673ae58-f856-4633-8a39-7e0591d690c7}">
+          <x14:cfRule type="containsText" priority="666" operator="containsText" id="{b93ddda6-104e-4b83-9dff-8fa85ba90c13}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20395,7 +20640,7 @@
           <xm:sqref>A168 H168 C168:F168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="607" operator="containsText" id="{db3533cb-8173-466b-8ff9-78091457446c}">
+          <x14:cfRule type="containsText" priority="621" operator="containsText" id="{c3602aa5-2d6c-4838-9148-8fa815d8f9a9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20410,7 +20655,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="608" operator="containsText" id="{030cac0b-e4b1-4d50-b218-5f5d17a53ef0}">
+          <x14:cfRule type="containsText" priority="622" operator="containsText" id="{f0ab27d1-bc88-479f-b840-26b6066291cb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20428,7 +20673,7 @@
           <xm:sqref>A170:A181 A183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="609" operator="containsText" id="{1f3c7bef-926e-4c46-b8c3-ba26421333d6}">
+          <x14:cfRule type="containsText" priority="623" operator="containsText" id="{abe2edf7-ca3f-4cff-94bf-b63dbea04d98}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20443,7 +20688,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="610" operator="containsText" id="{aeb7d357-c951-4081-80d2-f153a3b7121f}">
+          <x14:cfRule type="containsText" priority="624" operator="containsText" id="{1f17ce57-8fd0-4447-a7ed-dc7b34fd94c8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20461,7 +20706,7 @@
           <xm:sqref>E170:F170 C183:F183 J181 M181 J172:M172 J176:M180 J175 J182:M183 C171:F181 J174:M174 H174:H181 H173:M173 H183 H170:H172</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="115" operator="containsText" id="{b975a8bd-22f1-4109-b729-66ae153a0acf}">
+          <x14:cfRule type="containsText" priority="129" operator="containsText" id="{f084841c-e02e-4602-ae63-99e9ab24c521}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20476,7 +20721,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="116" operator="containsText" id="{fae4d568-8421-49b8-8571-31c6f6bcac05}">
+          <x14:cfRule type="containsText" priority="130" operator="containsText" id="{9ab2adbf-6131-4e6f-9ddb-bda28fdc67e5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20494,7 +20739,7 @@
           <xm:sqref>G183 G170:G181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="611" operator="containsText" id="{d297fecb-18c5-4e59-993c-eef7cb46bd92}">
+          <x14:cfRule type="containsText" priority="625" operator="containsText" id="{240363bb-ecbb-4150-ae2f-160370d7eb56}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20509,7 +20754,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="612" operator="containsText" id="{9177b976-ad69-4682-9358-b4156c5400f1}">
+          <x14:cfRule type="containsText" priority="626" operator="containsText" id="{f469113a-7fca-482c-9cff-b19ea0dae94a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20527,7 +20772,7 @@
           <xm:sqref>M170 M175 J170:K170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="605" operator="containsText" id="{d5058800-a509-4bf3-bf89-bf0c0fa40997}">
+          <x14:cfRule type="containsText" priority="619" operator="containsText" id="{a6d12484-2ea8-42cd-a304-5ecaab936211}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20542,7 +20787,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="606" operator="containsText" id="{e2d089e4-950f-47d4-9481-7617c63aabef}">
+          <x14:cfRule type="containsText" priority="620" operator="containsText" id="{3baaf08e-0413-408a-a586-19a7d72433fe}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20560,7 +20805,7 @@
           <xm:sqref>A182 H182 C182:F182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="553" operator="containsText" id="{244dd781-6c1e-42c8-846a-23172531fcff}">
+          <x14:cfRule type="containsText" priority="567" operator="containsText" id="{0a9ab6cc-4b55-462c-8bbd-55ab3ac93925}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20575,7 +20820,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="554" operator="containsText" id="{4801c8df-7de7-49ca-a165-feb13165f7ad}">
+          <x14:cfRule type="containsText" priority="568" operator="containsText" id="{6ce28cde-8270-47da-a05d-26bf15fa3c3e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20593,7 +20838,7 @@
           <xm:sqref>A184:A195 A197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="555" operator="containsText" id="{c4b51fa9-55c8-477c-bbe3-286765809603}">
+          <x14:cfRule type="containsText" priority="569" operator="containsText" id="{63ca3d8b-cef0-40b5-ae23-c7abd907f8b6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20608,7 +20853,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="556" operator="containsText" id="{497e01b5-ef6a-454a-889f-f8eca3dd2a0f}">
+          <x14:cfRule type="containsText" priority="570" operator="containsText" id="{3ad25684-c08f-4931-8d82-a6fef713618a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20626,7 +20871,7 @@
           <xm:sqref>E184:F184 J195 M195 J186:M186 J190:M194 J189 J196:M197 C185:F191 J188:M188 C193:F194 C192:D192 F192 C195:D195 F195 H188:H195 H187:M187 H184:H186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="557" operator="containsText" id="{ca4a6710-d9d3-4989-962f-cb557bddad97}">
+          <x14:cfRule type="containsText" priority="571" operator="containsText" id="{76b6757a-036c-4f70-8d24-e58600c34088}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20641,7 +20886,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="558" operator="containsText" id="{d784c5eb-d51a-4d08-9ff9-825bf70a060a}">
+          <x14:cfRule type="containsText" priority="572" operator="containsText" id="{17f381cc-3275-45fd-8406-395cd10ddd19}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20659,7 +20904,7 @@
           <xm:sqref>M184 M189 J184:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="551" operator="containsText" id="{f5fa37e5-c9f5-4829-8d2f-b8c0f5a1cc4d}">
+          <x14:cfRule type="containsText" priority="565" operator="containsText" id="{a0be50d5-aeab-4772-b653-a8e7d03884b1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20674,7 +20919,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="552" operator="containsText" id="{5bd29da7-91c0-4a69-9b46-e2ce56d14cb4}">
+          <x14:cfRule type="containsText" priority="566" operator="containsText" id="{64a97259-be9c-4202-ba98-1e424a70ed52}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20692,7 +20937,7 @@
           <xm:sqref>A196 H196 C196:F196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="499" operator="containsText" id="{adce29e9-ba6d-4c99-9b41-7e9fbb615d37}">
+          <x14:cfRule type="containsText" priority="513" operator="containsText" id="{9cc205fd-5b55-43ef-b517-a1cae37e78ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20707,7 +20952,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="500" operator="containsText" id="{3d9174ff-096f-417c-bd99-fed9cb4eb04e}">
+          <x14:cfRule type="containsText" priority="514" operator="containsText" id="{93f6d790-6429-4d53-88a9-92c66510e2d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20725,7 +20970,7 @@
           <xm:sqref>A198:A209 A211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="501" operator="containsText" id="{2a23c39e-cf8d-4340-9399-ef6e7bd8cef8}">
+          <x14:cfRule type="containsText" priority="515" operator="containsText" id="{47944ccf-fa2f-4360-b0f5-6f4d062bae64}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20740,7 +20985,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="502" operator="containsText" id="{0f9202c2-3c78-4aac-ab9a-40fb93fe9614}">
+          <x14:cfRule type="containsText" priority="516" operator="containsText" id="{fa22aa51-358c-4ff3-8625-ecd53d9c5899}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20758,7 +21003,7 @@
           <xm:sqref>E198:F198 J209 M209 J200:M200 J204:M208 J203 J210:M211 C199:F204 J202:M202 C207:F208 C209:D209 C205:D206 F206 H202:H209 H201:M201 H198:H200</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="503" operator="containsText" id="{5cf3e385-54b4-4420-92af-b2ecb6ee8e27}">
+          <x14:cfRule type="containsText" priority="517" operator="containsText" id="{468c850c-facd-4f3e-9439-42bb5851b53b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20773,7 +21018,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="504" operator="containsText" id="{659f9182-172b-4638-8ba2-c958dd3b2c9e}">
+          <x14:cfRule type="containsText" priority="518" operator="containsText" id="{059bf97f-0f61-4c2b-8a7d-1a75ded63855}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20791,7 +21036,7 @@
           <xm:sqref>M198 M203 J198:K198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="497" operator="containsText" id="{35822c59-6448-4c06-b31c-62047a51fbc2}">
+          <x14:cfRule type="containsText" priority="511" operator="containsText" id="{c0c8fca8-371a-4268-903d-4cf57423553c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20806,7 +21051,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="498" operator="containsText" id="{14649d61-c5b2-4b98-86cd-67d565dac995}">
+          <x14:cfRule type="containsText" priority="512" operator="containsText" id="{29d72ecc-7d71-4eef-866e-768f3d5931c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20824,7 +21069,7 @@
           <xm:sqref>A210 H210 C210:F210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="505" operator="containsText" id="{254c3ad1-c1a9-49a0-83b4-228dfd79c599}">
+          <x14:cfRule type="containsText" priority="519" operator="containsText" id="{c6323e3d-55f3-49d1-a028-1a724f67c916}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20839,7 +21084,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="506" operator="containsText" id="{bb0f28b1-369d-4985-8652-69df8c2edb66}">
+          <x14:cfRule type="containsText" priority="520" operator="containsText" id="{2f071b5c-b1d5-4eab-a9a5-1e455df8e9d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20857,7 +21102,7 @@
           <xm:sqref>C211:D211 F211 H211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="445" operator="containsText" id="{0aeacd2e-7add-49ae-ae60-be7c4d269213}">
+          <x14:cfRule type="containsText" priority="459" operator="containsText" id="{197b3715-ee05-4493-b08f-f7088791c994}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20872,7 +21117,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="446" operator="containsText" id="{cea4727c-9420-46b7-a2cc-c99ca50a0853}">
+          <x14:cfRule type="containsText" priority="460" operator="containsText" id="{06ea2f1a-31aa-459d-9bbf-9ca9ab88a8f5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20890,7 +21135,7 @@
           <xm:sqref>A212:A223 A225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="447" operator="containsText" id="{17f57269-e79d-4811-80a5-440868da8408}">
+          <x14:cfRule type="containsText" priority="461" operator="containsText" id="{91ed35ef-9a00-4306-9bc5-ecc612c1fc79}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20905,7 +21150,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="448" operator="containsText" id="{cd5b8939-c92d-4752-bc1c-8b3fcd259b47}">
+          <x14:cfRule type="containsText" priority="462" operator="containsText" id="{0d6b0f9f-ff2d-4c61-870b-fd9eb122a3ff}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20923,7 +21168,7 @@
           <xm:sqref>E212:F212 J223 M223 J214:M214 J218:M222 J217 J224:M225 C213:F218 J216:M216 C221:F222 C223:D223 C219:D220 F220 H216:H223 H215:M215 H212:H214</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="449" operator="containsText" id="{7683967d-4a49-497d-a9cb-3013104660f9}">
+          <x14:cfRule type="containsText" priority="463" operator="containsText" id="{63dac31d-1100-4b1c-be36-5c2d17422009}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20938,7 +21183,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="450" operator="containsText" id="{ec9c8415-8be6-4944-b847-4c2fbc843300}">
+          <x14:cfRule type="containsText" priority="464" operator="containsText" id="{48b17701-5c54-46f0-830a-dbf8b1d4514f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20956,7 +21201,7 @@
           <xm:sqref>M212 M217 J212:K212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="443" operator="containsText" id="{d261b376-4145-412c-8391-88885b00540e}">
+          <x14:cfRule type="containsText" priority="457" operator="containsText" id="{54a27786-4e32-44bb-a5ad-45d4f38690f2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20971,7 +21216,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="444" operator="containsText" id="{f9ac4695-84c0-4b28-b039-a0462affe856}">
+          <x14:cfRule type="containsText" priority="458" operator="containsText" id="{e40431d8-e499-4f10-85ba-f99549a75460}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20989,7 +21234,7 @@
           <xm:sqref>A224 H224 C224:F224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="451" operator="containsText" id="{e453d316-f8ce-43b3-9feb-958bba237c23}">
+          <x14:cfRule type="containsText" priority="465" operator="containsText" id="{3292457e-2172-4983-ad30-f8a0a33699a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21004,7 +21249,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="452" operator="containsText" id="{fd8c1123-d234-4a24-879a-b3dadc596209}">
+          <x14:cfRule type="containsText" priority="466" operator="containsText" id="{769452ef-cc4e-48f9-ba12-6c72d6597fb7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21022,7 +21267,7 @@
           <xm:sqref>C225:D225 F225 H225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="393" operator="containsText" id="{9b8c0219-af9e-4a45-89df-1bdf4dfd3d43}">
+          <x14:cfRule type="containsText" priority="407" operator="containsText" id="{6f515748-906f-4871-9668-531e64fd93f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21037,7 +21282,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="394" operator="containsText" id="{6a2f5b84-0cd9-4510-9bf8-2903abf35eaa}">
+          <x14:cfRule type="containsText" priority="408" operator="containsText" id="{a5c2004d-4687-4fd3-98dd-238d61b165f1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21055,7 +21300,7 @@
           <xm:sqref>A226:A237 A239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="395" operator="containsText" id="{dac0b8de-1bcb-49e9-a4bc-2b8485d067a8}">
+          <x14:cfRule type="containsText" priority="409" operator="containsText" id="{e71ab788-4b0c-40f2-a4da-16c70e83f261}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21070,7 +21315,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="396" operator="containsText" id="{1b133dcb-98b7-406f-8fba-010e56da39ff}">
+          <x14:cfRule type="containsText" priority="410" operator="containsText" id="{ff0013cc-2ec3-4fe1-b9b8-c8426ea24d39}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21088,7 +21333,7 @@
           <xm:sqref>E226:F226 J237 M237 J232:M236 J231 J238:M239 C227:F233 C235:F236 C234:D234 F234 C237:D237 J228:M230 H226:H237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="397" operator="containsText" id="{96f60692-5718-4138-a4fe-ad41cd035567}">
+          <x14:cfRule type="containsText" priority="411" operator="containsText" id="{e6f4b8aa-fb6e-40df-b1d6-57125f6e038e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21103,7 +21348,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="398" operator="containsText" id="{e761eda0-feb1-4cf7-8304-613463d036b7}">
+          <x14:cfRule type="containsText" priority="412" operator="containsText" id="{5661a37f-b1e4-4ba3-8831-52ae6e86f785}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21121,7 +21366,7 @@
           <xm:sqref>M226 M231 J226:K226</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="391" operator="containsText" id="{9b6b4d63-54f3-4c8d-ab6d-c78411efe47a}">
+          <x14:cfRule type="containsText" priority="405" operator="containsText" id="{c3a9cc21-669a-4ded-9a21-f3bc091809c5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21136,7 +21381,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="392" operator="containsText" id="{02a26944-80c1-4bf4-97fc-ab873adfca0b}">
+          <x14:cfRule type="containsText" priority="406" operator="containsText" id="{b8ac57df-6e14-4002-9f62-412bccb19878}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21154,7 +21399,7 @@
           <xm:sqref>A238 H238 C238:F238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="399" operator="containsText" id="{55bea7e0-f1c5-46aa-a807-b7f8fe26b9ad}">
+          <x14:cfRule type="containsText" priority="413" operator="containsText" id="{73e30e84-7f14-4052-8d58-fe7cd2da0f5d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21169,7 +21414,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="400" operator="containsText" id="{8fcc4084-17cc-4d6e-8dd3-7db8102a0719}">
+          <x14:cfRule type="containsText" priority="414" operator="containsText" id="{942e003e-ce20-4259-bbf6-8c2288cfb220}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21187,7 +21432,7 @@
           <xm:sqref>C239:D239 F239 H239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="335" operator="containsText" id="{0819dbfc-ea75-43a4-98c3-9d1bf662dd53}">
+          <x14:cfRule type="containsText" priority="349" operator="containsText" id="{fd827a80-92d3-482c-8edc-3d8c2c8c4df8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21202,7 +21447,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="336" operator="containsText" id="{2f40bbaa-25ed-4731-97e1-d84e1eb80bec}">
+          <x14:cfRule type="containsText" priority="350" operator="containsText" id="{fbf4fb37-79e5-41af-abc1-70a0e13511fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21220,7 +21465,7 @@
           <xm:sqref>A240:A251 A253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="337" operator="containsText" id="{3650c7a5-1c98-468b-89ba-64ab27d5b49e}">
+          <x14:cfRule type="containsText" priority="351" operator="containsText" id="{0f445659-ef45-4090-89d0-cb5ff099b1ad}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21235,7 +21480,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="338" operator="containsText" id="{1d9d5b9c-2f89-4ab7-b6a2-f4e1e1f2fc43}">
+          <x14:cfRule type="containsText" priority="352" operator="containsText" id="{af913d95-cad5-43c3-b4b1-d182152318a1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21253,7 +21498,7 @@
           <xm:sqref>E240:F240 J251 M251 J246:M250 J245 J252:M253 C241:F246 C249:F250 C251:D251 J242:M244 C247:D248 F248 H240:H251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="339" operator="containsText" id="{132c5397-2731-4e95-9d78-6aed4990ddd7}">
+          <x14:cfRule type="containsText" priority="353" operator="containsText" id="{6e3af114-9e69-4451-b1ae-2e078c943a8b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21268,7 +21513,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="340" operator="containsText" id="{6732350c-cd3b-4ced-9b01-22fda12a4c65}">
+          <x14:cfRule type="containsText" priority="354" operator="containsText" id="{d2c39528-9bbe-4244-aff7-371d86a52fb9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21286,7 +21531,7 @@
           <xm:sqref>M240 M245 J240:K240 K245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="333" operator="containsText" id="{cd233a82-edd7-4f10-8591-a823ea672c43}">
+          <x14:cfRule type="containsText" priority="347" operator="containsText" id="{05d51bda-4f27-4ccc-805d-9651107df709}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21301,7 +21546,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="334" operator="containsText" id="{c64f8d66-d840-4250-a5e1-199335e11ce2}">
+          <x14:cfRule type="containsText" priority="348" operator="containsText" id="{2b7c31fe-d740-4857-9f25-5bf4db0a59f4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21319,7 +21564,7 @@
           <xm:sqref>A252 H252 C252:F252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="341" operator="containsText" id="{c6b310d2-288e-41e3-aa97-aaed299daf57}">
+          <x14:cfRule type="containsText" priority="355" operator="containsText" id="{ad00446b-30f5-427c-98ec-9d5e887e0dcc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21334,7 +21579,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="342" operator="containsText" id="{4c661cd2-5d48-4e4d-82f3-abad56ee9de3}">
+          <x14:cfRule type="containsText" priority="356" operator="containsText" id="{231a77b2-7ffd-4ecc-9a9d-14452fbb8162}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21352,7 +21597,7 @@
           <xm:sqref>C253:D253 F253 H253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="277" operator="containsText" id="{b64e7877-5006-4dd5-b2e0-79254a438f7c}">
+          <x14:cfRule type="containsText" priority="291" operator="containsText" id="{d9a69a14-d375-4dad-9cf2-d7fc1cd5fceb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21367,7 +21612,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="278" operator="containsText" id="{177b3ad7-4c57-495d-ae67-9a20015bbe80}">
+          <x14:cfRule type="containsText" priority="292" operator="containsText" id="{95ce4092-9915-423a-8b8a-9542031c0f67}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21385,7 +21630,7 @@
           <xm:sqref>A254:A265 A267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="279" operator="containsText" id="{db697c16-b71c-4739-95be-368d0f0fc6a1}">
+          <x14:cfRule type="containsText" priority="293" operator="containsText" id="{6f38eb4e-d4d9-4017-86f6-a9e3e1bb2346}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21400,7 +21645,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="280" operator="containsText" id="{e5c144e9-fdb6-4a6f-9d0d-b487b7bbf46a}">
+          <x14:cfRule type="containsText" priority="294" operator="containsText" id="{2795dcfe-7f48-48cd-8189-718ec56b6bb5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21418,7 +21663,7 @@
           <xm:sqref>E254:F254 J260:M263 J259 J266:M266 C255:F261 C264:F264 C265:D265 J256:M258 J264:J265 M264:M265 C262:D263 F262 H254:H265 K267:M267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="281" operator="containsText" id="{8bbb52f1-23ae-484f-bb68-74d74d8b12f1}">
+          <x14:cfRule type="containsText" priority="295" operator="containsText" id="{3be90c4e-02bb-4899-8d20-4b20f403250e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21433,7 +21678,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="282" operator="containsText" id="{db139a67-d761-44a2-b8cd-21e07dad8b8c}">
+          <x14:cfRule type="containsText" priority="296" operator="containsText" id="{a4a33018-0cca-4884-896b-7b3608e0cb86}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21451,7 +21696,7 @@
           <xm:sqref>M254 M259 J254:K254 K259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="275" operator="containsText" id="{0f301a51-9377-489a-ab1c-47fa41ddbb89}">
+          <x14:cfRule type="containsText" priority="289" operator="containsText" id="{01311b3d-c26b-4aef-9c0c-3dcee3be5948}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21466,7 +21711,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="276" operator="containsText" id="{1fd7f057-05f3-47b8-8cf9-6772be1ade3a}">
+          <x14:cfRule type="containsText" priority="290" operator="containsText" id="{9dbb7799-6406-4f6e-bb34-5e99a9d241a8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21484,7 +21729,7 @@
           <xm:sqref>A266 H266 C266:F266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="283" operator="containsText" id="{5310992f-f9a7-4a42-aeea-207c6a53ea39}">
+          <x14:cfRule type="containsText" priority="297" operator="containsText" id="{134bdd23-9064-4c58-983c-2e2bf5606c6e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21499,7 +21744,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="284" operator="containsText" id="{eaa0790c-8708-4482-8973-f9f9b9b48657}">
+          <x14:cfRule type="containsText" priority="298" operator="containsText" id="{9be47e75-1aa8-4a9d-b12b-dd3ea6896960}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21517,7 +21762,7 @@
           <xm:sqref>C267:D267 F267 H267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="48" operator="containsText" id="{4efbf9bf-1b2c-45eb-afc5-97325e4f5dc5}">
+          <x14:cfRule type="containsText" priority="62" operator="containsText" id="{28d4a018-9b18-44d0-ab45-0cde66a3cb6e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A268)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21532,7 +21777,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{216df3fd-dea9-4340-9e1d-59cf1e42ff8f}">
+          <x14:cfRule type="containsText" priority="61" operator="containsText" id="{52b7289a-c569-47b9-98b0-94ce0b893c3c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A268)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21550,7 +21795,7 @@
           <xm:sqref>A268:A279 A281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{968ebedc-a534-4f7c-b7d0-d149c9aed036}">
+          <x14:cfRule type="containsText" priority="55" operator="containsText" id="{0e451d72-c321-4fcd-b81a-84dbfc44731a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E268)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21565,7 +21810,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="42" operator="containsText" id="{3abe16c4-6658-44f0-84af-2056b250728b}">
+          <x14:cfRule type="containsText" priority="56" operator="containsText" id="{60958a11-bfbd-46b1-829d-0c97d7565160}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E268)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -4661,8 +4661,10 @@
       <c r="I59" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="J59" s="57" t="s">
-        <v>145</v>
+      <c r="J59" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4716, 4725</t>
+        </is>
       </c>
       <c r="K59" s="18" t="s">
         <v>21</v>
@@ -9771,8 +9773,16 @@
       <c r="G268" s="75"/>
       <c r="H268" s="74"/>
       <c r="I268" s="74"/>
-      <c r="J268" s="72"/>
-      <c r="K268" s="74"/>
+      <c r="J268" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3861, 3876, 3965, 3994, 3996, 4036, 4095, 4252</t>
+        </is>
+      </c>
+      <c r="K268" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
+      </c>
       <c r="L268" s="74"/>
       <c r="M268" s="74"/>
       <c r="N268" s="76"/>
@@ -9795,11 +9805,15 @@
       <c r="G269" s="75"/>
       <c r="H269" s="74"/>
       <c r="I269" s="74"/>
-      <c r="J269" s="63" t="s">
-        <v>503</v>
-      </c>
-      <c r="K269" s="18" t="s">
-        <v>302</v>
+      <c r="J269" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18, 341, 4324, 4340, 4368, 4517, 4565, 4638, 4710</t>
+        </is>
+      </c>
+      <c r="K269" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
       </c>
       <c r="L269" s="74"/>
       <c r="M269" s="74"/>
@@ -9825,8 +9839,16 @@
       </c>
       <c r="H270" s="74"/>
       <c r="I270" s="74"/>
-      <c r="J270" s="72"/>
-      <c r="K270" s="74"/>
+      <c r="J270" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7, 10, 3437, 3447, 3448, 3449, 3450, 3451, 3452, 3453, 3468, 3472, 3474, 3475, 3477, 3483, 3486, 3488, 3505, 3512, 3517, 3526, 3531, 3539, 3541, 3543, 3547, 3549, 3553, 3560, 3565, 3566, 3567, 3579, 3583, 3584, 3590, 3594, 3595, 3597, 3599, 3604, 3605, 3607, 3608, 3612, 3621, 3629, 3638, 3639, 3643, 3647, 3662, 3666</t>
+        </is>
+      </c>
+      <c r="K270" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
+      </c>
       <c r="L270" s="74"/>
       <c r="M270" s="74"/>
       <c r="N270" s="76"/>
@@ -9847,11 +9869,15 @@
       <c r="G271" s="75"/>
       <c r="H271" s="74"/>
       <c r="I271" s="74"/>
-      <c r="J271" s="63" t="s">
-        <v>505</v>
-      </c>
-      <c r="K271" s="18" t="s">
-        <v>302</v>
+      <c r="J271" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3656, 3692, 3724, 3764, 3772, 3809, 3850</t>
+        </is>
+      </c>
+      <c r="K271" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
       </c>
       <c r="L271" s="74"/>
       <c r="M271" s="74"/>
@@ -9875,11 +9901,15 @@
       </c>
       <c r="H272" s="74"/>
       <c r="I272" s="74"/>
-      <c r="J272" s="63" t="s">
-        <v>506</v>
-      </c>
-      <c r="K272" s="18" t="s">
-        <v>302</v>
+      <c r="J272" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1746, 1790, 1799, 1810, 1816, 1820, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1906, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2032, 2045, 2054, 2059, 2133, 2166, 2193, 2202, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2359, 2364, 2372, 2382, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2649, 2671, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
+        </is>
+      </c>
+      <c r="K272" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
       </c>
       <c r="L272" s="74"/>
       <c r="M272" s="74"/>
@@ -9905,11 +9935,15 @@
       </c>
       <c r="H273" s="74"/>
       <c r="I273" s="74"/>
-      <c r="J273" s="63" t="s">
-        <v>507</v>
-      </c>
-      <c r="K273" s="18" t="s">
-        <v>302</v>
+      <c r="J273" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3, 4, 15, 304, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3912, 3914, 3915, 3916, 3917, 3918, 3920, 3922, 3923, 3924, 3925, 3926, 3928, 3929, 3931, 3932, 3933, 3934, 3936, 3937, 3938, 3939, 3940, 3943, 3944, 3945, 3946, 3947, 3948, 3951, 3952, 3953, 3954, 3958, 3961, 3962, 3963, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4013, 4029, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4201, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4230, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
+        </is>
+      </c>
+      <c r="K273" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
       </c>
       <c r="L273" s="74"/>
       <c r="M273" s="74"/>
@@ -9935,11 +9969,15 @@
       </c>
       <c r="H274" s="74"/>
       <c r="I274" s="74"/>
-      <c r="J274" s="63" t="s">
-        <v>508</v>
-      </c>
-      <c r="K274" s="18" t="s">
-        <v>302</v>
+      <c r="J274" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000, 10002, 10005, 10006, 10007, 10008, 10009, 10010, 10013, 10014, 10015, 10016, 10019, 10021, 10022, 10024, 10026, 10028, 10031, 10032</t>
+        </is>
+      </c>
+      <c r="K274" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
       </c>
       <c r="L274" s="74"/>
       <c r="M274" s="74"/>
@@ -9961,8 +9999,16 @@
       </c>
       <c r="H275" s="74"/>
       <c r="I275" s="74"/>
-      <c r="J275" s="77"/>
-      <c r="K275" s="74"/>
+      <c r="J275" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333, 335, 4238, 4240, 4255, 4269, 4272, 4274, 4276, 4283, 4289, 4290, 4295, 4298, 4302, 4303, 4311, 4312, 4316, 4327, 4330, 4336, 4341, 4345, 4350, 4352, 4353, 4370, 4375, 4387, 4393, 4394, 4395, 4400, 4406, 4421, 4422, 4433, 4435, 4436, 4437, 4440, 4443, 4444, 4449, 4454, 4456, 4458, 4459, 4460, 4461, 4464, 4466, 4467, 4471, 4474, 4478, 4481, 4484, 4487, 4491, 4492, 4498, 4508, 4510, 4522, 4524, 4531, 4533, 4536, 4540, 4544, 4545, 4548, 4549, 4552</t>
+        </is>
+      </c>
+      <c r="K275" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
+      </c>
       <c r="L275" s="74"/>
       <c r="M275" s="74"/>
       <c r="N275" s="76"/>
@@ -9983,8 +10029,16 @@
       <c r="G276" s="75"/>
       <c r="H276" s="74"/>
       <c r="I276" s="74"/>
-      <c r="J276" s="77"/>
-      <c r="K276" s="74"/>
+      <c r="J276" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1245, 1262, 1268, 1289, 1290, 1296, 1297, 1304, 1307, 1314, 1325, 1332, 1342, 1377, 1392, 1393, 1397, 1404, 1405, 1407, 1408, 1413, 1416, 1423, 1424, 1427, 1436, 1440, 1456, 1466, 1472, 1496, 1499, 1526, 1532, 1537, 1553, 1632</t>
+        </is>
+      </c>
+      <c r="K276" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
+      </c>
       <c r="L276" s="74"/>
       <c r="M276" s="74"/>
       <c r="N276" s="76"/>
@@ -10005,8 +10059,16 @@
       <c r="G277" s="75"/>
       <c r="H277" s="74"/>
       <c r="I277" s="74"/>
-      <c r="J277" s="77"/>
-      <c r="K277" s="74"/>
+      <c r="J277" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2186, 2194, 2198, 2212, 2219, 2225, 2241, 2244, 2417, 2450, 2462, 2536, 2758, 2797, 2803, 2813, 2934, 3416, 3428</t>
+        </is>
+      </c>
+      <c r="K277" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
+      </c>
       <c r="L277" s="74"/>
       <c r="M277" s="74"/>
       <c r="N277" s="76"/>
@@ -10025,11 +10087,15 @@
       <c r="G278" s="75"/>
       <c r="H278" s="74"/>
       <c r="I278" s="74"/>
-      <c r="J278" s="63" t="s">
-        <v>509</v>
-      </c>
-      <c r="K278" s="18" t="s">
-        <v>302</v>
+      <c r="J278" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271, 1273, 1276, 1279, 1280, 1339, 1362, 1363, 1371, 1420, 1449, 1479, 1560, 1598, 1603, 1606, 1611, 1625</t>
+        </is>
+      </c>
+      <c r="K278" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
       </c>
       <c r="L278" s="74"/>
       <c r="M278" s="74"/>
@@ -10055,8 +10121,16 @@
       </c>
       <c r="H279" s="74"/>
       <c r="I279" s="74"/>
-      <c r="J279" s="77"/>
-      <c r="K279" s="74"/>
+      <c r="J279" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288, 2173, 2181, 2206, 2215, 2276, 2281, 2288, 2305, 2317, 2332, 2354, 2355, 2361, 2367, 2368, 2385, 2389, 2395, 2408, 2428, 2440, 2445, 2446, 2452, 2468, 2469, 2475, 2479, 2484, 2495, 2577, 2578, 2590, 2597, 2605, 2615, 2617, 2628, 2636, 2640, 2647, 2651, 2653, 2654, 2657, 2661, 2665, 2676, 2677, 2692, 2701, 2714, 2733, 2745, 2751, 2753, 2755, 2759, 2764, 2766, 2771, 2772, 2780, 2784, 2791, 2798, 2806, 2811, 2819, 2835, 2838, 2846, 2850, 2852, 2857, 2861, 2866, 2870, 2872, 2876, 2880, 2883, 2887, 2889, 2890, 2894, 2898, 2916, 2941, 2951, 2966, 2972, 2993, 3015, 3031, 3035, 3044, 3064, 3081, 3097, 3104, 3108, 3112</t>
+        </is>
+      </c>
+      <c r="K279" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
+      </c>
       <c r="L279" s="74"/>
       <c r="M279" s="74"/>
       <c r="N279" s="76"/>
@@ -10075,11 +10149,15 @@
       <c r="G280" s="75"/>
       <c r="H280" s="74"/>
       <c r="I280" s="74"/>
-      <c r="J280" s="63" t="s">
-        <v>511</v>
-      </c>
-      <c r="K280" s="18" t="s">
-        <v>302</v>
+      <c r="J280" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1394, 1845, 2042, 2047, 2052, 2060, 2063, 2087, 2112, 2113, 2144</t>
+        </is>
+      </c>
+      <c r="K280" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
       </c>
       <c r="L280" s="74"/>
       <c r="M280" s="74"/>
@@ -10105,8 +10183,16 @@
       </c>
       <c r="H281" s="74"/>
       <c r="I281" s="74"/>
-      <c r="J281" s="78"/>
-      <c r="K281" s="74"/>
+      <c r="J281" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80, 105, 522, 569, 571, 575, 577, 578, 579, 580, 581, 583, 584, 586, 590, 593, 595, 596, 600, 601, 602, 603, 604, 605, 606, 610, 614, 615, 616, 617, 618, 623, 625, 628, 632, 633, 634, 636, 639, 640, 642, 643, 644, 645, 646, 647, 648, 649, 650, 653, 654, 656, 660, 661, 664, 666, 670, 671, 673, 675, 677, 680, 682, 683, 686, 687, 690, 696, 705, 707, 711, 721, 729, 730, 731, 732, 745, 755, 758, 760, 761, 770, 772, 777, 779, 782, 784, 791, 803, 807, 813, 816, 821, 824, 837, 839, 861, 863, 864, 867, 868, 879, 882, 903, 943, 944, 949</t>
+        </is>
+      </c>
+      <c r="K281" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMPIO </t>
+        </is>
+      </c>
       <c r="L281" s="74"/>
       <c r="M281" s="74"/>
       <c r="N281" s="76"/>

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -2566,10 +2566,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9839,7 +9839,9 @@
       <c r="D268" s="74"/>
       <c r="E268" s="57"/>
       <c r="F268" s="74"/>
-      <c r="G268" s="75"/>
+      <c r="G268" s="57">
+        <v>30</v>
+      </c>
       <c r="H268" s="74"/>
       <c r="I268" s="74"/>
       <c r="J268" s="63" t="s">
@@ -9850,7 +9852,7 @@
       </c>
       <c r="L268" s="74"/>
       <c r="M268" s="74"/>
-      <c r="N268" s="76"/>
+      <c r="N268" s="75"/>
     </row>
     <row r="269" ht="141" customHeight="1" spans="1:14">
       <c r="A269" s="23" t="s">
@@ -9867,7 +9869,9 @@
       <c r="F269" s="57" t="s">
         <v>503</v>
       </c>
-      <c r="G269" s="75"/>
+      <c r="G269" s="57">
+        <v>13</v>
+      </c>
       <c r="H269" s="74"/>
       <c r="I269" s="74"/>
       <c r="J269" s="63" t="s">
@@ -9878,7 +9882,7 @@
       </c>
       <c r="L269" s="74"/>
       <c r="M269" s="74"/>
-      <c r="N269" s="76"/>
+      <c r="N269" s="75"/>
     </row>
     <row r="270" ht="141" customHeight="1" spans="1:14">
       <c r="A270" s="23" t="s">
@@ -9908,7 +9912,7 @@
       </c>
       <c r="L270" s="74"/>
       <c r="M270" s="74"/>
-      <c r="N270" s="76"/>
+      <c r="N270" s="75"/>
     </row>
     <row r="271" ht="141" customHeight="1" spans="1:14">
       <c r="A271" s="23" t="s">
@@ -9923,7 +9927,7 @@
         <v>486</v>
       </c>
       <c r="F271" s="74"/>
-      <c r="G271" s="75"/>
+      <c r="G271" s="76"/>
       <c r="H271" s="74"/>
       <c r="I271" s="74"/>
       <c r="J271" s="63" t="s">
@@ -9934,7 +9938,7 @@
       </c>
       <c r="L271" s="74"/>
       <c r="M271" s="74"/>
-      <c r="N271" s="76"/>
+      <c r="N271" s="75"/>
     </row>
     <row r="272" ht="141" customHeight="1" spans="1:14">
       <c r="A272" s="23" t="s">
@@ -9962,7 +9966,7 @@
       </c>
       <c r="L272" s="74"/>
       <c r="M272" s="74"/>
-      <c r="N272" s="76"/>
+      <c r="N272" s="75"/>
     </row>
     <row r="273" ht="141" customHeight="1" spans="1:14">
       <c r="A273" s="23" t="s">
@@ -9992,7 +9996,7 @@
       </c>
       <c r="L273" s="74"/>
       <c r="M273" s="74"/>
-      <c r="N273" s="76"/>
+      <c r="N273" s="75"/>
     </row>
     <row r="274" ht="141" customHeight="1" spans="1:14">
       <c r="A274" s="50" t="s">
@@ -10022,7 +10026,7 @@
       </c>
       <c r="L274" s="74"/>
       <c r="M274" s="74"/>
-      <c r="N274" s="76"/>
+      <c r="N274" s="75"/>
     </row>
     <row r="275" ht="141" customHeight="1" spans="1:14">
       <c r="A275" s="23" t="s">
@@ -10048,7 +10052,7 @@
       </c>
       <c r="L275" s="74"/>
       <c r="M275" s="74"/>
-      <c r="N275" s="76"/>
+      <c r="N275" s="75"/>
     </row>
     <row r="276" ht="141" customHeight="1" spans="1:14">
       <c r="A276" s="23" t="s">
@@ -10063,7 +10067,7 @@
         <v>490</v>
       </c>
       <c r="F276" s="74"/>
-      <c r="G276" s="75"/>
+      <c r="G276" s="76"/>
       <c r="H276" s="74"/>
       <c r="I276" s="74"/>
       <c r="J276" s="63" t="s">
@@ -10074,7 +10078,7 @@
       </c>
       <c r="L276" s="74"/>
       <c r="M276" s="74"/>
-      <c r="N276" s="76"/>
+      <c r="N276" s="75"/>
     </row>
     <row r="277" ht="141" customHeight="1" spans="1:14">
       <c r="A277" s="23" t="s">
@@ -10089,7 +10093,7 @@
         <v>492</v>
       </c>
       <c r="F277" s="74"/>
-      <c r="G277" s="75"/>
+      <c r="G277" s="76"/>
       <c r="H277" s="74"/>
       <c r="I277" s="74"/>
       <c r="J277" s="63" t="s">
@@ -10100,7 +10104,7 @@
       </c>
       <c r="L277" s="74"/>
       <c r="M277" s="74"/>
-      <c r="N277" s="76"/>
+      <c r="N277" s="75"/>
     </row>
     <row r="278" ht="141" customHeight="1" spans="1:14">
       <c r="A278" s="23" t="s">
@@ -10113,7 +10117,7 @@
       <c r="D278" s="74"/>
       <c r="E278" s="57"/>
       <c r="F278" s="74"/>
-      <c r="G278" s="75"/>
+      <c r="G278" s="76"/>
       <c r="H278" s="74"/>
       <c r="I278" s="74"/>
       <c r="J278" s="63" t="s">
@@ -10124,7 +10128,7 @@
       </c>
       <c r="L278" s="74"/>
       <c r="M278" s="74"/>
-      <c r="N278" s="76"/>
+      <c r="N278" s="75"/>
     </row>
     <row r="279" ht="141" customHeight="1" spans="1:14">
       <c r="A279" s="23" t="s">
@@ -10154,7 +10158,7 @@
       </c>
       <c r="L279" s="74"/>
       <c r="M279" s="74"/>
-      <c r="N279" s="76"/>
+      <c r="N279" s="75"/>
     </row>
     <row r="280" ht="141" customHeight="1" spans="1:14">
       <c r="A280" s="23" t="s">
@@ -10167,7 +10171,7 @@
       <c r="D280" s="74"/>
       <c r="E280" s="18"/>
       <c r="F280" s="74"/>
-      <c r="G280" s="75"/>
+      <c r="G280" s="76"/>
       <c r="H280" s="74"/>
       <c r="I280" s="74"/>
       <c r="J280" s="63" t="s">
@@ -10178,7 +10182,7 @@
       </c>
       <c r="L280" s="74"/>
       <c r="M280" s="74"/>
-      <c r="N280" s="76"/>
+      <c r="N280" s="75"/>
     </row>
     <row r="281" ht="141" customHeight="1" spans="1:14">
       <c r="A281" s="23" t="s">
@@ -10208,39 +10212,39 @@
       </c>
       <c r="L281" s="74"/>
       <c r="M281" s="74"/>
-      <c r="N281" s="76"/>
+      <c r="N281" s="75"/>
     </row>
     <row r="282" customHeight="1" spans="1:14">
-      <c r="A282" s="76"/>
-      <c r="B282" s="76"/>
-      <c r="C282" s="76"/>
-      <c r="D282" s="76"/>
-      <c r="E282" s="76"/>
-      <c r="F282" s="76"/>
+      <c r="A282" s="75"/>
+      <c r="B282" s="75"/>
+      <c r="C282" s="75"/>
+      <c r="D282" s="75"/>
+      <c r="E282" s="75"/>
+      <c r="F282" s="75"/>
       <c r="G282" s="77"/>
-      <c r="H282" s="76"/>
-      <c r="I282" s="76"/>
-      <c r="J282" s="76"/>
-      <c r="K282" s="76"/>
-      <c r="L282" s="76"/>
-      <c r="M282" s="76"/>
-      <c r="N282" s="76"/>
+      <c r="H282" s="75"/>
+      <c r="I282" s="75"/>
+      <c r="J282" s="75"/>
+      <c r="K282" s="75"/>
+      <c r="L282" s="75"/>
+      <c r="M282" s="75"/>
+      <c r="N282" s="75"/>
     </row>
     <row r="283" customHeight="1" spans="1:14">
-      <c r="A283" s="76"/>
-      <c r="B283" s="76"/>
-      <c r="C283" s="76"/>
-      <c r="D283" s="76"/>
-      <c r="E283" s="76"/>
-      <c r="F283" s="76"/>
+      <c r="A283" s="75"/>
+      <c r="B283" s="75"/>
+      <c r="C283" s="75"/>
+      <c r="D283" s="75"/>
+      <c r="E283" s="75"/>
+      <c r="F283" s="75"/>
       <c r="G283" s="77"/>
-      <c r="H283" s="76"/>
-      <c r="I283" s="76"/>
-      <c r="J283" s="76"/>
-      <c r="K283" s="76"/>
-      <c r="L283" s="76"/>
-      <c r="M283" s="76"/>
-      <c r="N283" s="76"/>
+      <c r="H283" s="75"/>
+      <c r="I283" s="75"/>
+      <c r="J283" s="75"/>
+      <c r="K283" s="75"/>
+      <c r="L283" s="75"/>
+      <c r="M283" s="75"/>
+      <c r="N283" s="75"/>
     </row>
     <row r="284" spans="1:14">
       <c r="G284" s="78"/>
@@ -10344,7 +10348,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="161" operator="containsText" id="{2e1be706-c91c-48a8-aaac-52878f60881e}">
+          <x14:cfRule type="containsText" priority="165" operator="containsText" id="{7e43147d-4fe2-453f-9f78-53ab33426ffb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G28)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10359,7 +10363,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="162" operator="containsText" id="{22ecb9a6-8654-4cc0-8610-0230a46286f5}">
+          <x14:cfRule type="containsText" priority="166" operator="containsText" id="{995923e3-9648-4c91-a190-aa9a9b04d2cb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G28)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10377,7 +10381,7 @@
           <xm:sqref>G28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="159" operator="containsText" id="{7bf6bcd2-4a1b-4a64-8ae9-6214ec18d63b}">
+          <x14:cfRule type="containsText" priority="163" operator="containsText" id="{1f455e5d-6282-400a-b0a2-dc779e3c1d20}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G42)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10392,7 +10396,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="160" operator="containsText" id="{c4d0feb0-ac4b-4b7f-992c-50eddf6d4ff0}">
+          <x14:cfRule type="containsText" priority="164" operator="containsText" id="{bed370d5-e130-49c2-84ad-59d797eb4b9c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G42)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10410,7 +10414,7 @@
           <xm:sqref>G42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="157" operator="containsText" id="{17789c19-37fc-400a-bfac-4a821bdd90b4}">
+          <x14:cfRule type="containsText" priority="161" operator="containsText" id="{649d1852-a581-412c-af32-5963293949d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G56)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10425,7 +10429,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="158" operator="containsText" id="{4c50c6df-b7a1-4a65-ac00-a8d125ee08da}">
+          <x14:cfRule type="containsText" priority="162" operator="containsText" id="{16230fe5-cb09-4f3b-b548-2245b630af2b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G56)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10443,7 +10447,7 @@
           <xm:sqref>G56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="155" operator="containsText" id="{89628399-7852-4c06-b467-0c591519ef81}">
+          <x14:cfRule type="containsText" priority="159" operator="containsText" id="{58c1c179-fef8-4e46-b2c1-b23b756995f1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G70)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10458,7 +10462,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="156" operator="containsText" id="{d8c95329-7cbb-4f10-92c3-ef485a565d41}">
+          <x14:cfRule type="containsText" priority="160" operator="containsText" id="{0712cccb-8e61-4e40-9b78-6e14dceb2b3d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G70)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10476,7 +10480,7 @@
           <xm:sqref>G70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="831" operator="containsText" id="{44655b47-0049-4ea9-b6ed-7a4f38710f89}">
+          <x14:cfRule type="containsText" priority="835" operator="containsText" id="{01c48221-10f6-4245-919e-a061d5af5a68}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K73)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10491,7 +10495,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="832" operator="containsText" id="{cb951d55-82e2-497f-b8fb-b7606438806e}">
+          <x14:cfRule type="containsText" priority="836" operator="containsText" id="{64b61c07-6296-42b9-84fa-660d0b217dc5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K73)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10509,7 +10513,7 @@
           <xm:sqref>K73</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="829" operator="containsText" id="{b26a2dd0-e240-4855-a63a-8dee7f70040f}">
+          <x14:cfRule type="containsText" priority="833" operator="containsText" id="{d515be14-c903-4a2a-a49d-cf96eac66961}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K83)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10524,7 +10528,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="830" operator="containsText" id="{174ba6e4-e176-48fc-9cb5-5bcec71aff91}">
+          <x14:cfRule type="containsText" priority="834" operator="containsText" id="{1ddfdf96-7f8b-44bd-b741-8e79bf721dc5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K83)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10542,7 +10546,7 @@
           <xm:sqref>K83</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="827" operator="containsText" id="{9bcf5d49-edf9-4bbf-9174-a976b68192d1}">
+          <x14:cfRule type="containsText" priority="831" operator="containsText" id="{1680db68-4163-4085-9e7d-a96f9f6f4e07}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K84)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10557,7 +10561,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="828" operator="containsText" id="{03ed4751-fd31-479c-aed6-b9f4fab44909}">
+          <x14:cfRule type="containsText" priority="832" operator="containsText" id="{464a12ad-7731-433e-a0b7-18807400b0a9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K84)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10575,7 +10579,7 @@
           <xm:sqref>K84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="855" operator="containsText" id="{ec40b6e8-1640-4fba-98ea-8445437953e8}">
+          <x14:cfRule type="containsText" priority="859" operator="containsText" id="{f3250457-73a5-4429-8a54-12d1e5ca392e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L87)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10590,7 +10594,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="856" operator="containsText" id="{f73a0559-2842-4f89-bcc9-3c34666eb828}">
+          <x14:cfRule type="containsText" priority="860" operator="containsText" id="{bd25bbba-4037-47b9-bcc8-4968b083db2d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L87)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10608,7 +10612,7 @@
           <xm:sqref>L87</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="853" operator="containsText" id="{71b43105-fc22-43e7-a9b1-e7634c28b6de}">
+          <x14:cfRule type="containsText" priority="857" operator="containsText" id="{1d5a4d62-64fd-4ce7-a4b2-057c5d81a869}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I92)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10623,7 +10627,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="854" operator="containsText" id="{0ed2747b-ee16-4956-a580-0600d3bc1da0}">
+          <x14:cfRule type="containsText" priority="858" operator="containsText" id="{6f5f8ad8-1322-4f6d-8541-1ad3142d2a88}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I92)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10641,7 +10645,7 @@
           <xm:sqref>I92</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="859" operator="containsText" id="{8b20f22c-4d37-4b1d-93ac-0a629296f378}">
+          <x14:cfRule type="containsText" priority="863" operator="containsText" id="{1556e9bc-bc12-49cd-8d95-a563bd14238a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I93)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10656,7 +10660,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="860" operator="containsText" id="{2f4fe931-d640-4a0d-84b8-b7e3437145b7}">
+          <x14:cfRule type="containsText" priority="864" operator="containsText" id="{d4b8003d-926b-476d-928d-5365d0e24db8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I93)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10674,7 +10678,7 @@
           <xm:sqref>I93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="857" operator="containsText" id="{0fcd1f83-5d3e-4b41-9e79-0fc860615e94}">
+          <x14:cfRule type="containsText" priority="861" operator="containsText" id="{3bcfae40-f3c9-42a9-b3fd-e3f578bbc2e2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I96)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10689,7 +10693,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="858" operator="containsText" id="{8a43e78a-8b21-48d6-a7b7-9eb2dc779ef2}">
+          <x14:cfRule type="containsText" priority="862" operator="containsText" id="{430a2ed9-44a1-43a4-a4c6-b2f130a2779d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I96)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10707,7 +10711,7 @@
           <xm:sqref>I96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="825" operator="containsText" id="{cb64b39e-51fb-4174-aed9-3108cdd09567}">
+          <x14:cfRule type="containsText" priority="829" operator="containsText" id="{7f550a7f-fc4c-4504-a16c-1666def0eaa9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K96)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10722,7 +10726,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="826" operator="containsText" id="{df4ffc7e-f196-45f9-9f77-037bb2e47c04}">
+          <x14:cfRule type="containsText" priority="830" operator="containsText" id="{a37a34e9-a3be-4da3-94d0-a6d9516e2717}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K96)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10740,7 +10744,7 @@
           <xm:sqref>K96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="863" operator="containsText" id="{682aad01-c428-4aee-94f4-0aa6f8644cb8}">
+          <x14:cfRule type="containsText" priority="867" operator="containsText" id="{63cbd2a1-cd86-44e8-9ba3-169b8d58d54f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10755,7 +10759,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="864" operator="containsText" id="{99197c29-65f1-4f01-8b82-0363efaa241c}">
+          <x14:cfRule type="containsText" priority="868" operator="containsText" id="{6f05766b-7125-4375-bf6f-44b8cfdc9ffe}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10773,7 +10777,7 @@
           <xm:sqref>I97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="823" operator="containsText" id="{1da7854f-c14c-4e66-ba76-f8c727db20e1}">
+          <x14:cfRule type="containsText" priority="827" operator="containsText" id="{76101755-1cd9-4181-ba10-0e4e78177bf1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10788,7 +10792,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="824" operator="containsText" id="{5d302c11-c732-422d-921b-9aadea1c0e31}">
+          <x14:cfRule type="containsText" priority="828" operator="containsText" id="{52628e9c-45ff-442f-9da2-c0502037bf7f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10806,7 +10810,7 @@
           <xm:sqref>K97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="861" operator="containsText" id="{79990323-fc67-43a2-82b1-bf2916603c7e}">
+          <x14:cfRule type="containsText" priority="865" operator="containsText" id="{a2a3c3ae-2467-4857-8d5b-8dce8ef72e2c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10821,7 +10825,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="862" operator="containsText" id="{4019a032-804e-4a1c-b885-65fe168cf7a0}">
+          <x14:cfRule type="containsText" priority="866" operator="containsText" id="{3de49a0b-191e-45bb-a11a-615681a7e7d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10839,7 +10843,7 @@
           <xm:sqref>L97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="151" operator="containsText" id="{c8c1f844-da18-4ce2-8e2d-88cd1e50a039}">
+          <x14:cfRule type="containsText" priority="155" operator="containsText" id="{40956c1f-07c4-4da4-8ace-9b2c0af9e549}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G98)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10854,7 +10858,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="152" operator="containsText" id="{07fcc8c0-b52a-4f66-8de1-b4b40d541a88}">
+          <x14:cfRule type="containsText" priority="156" operator="containsText" id="{f861a684-3889-41e7-a905-3b010b29d300}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G98)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10872,7 +10876,7 @@
           <xm:sqref>G98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="837" operator="containsText" id="{86e231e9-054f-4759-8fce-6be57c020a71}">
+          <x14:cfRule type="containsText" priority="841" operator="containsText" id="{ccba35ad-f6f5-41fa-888d-a06cf6704dba}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L101)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10887,7 +10891,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="838" operator="containsText" id="{c9f20098-3f9a-4f1c-aad8-0feba9eeb9f9}">
+          <x14:cfRule type="containsText" priority="842" operator="containsText" id="{f37f096d-9a88-4c18-81b1-a4189a85510a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L101)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10905,7 +10909,7 @@
           <xm:sqref>L101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="809" operator="containsText" id="{cacd5c28-4949-434b-9cf3-b268e8d33aed}">
+          <x14:cfRule type="containsText" priority="813" operator="containsText" id="{821a930d-64cd-4a6b-ad76-d74c295dd347}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I102)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10920,7 +10924,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="810" operator="containsText" id="{3a9e132a-1f0a-4387-a0b0-66c2c4688fbc}">
+          <x14:cfRule type="containsText" priority="814" operator="containsText" id="{d5afe392-e8af-40a3-b1ac-2cdc0013e4fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I102)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10938,7 +10942,7 @@
           <xm:sqref>I102</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="813" operator="containsText" id="{ffd31c8d-6206-4f86-97f8-d070ae197cc3}">
+          <x14:cfRule type="containsText" priority="817" operator="containsText" id="{e023e743-abc2-4d89-9bd2-cbbf6caaed0e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I106)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10953,7 +10957,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="814" operator="containsText" id="{48fd49ad-2752-4e6d-a445-a4ef44e52d29}">
+          <x14:cfRule type="containsText" priority="818" operator="containsText" id="{e65b42c1-4477-4b0f-9cd3-c693abb09878}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I106)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10971,7 +10975,7 @@
           <xm:sqref>I106</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="811" operator="containsText" id="{0e82b895-b842-4cb7-ba6c-02b17b7cc5d3}">
+          <x14:cfRule type="containsText" priority="815" operator="containsText" id="{ce1f8500-b81b-438f-9b80-aba8bdf9a166}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I107)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10986,7 +10990,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="812" operator="containsText" id="{45d06333-291c-4ea6-8aed-4e3a948baba4}">
+          <x14:cfRule type="containsText" priority="816" operator="containsText" id="{11359b0e-f677-4ff0-8727-7e4c93ddb156}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I107)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11004,7 +11008,7 @@
           <xm:sqref>I107</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="815" operator="containsText" id="{34e22241-0ca0-431a-ac1b-42013360dc0c}">
+          <x14:cfRule type="containsText" priority="819" operator="containsText" id="{59d2c37a-7a1f-4a67-9690-4414d76c2950}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I110)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11019,7 +11023,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="816" operator="containsText" id="{7d6698a0-334a-4b41-8162-b352da0f345b}">
+          <x14:cfRule type="containsText" priority="820" operator="containsText" id="{678b6d51-af5f-497d-85db-06347db154dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I110)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11037,7 +11041,7 @@
           <xm:sqref>I110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="833" operator="containsText" id="{12fc1fa9-eb7a-4185-8db6-de59c4882a15}">
+          <x14:cfRule type="containsText" priority="837" operator="containsText" id="{1f25ff6a-e63f-441a-8f34-d2667106ff4f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11052,7 +11056,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="834" operator="containsText" id="{3f295827-1977-443d-aa64-544a6fed1d0f}">
+          <x14:cfRule type="containsText" priority="838" operator="containsText" id="{9e2f6e82-76ec-4e5e-a0c9-fffcd5ec4e58}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11070,7 +11074,7 @@
           <xm:sqref>I111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="821" operator="containsText" id="{278b7ef0-6c7a-48fe-ab9a-20e3913243db}">
+          <x14:cfRule type="containsText" priority="825" operator="containsText" id="{801c6ddd-db1e-4267-9683-2f7955480241}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11085,7 +11089,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="822" operator="containsText" id="{825beac9-44d1-4db6-96b0-24228474ae3e}">
+          <x14:cfRule type="containsText" priority="826" operator="containsText" id="{1e449b38-f305-4a84-8d26-1f702339761e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11103,7 +11107,7 @@
           <xm:sqref>K111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="819" operator="containsText" id="{b4c50046-5a9d-484d-af10-d95dda1ddc21}">
+          <x14:cfRule type="containsText" priority="823" operator="containsText" id="{9e192cb4-c0e5-4d7b-8efd-d99bfdbc3087}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11118,7 +11122,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="820" operator="containsText" id="{d5966c5a-44b6-4c80-a09f-a2b2b4a6457e}">
+          <x14:cfRule type="containsText" priority="824" operator="containsText" id="{a102dbf5-c4ba-450d-a64d-16d0be44c333}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11136,7 +11140,7 @@
           <xm:sqref>L111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="147" operator="containsText" id="{b052d2c7-4fc8-4d14-91fb-9a0e116c3ce3}">
+          <x14:cfRule type="containsText" priority="151" operator="containsText" id="{b99bd2f6-7fc0-4be4-b477-a03ef2bb6ed4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11151,7 +11155,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="148" operator="containsText" id="{f8d55d7a-c796-47e3-81bd-3101da990f3f}">
+          <x14:cfRule type="containsText" priority="152" operator="containsText" id="{cfb7d3ea-e601-46df-aa31-e68c618820d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11169,7 +11173,7 @@
           <xm:sqref>G112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="817" operator="containsText" id="{e91385d3-42c5-4362-ac2a-d877f399fd2f}">
+          <x14:cfRule type="containsText" priority="821" operator="containsText" id="{738d6050-0184-47d1-a901-0d691ecb6e9a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11184,7 +11188,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="818" operator="containsText" id="{17a61a64-f631-4224-b46c-e9d547734ffb}">
+          <x14:cfRule type="containsText" priority="822" operator="containsText" id="{ca821c41-33c5-4c59-ba8d-33fb88da4aec}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11202,7 +11206,7 @@
           <xm:sqref>I112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="783" operator="containsText" id="{d7a02dee-0e1e-42ac-8e5b-73b17825c55e}">
+          <x14:cfRule type="containsText" priority="787" operator="containsText" id="{480b0bff-31cf-47d3-b505-cf92dfb1db77}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11217,7 +11221,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="784" operator="containsText" id="{1b4b3178-dcd2-46d4-a1ea-fb115d475e07}">
+          <x14:cfRule type="containsText" priority="788" operator="containsText" id="{cf0ce3a6-2248-4ff9-9435-f2817269cb60}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11235,7 +11239,7 @@
           <xm:sqref>I114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="801" operator="containsText" id="{cd1119a8-3b9b-474b-a8a4-c34b95c57b26}">
+          <x14:cfRule type="containsText" priority="805" operator="containsText" id="{0aafb8c9-b8c7-4eba-a307-c54c962eea32}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L115)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11250,7 +11254,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="802" operator="containsText" id="{06c3b096-9ca0-437b-8a1d-97958d04687d}">
+          <x14:cfRule type="containsText" priority="806" operator="containsText" id="{6b52d5aa-4263-43aa-a5e6-4bbc9d576ec7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L115)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11268,7 +11272,7 @@
           <xm:sqref>L115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="785" operator="containsText" id="{14f1d26a-8b9d-4e74-9141-50c1948ae939}">
+          <x14:cfRule type="containsText" priority="789" operator="containsText" id="{81c4f33b-53ea-474c-93bd-ffdce96ef4c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I116)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11283,7 +11287,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="786" operator="containsText" id="{1178149e-c062-4de3-ab3b-7c7e13143c59}">
+          <x14:cfRule type="containsText" priority="790" operator="containsText" id="{e96a2b3d-5b34-41fd-a0fe-3694478b29a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I116)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11301,7 +11305,7 @@
           <xm:sqref>I116</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="777" operator="containsText" id="{2fb8b832-16c4-4987-917d-a6dfa91e0809}">
+          <x14:cfRule type="containsText" priority="781" operator="containsText" id="{a8940fc9-a333-4df6-95ee-4545323493dc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I120)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11316,7 +11320,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="778" operator="containsText" id="{b89f6b27-cf9a-4c0a-944e-ca4f6f8141f7}">
+          <x14:cfRule type="containsText" priority="782" operator="containsText" id="{3369de4f-11da-4b26-8c83-a7e184e1ef5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I120)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11334,7 +11338,7 @@
           <xm:sqref>I120</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="773" operator="containsText" id="{ffaa16dc-22ce-44d3-a972-e7f0fbb94a9a}">
+          <x14:cfRule type="containsText" priority="777" operator="containsText" id="{93c37f72-d514-4cb4-8caa-df371bbcd40f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I121)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11349,7 +11353,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="774" operator="containsText" id="{34c028c1-11fd-42b6-8362-89e98bd91f5b}">
+          <x14:cfRule type="containsText" priority="778" operator="containsText" id="{f333d75a-1fb1-42eb-a8f1-61a514acf6cd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I121)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11367,7 +11371,7 @@
           <xm:sqref>I121</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="775" operator="containsText" id="{95c40bc2-379b-4893-b6e2-b0e4270a55ac}">
+          <x14:cfRule type="containsText" priority="779" operator="containsText" id="{d90482bc-4d51-403d-a160-d39e6cbbb83a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I122)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11382,7 +11386,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="776" operator="containsText" id="{4b51b148-8e6b-4efd-aa8f-88ccb74618d2}">
+          <x14:cfRule type="containsText" priority="780" operator="containsText" id="{6678aa6d-9b2d-419f-aa5a-091da2a72286}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I122)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11400,7 +11404,7 @@
           <xm:sqref>I122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="769" operator="containsText" id="{7283daad-83a2-43fb-b0e2-e8f4af41d51c}">
+          <x14:cfRule type="containsText" priority="773" operator="containsText" id="{d626748e-2ebe-47cb-9520-9cc7de221d05}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I123)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11415,7 +11419,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="770" operator="containsText" id="{c39ab0b2-6a49-42ce-856e-d8217dac99c7}">
+          <x14:cfRule type="containsText" priority="774" operator="containsText" id="{9ce86512-1f24-401e-af2e-865701cacc95}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I123)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11433,7 +11437,7 @@
           <xm:sqref>I123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="791" operator="containsText" id="{2873107c-1ba8-4f25-9cf7-7370cf7b63e0}">
+          <x14:cfRule type="containsText" priority="795" operator="containsText" id="{32f03339-324a-4802-a1ec-f68fd9a9b391}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I124)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11448,7 +11452,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="792" operator="containsText" id="{53d2f4c4-2777-49e7-8f72-84d8b033ae21}">
+          <x14:cfRule type="containsText" priority="796" operator="containsText" id="{eb1d4105-48e5-4668-bce7-5d8c514f01bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I124)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11466,7 +11470,7 @@
           <xm:sqref>I124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="781" operator="containsText" id="{2c6400c4-01d2-4c74-ac63-abcb30bcc478}">
+          <x14:cfRule type="containsText" priority="785" operator="containsText" id="{b3f717ab-3e79-47f9-95c0-36c3fd2a5f54}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11481,7 +11485,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="782" operator="containsText" id="{d97a1427-c7bd-4157-91ae-bac34f868cef}">
+          <x14:cfRule type="containsText" priority="786" operator="containsText" id="{94f87c30-d519-4a5e-b121-163fd3af85cf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11499,7 +11503,7 @@
           <xm:sqref>I125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="797" operator="containsText" id="{f74209ca-16ed-4f06-84a3-df2b1bac4529}">
+          <x14:cfRule type="containsText" priority="801" operator="containsText" id="{7bf56905-84e2-486e-bfc9-4ed959633b3d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11514,7 +11518,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="798" operator="containsText" id="{4a57eee1-1ca1-40cc-b6a2-07cefccb2bba}">
+          <x14:cfRule type="containsText" priority="802" operator="containsText" id="{1beea190-824d-4af6-916c-b7b748dc82ba}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11532,7 +11536,7 @@
           <xm:sqref>K125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="779" operator="containsText" id="{9b030a83-f659-49ef-9a90-9ea2429e1ae8}">
+          <x14:cfRule type="containsText" priority="783" operator="containsText" id="{deab5508-945d-4404-97fd-fbe8e082cf62}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11547,7 +11551,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="780" operator="containsText" id="{bcc51055-3a04-4e1d-aa46-e07488ffd998}">
+          <x14:cfRule type="containsText" priority="784" operator="containsText" id="{b4e3c12f-5b3b-453d-9ed8-ae10695c737b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11565,7 +11569,7 @@
           <xm:sqref>L125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="143" operator="containsText" id="{926996f1-c0a0-46c7-a29a-dea3ffb1bd00}">
+          <x14:cfRule type="containsText" priority="147" operator="containsText" id="{6d293715-cebd-4264-baa7-15e53d329f44}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11580,7 +11584,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="144" operator="containsText" id="{2363aa72-7012-4bdf-a2cb-281d1294abf3}">
+          <x14:cfRule type="containsText" priority="148" operator="containsText" id="{646728e0-9ec8-4b9c-b78a-70f6e3e8035d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11598,7 +11602,7 @@
           <xm:sqref>G126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="771" operator="containsText" id="{4b66dbc3-c0dd-43ef-bd8a-67149da889e5}">
+          <x14:cfRule type="containsText" priority="775" operator="containsText" id="{87be6d60-fc90-4211-8f43-ad165b8419ab}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11613,7 +11617,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="772" operator="containsText" id="{f98c6346-e385-4aa7-9abe-8e7c3d579d93}">
+          <x14:cfRule type="containsText" priority="776" operator="containsText" id="{0eebaded-a634-409f-9c3b-36baa5a98a12}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11631,7 +11635,7 @@
           <xm:sqref>I126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="753" operator="containsText" id="{7dd2a6ad-95f3-4698-abd3-78ebf4b62238}">
+          <x14:cfRule type="containsText" priority="757" operator="containsText" id="{a9b52c19-c387-4398-8479-df2776774437}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11646,7 +11650,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="754" operator="containsText" id="{86e42763-a76a-4880-8c3f-d2032b7fe4d4}">
+          <x14:cfRule type="containsText" priority="758" operator="containsText" id="{1bddb6dd-09da-4f71-9c17-b415664e741c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11664,7 +11668,7 @@
           <xm:sqref>I128</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="729" operator="containsText" id="{117bfda7-2f2d-4195-a1d5-2ec0f61100e2}">
+          <x14:cfRule type="containsText" priority="733" operator="containsText" id="{6af42e14-986d-42ea-916c-fa7063d7174a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I129)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11679,7 +11683,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="730" operator="containsText" id="{a61c9625-15d0-41a3-b5f2-b78258a120cf}">
+          <x14:cfRule type="containsText" priority="734" operator="containsText" id="{a6bbdfbf-debb-4dd0-ae61-a34bbb9bd94a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I129)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11697,7 +11701,7 @@
           <xm:sqref>I129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="761" operator="containsText" id="{c884b261-c001-40c3-84a8-b007f55fe120}">
+          <x14:cfRule type="containsText" priority="765" operator="containsText" id="{5f87015e-28a5-4d84-bba5-9160348955d2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L129)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11712,7 +11716,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="762" operator="containsText" id="{e615f19d-c92e-4d01-b78a-178e9f825802}">
+          <x14:cfRule type="containsText" priority="766" operator="containsText" id="{c8aad775-b0ab-4de7-86c4-d8f15f8e6d2b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L129)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11730,7 +11734,7 @@
           <xm:sqref>L129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="755" operator="containsText" id="{cca20be1-41cb-405b-85e8-6a2a5ebf3451}">
+          <x14:cfRule type="containsText" priority="759" operator="containsText" id="{10905b8c-d593-4635-bc12-a0554abe593f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I130)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11745,7 +11749,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="756" operator="containsText" id="{e4708913-f2fb-4a3a-a692-092f7c0a4c8d}">
+          <x14:cfRule type="containsText" priority="760" operator="containsText" id="{edd8d910-73e4-4eb3-b5c8-8e28bd5eb9e6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I130)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11763,7 +11767,7 @@
           <xm:sqref>I130</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="733" operator="containsText" id="{25a4c4b2-f679-474a-90e4-0dae2c054f19}">
+          <x14:cfRule type="containsText" priority="737" operator="containsText" id="{8ec90d1c-fb78-429b-b0e6-327c4f386c2e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11778,7 +11782,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="734" operator="containsText" id="{5c8195c3-94ed-454d-b2c8-c240aac9ee67}">
+          <x14:cfRule type="containsText" priority="738" operator="containsText" id="{5a199fb9-e485-4108-90fb-23eb90fc39cb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11796,7 +11800,7 @@
           <xm:sqref>I133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="673" operator="containsText" id="{e1e05f00-0361-4c17-859c-43841894ddd9}">
+          <x14:cfRule type="containsText" priority="677" operator="containsText" id="{e0a93478-4d03-4a2c-a700-efafb700049e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11811,7 +11815,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="674" operator="containsText" id="{08b9d4e3-6b25-4ef8-b32e-29cabc3f5f6d}">
+          <x14:cfRule type="containsText" priority="678" operator="containsText" id="{c573a633-d330-4f98-b56c-a805c0d10579}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11829,7 +11833,7 @@
           <xm:sqref>K133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="731" operator="containsText" id="{700ba0e9-c22e-4997-8645-2f7c93cce28b}">
+          <x14:cfRule type="containsText" priority="735" operator="containsText" id="{9c92ace1-9cfa-4ba2-a124-ea907f4be73a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11844,7 +11848,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="732" operator="containsText" id="{292548c4-c439-48ea-b7de-dd86348d9482}">
+          <x14:cfRule type="containsText" priority="736" operator="containsText" id="{fff9bea7-5193-4a81-94ff-20d43edc9971}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11862,7 +11866,7 @@
           <xm:sqref>L133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="725" operator="containsText" id="{85c61a7a-69d7-4a58-b448-50768d4530dd}">
+          <x14:cfRule type="containsText" priority="729" operator="containsText" id="{9bf2d572-a5c2-484e-a487-491852437638}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I134)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11877,7 +11881,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="726" operator="containsText" id="{24378a4c-2351-42a6-8f84-41107335fb63}">
+          <x14:cfRule type="containsText" priority="730" operator="containsText" id="{ca657395-ffc7-41cb-bffc-cdb1e156af75}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I134)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11895,7 +11899,7 @@
           <xm:sqref>I134</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="727" operator="containsText" id="{c8b1e153-f4b9-4a26-ac25-d2798258f4d9}">
+          <x14:cfRule type="containsText" priority="731" operator="containsText" id="{d43621b8-b2b6-46b5-b3c6-3e0ec54a1208}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I135)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11910,7 +11914,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="728" operator="containsText" id="{40aba14f-ebb1-4993-8946-8351a848956f}">
+          <x14:cfRule type="containsText" priority="732" operator="containsText" id="{5f6f3bad-ce82-4684-9352-528370163a18}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I135)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11928,7 +11932,7 @@
           <xm:sqref>I135</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="739" operator="containsText" id="{817009ec-bedd-4434-8537-783989072fb3}">
+          <x14:cfRule type="containsText" priority="743" operator="containsText" id="{d76b0c6f-52f7-44dc-b7f2-697ea486fc86}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I137)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11943,7 +11947,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="740" operator="containsText" id="{9e7e77ec-024b-4d2f-b4ad-a1fc280ccf8c}">
+          <x14:cfRule type="containsText" priority="744" operator="containsText" id="{105a0b99-17ba-41f5-9470-6603bd42d3bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I137)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11961,7 +11965,7 @@
           <xm:sqref>I137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="757" operator="containsText" id="{7e0aa03c-a11a-4529-abfb-0b96bacb6dbc}">
+          <x14:cfRule type="containsText" priority="761" operator="containsText" id="{977a957c-8855-493c-aa16-c173348df503}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I138)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11976,7 +11980,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="758" operator="containsText" id="{7b98f69b-7d4c-4411-91ef-02a8a13a8609}">
+          <x14:cfRule type="containsText" priority="762" operator="containsText" id="{8aa05739-56a5-40e8-869f-668f9dd3e7be}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I138)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11994,7 +11998,7 @@
           <xm:sqref>I138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="737" operator="containsText" id="{85fd6a40-af19-4fe5-858c-50f01fe3cd51}">
+          <x14:cfRule type="containsText" priority="741" operator="containsText" id="{cb6affa2-1c69-4dcc-ad9e-5e4351f58c49}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12009,7 +12013,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="738" operator="containsText" id="{007d2aa1-9964-4a10-80f8-dfb8c4ac3b13}">
+          <x14:cfRule type="containsText" priority="742" operator="containsText" id="{f6756949-6c2e-4847-b5a7-0b1d3b4fb786}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12027,7 +12031,7 @@
           <xm:sqref>I139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="687" operator="containsText" id="{510e8d69-48f7-4cb5-87ab-7f29402e4be5}">
+          <x14:cfRule type="containsText" priority="691" operator="containsText" id="{1debb3a1-202c-47f6-ab4e-b5451065f194}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12042,7 +12046,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="688" operator="containsText" id="{b59b3b57-3172-4b2a-8fad-0814cc27388d}">
+          <x14:cfRule type="containsText" priority="692" operator="containsText" id="{fbad31be-4280-49b3-87ec-7c7a65367b24}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12060,7 +12064,7 @@
           <xm:sqref>K139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="735" operator="containsText" id="{9dd72eb7-978b-4747-a7ac-abe76e62c332}">
+          <x14:cfRule type="containsText" priority="739" operator="containsText" id="{ae20c341-d8b2-4ba7-b6ca-3f1bf8ba3349}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12075,7 +12079,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="736" operator="containsText" id="{86332b07-a34f-4046-abe1-638e3f968a0c}">
+          <x14:cfRule type="containsText" priority="740" operator="containsText" id="{cf97498a-93a3-45e0-a588-6d3a35a3bfbf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12093,7 +12097,7 @@
           <xm:sqref>L139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="139" operator="containsText" id="{93629b40-df50-4d57-8e33-920979967914}">
+          <x14:cfRule type="containsText" priority="143" operator="containsText" id="{56dfa5ac-08da-4545-91e6-41422bf8e737}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12108,7 +12112,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="140" operator="containsText" id="{cd2518de-20aa-4a22-ae3a-a341a1061c2a}">
+          <x14:cfRule type="containsText" priority="144" operator="containsText" id="{30d58cb3-9421-4aeb-bccf-7bbfda925b78}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12126,7 +12130,7 @@
           <xm:sqref>G140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="741" operator="containsText" id="{f07ec866-0038-4ccf-a17d-274435fce5d1}">
+          <x14:cfRule type="containsText" priority="745" operator="containsText" id="{e6b5434e-286b-4407-b58e-66146b224b87}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12141,7 +12145,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="742" operator="containsText" id="{c452ccb1-3f48-4309-a665-0f86abd540a0}">
+          <x14:cfRule type="containsText" priority="746" operator="containsText" id="{1628d202-c1be-4bf1-9ae6-0343fc4fa990}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12159,7 +12163,7 @@
           <xm:sqref>I140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="709" operator="containsText" id="{23f1a997-1c55-41fe-9047-cb41e031a37b}">
+          <x14:cfRule type="containsText" priority="713" operator="containsText" id="{14da99ea-a210-4859-a508-fa56e9c0616d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12174,7 +12178,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="710" operator="containsText" id="{c36e0140-8285-4c89-bc98-d8d887788ae7}">
+          <x14:cfRule type="containsText" priority="714" operator="containsText" id="{9852ff2d-7847-4099-999d-455ce1bdd529}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12192,7 +12196,7 @@
           <xm:sqref>I142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="689" operator="containsText" id="{a0085672-b4e6-4b20-a24c-2129e3f8594d}">
+          <x14:cfRule type="containsText" priority="693" operator="containsText" id="{b1873d6b-9754-445d-ae70-9df72b5a0350}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12207,7 +12211,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="690" operator="containsText" id="{1d3a7774-a155-44c2-802c-b0b56c1a3b66}">
+          <x14:cfRule type="containsText" priority="694" operator="containsText" id="{ce0609cf-8fe7-434b-981e-23227f966ab4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12225,7 +12229,7 @@
           <xm:sqref>L142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="711" operator="containsText" id="{1335c9a9-a218-4273-adc1-6299a220e46a}">
+          <x14:cfRule type="containsText" priority="715" operator="containsText" id="{2c2ba472-9c16-4615-9b6f-4c1bdafe554b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I144)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12240,7 +12244,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="712" operator="containsText" id="{4b7369a8-b146-4efe-ba96-118b589e9115}">
+          <x14:cfRule type="containsText" priority="716" operator="containsText" id="{65ab8045-01f6-4b61-912e-3af69429014a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I144)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12258,7 +12262,7 @@
           <xm:sqref>I144</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="677" operator="containsText" id="{200e55da-48fd-4f4e-816e-17411f1effd5}">
+          <x14:cfRule type="containsText" priority="681" operator="containsText" id="{e8c614cc-24e0-4043-b344-30adce1b1fb2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I146)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12273,7 +12277,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="678" operator="containsText" id="{b7dec32a-397e-40a2-a3f1-35decf250e6d}">
+          <x14:cfRule type="containsText" priority="682" operator="containsText" id="{e5a40cd5-3fa9-4c56-9cc6-c7262bbfc072}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I146)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12291,7 +12295,7 @@
           <xm:sqref>I146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="675" operator="containsText" id="{1178600b-04b8-4db3-b91f-9259903e9311}">
+          <x14:cfRule type="containsText" priority="679" operator="containsText" id="{7fbfbdff-d26a-4a01-8c83-292d70d07ecd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I147)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12306,7 +12310,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="676" operator="containsText" id="{8b51a9e0-fad7-40ec-9331-747f2f094f16}">
+          <x14:cfRule type="containsText" priority="680" operator="containsText" id="{3c42fd32-6ff4-40b1-bf75-0d762f7e1251}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I147)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12324,7 +12328,7 @@
           <xm:sqref>I147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="681" operator="containsText" id="{5cccd012-765e-45af-b426-8aea25ea2614}">
+          <x14:cfRule type="containsText" priority="685" operator="containsText" id="{1b0f0b24-c430-4df7-be84-278f7acf0a2c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L147)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12339,7 +12343,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="682" operator="containsText" id="{d9dd63e8-6450-4811-96b1-211310a2ac6e}">
+          <x14:cfRule type="containsText" priority="686" operator="containsText" id="{2af754c9-73ed-4822-81b8-187a491a64e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L147)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12357,7 +12361,7 @@
           <xm:sqref>L147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="679" operator="containsText" id="{c0a81d06-7709-4f47-bb9b-0b0dfa40bd75}">
+          <x14:cfRule type="containsText" priority="683" operator="containsText" id="{16909bc2-3ad5-4f39-898e-460279ccb30a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I148)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12372,7 +12376,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="680" operator="containsText" id="{fa16d019-31ea-477f-80c8-fdd7aa9a48fe}">
+          <x14:cfRule type="containsText" priority="684" operator="containsText" id="{e1c8813d-96c8-4c97-8a7d-57beb730d074}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I148)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12390,7 +12394,7 @@
           <xm:sqref>I148</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="683" operator="containsText" id="{84494907-2003-495d-96cf-5bc9f6e82270}">
+          <x14:cfRule type="containsText" priority="687" operator="containsText" id="{7a56c603-cc67-46ce-8c7e-5fab1ed260d7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I149)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12405,7 +12409,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="684" operator="containsText" id="{d045ae0d-e642-444c-8066-0bd665e7c2ba}">
+          <x14:cfRule type="containsText" priority="688" operator="containsText" id="{6f2fdf32-2e1f-4281-a635-bbeafaa2ba0b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I149)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12423,7 +12427,7 @@
           <xm:sqref>I149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="705" operator="containsText" id="{f6ee38a6-e3e1-4060-a77c-9c91216ecc12}">
+          <x14:cfRule type="containsText" priority="709" operator="containsText" id="{91077e60-37d0-41f0-94ec-983f67f701b2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I151)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12438,7 +12442,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="706" operator="containsText" id="{fbd2470e-5ccb-4738-a54e-7d970466d05d}">
+          <x14:cfRule type="containsText" priority="710" operator="containsText" id="{f5b91b6c-4ae1-4721-bf10-f8f04f8ffc58}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I151)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12456,7 +12460,7 @@
           <xm:sqref>I151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="713" operator="containsText" id="{24b0d7ec-5fab-4ebb-a797-7d3a0a026164}">
+          <x14:cfRule type="containsText" priority="717" operator="containsText" id="{1c8bbd67-dbe3-4c09-852a-653f672c5ca7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I152)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12471,7 +12475,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="714" operator="containsText" id="{80fc7de6-8f85-4e77-bd5c-4f55c6b7425e}">
+          <x14:cfRule type="containsText" priority="718" operator="containsText" id="{31a1a5ad-4add-480a-9c81-b17b782c0aad}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I152)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12489,7 +12493,7 @@
           <xm:sqref>I152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="703" operator="containsText" id="{ff7656de-c16f-4051-a2e1-04e4acd87eb3}">
+          <x14:cfRule type="containsText" priority="707" operator="containsText" id="{050cf5c9-e45e-4fc8-a248-4db41aa20f97}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12504,7 +12508,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="704" operator="containsText" id="{85c8834f-74fe-4741-853b-dcebe98a768b}">
+          <x14:cfRule type="containsText" priority="708" operator="containsText" id="{7ee1a027-4245-48ac-bb5a-201baf38e9f7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12522,7 +12526,7 @@
           <xm:sqref>I153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="715" operator="containsText" id="{8160dabf-2c46-42ed-8df8-13f0a574a4b2}">
+          <x14:cfRule type="containsText" priority="719" operator="containsText" id="{5cd60511-964b-4913-b830-8c3c8edc203f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12537,7 +12541,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="716" operator="containsText" id="{83f61f3d-0034-4d34-8d5f-5bda977212b2}">
+          <x14:cfRule type="containsText" priority="720" operator="containsText" id="{8eae5917-1694-49f6-b173-8f86c9fd28bc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12555,7 +12559,7 @@
           <xm:sqref>K153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="701" operator="containsText" id="{37eac9fb-40d7-4ba0-9230-6f8c0cae5c4d}">
+          <x14:cfRule type="containsText" priority="705" operator="containsText" id="{26c146fb-5f5d-4ebb-82da-08d5aa11351c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12570,7 +12574,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="702" operator="containsText" id="{ec0913ec-72e3-40da-9fbd-0fbd61725e25}">
+          <x14:cfRule type="containsText" priority="706" operator="containsText" id="{facbce47-8d3a-4ec0-bb6e-81f3409f0678}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12588,7 +12592,7 @@
           <xm:sqref>L153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="135" operator="containsText" id="{79f58903-68a6-4d2c-bef9-79bb6ce5bfcf}">
+          <x14:cfRule type="containsText" priority="139" operator="containsText" id="{87b9edd5-1945-49cc-a4d6-61809b2ab77d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12603,7 +12607,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="136" operator="containsText" id="{6ed9ecc4-9107-49e5-8430-34e639fd42d7}">
+          <x14:cfRule type="containsText" priority="140" operator="containsText" id="{709bdb2b-8801-4da2-8899-0967369c388e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12621,7 +12625,7 @@
           <xm:sqref>G154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="707" operator="containsText" id="{3ae59c87-53b8-4516-a043-774de5ba3828}">
+          <x14:cfRule type="containsText" priority="711" operator="containsText" id="{5eb58d26-4034-4c2c-aefa-a50a7883cc23}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12636,7 +12640,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="708" operator="containsText" id="{4aea6aaf-189f-4506-95de-c3e6c1db5f67}">
+          <x14:cfRule type="containsText" priority="712" operator="containsText" id="{6500745a-f5e8-4395-857b-c7466487e5d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12654,7 +12658,7 @@
           <xm:sqref>I154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="685" operator="containsText" id="{27fed1f3-e2fc-4e08-8610-625e8e15a296}">
+          <x14:cfRule type="containsText" priority="689" operator="containsText" id="{168cef30-36bb-4a63-a306-68f48256d862}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I155)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12669,7 +12673,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="686" operator="containsText" id="{7149674d-9cf7-4b56-a32e-5943ee167ab3}">
+          <x14:cfRule type="containsText" priority="690" operator="containsText" id="{763f584e-3d10-421f-a2f5-63c807b29480}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I155)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12687,7 +12691,7 @@
           <xm:sqref>I155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="657" operator="containsText" id="{f23cc0be-dd2a-4275-9258-1f0c2a214cc5}">
+          <x14:cfRule type="containsText" priority="661" operator="containsText" id="{f54c40bc-2870-45e6-9b97-0eca0a9089d0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12702,7 +12706,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="658" operator="containsText" id="{569f7812-eb6e-4346-8498-d681937c996a}">
+          <x14:cfRule type="containsText" priority="662" operator="containsText" id="{00f45b74-c2bf-447e-b839-2ea3f410c19c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12720,7 +12724,7 @@
           <xm:sqref>I156</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="647" operator="containsText" id="{71be51f8-02d7-495e-9abb-77dafac85fb5}">
+          <x14:cfRule type="containsText" priority="651" operator="containsText" id="{59194be3-6d38-45e8-8f98-8f406cc1476b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12735,7 +12739,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="648" operator="containsText" id="{ed9bdda7-5062-4d34-926a-eb9c2f6c5b8c}">
+          <x14:cfRule type="containsText" priority="652" operator="containsText" id="{1ed14ae9-1da7-4c9c-8133-97d174f04e38}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12753,7 +12757,7 @@
           <xm:sqref>L156</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="659" operator="containsText" id="{91802059-31e0-4590-8a2b-4e881ee8e843}">
+          <x14:cfRule type="containsText" priority="663" operator="containsText" id="{4851811c-ad76-484b-a7da-92f8f4de1a6c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I158)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12768,7 +12772,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="660" operator="containsText" id="{241bb28a-3985-49f3-98ad-80dc0bed717a}">
+          <x14:cfRule type="containsText" priority="664" operator="containsText" id="{288a9513-7cca-45fa-8327-baaa9a0ff861}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I158)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12786,7 +12790,7 @@
           <xm:sqref>I158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="637" operator="containsText" id="{631c4312-4f9c-4b35-b97e-919146b90483}">
+          <x14:cfRule type="containsText" priority="641" operator="containsText" id="{339ef32e-6959-4ae7-a9f1-b2c3594565b5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I160)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12801,7 +12805,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="638" operator="containsText" id="{6f404a6f-4b96-47fe-8a76-cad0b0348391}">
+          <x14:cfRule type="containsText" priority="642" operator="containsText" id="{05589ec1-348a-44b2-a2ff-b5e9d4e5ca17}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I160)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12819,7 +12823,7 @@
           <xm:sqref>I160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="635" operator="containsText" id="{0b5894fe-5f07-4674-8756-be52e98b2657}">
+          <x14:cfRule type="containsText" priority="639" operator="containsText" id="{942416ee-8d06-47cb-a92d-d9ca9e284ee9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I161)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12834,7 +12838,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="636" operator="containsText" id="{1157bf09-a334-4586-91fe-eca4d4fb2595}">
+          <x14:cfRule type="containsText" priority="640" operator="containsText" id="{d588fe28-64b7-4d63-8bb8-c851ed82c23a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I161)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12852,7 +12856,7 @@
           <xm:sqref>I161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="641" operator="containsText" id="{4b392c28-7645-40ff-8113-11eadfd78f13}">
+          <x14:cfRule type="containsText" priority="645" operator="containsText" id="{705d6538-684d-4349-a1f1-c7301f17b14a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L161)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12867,7 +12871,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="642" operator="containsText" id="{8cf1d857-8ccd-40cc-9faf-8e45e69c0ce8}">
+          <x14:cfRule type="containsText" priority="646" operator="containsText" id="{1a4c1f46-2925-4507-8a92-c17cbf4b9c13}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L161)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12885,7 +12889,7 @@
           <xm:sqref>L161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="627" operator="containsText" id="{a199c701-da07-4a66-b06a-66dccccac084}">
+          <x14:cfRule type="containsText" priority="631" operator="containsText" id="{6f855ae2-4fc8-42a2-bfa0-84ebe71c11a1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I162)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12900,7 +12904,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="628" operator="containsText" id="{7554b388-9a70-4c0a-a000-1e09473e54e6}">
+          <x14:cfRule type="containsText" priority="632" operator="containsText" id="{9567272a-116d-41a0-a87e-d955eceba593}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I162)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12918,7 +12922,7 @@
           <xm:sqref>I162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="629" operator="containsText" id="{0bdddd7c-2680-48de-8b97-6cc07992ee57}">
+          <x14:cfRule type="containsText" priority="633" operator="containsText" id="{2c8ebddc-829c-4b81-a582-14f1491a094b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I163)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12933,7 +12937,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="630" operator="containsText" id="{89665347-23bc-4f32-aa98-bfc82b87472a}">
+          <x14:cfRule type="containsText" priority="634" operator="containsText" id="{04aa567b-9a17-42b4-b679-2805b8012d8d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I163)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12951,7 +12955,7 @@
           <xm:sqref>I163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="653" operator="containsText" id="{44a94eb4-4dc0-4574-86a4-ba2c19919101}">
+          <x14:cfRule type="containsText" priority="657" operator="containsText" id="{d65f5e13-3f34-42dd-9819-f08eeb91d53b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I165)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12966,7 +12970,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="654" operator="containsText" id="{a2af1a94-a863-4905-a173-a7e9b945079d}">
+          <x14:cfRule type="containsText" priority="658" operator="containsText" id="{62b6a08d-942f-4c17-a2b9-eed49993ebc1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I165)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12984,7 +12988,7 @@
           <xm:sqref>I165</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="661" operator="containsText" id="{fd2d6bcc-cb84-4c24-b292-606dd5d8175a}">
+          <x14:cfRule type="containsText" priority="665" operator="containsText" id="{6299d295-0c60-4ec1-8e2e-ed8714a5da53}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I166)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12999,7 +13003,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="662" operator="containsText" id="{adb83908-fdf2-448d-8a2e-afd9ff59283f}">
+          <x14:cfRule type="containsText" priority="666" operator="containsText" id="{eea03c8f-4810-4b51-be83-3e4aabc13c59}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I166)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13017,7 +13021,7 @@
           <xm:sqref>I166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="633" operator="containsText" id="{bef1d632-abfa-4f34-bc93-6c3efd2e593c}">
+          <x14:cfRule type="containsText" priority="637" operator="containsText" id="{f1a81c02-557f-45de-b911-a419c1c524ca}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13032,7 +13036,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="634" operator="containsText" id="{b9b43da1-d473-449b-aad5-b95ca525c23a}">
+          <x14:cfRule type="containsText" priority="638" operator="containsText" id="{f937609b-bc52-4b3e-8cf4-e76dd5175092}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13050,7 +13054,7 @@
           <xm:sqref>I167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="663" operator="containsText" id="{657b0ac5-f0f5-4424-a42e-7b46feeeb367}">
+          <x14:cfRule type="containsText" priority="667" operator="containsText" id="{70742a24-1376-4438-b0fc-4ee191d96c5a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13065,7 +13069,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="664" operator="containsText" id="{a53323b6-a014-49a9-8137-c31efc32d935}">
+          <x14:cfRule type="containsText" priority="668" operator="containsText" id="{373fb17d-8ea0-40db-868b-ed0f4b6a5cf3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13083,7 +13087,7 @@
           <xm:sqref>K167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="631" operator="containsText" id="{ef73bd9e-13c7-484f-8367-03954d5f1906}">
+          <x14:cfRule type="containsText" priority="635" operator="containsText" id="{dd24a093-036c-4806-a3b9-078ebcf3367c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13098,7 +13102,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="632" operator="containsText" id="{0c17fafc-d632-4cd0-ad5b-9f90a5fb889b}">
+          <x14:cfRule type="containsText" priority="636" operator="containsText" id="{91fa7669-08cd-4580-8223-6940de825003}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13116,7 +13120,7 @@
           <xm:sqref>L167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="131" operator="containsText" id="{94ffc299-3749-410f-b82b-16f9e2271c97}">
+          <x14:cfRule type="containsText" priority="135" operator="containsText" id="{d8e89015-0b5a-4787-a528-0a6ff6a3f344}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13131,7 +13135,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="132" operator="containsText" id="{6323adde-bc98-4311-9a3f-7c49cf425d0c}">
+          <x14:cfRule type="containsText" priority="136" operator="containsText" id="{4e0f3b09-0e57-412c-b38c-b77b6b9a38d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13149,7 +13153,7 @@
           <xm:sqref>G168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="655" operator="containsText" id="{1a49caae-df6c-416e-a746-110bb5d2d9a3}">
+          <x14:cfRule type="containsText" priority="659" operator="containsText" id="{d40d3b10-3569-433b-b519-8d4ddd93fe79}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13164,7 +13168,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="656" operator="containsText" id="{734db575-cf4b-4469-80f8-adc852a32b60}">
+          <x14:cfRule type="containsText" priority="660" operator="containsText" id="{886ee901-cdee-4a4d-9c27-5329448c2025}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13182,7 +13186,7 @@
           <xm:sqref>I168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="645" operator="containsText" id="{effb5014-46f2-4bc6-98eb-9257711df5ac}">
+          <x14:cfRule type="containsText" priority="649" operator="containsText" id="{7b16fdf3-0bf2-4e6e-999b-eb69ad288daf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I169)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13197,7 +13201,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="646" operator="containsText" id="{0b5b9e14-244c-4469-b3ea-63eea299b776}">
+          <x14:cfRule type="containsText" priority="650" operator="containsText" id="{8699d35b-433e-4180-b6be-d7b59ffe0c44}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I169)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13215,7 +13219,7 @@
           <xm:sqref>I169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="611" operator="containsText" id="{d6f8fd5a-8263-4c81-98c2-7aff128bd8c3}">
+          <x14:cfRule type="containsText" priority="615" operator="containsText" id="{a99bc9e5-6343-4994-ac71-6caffb406ca1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13230,7 +13234,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="612" operator="containsText" id="{396c35b0-3436-4f4d-a00a-4d30c63b9ae7}">
+          <x14:cfRule type="containsText" priority="616" operator="containsText" id="{22706584-b34a-41db-af88-88b3c819775c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13248,7 +13252,7 @@
           <xm:sqref>I170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="605" operator="containsText" id="{0d37b4dc-c488-4ab7-a304-3f31ca9c902b}">
+          <x14:cfRule type="containsText" priority="609" operator="containsText" id="{17ef0ff9-5a1f-40ed-b785-a024ce008dc6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13263,7 +13267,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="606" operator="containsText" id="{29ef9957-2252-4f35-998b-4e4d7508e3bf}">
+          <x14:cfRule type="containsText" priority="610" operator="containsText" id="{d706fc80-491a-40cf-bd70-7ccb90af79f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13281,7 +13285,7 @@
           <xm:sqref>L170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="581" operator="containsText" id="{65ded0fe-d0dc-4ef9-b6aa-4304d3b2aa39}">
+          <x14:cfRule type="containsText" priority="585" operator="containsText" id="{bc2c930c-2d42-45c1-b2b4-63e451c6292b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13296,7 +13300,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="582" operator="containsText" id="{1ca74d4d-f95a-4f8f-874a-2c647084dcca}">
+          <x14:cfRule type="containsText" priority="586" operator="containsText" id="{8257bb3d-ba60-47f8-9e77-0715bfff648e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13314,7 +13318,7 @@
           <xm:sqref>I171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="165" operator="containsText" id="{b86b626c-1c94-48cf-94e9-54bf56777d58}">
+          <x14:cfRule type="containsText" priority="169" operator="containsText" id="{72eed64b-d84a-4791-b2e8-4af74b9d2785}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13329,7 +13333,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="166" operator="containsText" id="{54ea67e3-02cd-49e2-b0a1-d500b540a4d9}">
+          <x14:cfRule type="containsText" priority="170" operator="containsText" id="{4e4d382c-73f4-4b96-9189-ce5295e3d722}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13347,7 +13351,7 @@
           <xm:sqref>K171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="579" operator="containsText" id="{cb64024e-343e-4e63-ad6d-314acd858f00}">
+          <x14:cfRule type="containsText" priority="583" operator="containsText" id="{acd7ab71-a2e6-4bb4-bb1b-ad436604eaf1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13362,7 +13366,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="580" operator="containsText" id="{c37a0d7b-d319-47f1-9c78-00a4d03c849f}">
+          <x14:cfRule type="containsText" priority="584" operator="containsText" id="{48c6bb50-9e14-41fa-a8dc-d2256595887e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13380,7 +13384,7 @@
           <xm:sqref>L171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="613" operator="containsText" id="{8b018cdb-edb6-4687-ba1d-dce7f7d6c385}">
+          <x14:cfRule type="containsText" priority="617" operator="containsText" id="{4a3d9aeb-7bf6-4c32-9c3a-10a4abae569a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I172)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13395,7 +13399,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="614" operator="containsText" id="{4913573e-616e-4156-8513-e1316c952c19}">
+          <x14:cfRule type="containsText" priority="618" operator="containsText" id="{e8c2e97d-85f7-49d1-bf10-9e5a970690b5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I172)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13413,7 +13417,7 @@
           <xm:sqref>I172</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="599" operator="containsText" id="{fc8fee42-860b-4867-a65e-2eeb3a3b3d85}">
+          <x14:cfRule type="containsText" priority="603" operator="containsText" id="{fe062484-28c3-46f6-9c7e-c5fff1da949b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I174)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13428,7 +13432,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="600" operator="containsText" id="{6cd7d8cf-67d9-4880-82c2-647d2fcea3e5}">
+          <x14:cfRule type="containsText" priority="604" operator="containsText" id="{1ec4441d-b6a7-4a94-bec2-e2895e4c1477}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I174)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13446,7 +13450,7 @@
           <xm:sqref>I174</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="597" operator="containsText" id="{abdf1c35-81f0-4631-8e90-d09331f655b4}">
+          <x14:cfRule type="containsText" priority="601" operator="containsText" id="{82251464-571e-4312-a37c-45ab3efdfdbc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13461,7 +13465,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="598" operator="containsText" id="{c0261998-fa7d-4473-a919-6a34c8968583}">
+          <x14:cfRule type="containsText" priority="602" operator="containsText" id="{fb91e405-f92d-49aa-bf4e-34bcc3eb8763}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13479,7 +13483,7 @@
           <xm:sqref>I175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="521" operator="containsText" id="{6f8124b3-22ee-48d1-b2f3-8019df539477}">
+          <x14:cfRule type="containsText" priority="525" operator="containsText" id="{f0786853-a5b2-46a3-9db3-b9c76e598b40}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13494,7 +13498,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="522" operator="containsText" id="{20561496-dd56-440c-9e67-be366f070f14}">
+          <x14:cfRule type="containsText" priority="526" operator="containsText" id="{9479d8ab-dc31-4cb0-a707-6fe7f80e2e7b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13512,7 +13516,7 @@
           <xm:sqref>K175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="573" operator="containsText" id="{5acde14a-7ba3-4a89-9077-558832ab82a0}">
+          <x14:cfRule type="containsText" priority="577" operator="containsText" id="{ca0acf9a-7e6a-4d37-8610-44a32ad17228}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13527,7 +13531,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="574" operator="containsText" id="{11a26de4-6dc3-432e-acf4-b1141acd0b53}">
+          <x14:cfRule type="containsText" priority="578" operator="containsText" id="{ca3c154c-6568-4505-91ee-aca041f928ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13545,7 +13549,7 @@
           <xm:sqref>L175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="575" operator="containsText" id="{12873458-244f-441c-bcee-8700469d67c6}">
+          <x14:cfRule type="containsText" priority="579" operator="containsText" id="{8e87ff89-9b77-4d1c-a199-b7f493058a84}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I176)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13560,7 +13564,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="576" operator="containsText" id="{cf3963f1-217a-410e-ba97-9e0a1cf68271}">
+          <x14:cfRule type="containsText" priority="580" operator="containsText" id="{feac389e-1d0b-4875-9aa6-0a86509efbc6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I176)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13578,7 +13582,7 @@
           <xm:sqref>I176</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="577" operator="containsText" id="{2d3c0079-7853-4a45-94c5-57642702eecd}">
+          <x14:cfRule type="containsText" priority="581" operator="containsText" id="{801365e4-7e7b-447b-bf95-e285d656a795}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I177)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13593,7 +13597,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="578" operator="containsText" id="{dbc20c60-17f0-46c7-85f6-e8b03e15b482}">
+          <x14:cfRule type="containsText" priority="582" operator="containsText" id="{93128d1d-16a8-48ee-8b97-a0b7703b353e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I177)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13611,7 +13615,7 @@
           <xm:sqref>I177</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="607" operator="containsText" id="{129d3073-8dcf-4bb8-bad5-d1e402f209ae}">
+          <x14:cfRule type="containsText" priority="611" operator="containsText" id="{61e2f26b-d03c-460f-9352-9459d894c6f7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I179)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13626,7 +13630,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="608" operator="containsText" id="{5e9d0af4-96b6-4d22-b76c-fe7c93ad754a}">
+          <x14:cfRule type="containsText" priority="612" operator="containsText" id="{ae7a18ff-8bf2-4477-98ed-2257148b6dbb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I179)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13644,7 +13648,7 @@
           <xm:sqref>I179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="615" operator="containsText" id="{e38373a4-0964-4203-b164-bcd0777d694f}">
+          <x14:cfRule type="containsText" priority="619" operator="containsText" id="{3cfd65e8-16cf-4395-aae3-2e61c6a342d2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I180)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13659,7 +13663,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="616" operator="containsText" id="{68957e88-4200-439f-86ce-4082756b21af}">
+          <x14:cfRule type="containsText" priority="620" operator="containsText" id="{3049c8f9-9c62-4679-aacd-516f0b23c6d4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I180)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13677,7 +13681,7 @@
           <xm:sqref>I180</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="585" operator="containsText" id="{b2288fd9-8467-49f1-b75a-174f31695929}">
+          <x14:cfRule type="containsText" priority="589" operator="containsText" id="{522ad13a-9683-4bef-9542-4db88fe9b3ab}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13692,7 +13696,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="586" operator="containsText" id="{dde03191-958c-45fe-bebe-36a6a994aab5}">
+          <x14:cfRule type="containsText" priority="590" operator="containsText" id="{ea232405-791f-4dce-8b87-7244cdb6f9a9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13710,7 +13714,7 @@
           <xm:sqref>I181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="617" operator="containsText" id="{6167bef8-3a5c-42d0-850a-5eb6d3ee96e2}">
+          <x14:cfRule type="containsText" priority="621" operator="containsText" id="{457cb0cd-dc06-4322-aee9-63f18e9f43a9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13725,7 +13729,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="618" operator="containsText" id="{9c376bf8-2c01-489e-8b9c-f4e8e8acebc6}">
+          <x14:cfRule type="containsText" priority="622" operator="containsText" id="{88bd5252-2d38-4dcf-97a1-dfddb64725c5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13743,7 +13747,7 @@
           <xm:sqref>K181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="583" operator="containsText" id="{e830a243-7d61-4032-b6cf-7b7568b7091d}">
+          <x14:cfRule type="containsText" priority="587" operator="containsText" id="{3794af57-ed10-4f79-80cd-ab2750ce88ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13758,7 +13762,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="584" operator="containsText" id="{f3b811de-1704-462f-9bff-9dcf5c8d5727}">
+          <x14:cfRule type="containsText" priority="588" operator="containsText" id="{77268c3e-23a5-429a-91cd-aeede501264c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13776,7 +13780,7 @@
           <xm:sqref>L181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="127" operator="containsText" id="{e5ff24e0-dfe7-48e2-b0a1-baa421455a67}">
+          <x14:cfRule type="containsText" priority="131" operator="containsText" id="{ab27fc92-dbd5-4d48-9fad-c139d70489db}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13791,7 +13795,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="128" operator="containsText" id="{c650b3db-a51b-4b2e-a25c-faf5b0c9a819}">
+          <x14:cfRule type="containsText" priority="132" operator="containsText" id="{22ae9cec-09c8-4599-9ac5-f158a3bd2afa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13809,7 +13813,7 @@
           <xm:sqref>G182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="609" operator="containsText" id="{6fa2d780-8204-4ded-9e4b-c0a01fa12346}">
+          <x14:cfRule type="containsText" priority="613" operator="containsText" id="{ab33aad0-4d57-4511-b8a5-78f6af9ccf37}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13824,7 +13828,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="610" operator="containsText" id="{b49a2c72-2c9f-4925-b078-c07633cd642e}">
+          <x14:cfRule type="containsText" priority="614" operator="containsText" id="{8724bb6a-7f41-408d-8fdb-395c9ad298ef}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13842,7 +13846,7 @@
           <xm:sqref>I182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="587" operator="containsText" id="{e94f60b8-efec-4af3-95a3-4f31070e715f}">
+          <x14:cfRule type="containsText" priority="591" operator="containsText" id="{4ed206cc-d004-4089-9214-57dfd6d1a1cb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I183)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13857,7 +13861,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="588" operator="containsText" id="{a9069e08-8857-4a30-8826-66dc78c5b001}">
+          <x14:cfRule type="containsText" priority="592" operator="containsText" id="{40c02543-4a04-4aa7-8471-b086729073b4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I183)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13875,7 +13879,7 @@
           <xm:sqref>I183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="557" operator="containsText" id="{7b64d8f7-2497-4258-b55f-2a6afcc50f48}">
+          <x14:cfRule type="containsText" priority="561" operator="containsText" id="{9d28a55b-a1b6-4452-aa2b-819263dc3af7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13890,7 +13894,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="558" operator="containsText" id="{3e1fbaf6-07b5-495a-b0bb-46e1edf36598}">
+          <x14:cfRule type="containsText" priority="562" operator="containsText" id="{899e3732-5a12-48f2-ad66-de6ffe8a902c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13908,7 +13912,7 @@
           <xm:sqref>I184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="551" operator="containsText" id="{c8198324-84dc-4614-8283-13c8cf356dbc}">
+          <x14:cfRule type="containsText" priority="555" operator="containsText" id="{9781c74c-667a-4a6e-b88a-e67823e39fb3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13923,7 +13927,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="552" operator="containsText" id="{63ab43a3-8e4b-4de0-8cf5-898845d762dc}">
+          <x14:cfRule type="containsText" priority="556" operator="containsText" id="{606ff761-452b-450a-8566-a5d1cd91d661}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13941,7 +13945,7 @@
           <xm:sqref>L184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="539" operator="containsText" id="{7005a0e2-e77c-4343-8a8b-b0b8e9aefc75}">
+          <x14:cfRule type="containsText" priority="543" operator="containsText" id="{f062e32d-b24d-4720-bb3b-366f5f9655bc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I185)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13956,7 +13960,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="540" operator="containsText" id="{1b6975eb-055f-43a0-b8d2-a79ffeab13e9}">
+          <x14:cfRule type="containsText" priority="544" operator="containsText" id="{141c285d-5c66-4cd8-955d-b949bf738045}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I185)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13974,7 +13978,7 @@
           <xm:sqref>I185</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="537" operator="containsText" id="{4b98acd7-51bd-47f1-b9dd-9754273797f2}">
+          <x14:cfRule type="containsText" priority="541" operator="containsText" id="{27b96349-30b1-4431-ac48-b8524b3ff280}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L185)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13989,7 +13993,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="538" operator="containsText" id="{a7cc4412-4ec0-4283-9f77-0c48b63ca9d4}">
+          <x14:cfRule type="containsText" priority="542" operator="containsText" id="{22937210-f71a-449c-8d14-866bc08f0886}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L185)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14007,7 +14011,7 @@
           <xm:sqref>L185</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="559" operator="containsText" id="{1957ccec-e5aa-40fb-8b02-9f5d9f902caa}">
+          <x14:cfRule type="containsText" priority="563" operator="containsText" id="{3c1149dc-20b4-4ca0-be31-a0ed3c76ea2c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I186)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14022,7 +14026,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="560" operator="containsText" id="{043597c9-e958-48fb-b6a4-139d8b1a46b9}">
+          <x14:cfRule type="containsText" priority="564" operator="containsText" id="{42a632d4-398b-4ef6-a29e-e9a46608eeab}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I186)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14040,7 +14044,7 @@
           <xm:sqref>I186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="549" operator="containsText" id="{1ae7acde-d6f3-4ddf-b1f2-ddae38ed20aa}">
+          <x14:cfRule type="containsText" priority="553" operator="containsText" id="{cb318a82-f4fe-4f63-b197-1156213664d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I188)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14055,7 +14059,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="550" operator="containsText" id="{b8e1a9be-815c-4747-874e-9e77f4c4a147}">
+          <x14:cfRule type="containsText" priority="554" operator="containsText" id="{a1b96868-aada-4b69-a711-478fea43ae4e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I188)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14073,7 +14077,7 @@
           <xm:sqref>I188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="547" operator="containsText" id="{027bc55f-3da6-4626-b3fd-cc567ab6ce0b}">
+          <x14:cfRule type="containsText" priority="551" operator="containsText" id="{003cf212-ed62-4e63-9217-dc2050647a92}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14088,7 +14092,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="548" operator="containsText" id="{3d91710f-b580-4e5d-aba5-a87e15593fc3}">
+          <x14:cfRule type="containsText" priority="552" operator="containsText" id="{4ebef25b-6e52-42c8-9fa1-b27939d25ea7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14106,7 +14110,7 @@
           <xm:sqref>I189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="193" operator="containsText" id="{7a4928ed-89eb-4b78-80fb-df6e4b2210f7}">
+          <x14:cfRule type="containsText" priority="197" operator="containsText" id="{8168bdaa-4699-460a-b87e-29a4797137bd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14121,7 +14125,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="194" operator="containsText" id="{b3b1add8-a07a-4383-9abe-e847bf1bde65}">
+          <x14:cfRule type="containsText" priority="198" operator="containsText" id="{85ea8c9f-fcd5-473b-860a-40430b79c714}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14139,7 +14143,7 @@
           <xm:sqref>K189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="525" operator="containsText" id="{9e4ead94-07f4-4a95-84fa-517e6ab40415}">
+          <x14:cfRule type="containsText" priority="529" operator="containsText" id="{c30f68c7-955f-492d-9dcb-d3912b05d575}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14154,7 +14158,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="526" operator="containsText" id="{cc4270c0-a6db-4f23-ab38-659e7ffa3996}">
+          <x14:cfRule type="containsText" priority="530" operator="containsText" id="{fcc84951-6fa7-451d-bb51-f255d59f022c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14172,7 +14176,7 @@
           <xm:sqref>L189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="523" operator="containsText" id="{118f544c-0701-43e0-94f3-c60158fb5f6f}">
+          <x14:cfRule type="containsText" priority="527" operator="containsText" id="{8e706633-1e2f-4310-bd83-04d29591f90d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I190)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14187,7 +14191,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="524" operator="containsText" id="{a2a19ea8-29fd-405c-be3d-7267055635bc}">
+          <x14:cfRule type="containsText" priority="528" operator="containsText" id="{b55ad885-00b8-4f97-90ee-09447736f865}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I190)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14205,7 +14209,7 @@
           <xm:sqref>I190</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="535" operator="containsText" id="{f75fbca1-ffcc-460c-b5ec-493404eff576}">
+          <x14:cfRule type="containsText" priority="539" operator="containsText" id="{f2ccd662-db5e-4a0b-99ac-dfbaed78c1d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I191)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14220,7 +14224,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="536" operator="containsText" id="{82210061-a00a-49db-95cd-ba9a97be070a}">
+          <x14:cfRule type="containsText" priority="540" operator="containsText" id="{33136aed-380a-4cb3-bd4d-884e906e3653}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I191)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14238,7 +14242,7 @@
           <xm:sqref>I191</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="553" operator="containsText" id="{ccf1f531-4c36-41f8-b0ca-b52dbb597a5f}">
+          <x14:cfRule type="containsText" priority="557" operator="containsText" id="{ead7313b-2684-4730-b1b5-787dec4ccdff}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I193)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14253,7 +14257,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="554" operator="containsText" id="{3f141ab7-d808-4bf6-aa01-f842d7e4548d}">
+          <x14:cfRule type="containsText" priority="558" operator="containsText" id="{a1a09dee-7185-468a-8894-90acf469ed54}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I193)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14271,7 +14275,7 @@
           <xm:sqref>I193</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="561" operator="containsText" id="{9c5e0f2d-8fc6-40da-b6ab-deb6b3825003}">
+          <x14:cfRule type="containsText" priority="565" operator="containsText" id="{0dcec330-5d3f-4d45-b92c-e83da4e59427}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I194)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14286,7 +14290,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="562" operator="containsText" id="{7e6cc048-4ae9-4ab2-be46-7efb55d8e886}">
+          <x14:cfRule type="containsText" priority="566" operator="containsText" id="{a6b78553-3860-4bd6-ad76-35ad311417e4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I194)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14304,7 +14308,7 @@
           <xm:sqref>I194</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="529" operator="containsText" id="{f6b9c084-adfc-46f3-9cde-57ce086faeec}">
+          <x14:cfRule type="containsText" priority="533" operator="containsText" id="{6d99bca6-0b8a-434c-a89f-280b870e1dcb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14319,7 +14323,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="530" operator="containsText" id="{2fa63837-bc88-4e33-aa9f-0e0cdc899529}">
+          <x14:cfRule type="containsText" priority="534" operator="containsText" id="{2cc7fd00-7e87-47e0-bdef-94cae5942981}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14337,7 +14341,7 @@
           <xm:sqref>I195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="191" operator="containsText" id="{77c2b421-9811-4e32-8eba-207ad645d432}">
+          <x14:cfRule type="containsText" priority="195" operator="containsText" id="{1c78a6c4-74ca-40df-95f1-c9de4ccb7b32}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14352,7 +14356,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="192" operator="containsText" id="{4d83edf8-1cf2-4b95-93a8-dadfa0968503}">
+          <x14:cfRule type="containsText" priority="196" operator="containsText" id="{6c817f29-f7db-49ed-b100-cb4513d57c48}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14370,7 +14374,7 @@
           <xm:sqref>K195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="527" operator="containsText" id="{795a3eac-7422-494c-8dae-89d00abfeed5}">
+          <x14:cfRule type="containsText" priority="531" operator="containsText" id="{d0473a1f-8bca-4b0a-8825-41f820bc5e37}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14385,7 +14389,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="528" operator="containsText" id="{2d8c86f9-f199-46d4-8b7d-9330696c1275}">
+          <x14:cfRule type="containsText" priority="532" operator="containsText" id="{1954573d-46f4-4bf1-a314-cfe9f0903b56}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14403,7 +14407,7 @@
           <xm:sqref>L195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="123" operator="containsText" id="{5787d751-b7ea-4d1a-a6b4-96add8a2e5f7}">
+          <x14:cfRule type="containsText" priority="127" operator="containsText" id="{b7475e8d-e37c-4dfd-94e5-a52ac6efd36a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14418,7 +14422,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="124" operator="containsText" id="{720d86a5-d107-494c-9680-5ddebb3691d9}">
+          <x14:cfRule type="containsText" priority="128" operator="containsText" id="{92742e0a-c0e7-467d-822b-84800b46d0ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14436,7 +14440,7 @@
           <xm:sqref>G196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="555" operator="containsText" id="{bc395d95-b640-47e1-8feb-8ed2455d0e2d}">
+          <x14:cfRule type="containsText" priority="559" operator="containsText" id="{217ab5ca-e0d4-433f-a1a4-632e473b0c06}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14451,7 +14455,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="556" operator="containsText" id="{432e3e95-a210-4b84-9233-3e54fa7f0696}">
+          <x14:cfRule type="containsText" priority="560" operator="containsText" id="{48d5e071-18cb-4e33-a06f-49cee11d6c06}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14469,7 +14473,7 @@
           <xm:sqref>I196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="545" operator="containsText" id="{631ffaeb-e9d1-416d-a1e2-c8d80b777c35}">
+          <x14:cfRule type="containsText" priority="549" operator="containsText" id="{5db8d270-f975-4ea9-8835-1b2f2cf7f885}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I197)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14484,7 +14488,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="546" operator="containsText" id="{4def7f2e-2028-4f47-9958-f1058d3d6798}">
+          <x14:cfRule type="containsText" priority="550" operator="containsText" id="{2c5b27f9-c5ac-4e41-a271-d7b28a1cfe3c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I197)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14502,7 +14506,7 @@
           <xm:sqref>I197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="503" operator="containsText" id="{5bf1f2cc-79e4-4a00-afc5-1065754b8810}">
+          <x14:cfRule type="containsText" priority="507" operator="containsText" id="{f5f56b7a-4196-4d7c-97b9-3e752ced3ab2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14517,7 +14521,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="504" operator="containsText" id="{27530d66-33ff-4274-9ffc-c17c6f70b5c2}">
+          <x14:cfRule type="containsText" priority="508" operator="containsText" id="{c584374c-6964-4f93-807b-9a516de15c1a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14535,7 +14539,7 @@
           <xm:sqref>I198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="497" operator="containsText" id="{0cfe1cc5-9b88-4448-ac1f-443bcf3145cb}">
+          <x14:cfRule type="containsText" priority="501" operator="containsText" id="{9f64e0be-d59d-4eca-ad6b-99543191e874}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14550,7 +14554,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="498" operator="containsText" id="{40468cd2-8019-476d-8111-d207974def82}">
+          <x14:cfRule type="containsText" priority="502" operator="containsText" id="{4c772447-43d1-474e-bd8b-e9d2f27da5d4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14568,7 +14572,7 @@
           <xm:sqref>L198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="489" operator="containsText" id="{1aecd6f7-fc87-49c8-97bc-b11fe106363a}">
+          <x14:cfRule type="containsText" priority="493" operator="containsText" id="{6e6ca853-a125-409a-a16e-7f22c2234b72}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14583,7 +14587,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="490" operator="containsText" id="{f2a25bc8-1573-46b2-a78e-3600a68e4fe5}">
+          <x14:cfRule type="containsText" priority="494" operator="containsText" id="{3d9a75b9-48c2-47f9-80d2-d4e563306c2b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14601,7 +14605,7 @@
           <xm:sqref>I199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="189" operator="containsText" id="{da99c879-3da9-4c0c-83fc-3dc055c7c450}">
+          <x14:cfRule type="containsText" priority="193" operator="containsText" id="{5458daed-cb40-4ff1-914f-9b0f02af789d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14616,7 +14620,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="190" operator="containsText" id="{c06a1978-edab-4f4c-82c0-0412bfd46b89}">
+          <x14:cfRule type="containsText" priority="194" operator="containsText" id="{23ad668e-2c32-431c-a6e7-2de3beac4091}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14634,7 +14638,7 @@
           <xm:sqref>K199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="469" operator="containsText" id="{5df59a46-f842-43a1-b3c9-6dea689c8dfb}">
+          <x14:cfRule type="containsText" priority="473" operator="containsText" id="{65dcbbf2-9ba5-4141-a343-d839d752c5b4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14649,7 +14653,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="470" operator="containsText" id="{18da2eb0-0621-403a-911b-17aa5788b580}">
+          <x14:cfRule type="containsText" priority="474" operator="containsText" id="{b5caa2a0-38c4-486b-9dc0-e02d6af474f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14667,7 +14671,7 @@
           <xm:sqref>L199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="505" operator="containsText" id="{679f90b7-1d51-4218-adce-65ba0cc8615c}">
+          <x14:cfRule type="containsText" priority="509" operator="containsText" id="{5107fdc3-f60d-4597-8c27-c85ef4e103d7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I200)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14682,7 +14686,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="506" operator="containsText" id="{ac7ae4ac-bd9e-409d-8504-3be4ddf63874}">
+          <x14:cfRule type="containsText" priority="510" operator="containsText" id="{dc117160-6f6a-40e3-9ac1-1cc220535966}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I200)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14700,7 +14704,7 @@
           <xm:sqref>I200</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="495" operator="containsText" id="{932e9867-085f-412c-87a4-cf8940e361fb}">
+          <x14:cfRule type="containsText" priority="499" operator="containsText" id="{41552385-7d7d-45d0-87e1-848c6d8f1466}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I202)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14715,7 +14719,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="496" operator="containsText" id="{37d06be6-2185-4a6b-996c-2bc187e6a9e4}">
+          <x14:cfRule type="containsText" priority="500" operator="containsText" id="{b297b497-8da2-4182-ade5-029690d49d18}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I202)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14733,7 +14737,7 @@
           <xm:sqref>I202</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="493" operator="containsText" id="{ef30578d-d248-4f40-b221-cfeb57a532b4}">
+          <x14:cfRule type="containsText" priority="497" operator="containsText" id="{63234021-04db-48da-bce7-f96e1d0ead00}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14748,7 +14752,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="494" operator="containsText" id="{86d5bd8a-a71d-467e-b982-0ecc1718f314}">
+          <x14:cfRule type="containsText" priority="498" operator="containsText" id="{a84c91eb-6731-48ad-8c33-a71891a2cacc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14766,7 +14770,7 @@
           <xm:sqref>I203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="187" operator="containsText" id="{1dd42326-8c09-4efb-808c-1032d9e3f732}">
+          <x14:cfRule type="containsText" priority="191" operator="containsText" id="{228045c3-7a56-4a60-97a1-f971ce93fea7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14781,7 +14785,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="188" operator="containsText" id="{1e83a46a-a790-406a-83f6-228386646a46}">
+          <x14:cfRule type="containsText" priority="192" operator="containsText" id="{e00085e0-e97f-47a0-954e-ea4f593a2e1e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14799,7 +14803,7 @@
           <xm:sqref>K203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="475" operator="containsText" id="{3417420a-395d-4208-a0d8-5e68e0640fcb}">
+          <x14:cfRule type="containsText" priority="479" operator="containsText" id="{f55d9101-309f-4ac1-8ea7-51c8dcf51cd6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14814,7 +14818,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="476" operator="containsText" id="{b357eb25-9243-4ac6-9789-96b45cf2d78a}">
+          <x14:cfRule type="containsText" priority="480" operator="containsText" id="{7f8fb459-3144-4da2-ba18-31543de4e9e2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14832,7 +14836,7 @@
           <xm:sqref>L203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="477" operator="containsText" id="{e8edc385-966a-4dce-9b99-9ffa5b3d2d9c}">
+          <x14:cfRule type="containsText" priority="481" operator="containsText" id="{7e102ad1-d861-4666-8763-a3178b38c1e3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I204)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14847,7 +14851,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="478" operator="containsText" id="{7fd07f66-73c6-4512-b285-03242592d154}">
+          <x14:cfRule type="containsText" priority="482" operator="containsText" id="{e7937902-cb63-427d-9489-cd1a79690628}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I204)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14865,7 +14869,7 @@
           <xm:sqref>I204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="467" operator="containsText" id="{3b12be5d-be1d-4bb1-9d0c-a955c56e9218}">
+          <x14:cfRule type="containsText" priority="471" operator="containsText" id="{30f396ff-b0dc-44f2-a996-9efff5221695}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I205)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14880,7 +14884,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="468" operator="containsText" id="{b3809bfe-3a10-410c-b7d2-c7b4cadfcdae}">
+          <x14:cfRule type="containsText" priority="472" operator="containsText" id="{b7730a22-96cf-4a68-8670-ecfa2b0448ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I205)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14898,7 +14902,7 @@
           <xm:sqref>I205</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="499" operator="containsText" id="{4823f996-1e63-4510-9aae-b21e4a32aa6f}">
+          <x14:cfRule type="containsText" priority="503" operator="containsText" id="{d2565371-de26-402c-a0d7-9bbfa07f872d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I207)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14913,7 +14917,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="500" operator="containsText" id="{dd70745d-a71f-4e5d-85e4-1f7228096b77}">
+          <x14:cfRule type="containsText" priority="504" operator="containsText" id="{9420980b-51da-4d05-b16a-9dae03be8e28}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I207)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14931,7 +14935,7 @@
           <xm:sqref>I207</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="507" operator="containsText" id="{2e93e078-af04-444a-9c98-01341a61ead1}">
+          <x14:cfRule type="containsText" priority="511" operator="containsText" id="{44808e3c-9c96-4698-b205-26d26e9eaab2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I208)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14946,7 +14950,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="508" operator="containsText" id="{ce386302-1e8d-4b5d-ba1d-630d168cec8e}">
+          <x14:cfRule type="containsText" priority="512" operator="containsText" id="{e75c4ed9-45de-4c4d-86b6-3a6646ef9b78}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I208)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14964,7 +14968,7 @@
           <xm:sqref>I208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="473" operator="containsText" id="{5a31be16-8217-4b9f-8a53-85599a2f6e75}">
+          <x14:cfRule type="containsText" priority="477" operator="containsText" id="{adf8825e-3058-464a-aabd-c40a51f5db39}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14979,7 +14983,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="474" operator="containsText" id="{e3148551-f94c-4c36-9f59-42565f3dde3e}">
+          <x14:cfRule type="containsText" priority="478" operator="containsText" id="{4f395a5b-f6a9-4dd1-83cc-631a96c311ab}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14997,7 +15001,7 @@
           <xm:sqref>I209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="185" operator="containsText" id="{6068834b-2be2-4b7b-8ab2-5e1f12d175bb}">
+          <x14:cfRule type="containsText" priority="189" operator="containsText" id="{77797935-38c4-4ffd-91cb-8ee9531569e2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15012,7 +15016,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="186" operator="containsText" id="{e16d7c47-606c-4ee3-838d-d88e20e3d4de}">
+          <x14:cfRule type="containsText" priority="190" operator="containsText" id="{6dd76db5-6bcc-4f5d-bf1e-c13ae79e01e0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15030,7 +15034,7 @@
           <xm:sqref>K209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="471" operator="containsText" id="{ac1ca2b1-2ed0-4995-835f-37f0c6eb72eb}">
+          <x14:cfRule type="containsText" priority="475" operator="containsText" id="{030f550a-147e-40ab-b9b7-fe41c009ae18}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15045,7 +15049,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="472" operator="containsText" id="{e87825d8-119f-4512-97cf-6f6f5fed9596}">
+          <x14:cfRule type="containsText" priority="476" operator="containsText" id="{5be02b10-caf1-4e40-82be-c5689eb4f0e8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15063,7 +15067,7 @@
           <xm:sqref>L209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="117" operator="containsText" id="{6b53e1f8-218a-4227-9ce4-9699afc9b479}">
+          <x14:cfRule type="containsText" priority="121" operator="containsText" id="{62276a20-eac1-4a65-b40d-e2020e6d354b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15078,7 +15082,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="118" operator="containsText" id="{67bd23fb-4cc5-44bc-bc4c-eaa3a4a40f61}">
+          <x14:cfRule type="containsText" priority="122" operator="containsText" id="{45a80e83-f5fd-4ace-8051-0c958a0b9647}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15096,7 +15100,7 @@
           <xm:sqref>G210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="501" operator="containsText" id="{178e0381-1fa5-4a84-a0bc-35c26f5ba087}">
+          <x14:cfRule type="containsText" priority="505" operator="containsText" id="{3ce27e2a-d5bd-4265-9227-de4bf1e0ade6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15111,7 +15115,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="502" operator="containsText" id="{197da257-15c4-4996-9d21-a004da2b878a}">
+          <x14:cfRule type="containsText" priority="506" operator="containsText" id="{7861c9fb-570b-4e0e-9b6b-3cfe24a6364b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15129,7 +15133,7 @@
           <xm:sqref>I210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="121" operator="containsText" id="{e785254a-a441-4113-ae00-0f7af4ec5ecb}">
+          <x14:cfRule type="containsText" priority="125" operator="containsText" id="{9055d412-4b5c-4912-b25e-5455ba94b03b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15144,7 +15148,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="122" operator="containsText" id="{68981bfa-1209-4d31-9862-5c51b6a9c36e}">
+          <x14:cfRule type="containsText" priority="126" operator="containsText" id="{5c574cf1-8638-4567-8f4b-9010923a07a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15162,7 +15166,7 @@
           <xm:sqref>G211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="491" operator="containsText" id="{ffd492c6-bec3-441a-ab75-9c380a553ee4}">
+          <x14:cfRule type="containsText" priority="495" operator="containsText" id="{5e3d1c88-3b9a-4876-8393-36f64ec5e175}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15177,7 +15181,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="492" operator="containsText" id="{73bbafe9-490d-4cea-a273-57c387ade76f}">
+          <x14:cfRule type="containsText" priority="496" operator="containsText" id="{ecf76981-ff9f-488e-8a5d-885d4665399f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15195,7 +15199,7 @@
           <xm:sqref>I211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="449" operator="containsText" id="{e96dcc22-4fc1-4f83-817d-2c6b6006c93d}">
+          <x14:cfRule type="containsText" priority="453" operator="containsText" id="{342fd05e-8e53-469b-a5b7-993ae176cec8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15210,7 +15214,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="450" operator="containsText" id="{46cc8d57-7a3a-48de-9265-45b1632ad453}">
+          <x14:cfRule type="containsText" priority="454" operator="containsText" id="{4d53f335-0e88-4f89-91f7-e6b17f20635a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15228,7 +15232,7 @@
           <xm:sqref>I212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="443" operator="containsText" id="{73ddeb88-c7fc-44cd-a5ce-80f0ed0642df}">
+          <x14:cfRule type="containsText" priority="447" operator="containsText" id="{6ef08daa-5646-415d-b59e-e9d80c7d4207}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15243,7 +15247,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="444" operator="containsText" id="{e987f832-cc8b-4c61-9f34-fa48eef25d14}">
+          <x14:cfRule type="containsText" priority="448" operator="containsText" id="{b1001647-5ce9-4686-85c6-a3c8c8f031a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15261,7 +15265,7 @@
           <xm:sqref>L212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="435" operator="containsText" id="{0139c81f-3a9a-4e00-a56d-a96b0fc9cb1a}">
+          <x14:cfRule type="containsText" priority="439" operator="containsText" id="{322c6696-a9c2-4252-8acf-73a52fa5ea9f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I213)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15276,7 +15280,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="436" operator="containsText" id="{df496a2d-dd1a-4010-b631-82638bbc4bb0}">
+          <x14:cfRule type="containsText" priority="440" operator="containsText" id="{316cb8a9-c971-4476-870e-606ec8609607}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I213)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15294,7 +15298,7 @@
           <xm:sqref>I213</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="425" operator="containsText" id="{b4e7fb56-592c-47c4-92a7-810fb37e383e}">
+          <x14:cfRule type="containsText" priority="429" operator="containsText" id="{a92b5d18-2ac2-4527-9687-d36b12c1e53e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L213)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15309,7 +15313,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="426" operator="containsText" id="{3ce801f4-15ba-4c5a-82e5-ec2901cef202}">
+          <x14:cfRule type="containsText" priority="430" operator="containsText" id="{19270182-523b-46d3-bc9f-94be3b95e8eb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L213)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15327,7 +15331,7 @@
           <xm:sqref>L213</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="451" operator="containsText" id="{d6122c42-0662-45a8-b042-4ecc469677c3}">
+          <x14:cfRule type="containsText" priority="455" operator="containsText" id="{d74bfda3-90d3-4761-8857-592e1ea10d79}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I214)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15342,7 +15346,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="452" operator="containsText" id="{8e2aa637-b393-4df0-b58f-3f79998a6f1d}">
+          <x14:cfRule type="containsText" priority="456" operator="containsText" id="{ada7bd54-7b24-4dc6-8774-94f529fcf0bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I214)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15360,7 +15364,7 @@
           <xm:sqref>I214</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="441" operator="containsText" id="{3b9537b9-fb75-4b22-afa9-4fdd0a7a08ff}">
+          <x14:cfRule type="containsText" priority="445" operator="containsText" id="{a15a7e82-fa85-46b9-ae60-7ce6b45a0d73}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I216)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15375,7 +15379,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="442" operator="containsText" id="{8621288a-f3a2-43c5-914e-15f15939392a}">
+          <x14:cfRule type="containsText" priority="446" operator="containsText" id="{3e1c6db6-5c2c-4bc6-b4c9-0407a8fa17bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I216)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15393,7 +15397,7 @@
           <xm:sqref>I216</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="415" operator="containsText" id="{4d2833b3-56bd-456d-98dc-e8a905dd84ac}">
+          <x14:cfRule type="containsText" priority="419" operator="containsText" id="{32727733-b887-445f-bed2-73c7b92aab5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15408,7 +15412,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="416" operator="containsText" id="{2a2d81ae-d17c-45b8-b837-463b40256b17}">
+          <x14:cfRule type="containsText" priority="420" operator="containsText" id="{b3bb4ee2-e408-41ab-b508-cf87da67f88d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15426,7 +15430,7 @@
           <xm:sqref>I217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="183" operator="containsText" id="{6a183438-23a1-42ae-9df5-44e22b9f9e8c}">
+          <x14:cfRule type="containsText" priority="187" operator="containsText" id="{0d3b0b91-2759-441a-9adf-36e3117e4615}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15441,7 +15445,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="184" operator="containsText" id="{3fb0804b-f474-460a-ba65-118a3bf1ab83}">
+          <x14:cfRule type="containsText" priority="188" operator="containsText" id="{c9994dbb-80f4-4741-b70b-a022512cc81e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15459,7 +15463,7 @@
           <xm:sqref>K217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="417" operator="containsText" id="{b39b7d38-77b1-4f16-8e7e-df497974aebb}">
+          <x14:cfRule type="containsText" priority="421" operator="containsText" id="{b5cbd911-1a8f-4246-8128-bd1293ab3b48}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15474,7 +15478,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="418" operator="containsText" id="{b10034ea-1567-4332-afe7-fdeb91c0b2ec}">
+          <x14:cfRule type="containsText" priority="422" operator="containsText" id="{4222ba67-4eeb-4a71-8c2a-847de1c5b758}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15492,7 +15496,7 @@
           <xm:sqref>L217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="433" operator="containsText" id="{16f19a54-ee3c-443e-8c7f-785acdd68ee5}">
+          <x14:cfRule type="containsText" priority="437" operator="containsText" id="{02443ff4-cdb7-4d62-bb56-950c4cf10117}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I218)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15507,7 +15511,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="434" operator="containsText" id="{d894e1ca-eefe-47dd-9002-62f7fe9913b8}">
+          <x14:cfRule type="containsText" priority="438" operator="containsText" id="{b3cf0c21-8d90-4cad-a5df-c96283f2cb16}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I218)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15525,7 +15529,7 @@
           <xm:sqref>I218</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="369" operator="containsText" id="{7d251a8e-d1c5-4abb-b3e6-389605abd0e7}">
+          <x14:cfRule type="containsText" priority="373" operator="containsText" id="{a0840775-cd0e-44bd-b5ca-ad51175bc576}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I219)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15540,7 +15544,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="370" operator="containsText" id="{fb7e22f3-f9c2-4c88-9072-36548a1ab634}">
+          <x14:cfRule type="containsText" priority="374" operator="containsText" id="{d7cc6cd0-447d-4488-bea2-6e45a6ba0d63}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I219)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15558,7 +15562,7 @@
           <xm:sqref>I219</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="445" operator="containsText" id="{3cefa8e6-c1a5-4daf-b255-8f100bcc8257}">
+          <x14:cfRule type="containsText" priority="449" operator="containsText" id="{0a09f3d3-2ec0-475d-bb00-ba2083272902}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I221)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15573,7 +15577,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="446" operator="containsText" id="{93724007-de34-4ff2-ba68-0b5f263d7ac3}">
+          <x14:cfRule type="containsText" priority="450" operator="containsText" id="{9b46b73f-c28c-4a31-8dfc-83d74df92f10}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I221)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15591,7 +15595,7 @@
           <xm:sqref>I221</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="453" operator="containsText" id="{8c48efb4-d061-462c-8292-26f1d619f4fa}">
+          <x14:cfRule type="containsText" priority="457" operator="containsText" id="{6a252371-09c6-49af-83ff-7224ce735c69}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I222)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15606,7 +15610,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="454" operator="containsText" id="{62bedbdd-f4b2-4c57-83cd-cedb12d599af}">
+          <x14:cfRule type="containsText" priority="458" operator="containsText" id="{3ad56b3e-2f92-465d-8b9a-4a7fbb8d8104}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I222)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15624,7 +15628,7 @@
           <xm:sqref>I222</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="421" operator="containsText" id="{7e67d8b7-b96a-4a79-a23c-ca26df62c891}">
+          <x14:cfRule type="containsText" priority="425" operator="containsText" id="{3e9ad81b-e0f4-4450-8d12-4a93e40ab523}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15639,7 +15643,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="422" operator="containsText" id="{42e8e714-1764-4e6a-a8e8-c2656ed9e7f5}">
+          <x14:cfRule type="containsText" priority="426" operator="containsText" id="{ae10160c-5a1c-46e8-bffd-ca29ff857d01}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15657,7 +15661,7 @@
           <xm:sqref>I223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="181" operator="containsText" id="{06bf5eac-843a-49ca-ac56-4c8c4b38f160}">
+          <x14:cfRule type="containsText" priority="185" operator="containsText" id="{09c51489-9a24-41e3-a8a3-a5e2d4cdbdda}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15672,7 +15676,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="182" operator="containsText" id="{55bb11c0-599f-4e15-a8c6-2d1a8d7795c3}">
+          <x14:cfRule type="containsText" priority="186" operator="containsText" id="{a0a091ef-806e-4ac0-80cd-2d197e746b92}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15690,7 +15694,7 @@
           <xm:sqref>K223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="419" operator="containsText" id="{5b5e9c4f-2c11-4c24-b5e8-81968ff45c3f}">
+          <x14:cfRule type="containsText" priority="423" operator="containsText" id="{7d1b0d46-215d-4f0a-84d7-c4334378b794}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15705,7 +15709,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="420" operator="containsText" id="{e54c92ad-d764-488c-99b9-9ecabdbc9d43}">
+          <x14:cfRule type="containsText" priority="424" operator="containsText" id="{1b84e5e1-5fec-4680-89b3-04691983efc4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15723,7 +15727,7 @@
           <xm:sqref>L223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{1559ac24-d7a5-45ae-9252-c78c79bd8ad9}">
+          <x14:cfRule type="containsText" priority="115" operator="containsText" id="{9edf96bd-1f85-4bfb-90ee-92523ca3db12}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15738,7 +15742,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="112" operator="containsText" id="{bab70201-a86f-4d65-a767-0ebec42f40f3}">
+          <x14:cfRule type="containsText" priority="116" operator="containsText" id="{54f172fc-7d9a-43a4-b4f2-b2f8e094f339}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15756,7 +15760,7 @@
           <xm:sqref>G224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="447" operator="containsText" id="{4efdd1a7-15f3-42d4-945b-a6b7c85d424f}">
+          <x14:cfRule type="containsText" priority="451" operator="containsText" id="{ce52a766-ec74-4db0-ba9c-c81b12962345}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15771,7 +15775,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="448" operator="containsText" id="{3c8453e5-ce65-4587-b41f-bd52daafefc1}">
+          <x14:cfRule type="containsText" priority="452" operator="containsText" id="{ea994c35-b909-4809-a8a9-93ad6d1902e0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15789,7 +15793,7 @@
           <xm:sqref>I224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="115" operator="containsText" id="{7a938e19-59fa-4276-bb90-3662a6df671e}">
+          <x14:cfRule type="containsText" priority="119" operator="containsText" id="{741a0013-7235-40c7-b842-8967b4e6a74b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15804,7 +15808,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="116" operator="containsText" id="{12c89d81-b3a4-4840-8b73-9fa40e75d1a9}">
+          <x14:cfRule type="containsText" priority="120" operator="containsText" id="{afc6c2f1-63f1-40b8-bbc7-c5030ef35f75}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15822,7 +15826,7 @@
           <xm:sqref>G225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="437" operator="containsText" id="{dbee362e-18fe-47e8-b36c-5cc6ff9bee68}">
+          <x14:cfRule type="containsText" priority="441" operator="containsText" id="{c2fc2abb-1c19-4b97-b5a4-fbbcf0140c6c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15837,7 +15841,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="438" operator="containsText" id="{297167b6-788b-4aa2-8c32-db4a811793fb}">
+          <x14:cfRule type="containsText" priority="442" operator="containsText" id="{f12d1f36-2ca6-4070-a023-662468c8d10f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15855,7 +15859,7 @@
           <xm:sqref>I225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="391" operator="containsText" id="{a8d790e2-783f-4653-9b4b-bc4a5eec22f2}">
+          <x14:cfRule type="containsText" priority="395" operator="containsText" id="{67f46371-5c4f-4d71-9f03-a98402f53531}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15870,7 +15874,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="392" operator="containsText" id="{1941340b-8951-414f-b512-cfb62a04b396}">
+          <x14:cfRule type="containsText" priority="396" operator="containsText" id="{04ed9e8a-2faf-454d-8bbf-085d98318635}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15888,7 +15892,7 @@
           <xm:sqref>L226</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="385" operator="containsText" id="{7148199b-bed7-4438-933e-304b960eb396}">
+          <x14:cfRule type="containsText" priority="389" operator="containsText" id="{5355b66b-5de9-45ea-a91b-1f6ccfbc2c3d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I227)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15903,7 +15907,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="386" operator="containsText" id="{95db8117-a0d6-4498-8c36-cbed278e8479}">
+          <x14:cfRule type="containsText" priority="390" operator="containsText" id="{0127f0a8-a361-450c-9b0c-4f662fca3082}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I227)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15921,7 +15925,7 @@
           <xm:sqref>I227</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="381" operator="containsText" id="{d7fbcd3b-2496-46b0-b5aa-84d18db29a21}">
+          <x14:cfRule type="containsText" priority="385" operator="containsText" id="{0ebefbdb-4fa0-444a-8b6f-73b2ba8ed63c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L227)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15936,7 +15940,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="382" operator="containsText" id="{d7bafb76-fdbf-4db2-b259-ae6f880b17b1}">
+          <x14:cfRule type="containsText" priority="386" operator="containsText" id="{214601d3-f0b6-45f6-8fb9-f73d279996a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L227)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15954,7 +15958,7 @@
           <xm:sqref>L227</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="399" operator="containsText" id="{c5f0df15-2f49-4be5-90b2-eb811ddbf62c}">
+          <x14:cfRule type="containsText" priority="403" operator="containsText" id="{f255b9d9-9c07-4efa-ad1a-36a28c2b1cce}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I228)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15969,7 +15973,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="400" operator="containsText" id="{f7183582-7247-4009-afd0-e517f423a2fa}">
+          <x14:cfRule type="containsText" priority="404" operator="containsText" id="{57010cd6-9820-472a-b0f8-c4592b95da0c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I228)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15987,7 +15991,7 @@
           <xm:sqref>I228</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="363" operator="containsText" id="{a82d3358-ff8c-4c48-8b07-6eb2141560be}">
+          <x14:cfRule type="containsText" priority="367" operator="containsText" id="{0de76176-2d3f-4c8c-9d36-691500aa7b71}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I229)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16002,7 +16006,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="364" operator="containsText" id="{7fca8df9-8cdf-4258-b8c0-27a6b9f91675}">
+          <x14:cfRule type="containsText" priority="368" operator="containsText" id="{7ea20c5c-984f-4f19-b490-d5aab365f240}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I229)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16020,7 +16024,7 @@
           <xm:sqref>I229</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="389" operator="containsText" id="{04778371-8e3a-4b0b-912b-4e7ef8bc952c}">
+          <x14:cfRule type="containsText" priority="393" operator="containsText" id="{a55dc327-9408-4a6a-b062-a11b4773b20d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I230)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16035,7 +16039,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="390" operator="containsText" id="{904e75f2-576b-4b58-81b0-404a243fd0b7}">
+          <x14:cfRule type="containsText" priority="394" operator="containsText" id="{741f13be-7fc2-4630-b9b7-20c844ef6587}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I230)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16053,7 +16057,7 @@
           <xm:sqref>I230</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="371" operator="containsText" id="{7fdf23b1-5140-41fb-8f6d-17e97b529803}">
+          <x14:cfRule type="containsText" priority="375" operator="containsText" id="{c3e41b6c-40d3-40be-a38b-e46a740f66fb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16068,7 +16072,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="372" operator="containsText" id="{2d86d121-a978-4943-a09e-107cbed1b54f}">
+          <x14:cfRule type="containsText" priority="376" operator="containsText" id="{7b07cff6-2442-40d9-9f5b-1833d6ab6973}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16086,7 +16090,7 @@
           <xm:sqref>I231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="179" operator="containsText" id="{35f6a0b5-875b-466e-85fd-31d9130c9b5b}">
+          <x14:cfRule type="containsText" priority="183" operator="containsText" id="{6a4790ae-7fe0-4a74-8053-ae2c35319f8e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16101,7 +16105,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="180" operator="containsText" id="{8c9eba4c-18fc-4eb6-ab32-c4669c42868c}">
+          <x14:cfRule type="containsText" priority="184" operator="containsText" id="{62a2688b-3b45-4f0e-8b50-d7704927c52b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16119,7 +16123,7 @@
           <xm:sqref>K231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="361" operator="containsText" id="{170d5c79-e2d1-4922-9f83-bf2022bb6ea3}">
+          <x14:cfRule type="containsText" priority="365" operator="containsText" id="{78e32408-668f-40d8-98c6-64d481b96190}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16134,7 +16138,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="362" operator="containsText" id="{8273091a-78e4-4b98-bb57-64abc366a67d}">
+          <x14:cfRule type="containsText" priority="366" operator="containsText" id="{fa8a355a-c972-4d2b-931c-490a1d4d6aaf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16152,7 +16156,7 @@
           <xm:sqref>L231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="383" operator="containsText" id="{209af09c-4806-4d03-bbc4-4c19b79eb5f9}">
+          <x14:cfRule type="containsText" priority="387" operator="containsText" id="{8a1d93ed-eb0f-40ad-8cda-6db4e08b803e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I232)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16167,7 +16171,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="384" operator="containsText" id="{059ebd71-f3f6-4125-a3cc-ce505854be24}">
+          <x14:cfRule type="containsText" priority="388" operator="containsText" id="{b32768b5-78c6-4d0e-95c8-448f468cc773}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I232)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16185,7 +16189,7 @@
           <xm:sqref>I232</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="359" operator="containsText" id="{ef7928dd-ca0c-4924-9805-aa7fc46fc7f3}">
+          <x14:cfRule type="containsText" priority="363" operator="containsText" id="{c4b7bc3a-1696-49cd-bfe0-ae5a75280af7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I233)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16200,7 +16204,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="360" operator="containsText" id="{3ffbd062-9007-4c7f-b53e-efd5a11d29fb}">
+          <x14:cfRule type="containsText" priority="364" operator="containsText" id="{f24b6e20-f55f-45b9-8085-13fe8fe79ff0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I233)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16218,7 +16222,7 @@
           <xm:sqref>I233</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="393" operator="containsText" id="{5aa50d62-465b-4c02-ab4a-67374d1e1b2b}">
+          <x14:cfRule type="containsText" priority="397" operator="containsText" id="{e99331d7-a78c-416d-b953-3c636f043244}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I235)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16233,7 +16237,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="394" operator="containsText" id="{7bd73995-0f74-47d0-b0af-134b2761d603}">
+          <x14:cfRule type="containsText" priority="398" operator="containsText" id="{d4a3a6a5-cf67-4033-a2b0-5a8351ab5b63}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I235)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16251,7 +16255,7 @@
           <xm:sqref>I235</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="401" operator="containsText" id="{40c90638-aa03-46f5-8ca4-601b7ecc6c28}">
+          <x14:cfRule type="containsText" priority="405" operator="containsText" id="{4a017250-a589-4fbe-99cb-0c36ed464292}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I236)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16266,7 +16270,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="402" operator="containsText" id="{e98cf1e4-be9f-4332-a3e3-4926231cd7fa}">
+          <x14:cfRule type="containsText" priority="406" operator="containsText" id="{90dd0610-b617-4244-a66e-8849c28988aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I236)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16284,7 +16288,7 @@
           <xm:sqref>I236</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="367" operator="containsText" id="{428bf205-2cb3-423f-8c78-660b29dcb691}">
+          <x14:cfRule type="containsText" priority="371" operator="containsText" id="{75b29738-57fb-4e6c-9f1a-3f01c6776aea}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16299,7 +16303,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="368" operator="containsText" id="{c444d72a-e3fe-45d2-b348-304fba33edf1}">
+          <x14:cfRule type="containsText" priority="372" operator="containsText" id="{5061fabf-2cd0-425d-8e02-89547d50bf49}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16317,7 +16321,7 @@
           <xm:sqref>I237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="177" operator="containsText" id="{06391b9f-2eb6-4bf2-ae94-116cdd2db751}">
+          <x14:cfRule type="containsText" priority="181" operator="containsText" id="{a390f8d0-ed16-49aa-b110-da2e9604593c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16332,7 +16336,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="178" operator="containsText" id="{a143662a-64d5-45b7-973a-d00e27f30e40}">
+          <x14:cfRule type="containsText" priority="182" operator="containsText" id="{110fecfd-7c5c-469e-bf93-fb3f830bbaeb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16350,7 +16354,7 @@
           <xm:sqref>K237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="365" operator="containsText" id="{b60845db-45c1-42ce-8237-e4826b51e393}">
+          <x14:cfRule type="containsText" priority="369" operator="containsText" id="{524f00f4-88d9-49ff-aa3f-52cf482ef748}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16365,7 +16369,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="366" operator="containsText" id="{0ff8146c-1d33-47b4-93a9-960624c9a266}">
+          <x14:cfRule type="containsText" priority="370" operator="containsText" id="{044aea91-c325-4b8a-b85e-57b83213176c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16383,7 +16387,7 @@
           <xm:sqref>L237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="105" operator="containsText" id="{deb0146c-90df-4172-b038-e834e08ab142}">
+          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{a6c1ec6a-8ecf-4983-87a1-f8ba1e804906}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16398,7 +16402,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="106" operator="containsText" id="{64369da4-8b54-4fb2-9e7b-6dc707c2f7a5}">
+          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{8dcd1f5b-c41d-4577-bd33-7d73f5638dea}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16416,7 +16420,7 @@
           <xm:sqref>G238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="357" operator="containsText" id="{214d2b60-0546-4b15-87a6-c63dc7450ba7}">
+          <x14:cfRule type="containsText" priority="361" operator="containsText" id="{845f0550-b58a-4c5c-ae62-7b66ae5762fb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16431,7 +16435,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="358" operator="containsText" id="{56115ec7-31b4-4264-8dfe-42b4982a27a5}">
+          <x14:cfRule type="containsText" priority="362" operator="containsText" id="{05b62bab-b7cd-49a5-8434-e04cce444aef}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16449,7 +16453,7 @@
           <xm:sqref>I238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{ca51af31-1a54-4d23-a79e-8b4962a9ca16}">
+          <x14:cfRule type="containsText" priority="113" operator="containsText" id="{3bc87748-6ed0-47ad-86f8-36dfc8a69b14}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16464,7 +16468,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{1c35199c-8f5c-4bd0-90c5-26a5208bc983}">
+          <x14:cfRule type="containsText" priority="114" operator="containsText" id="{6a80f14d-7b3c-4de2-91a9-fb87d0635b5a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16482,7 +16486,7 @@
           <xm:sqref>G239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="387" operator="containsText" id="{78af9914-0cf6-4f50-a375-6905336e6b25}">
+          <x14:cfRule type="containsText" priority="391" operator="containsText" id="{946ef5fa-bb2e-4e15-9ad9-0dabed2f8851}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16497,7 +16501,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="388" operator="containsText" id="{05f81c6e-62a3-4178-b2eb-c56fed6fef3a}">
+          <x14:cfRule type="containsText" priority="392" operator="containsText" id="{0ffe183e-7d59-45a2-9a6f-b4f44e347be0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16515,7 +16519,7 @@
           <xm:sqref>I239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="307" operator="containsText" id="{af175a7d-745b-413d-812a-dd0ada2d37f1}">
+          <x14:cfRule type="containsText" priority="311" operator="containsText" id="{d878e98d-6c93-457b-abc4-f87f19c490a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16530,7 +16534,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="308" operator="containsText" id="{f862a3ea-cd75-47f2-9cf0-3e5af70e4986}">
+          <x14:cfRule type="containsText" priority="312" operator="containsText" id="{d287b3bf-a4e4-4fbc-9a7c-6bcc672fec71}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16548,7 +16552,7 @@
           <xm:sqref>I240</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="337" operator="containsText" id="{7a24389b-0b35-42d2-a8a0-59c2289997a2}">
+          <x14:cfRule type="containsText" priority="341" operator="containsText" id="{ec6d0fb2-0cfb-443e-b131-fe057b266a30}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16563,7 +16567,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="338" operator="containsText" id="{d8536808-4ce8-4a10-aa26-2d420fda7dea}">
+          <x14:cfRule type="containsText" priority="342" operator="containsText" id="{67f5c876-a726-42ba-a158-01057bbe1a2a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16581,7 +16585,7 @@
           <xm:sqref>L240</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="331" operator="containsText" id="{de0fd250-ba92-46a4-9cbe-8f817ee38954}">
+          <x14:cfRule type="containsText" priority="335" operator="containsText" id="{93faae9c-e5fd-4c0f-96a9-b45ed7f31b45}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16596,7 +16600,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="332" operator="containsText" id="{a5f584f7-a679-40fb-942b-b38e963dd4c8}">
+          <x14:cfRule type="containsText" priority="336" operator="containsText" id="{97918213-eef8-44ef-918c-e0d11a6b0567}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16614,7 +16618,7 @@
           <xm:sqref>I241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="175" operator="containsText" id="{53e649c9-22e5-4863-9a33-c056f3f7857d}">
+          <x14:cfRule type="containsText" priority="179" operator="containsText" id="{879ea46c-03a5-45e3-9142-68d297e6065e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16629,7 +16633,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="176" operator="containsText" id="{78eae5db-9d20-40cb-90a7-80bed4793c66}">
+          <x14:cfRule type="containsText" priority="180" operator="containsText" id="{d60aeae9-d5d1-4407-9d89-960348f1716c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16647,7 +16651,7 @@
           <xm:sqref>K241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="305" operator="containsText" id="{1ba063bb-8014-48d9-94d8-24dd5a79173b}">
+          <x14:cfRule type="containsText" priority="309" operator="containsText" id="{47637354-0110-419a-b41f-1047c0187f9e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16662,7 +16666,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="306" operator="containsText" id="{ef976196-b58f-4477-b58d-3e3579c1d7db}">
+          <x14:cfRule type="containsText" priority="310" operator="containsText" id="{4e0c7d9d-10d5-4445-8518-6a2281270f0a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16680,7 +16684,7 @@
           <xm:sqref>L241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="301" operator="containsText" id="{5c176b44-7826-411a-8960-91f80ebd293c}">
+          <x14:cfRule type="containsText" priority="305" operator="containsText" id="{e2b49e49-dad7-4031-8dc3-7fefd205314e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I242)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16695,7 +16699,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="302" operator="containsText" id="{50ef0bca-ee1d-40a4-8ed9-8b013571d762}">
+          <x14:cfRule type="containsText" priority="306" operator="containsText" id="{7324bc5f-de5a-4907-a48d-d76b4c8e0bfd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I242)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16713,7 +16717,7 @@
           <xm:sqref>I242</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="319" operator="containsText" id="{1962db9b-037c-472b-98b0-f4e8c9a25d3a}">
+          <x14:cfRule type="containsText" priority="323" operator="containsText" id="{25eac937-96a8-487d-b9a0-85ac678939b2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I243)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16728,7 +16732,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="320" operator="containsText" id="{07098844-5c78-4eda-ad89-d9ef4a35582f}">
+          <x14:cfRule type="containsText" priority="324" operator="containsText" id="{ddabc77b-894c-4467-817e-6e91c0d0a34d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I243)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16746,7 +16750,7 @@
           <xm:sqref>I243</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="335" operator="containsText" id="{974d7816-ca6c-4f34-95d6-63368b45d542}">
+          <x14:cfRule type="containsText" priority="339" operator="containsText" id="{0f320392-b056-4d8d-a4cf-deae490a6cf6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I244)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16761,7 +16765,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="336" operator="containsText" id="{07736083-9786-4321-ba60-90086581972c}">
+          <x14:cfRule type="containsText" priority="340" operator="containsText" id="{f983004f-f38a-4e87-b99c-ef5c208524d9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I244)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16779,7 +16783,7 @@
           <xm:sqref>I244</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="325" operator="containsText" id="{e90fe577-6bdd-48ff-8c04-b326285a0752}">
+          <x14:cfRule type="containsText" priority="329" operator="containsText" id="{25d95939-c95c-4366-a991-8fdf5146d085}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I245)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16794,7 +16798,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="326" operator="containsText" id="{d0c2a0d0-9bb8-4126-9baa-3cb7b860bca6}">
+          <x14:cfRule type="containsText" priority="330" operator="containsText" id="{c6dd0946-8266-474e-94e5-339b9c311268}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I245)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16812,7 +16816,7 @@
           <xm:sqref>I245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="317" operator="containsText" id="{75858a68-98cb-4311-9d02-cf41474805a0}">
+          <x14:cfRule type="containsText" priority="321" operator="containsText" id="{d4b02767-bd13-4c52-9db3-4bd31fa6bb82}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L245)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16827,7 +16831,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="318" operator="containsText" id="{df586a4b-367e-4525-aea3-3e1fe3baa49b}">
+          <x14:cfRule type="containsText" priority="322" operator="containsText" id="{27a10059-c40e-452d-8054-3fe5a7d1597a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L245)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16845,7 +16849,7 @@
           <xm:sqref>L245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="329" operator="containsText" id="{3d8a562b-3f55-408b-b803-c32358be676c}">
+          <x14:cfRule type="containsText" priority="333" operator="containsText" id="{cb9c9d59-d60f-4fc7-bc26-5def0bacc965}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I246)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16860,7 +16864,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="330" operator="containsText" id="{abd9dedc-b6de-4149-8aae-8281c02c3555}">
+          <x14:cfRule type="containsText" priority="334" operator="containsText" id="{8ef6e34c-4f9b-4769-be46-ceef9f3a7165}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I246)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16878,7 +16882,7 @@
           <xm:sqref>I246</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="303" operator="containsText" id="{046b6841-1f42-4c4b-90fb-fb0de6b12149}">
+          <x14:cfRule type="containsText" priority="307" operator="containsText" id="{3ac52106-e619-4e6b-931c-c0af81ee68c7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I247)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16893,7 +16897,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="304" operator="containsText" id="{c860f342-6cf2-485f-af55-499e422e2003}">
+          <x14:cfRule type="containsText" priority="308" operator="containsText" id="{80292fbe-3ebe-4ac5-90c7-8de04baa686c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I247)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16911,7 +16915,7 @@
           <xm:sqref>I247</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="339" operator="containsText" id="{71aab1d6-fabb-4f11-bdaf-bd9c4f4c3839}">
+          <x14:cfRule type="containsText" priority="343" operator="containsText" id="{42bffc50-f959-4b47-aa73-1d0fb8515398}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I249)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16926,7 +16930,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="340" operator="containsText" id="{c617b4b3-5d89-4973-bc9d-fc9a57552928}">
+          <x14:cfRule type="containsText" priority="344" operator="containsText" id="{92b3df69-cfe5-4eca-8c1e-2a4cbddaeda3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I249)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16944,7 +16948,7 @@
           <xm:sqref>I249</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="299" operator="containsText" id="{f8d78ce6-4cf3-4cc9-b7a0-1184dfd69e74}">
+          <x14:cfRule type="containsText" priority="303" operator="containsText" id="{8cda39fc-8abc-491f-85e0-ef5364e55962}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I250)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16959,7 +16963,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="300" operator="containsText" id="{492bdb95-9e36-4076-81b5-aa74ca7b1e34}">
+          <x14:cfRule type="containsText" priority="304" operator="containsText" id="{f0d41ce4-4014-4b85-9c86-4cf8a59a0ee8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I250)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16977,7 +16981,7 @@
           <xm:sqref>I250</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="311" operator="containsText" id="{59f504fd-230e-4fc8-a878-d7d7fa25e151}">
+          <x14:cfRule type="containsText" priority="315" operator="containsText" id="{fcd6c067-2a8d-40be-9b4a-684ea8e04efd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16992,7 +16996,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="312" operator="containsText" id="{044120bd-dcb1-4dc9-9f2a-47d77bd4be98}">
+          <x14:cfRule type="containsText" priority="316" operator="containsText" id="{62b90f1c-6358-4513-a1cc-6b1f28a84ac0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17010,7 +17014,7 @@
           <xm:sqref>I251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="173" operator="containsText" id="{14a92ec5-c470-43e9-96e8-ea436a197c52}">
+          <x14:cfRule type="containsText" priority="177" operator="containsText" id="{06c181ce-ab74-4ff2-b260-328f96328db6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17025,7 +17029,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="174" operator="containsText" id="{9c785760-0a50-4655-948b-c4d95bdeea9c}">
+          <x14:cfRule type="containsText" priority="178" operator="containsText" id="{34878dde-57d2-4168-a9ac-976e6c027bc1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17043,7 +17047,7 @@
           <xm:sqref>K251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="309" operator="containsText" id="{47674de7-4c59-4c5d-9fc3-f48849cd03b2}">
+          <x14:cfRule type="containsText" priority="313" operator="containsText" id="{bc169476-81d8-413d-9127-7f4fe760cd10}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17058,7 +17062,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="310" operator="containsText" id="{e40bbaeb-cb5d-43c7-8aee-6327502749b9}">
+          <x14:cfRule type="containsText" priority="314" operator="containsText" id="{815fa8b9-36fb-4edd-9dc0-1124e7480e0d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17076,7 +17080,7 @@
           <xm:sqref>L251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="99" operator="containsText" id="{ee7fc742-600d-4a87-8c43-7e05998bb3ee}">
+          <x14:cfRule type="containsText" priority="103" operator="containsText" id="{174a6dc8-65c3-4e42-9a1f-073994fbef9c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17091,7 +17095,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="100" operator="containsText" id="{37b539c8-5b55-4344-876a-d5c53e847d26}">
+          <x14:cfRule type="containsText" priority="104" operator="containsText" id="{c4ec1aa0-51f0-42f1-ae2a-be3d53bc77f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17109,7 +17113,7 @@
           <xm:sqref>G252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="207" operator="containsText" id="{2c7bf559-9804-4e35-a269-0baeea41631c}">
+          <x14:cfRule type="containsText" priority="211" operator="containsText" id="{06afff89-7f24-4191-81a2-66011e506b67}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17124,7 +17128,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="208" operator="containsText" id="{dd1a52a9-2ace-4e8c-b3d3-8f2fa15082e1}">
+          <x14:cfRule type="containsText" priority="212" operator="containsText" id="{d632f8a4-4b7d-4446-8965-a7ac6714b025}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17142,7 +17146,7 @@
           <xm:sqref>I252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="103" operator="containsText" id="{09ae2207-57d3-4255-bebf-adeab29e41ad}">
+          <x14:cfRule type="containsText" priority="107" operator="containsText" id="{be061586-a85d-4987-9575-33356e375bd9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17157,7 +17161,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="104" operator="containsText" id="{b88cf4f8-08a6-40fe-8dd5-844ac6d19ce0}">
+          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{5070072a-2bdf-4c43-bf7b-b65297f36d77}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17175,7 +17179,7 @@
           <xm:sqref>G253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="333" operator="containsText" id="{a23d9396-70df-415b-9e36-6ba529c87edd}">
+          <x14:cfRule type="containsText" priority="337" operator="containsText" id="{4c1a76dd-a39d-49c8-a5c1-67312db59985}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17190,7 +17194,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="334" operator="containsText" id="{cab7ae01-0209-4322-8dc0-3bdae3191ef1}">
+          <x14:cfRule type="containsText" priority="338" operator="containsText" id="{9165838b-a7e9-46da-8d63-0756557ab6a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17208,7 +17212,7 @@
           <xm:sqref>I253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="199" operator="containsText" id="{f692ebc0-aa6d-4077-816f-4356b808c1f9}">
+          <x14:cfRule type="containsText" priority="203" operator="containsText" id="{0521ef64-6842-4e2b-ad42-6954e19ca75d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17223,7 +17227,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="200" operator="containsText" id="{48ea3780-bfb1-4cbf-90be-bb62aef292e5}">
+          <x14:cfRule type="containsText" priority="204" operator="containsText" id="{7cea0b57-da61-4a58-8273-fe670af5e383}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17241,7 +17245,7 @@
           <xm:sqref>I254</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="279" operator="containsText" id="{9b03c7df-4956-4114-a58c-8c6f1e798da2}">
+          <x14:cfRule type="containsText" priority="283" operator="containsText" id="{c4709827-e280-46d4-8294-ca2f11e26208}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17256,7 +17260,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="280" operator="containsText" id="{0ac00845-3e89-445c-b787-3ef35c103b9d}">
+          <x14:cfRule type="containsText" priority="284" operator="containsText" id="{8bf86a23-d53a-4c66-bd6f-98363b586127}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17274,7 +17278,7 @@
           <xm:sqref>L254</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="273" operator="containsText" id="{a27b668d-ea58-44fb-9b53-709d35ab0d7e}">
+          <x14:cfRule type="containsText" priority="277" operator="containsText" id="{fd0b3f7b-9ee6-4bd7-9673-f05890112f9e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17289,7 +17293,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="274" operator="containsText" id="{0a45b9fb-d209-456e-bae6-12076cbba404}">
+          <x14:cfRule type="containsText" priority="278" operator="containsText" id="{6dba8172-8281-4e5a-8b50-614ffc08be05}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17307,7 +17311,7 @@
           <xm:sqref>I255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="171" operator="containsText" id="{c4e41681-6a50-43ac-9487-b8709d178cd3}">
+          <x14:cfRule type="containsText" priority="175" operator="containsText" id="{accaaea4-bc77-429e-9688-6840e06e17c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17322,7 +17326,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="172" operator="containsText" id="{cf653bd1-40c9-4cde-a07c-caf248f1f526}">
+          <x14:cfRule type="containsText" priority="176" operator="containsText" id="{c398fdfb-7bf0-4314-8a56-4a44d9607145}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17340,7 +17344,7 @@
           <xm:sqref>K255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="197" operator="containsText" id="{7a54ee91-0f70-4768-b254-7cc777dc20ea}">
+          <x14:cfRule type="containsText" priority="201" operator="containsText" id="{a866c8fd-2194-495d-ae70-26e459ac4849}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17355,7 +17359,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="198" operator="containsText" id="{ac2dabac-f635-4299-b389-a02f0c394b7a}">
+          <x14:cfRule type="containsText" priority="202" operator="containsText" id="{2f13eee5-e4ed-425f-8a85-4a1a8cbefb65}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17373,7 +17377,7 @@
           <xm:sqref>L255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="283" operator="containsText" id="{c873d893-3b53-4a1e-ab55-be7d37b10046}">
+          <x14:cfRule type="containsText" priority="287" operator="containsText" id="{2e9b1b6b-1cd0-4e10-b264-431778cfc6e0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I256)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17388,7 +17392,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="284" operator="containsText" id="{28276373-81ae-43a7-a256-bb588ab10d10}">
+          <x14:cfRule type="containsText" priority="288" operator="containsText" id="{85a20ff2-d686-41ef-a011-aba9d9bb4de3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I256)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17406,7 +17410,7 @@
           <xm:sqref>I256</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="261" operator="containsText" id="{a82b7c84-66de-414e-914f-e6b040af84ff}">
+          <x14:cfRule type="containsText" priority="265" operator="containsText" id="{a20b5415-1f92-47aa-81ff-d27233522cd4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I257)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17421,7 +17425,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="262" operator="containsText" id="{dc7a3cb5-9ef6-446b-83f2-b1dfafa22237}">
+          <x14:cfRule type="containsText" priority="266" operator="containsText" id="{6bcbf0c2-4595-4060-831f-95f01611da0b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I257)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17439,7 +17443,7 @@
           <xm:sqref>I257</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="277" operator="containsText" id="{8306028d-5113-4071-b935-3314c8ea2f7f}">
+          <x14:cfRule type="containsText" priority="281" operator="containsText" id="{68272c03-66c2-418f-aceb-3263db0e2634}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I258)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17454,7 +17458,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="278" operator="containsText" id="{f80a352d-173b-4710-896a-25274df934b9}">
+          <x14:cfRule type="containsText" priority="282" operator="containsText" id="{304aca95-74c3-4c6c-b0b2-686fb1b7c886}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I258)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17472,7 +17476,7 @@
           <xm:sqref>I258</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="267" operator="containsText" id="{420ca2b3-a4bc-419f-8c84-94f4a7b117eb}">
+          <x14:cfRule type="containsText" priority="271" operator="containsText" id="{aa45bdba-5e2d-4bf3-bb1c-5d6a50a2163f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I259)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17487,7 +17491,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="268" operator="containsText" id="{7859e268-3589-4f27-9f56-78eec154f6d3}">
+          <x14:cfRule type="containsText" priority="272" operator="containsText" id="{e4af479f-bd70-4b08-91bc-f6a516d2412f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I259)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17505,7 +17509,7 @@
           <xm:sqref>I259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="259" operator="containsText" id="{1ee46f06-4506-46ce-9b57-c46da704c70b}">
+          <x14:cfRule type="containsText" priority="263" operator="containsText" id="{7a3d9d08-7202-4148-b078-decea23ca4a6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L259)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17520,7 +17524,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="260" operator="containsText" id="{810ee9b7-71d7-411e-b0ce-f33723ac80c0}">
+          <x14:cfRule type="containsText" priority="264" operator="containsText" id="{33692436-ca8a-45af-98df-2601b0afa2bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L259)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17538,7 +17542,7 @@
           <xm:sqref>L259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="271" operator="containsText" id="{ebec5f0f-6bdf-4f90-8f9b-56290090fd37}">
+          <x14:cfRule type="containsText" priority="275" operator="containsText" id="{ecb48943-ac01-437b-a4b4-fff390874a79}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I260)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17553,7 +17557,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="272" operator="containsText" id="{543d2042-dcae-48fc-b778-24fb973aa73f}">
+          <x14:cfRule type="containsText" priority="276" operator="containsText" id="{f6e60aa8-a6f3-4289-a792-1c3644087176}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I260)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17571,7 +17575,7 @@
           <xm:sqref>I260</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="257" operator="containsText" id="{8bf8b25a-97b1-4c95-97ea-1bdd0ad117a1}">
+          <x14:cfRule type="containsText" priority="261" operator="containsText" id="{bea838c5-70ff-414c-ab5a-64d57878bee7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I261)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17586,7 +17590,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="258" operator="containsText" id="{0e0bc10e-2b6c-44ab-916f-b2244abea49d}">
+          <x14:cfRule type="containsText" priority="262" operator="containsText" id="{b1bee444-5843-4f85-828e-a5e99e7a857f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I261)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17604,7 +17608,7 @@
           <xm:sqref>I261</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="195" operator="containsText" id="{f438e12f-91e9-4eb1-acec-f1865cb6e001}">
+          <x14:cfRule type="containsText" priority="199" operator="containsText" id="{382da7fc-f7be-41c5-a565-3426e718f3d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I263)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17619,7 +17623,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="196" operator="containsText" id="{cfbd6c46-01f8-4eb3-9553-0853278d78a5}">
+          <x14:cfRule type="containsText" priority="200" operator="containsText" id="{28e24f35-da40-488b-a03d-c5aab248d14b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I263)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17637,7 +17641,7 @@
           <xm:sqref>I263</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="285" operator="containsText" id="{5dab4d5e-8b0c-40c6-95a9-dda34e6fabe0}">
+          <x14:cfRule type="containsText" priority="289" operator="containsText" id="{e2b8236c-63ed-484e-9b4f-c509bc35be24}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17652,7 +17656,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="286" operator="containsText" id="{c2157ca4-8eac-410f-83ee-9882d011ccc9}">
+          <x14:cfRule type="containsText" priority="290" operator="containsText" id="{a4e29131-34d9-46f4-ae51-6557d1500a86}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17670,7 +17674,7 @@
           <xm:sqref>I264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="169" operator="containsText" id="{81b90967-75ff-430f-82a1-7305b89222f3}">
+          <x14:cfRule type="containsText" priority="173" operator="containsText" id="{e93118d6-4f13-4e0a-b393-0f66cbc1bad0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17685,7 +17689,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="170" operator="containsText" id="{c46816f8-57e4-4bbc-82ad-6a46d0485c7e}">
+          <x14:cfRule type="containsText" priority="174" operator="containsText" id="{589fed5e-7f9d-497b-9e93-0a80d94b9226}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17703,7 +17707,7 @@
           <xm:sqref>K264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="201" operator="containsText" id="{24cb0da9-1058-4cf9-a3c6-7cdb17677556}">
+          <x14:cfRule type="containsText" priority="205" operator="containsText" id="{ff69bee0-7da8-4fda-bd61-c2c8858751ea}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17718,7 +17722,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="202" operator="containsText" id="{27b34669-f821-4ff6-8e38-47b35663f7bd}">
+          <x14:cfRule type="containsText" priority="206" operator="containsText" id="{f0668e30-dd4f-4d24-a1c4-5e66dfb26b75}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17736,7 +17740,7 @@
           <xm:sqref>L264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="205" operator="containsText" id="{27d582c4-ee0d-4d7c-a572-68125f554565}">
+          <x14:cfRule type="containsText" priority="209" operator="containsText" id="{e0db1969-614e-457f-ab65-cdbd62779c23}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17751,7 +17755,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="206" operator="containsText" id="{f3bbdef1-b5ff-4749-b789-75a937244653}">
+          <x14:cfRule type="containsText" priority="210" operator="containsText" id="{71fa146f-60e0-49ca-ba05-2e527be37290}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17769,7 +17773,7 @@
           <xm:sqref>I265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="167" operator="containsText" id="{50d0d0c2-8b4a-4b58-b3cb-2ea17a44dfab}">
+          <x14:cfRule type="containsText" priority="171" operator="containsText" id="{7d670334-89bb-4634-8bab-eadf1755bfa5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17784,7 +17788,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="168" operator="containsText" id="{97a6508c-5f64-4956-a1dd-3a22483d24b0}">
+          <x14:cfRule type="containsText" priority="172" operator="containsText" id="{f2797330-2bb5-466e-a860-ca894d10989e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17802,7 +17806,7 @@
           <xm:sqref>K265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="203" operator="containsText" id="{67c604f2-a0bf-429e-950c-69ad55fa842e}">
+          <x14:cfRule type="containsText" priority="207" operator="containsText" id="{ddc4c8c5-1659-49ec-9e41-0bfabb1f3308}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17817,7 +17821,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="204" operator="containsText" id="{fb957f3c-e4ff-43fc-9fc8-c65973a3a706}">
+          <x14:cfRule type="containsText" priority="208" operator="containsText" id="{8e50916e-7116-4884-8c1a-0fae478bb4f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17835,7 +17839,7 @@
           <xm:sqref>L265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="93" operator="containsText" id="{51bf7a4c-1c6c-4d81-908c-9b566e6f2a06}">
+          <x14:cfRule type="containsText" priority="97" operator="containsText" id="{542ec13c-24a8-493a-a468-157d2d518155}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17850,7 +17854,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="94" operator="containsText" id="{193034a0-38e8-4ed3-8eae-d4d8f1876406}">
+          <x14:cfRule type="containsText" priority="98" operator="containsText" id="{f36b013e-dec5-4b3b-8b96-123690914cbd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17868,7 +17872,7 @@
           <xm:sqref>G266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="255" operator="containsText" id="{9b1fdf4e-f9f0-4710-995d-5988f048abe9}">
+          <x14:cfRule type="containsText" priority="259" operator="containsText" id="{08f593b4-907a-4a43-b990-f3b7b857b2bd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17883,7 +17887,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="256" operator="containsText" id="{0d96e134-e70f-41ab-bd0e-e69984a1a40e}">
+          <x14:cfRule type="containsText" priority="260" operator="containsText" id="{1a3e6696-49f7-4075-826b-1bdc7b7bfc64}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17901,7 +17905,7 @@
           <xm:sqref>I266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="97" operator="containsText" id="{284667a8-f388-4940-b99d-678e2aba2efe}">
+          <x14:cfRule type="containsText" priority="101" operator="containsText" id="{6f536437-c19e-4c16-ab4e-39bcb042a377}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17916,7 +17920,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="98" operator="containsText" id="{771b30a6-43b4-4055-9d55-1335b5ccded1}">
+          <x14:cfRule type="containsText" priority="102" operator="containsText" id="{7b05600b-9ebc-4f03-8187-be830c02b30c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17934,7 +17938,7 @@
           <xm:sqref>G267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="275" operator="containsText" id="{616f0701-4931-4011-bfc6-fad7311cd1ba}">
+          <x14:cfRule type="containsText" priority="279" operator="containsText" id="{4d050d65-ac0e-432f-8560-f3b6701933b7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17949,7 +17953,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="276" operator="containsText" id="{7bf8f723-accb-4412-b1e4-d5772fbb0967}">
+          <x14:cfRule type="containsText" priority="280" operator="containsText" id="{b6e8dfdc-cee4-4ecd-9bd2-71e90bdd9d1f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17967,7 +17971,40 @@
           <xm:sqref>I267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="51" operator="containsText" id="{367b30d5-5302-4f54-931a-284ee3ecc83b}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{7ec6a4de-f3c5-4860-8f1e-b1b00865c975}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,G268)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{f7c0e50a-3ac2-4959-9974-8aef476509c5}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,G268)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G268</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="55" operator="containsText" id="{12a3fae9-208e-4264-be45-f42fa995c8e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17982,7 +18019,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="52" operator="containsText" id="{a8ef4468-0295-4a6b-a09e-cf36e0485731}">
+          <x14:cfRule type="containsText" priority="56" operator="containsText" id="{a96f752d-3829-41e4-9de3-34b22ac69484}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18000,7 +18037,40 @@
           <xm:sqref>F269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{24e34e15-c88e-4391-a82e-a23c83e2cd4e}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{c0ce0155-55f2-4921-8d93-1cc9cf355104}">
+            <xm:f>NOT(ISERROR(SEARCH($A$2,G269)))</xm:f>
+            <xm:f>$A$2</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{cf4843b2-83a3-48a3-8b38-2cd4cbce205a}">
+            <xm:f>NOT(ISERROR(SEARCH($A$15,G269)))</xm:f>
+            <xm:f>$A$15</xm:f>
+            <x14:dxf>
+              <font>
+                <b val="1"/>
+                <i val="1"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <bgColor theme="9"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G269</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{13590551-a5ea-4b12-8194-7213e5e185b3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18015,7 +18085,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="27" operator="containsText" id="{fc0aa6e0-1b8f-4ae5-9276-f8bf7846e661}">
+          <x14:cfRule type="containsText" priority="31" operator="containsText" id="{79f1ec33-bb37-4b2b-acc1-4bd121a9624e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18033,7 +18103,7 @@
           <xm:sqref>J269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{b12d2ea5-5dae-4266-89ff-2c797c565b91}">
+          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{150b8d53-1864-4a03-98ac-ef2354f8c471}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18048,7 +18118,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{64e7ff3e-44f9-4e97-aafc-7b45e9a0e238}">
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{fbee82d2-4fba-4f95-ab2d-3e6a1f359567}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18066,7 +18136,7 @@
           <xm:sqref>K269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{006cfe37-227d-4f02-877c-e972bbbe6cad}">
+          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{4f22903b-51d3-4c2d-b1ea-26c6819486dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F270)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18081,7 +18151,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="50" operator="containsText" id="{0188614f-623b-4ed3-afa4-3bd93bce2ae8}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{392f0e95-608f-4534-9483-43e65c534032}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F270)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18099,7 +18169,7 @@
           <xm:sqref>F270</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{f335c62e-e745-4863-91dd-8c59086b6d60}">
+          <x14:cfRule type="containsText" priority="51" operator="containsText" id="{5b8c6c08-74de-4a2d-b2d9-f0755aaa79fa}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G270)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18114,7 +18184,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="48" operator="containsText" id="{0930d897-2cc0-4e37-abc8-01499e2c62e5}">
+          <x14:cfRule type="containsText" priority="52" operator="containsText" id="{13a9ef32-1b5f-420d-94e0-9f32ea07a1df}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G270)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18132,7 +18202,7 @@
           <xm:sqref>G270</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{dda8a348-0ad5-4e55-9977-55a6d9a113ec}">
+          <x14:cfRule type="containsText" priority="30" operator="containsText" id="{bb23b3a8-8e74-451a-81ba-3b039e56e8c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J271)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18147,7 +18217,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="25" operator="containsText" id="{25553d4d-5e40-4fe1-81ad-e4050dfa7d67}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{14e30bca-4053-4970-ba3f-0d512d921723}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J271)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18165,7 +18235,7 @@
           <xm:sqref>J271</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{385d532a-ac2b-4b8b-9e06-13c3aecd9b3b}">
+          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{25194452-42c5-4cba-b19f-e5ab44980eea}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K271)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18180,7 +18250,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{1b5af0f7-eb79-4a0f-a0a8-e1729a077ea1}">
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{4e67eb27-e3f8-4c19-8ab8-ef606aafd321}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K271)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18198,7 +18268,7 @@
           <xm:sqref>K271</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="45" operator="containsText" id="{32ee9b58-2884-45b6-bee8-74f4c80cb4bd}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{4d5c2d10-0ae9-41ae-aeda-907cad0c1186}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18213,7 +18283,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="46" operator="containsText" id="{d39b8fb1-69d7-4ac3-99dd-a28929dea85d}">
+          <x14:cfRule type="containsText" priority="50" operator="containsText" id="{1b3e2fba-21db-47a6-8b90-aa98edfb9e3f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18231,7 +18301,7 @@
           <xm:sqref>G272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{0881f0f2-7cec-4f9e-b408-4e717c8da7d7}">
+          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{bb49e5ad-ec4f-42ed-a72d-4e5bfcc8b65b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18246,7 +18316,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="23" operator="containsText" id="{6bd5aea4-0f1d-42b9-a1bf-dabde82fa918}">
+          <x14:cfRule type="containsText" priority="27" operator="containsText" id="{3ae8ee18-6554-45a1-9b84-0c4d4bd9f491}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18264,7 +18334,7 @@
           <xm:sqref>J272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{44312f48-36b8-440a-862b-25592bf1f2cb}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{0eeedb5c-b9e7-42e4-a864-28e97f48a9d8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18279,7 +18349,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{bb88fa60-4ec5-4134-bb67-4ab115ecc338}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{502f985d-1b3d-478a-8984-17105151c3e3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18297,7 +18367,7 @@
           <xm:sqref>K272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{f76cb8e1-0466-4139-ba22-4f3fd8375d34}">
+          <x14:cfRule type="containsText" priority="45" operator="containsText" id="{24dce0cc-514c-4fe2-85bf-607e54464918}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18312,7 +18382,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="42" operator="containsText" id="{28633777-048c-49ab-a4b9-54af76304902}">
+          <x14:cfRule type="containsText" priority="46" operator="containsText" id="{43f465bd-6fb7-40fd-bd17-10b4ccaacfb2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18330,7 +18400,7 @@
           <xm:sqref>F273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="43" operator="containsText" id="{d4703cd7-c38f-416e-93ef-00de1128cf64}">
+          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{298dc70d-7205-41f5-8030-76688e205155}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18345,7 +18415,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{9e9a0510-538d-4a22-ae25-e3f729abd1e2}">
+          <x14:cfRule type="containsText" priority="48" operator="containsText" id="{5795fdc3-661f-4a5e-a678-1e0550248464}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18363,7 +18433,7 @@
           <xm:sqref>G273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{cada0728-b6ea-492d-86d8-a115448f3c48}">
+          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{2e4ef911-09af-45bb-bb01-0f7ea0a043b9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18378,7 +18448,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="21" operator="containsText" id="{d1411cf9-588a-43b9-9f3e-507dc6db68a3}">
+          <x14:cfRule type="containsText" priority="25" operator="containsText" id="{adb6da43-ec37-4e1a-ae91-36ca5ef70c81}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18396,7 +18466,7 @@
           <xm:sqref>J273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{a37c45f7-2ebe-4daa-8be3-d0031f62b181}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{3649d75e-85d9-468e-8cf6-4a3acb3b3669}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18411,7 +18481,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{28cce818-04d3-436e-be7d-815a34be0fba}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{73fa19f9-997f-4211-bdc6-b412585e2715}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18429,7 +18499,7 @@
           <xm:sqref>K273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{adf37fb2-8360-43c3-a34d-b7ca7318f9d7}">
+          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{0f14c9aa-42c5-42a3-ba53-62c02e2120bd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18444,7 +18514,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{9a1bde54-f86e-4571-a57a-8db89e94befd}">
+          <x14:cfRule type="containsText" priority="42" operator="containsText" id="{65b0fa8b-2b77-47f9-b2ca-e4a8a3257fa6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18462,7 +18532,7 @@
           <xm:sqref>F274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{6bec1d3c-377a-4c05-b735-b14f1fbb35bb}">
+          <x14:cfRule type="containsText" priority="43" operator="containsText" id="{84aa3e53-b6ca-400d-86d1-f0f5944c81e2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18477,7 +18547,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="40" operator="containsText" id="{4ed1a0c0-1c89-47c9-ac11-87b69f2b7a84}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{adbc6e29-2cf0-4ace-a705-72997c668855}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18495,7 +18565,7 @@
           <xm:sqref>G274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{1d7e56b1-83a7-41d3-835a-c85f1d00fb53}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{f308146a-5c1e-4975-b0cb-c407774e8c98}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18510,7 +18580,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="19" operator="containsText" id="{e6e064cd-93d9-42c7-afd1-d42468dbfbe6}">
+          <x14:cfRule type="containsText" priority="23" operator="containsText" id="{d98e49a4-672b-415d-b45b-4e634acc90db}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18528,7 +18598,7 @@
           <xm:sqref>J274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{c1a99cb0-39a2-457e-b9b0-f9ccdeb2ce38}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{0eee3764-8018-43dc-a7f9-1d2dbbf473bb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18543,7 +18613,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{064d3801-8289-46a6-a349-9ae1ee67fda2}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{8484ebb4-602d-4dec-a965-e321fb7de60e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18561,7 +18631,7 @@
           <xm:sqref>K274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{5aacb938-4fc1-4b38-bbea-40a47feecb58}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{c1b22c4c-c2f8-4d3e-acde-fedc3dfec777}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G275)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18576,7 +18646,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="36" operator="containsText" id="{12ff5ed5-47fc-44a9-8b74-4baca2314106}">
+          <x14:cfRule type="containsText" priority="40" operator="containsText" id="{e4bddf99-a3ca-417c-a211-7c10cf7121c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G275)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18594,7 +18664,7 @@
           <xm:sqref>G275</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{f3079b9c-774d-4023-a053-ba1620c17cbe}">
+          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{a77d2b53-b87d-409a-871b-ce68458ff0d1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J278)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18609,7 +18679,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{8ce665d9-694d-4af2-a21d-7897d3c2c379}">
+          <x14:cfRule type="containsText" priority="21" operator="containsText" id="{2a20ee2e-50cb-4f71-8c47-2512f3e4d3b7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J278)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18627,7 +18697,7 @@
           <xm:sqref>J278</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{e93b01f9-0783-4719-af36-1fda48f47a06}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{0c8cf9ea-c968-45e6-9715-859e2f6456da}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K278)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18642,7 +18712,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{ab391189-1345-4e64-8301-450d6762689d}">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{63eb3aa3-e5e8-499f-887c-b7a56710b972}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K278)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18660,7 +18730,7 @@
           <xm:sqref>K278</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="31" operator="containsText" id="{8caafe1a-fb23-40d6-9879-51ec37bf099c}">
+          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{4e08b522-fdef-47c9-af2f-357f403eb05b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F279)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18675,7 +18745,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{6f005568-0464-4e8e-83f5-f84358a901e1}">
+          <x14:cfRule type="containsText" priority="36" operator="containsText" id="{54281ddc-39a0-44d5-8442-db80f3c8043a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F279)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18693,7 +18763,7 @@
           <xm:sqref>F279</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{2480ff33-e210-430c-b239-a4914a6b2cde}">
+          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{eb2aa9fc-1726-40ce-8a30-7a42283a4884}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G279)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18708,7 +18778,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{23f0ee29-f687-4475-ab56-1af98a9a7a31}">
+          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{becc3c42-36d6-43b5-8709-6c95ae7bd207}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G279)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18726,7 +18796,7 @@
           <xm:sqref>G279</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="60" operator="containsText" id="{1299d384-9cea-403c-aa3b-03737759f917}">
+          <x14:cfRule type="containsText" priority="64" operator="containsText" id="{bcc0caa1-d0df-4fa5-87c8-6b357f1665ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18741,7 +18811,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="59" operator="containsText" id="{120511d6-2333-44b1-b969-de10c7f3e9e1}">
+          <x14:cfRule type="containsText" priority="63" operator="containsText" id="{fa4bc2bd-1218-4f25-b581-c76c00c86aba}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18759,7 +18829,7 @@
           <xm:sqref>A280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{97f6a392-dad2-48fe-b056-844cc733387a}">
+          <x14:cfRule type="containsText" priority="57" operator="containsText" id="{16bea4b2-c8a5-4936-a80c-7af013f5a492}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18774,7 +18844,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{6af9ad73-9c92-431c-8514-0caf9fa6e31d}">
+          <x14:cfRule type="containsText" priority="58" operator="containsText" id="{90ceae64-d22a-465e-b80c-5e41455c2fb1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18792,7 +18862,7 @@
           <xm:sqref>E280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{7e85dda1-3f19-451a-a0c6-e490c9819a9e}">
+          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{7ae55da5-ad64-4cd8-b672-cd458ef68e4a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18807,7 +18877,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{a00b4d21-36f7-4aac-abc9-5e06a818a300}">
+          <x14:cfRule type="containsText" priority="19" operator="containsText" id="{994c0ca7-34a4-44ee-8373-36e0a366d71f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18825,7 +18895,7 @@
           <xm:sqref>J280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{fad4c609-a8d6-4875-b66f-b71cbc277283}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{befd1658-0d06-47dd-b95a-198f55cab72f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18840,7 +18910,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{487c30d6-01ac-4d4d-8a0e-e3986963f272}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{e5755096-6072-472b-aaa3-550a1ecc169a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18858,7 +18928,7 @@
           <xm:sqref>K280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="57" operator="containsText" id="{6ac0d0be-71e4-42dd-a493-8820eb406ba8}">
+          <x14:cfRule type="containsText" priority="61" operator="containsText" id="{06802901-c55b-404b-b9c5-fcc2a6bc63e8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E281)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18873,7 +18943,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="58" operator="containsText" id="{7a738499-8e4b-4138-a5d1-3ed72ab98209}">
+          <x14:cfRule type="containsText" priority="62" operator="containsText" id="{6caf97c1-b4b3-4117-9b5f-86ca55fafd0c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E281)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18891,7 +18961,7 @@
           <xm:sqref>E281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{63300886-02f4-475e-8a9e-c541802f2551}">
+          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{f806374a-07c6-431c-aa66-2454325af19b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G281)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18906,7 +18976,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="30" operator="containsText" id="{516dbe27-b678-497a-8bdb-e937220ea1ac}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{3e8cf20e-397b-4702-934b-f73057ee8b98}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G281)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18924,7 +18994,7 @@
           <xm:sqref>G281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="89" operator="containsText" id="{07d2be2c-e2ea-4b9e-8578-ac2708347edd}">
+          <x14:cfRule type="containsText" priority="93" operator="containsText" id="{80ed6341-0d3f-4566-9931-4e989820ab3b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18939,7 +19009,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="90" operator="containsText" id="{97d6cd87-5571-453b-8a4d-e6b6229aef9a}">
+          <x14:cfRule type="containsText" priority="94" operator="containsText" id="{74860fd8-9ef3-4871-a23a-f03b86bf460e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18957,7 +19027,7 @@
           <xm:sqref>B86:B99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="87" operator="containsText" id="{ff03b783-97c2-457d-9e06-4623d9b9e337}">
+          <x14:cfRule type="containsText" priority="91" operator="containsText" id="{bd1aabe3-8e6c-4d28-a93a-04b851fbe726}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18972,7 +19042,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="88" operator="containsText" id="{f69002b1-a76d-4dd2-ad50-4daadf11604d}">
+          <x14:cfRule type="containsText" priority="92" operator="containsText" id="{869f9878-2cd8-4965-bdeb-54ff69be23f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18990,7 +19060,7 @@
           <xm:sqref>B100:B113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="85" operator="containsText" id="{f7099c45-d0a6-46c6-94a3-8abc7155be1e}">
+          <x14:cfRule type="containsText" priority="89" operator="containsText" id="{37ac2321-8f66-43e5-8036-0c45d63f9485}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19005,7 +19075,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="86" operator="containsText" id="{2ce0cd5f-f2aa-4521-b0b3-05fa711226ad}">
+          <x14:cfRule type="containsText" priority="90" operator="containsText" id="{28693bb0-3a75-4600-aacd-fbcb01ab80b5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19023,7 +19093,7 @@
           <xm:sqref>B114:B127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="83" operator="containsText" id="{1e8cc33c-98fd-4a16-b78b-429106e6e0ae}">
+          <x14:cfRule type="containsText" priority="87" operator="containsText" id="{5641189c-58fa-444e-8f83-d1f244dabf08}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19038,7 +19108,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="84" operator="containsText" id="{2f59af8f-1739-467f-adf2-bb67ccf2961e}">
+          <x14:cfRule type="containsText" priority="88" operator="containsText" id="{9bcc5ff2-60cc-4e24-aaa1-57046df821bf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19056,7 +19126,7 @@
           <xm:sqref>B128:B141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="81" operator="containsText" id="{ab6c50ac-ee18-4ffd-b079-bd6676340b26}">
+          <x14:cfRule type="containsText" priority="85" operator="containsText" id="{bde77a6d-5735-40f5-b54e-a6a7b7fea616}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19071,7 +19141,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="82" operator="containsText" id="{c570dfaa-3725-45b3-8147-2aab11887ff6}">
+          <x14:cfRule type="containsText" priority="86" operator="containsText" id="{b88bba71-b606-4523-8a59-b3f6523c18ca}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19089,7 +19159,7 @@
           <xm:sqref>B142:B155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="79" operator="containsText" id="{5461d53b-4539-42a3-92db-8d07f753add5}">
+          <x14:cfRule type="containsText" priority="83" operator="containsText" id="{93674b2a-289b-4fd5-acb9-e4cabd380c7f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19104,7 +19174,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="80" operator="containsText" id="{cf1d1f64-1fae-4693-8654-42be0ac594da}">
+          <x14:cfRule type="containsText" priority="84" operator="containsText" id="{b909b3c9-dc1b-4229-9b9f-60e7638979e3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19122,7 +19192,7 @@
           <xm:sqref>B156:B169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="77" operator="containsText" id="{5596a869-1e0d-486d-a243-0e85704a2806}">
+          <x14:cfRule type="containsText" priority="81" operator="containsText" id="{20e9c70f-5082-46ef-8a0b-0593c959cdf6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19137,7 +19207,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="78" operator="containsText" id="{08e32385-fb27-4c71-985a-8179de9eeed2}">
+          <x14:cfRule type="containsText" priority="82" operator="containsText" id="{b01b5613-f3b4-4afd-b23b-7e61466075b2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19155,7 +19225,7 @@
           <xm:sqref>B170:B183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="75" operator="containsText" id="{6452c356-1a60-4f58-91eb-58d76387c505}">
+          <x14:cfRule type="containsText" priority="79" operator="containsText" id="{694c9df4-fb47-4cb4-9d5b-c70440309a18}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19170,7 +19240,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="76" operator="containsText" id="{d5528175-25c9-4749-b304-6f0c1bc79bad}">
+          <x14:cfRule type="containsText" priority="80" operator="containsText" id="{da27927c-b2b3-4365-8eef-6f8a2237d768}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19188,7 +19258,7 @@
           <xm:sqref>B184:B197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="73" operator="containsText" id="{9206edb6-4a99-4031-8bff-71b82d85bb0e}">
+          <x14:cfRule type="containsText" priority="77" operator="containsText" id="{962e5900-9e22-400f-9bbe-057dd2567e4d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19203,7 +19273,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="74" operator="containsText" id="{36c6e642-abd2-4ebc-bb9f-a74653e9dc5b}">
+          <x14:cfRule type="containsText" priority="78" operator="containsText" id="{f39ba5bf-48ca-4ab6-908f-bcfb50aa1469}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19221,7 +19291,7 @@
           <xm:sqref>B198:B211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="71" operator="containsText" id="{07fb4c05-fca1-4928-a95f-b797d85baff6}">
+          <x14:cfRule type="containsText" priority="75" operator="containsText" id="{6c34f78a-4fe3-47bc-b1b7-125afcdcfa1d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19236,7 +19306,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="72" operator="containsText" id="{a24bb424-c29e-415d-b8a2-b364a022bcfa}">
+          <x14:cfRule type="containsText" priority="76" operator="containsText" id="{17c9f006-413c-4b8e-9114-6b8d86a09732}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19254,7 +19324,7 @@
           <xm:sqref>B212:B225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="69" operator="containsText" id="{e0181f78-51e0-4147-bb05-220d8129ad80}">
+          <x14:cfRule type="containsText" priority="73" operator="containsText" id="{ea7b90e9-ddef-44b8-8e36-8d2c54abc997}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19269,7 +19339,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="70" operator="containsText" id="{25603d72-f270-4a6b-9a9b-23f64f30d5f2}">
+          <x14:cfRule type="containsText" priority="74" operator="containsText" id="{7ef0ffb4-0559-4f78-b717-f07b176810ef}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19287,7 +19357,7 @@
           <xm:sqref>B226:B239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="67" operator="containsText" id="{0398f907-568b-4c8c-aa61-9d3c5305545e}">
+          <x14:cfRule type="containsText" priority="71" operator="containsText" id="{b8bf2f7f-06f9-4ff2-8805-145ee4b3b95b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19302,7 +19372,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="68" operator="containsText" id="{5b4c85a8-4b2a-4b99-92f9-21583bc0e705}">
+          <x14:cfRule type="containsText" priority="72" operator="containsText" id="{259bbf91-e300-4c96-92db-879592bb2888}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19320,7 +19390,7 @@
           <xm:sqref>B240:B253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="65" operator="containsText" id="{66003bbb-901f-44a6-8f2e-7c79c3d616e4}">
+          <x14:cfRule type="containsText" priority="69" operator="containsText" id="{9c2a86f0-a45b-4767-a98a-e6c2623954d4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19335,7 +19405,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="66" operator="containsText" id="{6fcab2c0-6b9a-468d-95dd-e15b7bb1cf6f}">
+          <x14:cfRule type="containsText" priority="70" operator="containsText" id="{246b71c4-7e2d-485a-a78a-6c47bda0f325}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19353,7 +19423,7 @@
           <xm:sqref>B254:B267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="125" operator="containsText" id="{160f9676-df1f-4331-a80f-f8664d7c53dc}">
+          <x14:cfRule type="containsText" priority="129" operator="containsText" id="{c7f830ed-79d8-476f-965a-4451eecbcd90}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19368,7 +19438,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="126" operator="containsText" id="{0fd15b92-18fd-47ab-93a1-e3b218e31cd2}">
+          <x14:cfRule type="containsText" priority="130" operator="containsText" id="{3a966e2c-f54a-4048-ace1-7e960cb345d3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19386,7 +19456,7 @@
           <xm:sqref>G184:G195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="119" operator="containsText" id="{43f8da4c-5147-446e-b122-e36eeb605ef1}">
+          <x14:cfRule type="containsText" priority="123" operator="containsText" id="{d36a0901-85be-4c22-a37a-631a78917666}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19401,7 +19471,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="120" operator="containsText" id="{6bf592ab-11ee-4a46-b815-7d9d44ca194a}">
+          <x14:cfRule type="containsText" priority="124" operator="containsText" id="{dce9b944-e4a8-4402-ad84-debd5ff1066d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19419,7 +19489,7 @@
           <xm:sqref>G198:G209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="113" operator="containsText" id="{b76b267b-6264-47f2-9120-a9b8e2893d31}">
+          <x14:cfRule type="containsText" priority="117" operator="containsText" id="{522a90e3-e4c9-44fd-b2e3-acaf4587cd4e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19434,7 +19504,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="114" operator="containsText" id="{d8b63ea8-61e4-456f-9af5-5118c15d3c3d}">
+          <x14:cfRule type="containsText" priority="118" operator="containsText" id="{09768b02-2c41-47a5-a99b-07b2778ba704}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19452,7 +19522,7 @@
           <xm:sqref>G212:G223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="107" operator="containsText" id="{59168fb7-0342-492c-8075-e3ce4c654325}">
+          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{15498f82-b6c4-41a1-91cb-4484033d32d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19467,7 +19537,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{dbcff081-bbd2-42ef-9742-6485777fc240}">
+          <x14:cfRule type="containsText" priority="112" operator="containsText" id="{c303b1d8-643b-4210-a4bc-766f7172de93}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19485,7 +19555,7 @@
           <xm:sqref>G226:G237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="101" operator="containsText" id="{71040a1a-ab14-4ecf-92e2-43d12847bcff}">
+          <x14:cfRule type="containsText" priority="105" operator="containsText" id="{81f89ffa-1522-406e-be18-60beccb74bad}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19500,7 +19570,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="102" operator="containsText" id="{e5dfd676-4eca-421c-a311-b44ed5c710ce}">
+          <x14:cfRule type="containsText" priority="106" operator="containsText" id="{2872d686-8568-406a-97fc-5fbb279bf124}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19518,7 +19588,7 @@
           <xm:sqref>G240:G251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="95" operator="containsText" id="{4cfe94b4-e4b9-4153-bcfc-28dd6b0a5405}">
+          <x14:cfRule type="containsText" priority="99" operator="containsText" id="{f4595b9f-9497-4c23-bb94-4a30b904426d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19533,7 +19603,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="96" operator="containsText" id="{55f9824c-bc21-493a-a384-e374d76fafe8}">
+          <x14:cfRule type="containsText" priority="100" operator="containsText" id="{19794811-44a3-45d6-9d0e-d69156c32b54}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19551,7 +19621,7 @@
           <xm:sqref>G254:G265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="883" operator="containsText" id="{8cae9520-3e70-464d-a532-e9daba8445ed}">
+          <x14:cfRule type="containsText" priority="887" operator="containsText" id="{e2d98991-4739-446a-9125-538f6b44200a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K69)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19566,7 +19636,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="884" operator="containsText" id="{7cd2b7a8-f64f-4630-87ca-5107d276b8ae}">
+          <x14:cfRule type="containsText" priority="888" operator="containsText" id="{6fdec2f8-26d3-488b-9e26-c11b5dc65dc9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K69)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19584,7 +19654,7 @@
           <xm:sqref>K69:K70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="885" operator="containsText" id="{d1acf69f-2a03-4153-878e-61e273c94c76}">
+          <x14:cfRule type="containsText" priority="889" operator="containsText" id="{a0ae69b8-3b66-4bd9-90ba-e3e8c09a9c1c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19599,7 +19669,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="890" operator="containsText" id="{e3ecf6ce-cb1e-4cc6-88ae-623393ff5f8d}">
+          <x14:cfRule type="containsText" priority="894" operator="containsText" id="{ed582c2f-61ca-497f-bc5c-e430025e466c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19617,7 +19687,7 @@
           <xm:sqref>L22:M22 M36 J38:M38 K21:M21 J31:M32 A29:A41 L58:M58 L67:M67 A71 L69:M70 A1:A27 E72:F72 J28:M28 A43:A55 J42:M42 A57:A69 J56:M56 J70 C85:F85 L73:M73 C73:F83 L83:M84 J84 L96:M96 J96:J97 M142 M147 C134:F134 J142:K142 K147 A284:F1048576 C197:D197 F197 E195 H197 H284:M1048576 H83:J83 H73:J73 H74:M82 H85:M85 H57:M57 H43:M55 H69:J69 H71:M72 H68:M68 H67:J67 H59:M66 H58:J58 H39:M41 H33:M35 H38 H37:M37 H36:K36 H21 H23:M27 H22:J22 H29:M29 H31:H32 H1:M20 C57:F69 C43:F55 C71:F71 C31:F41 C29:F29 C1:F27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="91" operator="containsText" id="{95807f59-adae-489f-bd51-a5ae74496a7d}">
+          <x14:cfRule type="containsText" priority="95" operator="containsText" id="{fed4ec08-b2f2-45fc-8703-d16394e6b66b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19632,7 +19702,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="92" operator="containsText" id="{40773776-cdda-4cd3-970a-6f486f295d8b}">
+          <x14:cfRule type="containsText" priority="96" operator="containsText" id="{de87173e-94ea-42f6-899a-c66a07f9a233}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19650,7 +19720,7 @@
           <xm:sqref>B1:B2 B4 B6 B8 B10 B12 B14 B16:B85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="163" operator="containsText" id="{98f5fb23-4399-4201-8731-9ebdbc9417d7}">
+          <x14:cfRule type="containsText" priority="167" operator="containsText" id="{db7c03a4-d33e-4268-8d74-9d8a181cf84a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19665,7 +19735,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="164" operator="containsText" id="{1df6a345-4906-48b0-a2cc-532180ac4cb0}">
+          <x14:cfRule type="containsText" priority="168" operator="containsText" id="{e657ab6d-7cfb-42d9-a3c4-6ceeeffeba14}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19683,7 +19753,7 @@
           <xm:sqref>G31 G29 G33:G41 G1:G27 G57:G69 G71:G85 G96:G97 G284:G1048576 G197 G43:G55</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="63" operator="containsText" id="{0039df48-552d-4715-bc52-0a7cde00a514}">
+          <x14:cfRule type="containsText" priority="67" operator="containsText" id="{4807ce80-b5ac-4f1a-9ddc-ac04f847aba0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B3)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19698,7 +19768,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="64" operator="containsText" id="{3caefcaa-3865-4d70-bff0-5bbd6b2edd3c}">
+          <x14:cfRule type="containsText" priority="68" operator="containsText" id="{635c63b0-5036-4e41-bf1a-139f194331fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B3)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19716,7 +19786,7 @@
           <xm:sqref>B3 B5 B7 B9 B11 B13 B15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="879" operator="containsText" id="{03ec8b68-1e7d-478d-9a24-1a534019c4c9}">
+          <x14:cfRule type="containsText" priority="883" operator="containsText" id="{50a856b7-0178-4f71-b5bb-bcf11837f985}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A28)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19731,7 +19801,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="880" operator="containsText" id="{289c038f-37fb-447d-a4fe-c45eaa651873}">
+          <x14:cfRule type="containsText" priority="884" operator="containsText" id="{665abc23-5892-47a0-8f08-45e770041cec}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A28)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19749,7 +19819,7 @@
           <xm:sqref>A28 H28:I28 C28:F28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="877" operator="containsText" id="{93854783-747a-4d8c-8911-1b1efee0f83f}">
+          <x14:cfRule type="containsText" priority="881" operator="containsText" id="{bbdd4d6b-58ef-4b3b-83b3-125659ce3c9c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A42)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19764,7 +19834,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="878" operator="containsText" id="{a4d13208-ef99-467f-aff9-83ef85977e03}">
+          <x14:cfRule type="containsText" priority="882" operator="containsText" id="{0e93222e-9a52-43e5-b356-943a8c18bac7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A42)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19782,7 +19852,7 @@
           <xm:sqref>A42 H42:I42 C42:F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="875" operator="containsText" id="{6fe918e8-464d-4348-a395-41927bd5fafa}">
+          <x14:cfRule type="containsText" priority="879" operator="containsText" id="{a3982c2a-59ba-4fea-badb-7acfd739310b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A56)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19797,7 +19867,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="876" operator="containsText" id="{95a24316-f06e-430e-b8a6-b3fdef9f68bc}">
+          <x14:cfRule type="containsText" priority="880" operator="containsText" id="{a53d5a0a-31a3-487c-8059-33b34e0a5b8e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A56)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19815,7 +19885,7 @@
           <xm:sqref>A56 H56:I56 C56:F56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="873" operator="containsText" id="{7786fafd-6732-47ff-b058-eaafb32ae857}">
+          <x14:cfRule type="containsText" priority="877" operator="containsText" id="{bb43d91f-541f-4730-8437-d6f13911523b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A70)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19830,7 +19900,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="874" operator="containsText" id="{06620eb1-880a-464f-a0a6-4c1c5f95a78c}">
+          <x14:cfRule type="containsText" priority="878" operator="containsText" id="{df838723-9db5-4ea6-bac1-9ed3978c247c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A70)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19848,7 +19918,7 @@
           <xm:sqref>A70 H70:I70 C70:F70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="881" operator="containsText" id="{1eaa76f4-627a-46ac-b73c-3fd9ccc05d08}">
+          <x14:cfRule type="containsText" priority="885" operator="containsText" id="{c73be821-df78-484d-a87f-5603b0493391}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A72)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19863,7 +19933,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="882" operator="containsText" id="{c23aca28-3a61-40a2-acb5-a338e7a90b7b}">
+          <x14:cfRule type="containsText" priority="886" operator="containsText" id="{4ee43f24-498a-4ae2-b1c6-f0a48c00a0d2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A72)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19881,7 +19951,7 @@
           <xm:sqref>A72:A83 A85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="871" operator="containsText" id="{3c4e383f-ef8e-41da-b459-9f0d848c0fd3}">
+          <x14:cfRule type="containsText" priority="875" operator="containsText" id="{113cd0a6-5a30-4fb1-aed3-e86b8699b27d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A84)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19896,7 +19966,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="872" operator="containsText" id="{bbcacdbd-96c0-4b64-aa46-f28b92cc0e07}">
+          <x14:cfRule type="containsText" priority="876" operator="containsText" id="{159e4d62-5f05-4c30-82f4-3aff768b5a6e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A84)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19914,7 +19984,7 @@
           <xm:sqref>A84 H84:I84 C84:F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="867" operator="containsText" id="{bd7f7e87-c1ed-474a-b034-d264978e30df}">
+          <x14:cfRule type="containsText" priority="871" operator="containsText" id="{37a976df-70e0-4ac9-8bf8-3972adcf4f62}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19929,7 +19999,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="868" operator="containsText" id="{7a8e4d74-50b7-4565-b499-92877134e790}">
+          <x14:cfRule type="containsText" priority="872" operator="containsText" id="{84c40a44-1288-4004-af66-7a107eff5d80}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19947,7 +20017,7 @@
           <xm:sqref>A86:A97 A99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="869" operator="containsText" id="{0580f2d5-1188-42c2-acc0-d547b1a729e5}">
+          <x14:cfRule type="containsText" priority="873" operator="containsText" id="{2af20f61-25d1-464e-b1c3-c60459d22b0c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19962,7 +20032,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="870" operator="containsText" id="{40d8e166-8557-44fe-8f99-88a28fe320e1}">
+          <x14:cfRule type="containsText" priority="874" operator="containsText" id="{f649de5e-7d45-4c48-b067-3f2d4b1fe9df}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19980,7 +20050,7 @@
           <xm:sqref>E86:F86 C99:F99 J98:M98 M97 M87 J92:M93 C87:F97 H96:H97 H92:H93 H87:K87 H88:M91 H94:M95 H99:M99 H86:M86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="153" operator="containsText" id="{0aaa9e23-baee-42a8-8c06-90e83ec2269a}">
+          <x14:cfRule type="containsText" priority="157" operator="containsText" id="{5788f371-28f1-4759-abab-a780f9c4bc45}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19995,7 +20065,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="154" operator="containsText" id="{5af56f2f-00ee-402a-b4bd-c8b6aa11e0fe}">
+          <x14:cfRule type="containsText" priority="158" operator="containsText" id="{8845b73b-a409-4366-b9b0-c0a4cbb47bb7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20013,7 +20083,7 @@
           <xm:sqref>G99 G86:G95</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="865" operator="containsText" id="{084ab000-ff52-4ae8-80b4-d1d06bc01fad}">
+          <x14:cfRule type="containsText" priority="869" operator="containsText" id="{ad06bfa6-c6e2-4a92-932a-e7edfec145d3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A98)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20028,7 +20098,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="866" operator="containsText" id="{abdfaf25-953d-4a59-91cf-cbd34e7763ae}">
+          <x14:cfRule type="containsText" priority="870" operator="containsText" id="{64735b89-7c8b-4e55-896e-6611edda3731}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A98)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20046,7 +20116,7 @@
           <xm:sqref>A98 H98:I98 C98:F98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="849" operator="containsText" id="{3645b6ff-b6a0-42cd-91e6-38d3857b2553}">
+          <x14:cfRule type="containsText" priority="853" operator="containsText" id="{ee18761b-7d15-45eb-b0f9-b6fcc4fae749}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20061,7 +20131,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="850" operator="containsText" id="{5652fd96-d124-4520-812f-fa189acdcc98}">
+          <x14:cfRule type="containsText" priority="854" operator="containsText" id="{61b81a55-240f-4a72-a8f1-2c94613bb34f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20079,7 +20149,7 @@
           <xm:sqref>A100:A111 A113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="851" operator="containsText" id="{90262ff8-6d80-4b38-b41b-e651ac7b9cd8}">
+          <x14:cfRule type="containsText" priority="855" operator="containsText" id="{89aaf2f5-2193-4760-a925-d0125e4e85a0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20094,7 +20164,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="852" operator="containsText" id="{ceb60df9-4a8e-4d7e-b5ff-36cec03d311f}">
+          <x14:cfRule type="containsText" priority="856" operator="containsText" id="{6e173993-3d22-4755-a21b-7c135baa6cf9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20112,7 +20182,7 @@
           <xm:sqref>E100:F100 C113:F113 J112:M112 J111 M111 J110:M110 M101 J106:M107 C101:F111 J102:M102 H102 H106:H107 H101:K101 H103:M105 H110:H111 H108:M109 H113:M113 H100:M100</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="149" operator="containsText" id="{bdb10b4f-8a01-4f7e-8eaf-3919383eeb43}">
+          <x14:cfRule type="containsText" priority="153" operator="containsText" id="{d2eeec47-a1eb-480e-9b28-dce4aed135fc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20127,7 +20197,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="150" operator="containsText" id="{4f7b4171-f5f7-4697-97d7-4870b9250259}">
+          <x14:cfRule type="containsText" priority="154" operator="containsText" id="{c78ddee1-8858-4471-b0db-69c325e975b5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20145,7 +20215,7 @@
           <xm:sqref>G113 G100:G111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="847" operator="containsText" id="{6521bceb-ca69-4342-9b1d-75055cae2804}">
+          <x14:cfRule type="containsText" priority="851" operator="containsText" id="{ff091134-6877-4943-ad43-a105604314a2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20160,7 +20230,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="848" operator="containsText" id="{e561461f-0dde-429b-ba1a-662d4a42bb91}">
+          <x14:cfRule type="containsText" priority="852" operator="containsText" id="{ac6d76da-3744-405e-b8f7-aa3545e41fbe}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20178,7 +20248,7 @@
           <xm:sqref>A112 H112 C112:F112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="805" operator="containsText" id="{b4ccae74-cb03-4c1f-b301-0bf0349359af}">
+          <x14:cfRule type="containsText" priority="809" operator="containsText" id="{ced1d119-f3ab-432f-8442-b2e9d3c082b2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20193,7 +20263,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="806" operator="containsText" id="{ba6cb1a5-11ce-4ed5-8091-6b2b14045052}">
+          <x14:cfRule type="containsText" priority="810" operator="containsText" id="{427fc127-f33e-46dc-aa69-57e1ab8befb1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20211,7 +20281,7 @@
           <xm:sqref>A114:A125 A127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="807" operator="containsText" id="{e5f54fa2-9deb-4d57-9b79-feb520d2feef}">
+          <x14:cfRule type="containsText" priority="811" operator="containsText" id="{494f474b-a962-4656-a364-09f4e0ac138f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20226,7 +20296,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="808" operator="containsText" id="{ecf7803c-962f-4a0a-967e-f45e5be94550}">
+          <x14:cfRule type="containsText" priority="812" operator="containsText" id="{84527ada-2eb5-4ea4-a97c-2022a91093e8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20244,7 +20314,7 @@
           <xm:sqref>E114:F114 C127:F127 J126:M126 J125 M125 M115 J116:M116 J114:M114 C115:F125 J120:M124 H120:H125 H116 H115:K115 H117:M119 H127:M127 H114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="145" operator="containsText" id="{12a376fa-e38a-402a-997d-b7eccd1c9541}">
+          <x14:cfRule type="containsText" priority="149" operator="containsText" id="{00d7c7eb-b057-4a76-a710-b3137419460e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20259,7 +20329,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="146" operator="containsText" id="{e541d2fd-b886-4cbf-8e9e-4436a67dd062}">
+          <x14:cfRule type="containsText" priority="150" operator="containsText" id="{3982a6d4-4e8d-409d-8dd1-19f69aca815f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20277,7 +20347,7 @@
           <xm:sqref>G127 G114:G125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="803" operator="containsText" id="{1e40c565-8790-4f50-9a7b-61465051f701}">
+          <x14:cfRule type="containsText" priority="807" operator="containsText" id="{b364f66d-61bb-4a09-8b49-3a470c5dd8c0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20292,7 +20362,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="804" operator="containsText" id="{a6bb9b83-b420-4529-9bf1-6fff85080daa}">
+          <x14:cfRule type="containsText" priority="808" operator="containsText" id="{3eb5667b-c4c8-42a5-9dcd-e15752c47092}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20310,7 +20380,7 @@
           <xm:sqref>A126 H126 C126:F126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="765" operator="containsText" id="{933bf83a-efd9-4fc1-9041-c4cca8b924b7}">
+          <x14:cfRule type="containsText" priority="769" operator="containsText" id="{28c1121d-1cc9-4a75-9007-e96b3b06905c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20325,7 +20395,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="766" operator="containsText" id="{0b1fe669-065e-474e-8525-d7b188dbe294}">
+          <x14:cfRule type="containsText" priority="770" operator="containsText" id="{a29328cd-57ff-44ad-a8b6-f959ef101c32}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20343,7 +20413,7 @@
           <xm:sqref>A128:A139 A141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="767" operator="containsText" id="{e011412e-b84e-4e73-b284-e8c1089c31e3}">
+          <x14:cfRule type="containsText" priority="771" operator="containsText" id="{f1df021e-9250-463e-a809-0609b15bbdbe}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20358,7 +20428,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="768" operator="containsText" id="{3548fd46-8af2-4559-adcc-f3fb9c4ecf44}">
+          <x14:cfRule type="containsText" priority="772" operator="containsText" id="{45363826-fd0f-425a-90f4-02a71e0424d3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20376,7 +20446,7 @@
           <xm:sqref>E128:F128 C141:F141 J140:M140 J139 M139 M129 J130:M130 J128:M128 C129:F133 J134:M138 J133 M133 J129:K129 C135:F139 H133:H139 H131:M132 H141:M141 H128:H130</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="141" operator="containsText" id="{c91d778a-6292-4227-9c83-2e462f86ad2c}">
+          <x14:cfRule type="containsText" priority="145" operator="containsText" id="{cffc2c02-9866-4808-a22f-2e4418ca5a7f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20391,7 +20461,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="142" operator="containsText" id="{d19ddcf0-bfe6-47c5-be73-3f6250ca10bb}">
+          <x14:cfRule type="containsText" priority="146" operator="containsText" id="{f25ef0b3-3f5f-4994-a753-3286d05c75b6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20409,7 +20479,7 @@
           <xm:sqref>G141 G128:G139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="763" operator="containsText" id="{9059cd52-5609-4834-9dda-d8fa1c38345c}">
+          <x14:cfRule type="containsText" priority="767" operator="containsText" id="{e3c254fb-b489-4e91-877a-ce7e827b32ad}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20424,7 +20494,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="764" operator="containsText" id="{1b7cbcbe-be2b-4a37-ba1a-d33af6cd9413}">
+          <x14:cfRule type="containsText" priority="768" operator="containsText" id="{dd8f774c-aa19-4d47-a961-0bd46e6a1d0a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20442,7 +20512,7 @@
           <xm:sqref>A140 H140 C140:F140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="721" operator="containsText" id="{f583524d-6cb8-4a92-af0f-4ea028cfb04f}">
+          <x14:cfRule type="containsText" priority="725" operator="containsText" id="{84324c1e-4732-4dca-a0b9-9dea26f39ca9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20457,7 +20527,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="722" operator="containsText" id="{55815cd1-4aee-4142-9ab2-0d7edb2668cb}">
+          <x14:cfRule type="containsText" priority="726" operator="containsText" id="{86116256-a3bf-4d9c-9b36-c1511512c493}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20475,7 +20545,7 @@
           <xm:sqref>A142:A153 A155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="723" operator="containsText" id="{1e05f633-2aa5-499d-8aef-1404f2514d5a}">
+          <x14:cfRule type="containsText" priority="727" operator="containsText" id="{53478697-26f4-4e56-8606-0ebde2f1de87}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20490,7 +20560,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="724" operator="containsText" id="{c92d53c3-2b28-4f51-83fd-0f14da2dd054}">
+          <x14:cfRule type="containsText" priority="728" operator="containsText" id="{e9be80ea-9cc5-4a70-a845-e222fe006ace}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20508,7 +20578,7 @@
           <xm:sqref>E142:F142 C155:F155 J153 M153 J144:M144 J148:M152 J147 J154:M155 C143:F153 J146:M146 H146:H153 H145:M145 H155 H142:H144</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="137" operator="containsText" id="{734467fb-8def-40ea-b22f-d5d3e72b6bf1}">
+          <x14:cfRule type="containsText" priority="141" operator="containsText" id="{580650eb-058e-4a9b-adb4-8b3640c7b6fc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20523,7 +20593,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="138" operator="containsText" id="{71e32526-6b9e-4116-9dcf-501b13e2ede5}">
+          <x14:cfRule type="containsText" priority="142" operator="containsText" id="{a0b31e18-fd55-4023-ad64-4d9b68f9bc7f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20541,7 +20611,7 @@
           <xm:sqref>G155 G142:G153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="719" operator="containsText" id="{d8d5ba61-2e56-4115-b576-f201ae278dff}">
+          <x14:cfRule type="containsText" priority="723" operator="containsText" id="{6f09e35d-69bd-4c93-953d-25872d6ca131}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20556,7 +20626,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="720" operator="containsText" id="{22c4f1ab-f87d-494f-80a8-8441bb9b19a7}">
+          <x14:cfRule type="containsText" priority="724" operator="containsText" id="{ad0fba92-37f7-4e4b-b9eb-98130ff1a401}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20574,7 +20644,7 @@
           <xm:sqref>A154 H154 C154:F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="667" operator="containsText" id="{94732e2e-ed9f-4b3b-8925-d31dd76e537c}">
+          <x14:cfRule type="containsText" priority="671" operator="containsText" id="{caa635c5-86e9-4d8e-9423-db6d74fd1989}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20589,7 +20659,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="668" operator="containsText" id="{0818e208-2089-45d3-b309-9a549f7c68c3}">
+          <x14:cfRule type="containsText" priority="672" operator="containsText" id="{046c21e6-d1ef-4631-b173-4f0539578194}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20607,7 +20677,7 @@
           <xm:sqref>A156:A167 A169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="669" operator="containsText" id="{9d7ab717-2ec0-42d0-804c-489c45efa8ef}">
+          <x14:cfRule type="containsText" priority="673" operator="containsText" id="{966cca24-eb9d-4e15-a08a-318978aff2ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20622,7 +20692,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="670" operator="containsText" id="{e6dd016d-abcb-45f6-8f4a-66836a0758f5}">
+          <x14:cfRule type="containsText" priority="674" operator="containsText" id="{db70bc40-6c61-441a-9c7c-f652b9fab7a1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20640,7 +20710,7 @@
           <xm:sqref>E156:F156 C169:F169 J167 M167 J158:M158 J162:M166 J161 J168:M169 C157:F167 J160:M160 H160:H167 H159:M159 H169 H156:H158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="133" operator="containsText" id="{3f278bdb-3c73-43be-8760-f7e3e7bcd911}">
+          <x14:cfRule type="containsText" priority="137" operator="containsText" id="{b3b91a03-3f74-4a58-88a1-a0b3746bce63}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20655,7 +20725,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="134" operator="containsText" id="{8148706f-b953-4db4-abc2-c3db82bbc26b}">
+          <x14:cfRule type="containsText" priority="138" operator="containsText" id="{2189249d-114b-4bbe-b418-4a91ec7b4a50}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20673,7 +20743,7 @@
           <xm:sqref>G169 G156:G167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="671" operator="containsText" id="{9e775667-0ebc-4694-9038-e5e21384320b}">
+          <x14:cfRule type="containsText" priority="675" operator="containsText" id="{886ba147-83b3-4827-940d-0eea08bd9f20}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20688,7 +20758,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="672" operator="containsText" id="{08a9b1ea-a56f-493f-b79f-0b40ecbde13c}">
+          <x14:cfRule type="containsText" priority="676" operator="containsText" id="{2c5c1d16-c30c-4c8f-b073-6b7dbf1a218a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20706,7 +20776,7 @@
           <xm:sqref>M156 M161 J156:K156 K161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="665" operator="containsText" id="{63dad340-3efe-4ae5-aa26-8d4e8522f117}">
+          <x14:cfRule type="containsText" priority="669" operator="containsText" id="{55aba8e2-d985-42de-8a56-4a330dc4abc3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20721,7 +20791,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="666" operator="containsText" id="{f3c5bb6f-3ea8-46ef-bc35-d55348c13738}">
+          <x14:cfRule type="containsText" priority="670" operator="containsText" id="{60e59a9b-5fdd-434a-a6e4-5e06e006d152}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20739,7 +20809,7 @@
           <xm:sqref>A168 H168 C168:F168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="621" operator="containsText" id="{bde4feb2-d786-431d-aa98-ca9566f9f0f6}">
+          <x14:cfRule type="containsText" priority="625" operator="containsText" id="{b462e88d-9775-441e-aa04-b2fb3d7e83a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20754,7 +20824,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="622" operator="containsText" id="{33be320d-3461-486c-94bb-67d30a466dec}">
+          <x14:cfRule type="containsText" priority="626" operator="containsText" id="{da99a171-05a2-4578-b31a-75528e8d39e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20772,7 +20842,7 @@
           <xm:sqref>A170:A181 A183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="623" operator="containsText" id="{8e876414-64a6-4669-adf2-9d8f5a717033}">
+          <x14:cfRule type="containsText" priority="627" operator="containsText" id="{ce299645-2851-4a23-b6a4-b4a9a6a75f54}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20787,7 +20857,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="624" operator="containsText" id="{02077c74-cf33-4ae8-b019-0b38a29cf89f}">
+          <x14:cfRule type="containsText" priority="628" operator="containsText" id="{b86dd520-9ae4-4caf-9715-c28433699c6e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20805,7 +20875,7 @@
           <xm:sqref>E170:F170 C183:F183 J181 M181 J172:M172 J176:M180 J175 J182:M183 C171:F181 J174:M174 H174:H181 H173:M173 H183 H170:H172</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="129" operator="containsText" id="{527b9ef6-7042-4451-bf7d-25ac91de2892}">
+          <x14:cfRule type="containsText" priority="133" operator="containsText" id="{1cee3b70-c0ab-4940-b299-b93abbd948f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20820,7 +20890,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="130" operator="containsText" id="{5d91e150-a425-4721-9fcd-705b99f8405d}">
+          <x14:cfRule type="containsText" priority="134" operator="containsText" id="{3d3756b2-3556-4b21-aeaa-dcd0b513cf60}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20838,7 +20908,7 @@
           <xm:sqref>G183 G170:G181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="625" operator="containsText" id="{5706ff62-bc4b-4431-b2ef-0df881fd3358}">
+          <x14:cfRule type="containsText" priority="629" operator="containsText" id="{eb34074c-79e4-4870-806b-73ac2cb04a58}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20853,7 +20923,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="626" operator="containsText" id="{4e1762fa-ade1-46fc-8098-6b64613f4ef7}">
+          <x14:cfRule type="containsText" priority="630" operator="containsText" id="{e9228857-0d4f-4d1f-ad4f-f0b5725a02a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20871,7 +20941,7 @@
           <xm:sqref>M170 M175 J170:K170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="619" operator="containsText" id="{be3350ce-68db-4ad8-af5d-46615f611f6c}">
+          <x14:cfRule type="containsText" priority="623" operator="containsText" id="{e8da05eb-33b9-44ee-b18b-607aa00e1293}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20886,7 +20956,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="620" operator="containsText" id="{5618417d-2fa7-4b5b-ac30-1b3865b80b0c}">
+          <x14:cfRule type="containsText" priority="624" operator="containsText" id="{67977d46-d38a-4171-a5f5-62a10ca0322d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20904,7 +20974,7 @@
           <xm:sqref>A182 H182 C182:F182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="567" operator="containsText" id="{1c400b87-6930-4851-a273-11c61d0552b6}">
+          <x14:cfRule type="containsText" priority="571" operator="containsText" id="{1dc67001-463b-4842-9aea-e3a6e27b9913}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20919,7 +20989,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="568" operator="containsText" id="{e5a9c49c-1b4e-4ab5-8509-754ce3191b03}">
+          <x14:cfRule type="containsText" priority="572" operator="containsText" id="{13c8cb87-ed64-4ac9-9bcf-1558a616bb9b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20937,7 +21007,7 @@
           <xm:sqref>A184:A195 A197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="569" operator="containsText" id="{963bd516-3dcd-4b27-a4bc-66beb03849fb}">
+          <x14:cfRule type="containsText" priority="573" operator="containsText" id="{e52debce-b1c1-4f24-aad6-e79039155720}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20952,7 +21022,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="570" operator="containsText" id="{760de46c-1002-4dc8-98f4-96dffeedccdc}">
+          <x14:cfRule type="containsText" priority="574" operator="containsText" id="{625b5ed1-59ed-4706-9ac2-3c3b704c6a17}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20970,7 +21040,7 @@
           <xm:sqref>E184:F184 J195 M195 J186:M186 J190:M194 J189 J196:M197 C185:F191 J188:M188 C193:F194 C192:D192 F192 C195:D195 F195 H188:H195 H187:M187 H184:H186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="571" operator="containsText" id="{ae1da254-449f-4a0d-9b76-5439aef90aba}">
+          <x14:cfRule type="containsText" priority="575" operator="containsText" id="{3c28f92c-6406-4f73-81e9-8c1fa0ecd983}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20985,7 +21055,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="572" operator="containsText" id="{32af5bef-286a-4641-b32f-c3a081b2affd}">
+          <x14:cfRule type="containsText" priority="576" operator="containsText" id="{47128c5a-90fe-4413-ba0b-77381a308757}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21003,7 +21073,7 @@
           <xm:sqref>M184 M189 J184:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="565" operator="containsText" id="{3e8b2b4d-b44f-4855-ac6c-9a91547910ef}">
+          <x14:cfRule type="containsText" priority="569" operator="containsText" id="{fc9decec-800a-4e36-96cd-f89fdf09d7a8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21018,7 +21088,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="566" operator="containsText" id="{77fea764-c425-4839-b706-1752815e15f9}">
+          <x14:cfRule type="containsText" priority="570" operator="containsText" id="{ab616c6b-ab6c-4119-918a-29946c176bf3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21036,7 +21106,7 @@
           <xm:sqref>A196 H196 C196:F196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="513" operator="containsText" id="{05567e8c-c2fd-494a-ae48-046d523dfcbd}">
+          <x14:cfRule type="containsText" priority="517" operator="containsText" id="{48f64060-77e6-428a-a2db-e70fce00dab3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21051,7 +21121,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="514" operator="containsText" id="{2b4f7d34-b16c-4b94-86ba-c8a2af27e24c}">
+          <x14:cfRule type="containsText" priority="518" operator="containsText" id="{ae145444-6ca5-4597-8553-93194ef88953}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21069,7 +21139,7 @@
           <xm:sqref>A198:A209 A211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="515" operator="containsText" id="{6ee23ad4-9adf-49b0-a2de-d69c43e6b66f}">
+          <x14:cfRule type="containsText" priority="519" operator="containsText" id="{c5d1b229-b282-4e85-b13c-8415ad58c97f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21084,7 +21154,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="516" operator="containsText" id="{02ca6311-d34e-42dc-9b98-26ab51fec2f7}">
+          <x14:cfRule type="containsText" priority="520" operator="containsText" id="{8c4a91f6-e374-4831-9d8b-d91e57df32c0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21102,7 +21172,7 @@
           <xm:sqref>E198:F198 J209 M209 J200:M200 J204:M208 J203 J210:M211 C199:F204 J202:M202 C207:F208 C209:D209 C205:D206 F206 H202:H209 H201:M201 H198:H200</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="517" operator="containsText" id="{f9faad0b-01f3-4158-80bf-45fe52c0e375}">
+          <x14:cfRule type="containsText" priority="521" operator="containsText" id="{86c0d695-4a2f-4ee0-843a-049d2ab0cf7d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21117,7 +21187,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="518" operator="containsText" id="{6e5526d8-e20a-4de0-86b3-0e5da917a507}">
+          <x14:cfRule type="containsText" priority="522" operator="containsText" id="{19f84bc2-44c9-4043-8fc2-77d9f973ff80}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21135,7 +21205,7 @@
           <xm:sqref>M198 M203 J198:K198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="511" operator="containsText" id="{c36eec62-c895-437d-99eb-dbb65f56e2ec}">
+          <x14:cfRule type="containsText" priority="515" operator="containsText" id="{c3573588-b472-4eee-9701-e7c6c678ce46}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21150,7 +21220,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="512" operator="containsText" id="{39555b71-9bb3-42fc-9dce-37cc98c12d23}">
+          <x14:cfRule type="containsText" priority="516" operator="containsText" id="{f9b5bb94-b345-4f7f-b5a1-392f21a4ead6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21168,7 +21238,7 @@
           <xm:sqref>A210 H210 C210:F210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="519" operator="containsText" id="{0e0548c7-24a8-4e5f-abc9-77d2efdebfac}">
+          <x14:cfRule type="containsText" priority="523" operator="containsText" id="{661f79f3-607a-448a-a0d1-f02f0a695b9f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21183,7 +21253,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="520" operator="containsText" id="{93d32757-4a25-4765-bbdb-59a5d79153fb}">
+          <x14:cfRule type="containsText" priority="524" operator="containsText" id="{8bcea746-2bee-442d-9529-5d80d97104b4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21201,7 +21271,7 @@
           <xm:sqref>C211:D211 F211 H211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="459" operator="containsText" id="{bf9cbb9c-26d5-49dd-84e0-0e383db6fe85}">
+          <x14:cfRule type="containsText" priority="463" operator="containsText" id="{41f103a0-f538-42e4-a9ad-453700e453a4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21216,7 +21286,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="460" operator="containsText" id="{05a600ec-a227-49c3-975e-a457f5710519}">
+          <x14:cfRule type="containsText" priority="464" operator="containsText" id="{91e05480-7bd9-4c61-a265-8761f9b12424}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21234,7 +21304,7 @@
           <xm:sqref>A212:A223 A225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="461" operator="containsText" id="{4a2bcc1e-3de5-4245-a22d-325325cfaccb}">
+          <x14:cfRule type="containsText" priority="465" operator="containsText" id="{016124af-b3fb-4ac1-8389-86f6379028ff}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21249,7 +21319,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="462" operator="containsText" id="{13eba75e-bebb-4a14-9695-b1c12a7600a2}">
+          <x14:cfRule type="containsText" priority="466" operator="containsText" id="{0ac4c39f-5fe2-4f7a-81cc-65985d781b0d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21267,7 +21337,7 @@
           <xm:sqref>E212:F212 J223 M223 J214:M214 J218:M222 J217 J224:M225 C213:F218 J216:M216 C221:F222 C223:D223 C219:D220 F220 H216:H223 H215:M215 H212:H214</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="463" operator="containsText" id="{f8f94052-94d3-488d-ae85-de2c904fb940}">
+          <x14:cfRule type="containsText" priority="467" operator="containsText" id="{569cf088-a36c-4a34-bb76-5a661725968b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21282,7 +21352,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="464" operator="containsText" id="{e5b188ec-3df7-4cf2-a402-53cbbd13fdff}">
+          <x14:cfRule type="containsText" priority="468" operator="containsText" id="{4745cc2a-7d67-49d3-90e8-37be69749acc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21300,7 +21370,7 @@
           <xm:sqref>M212 M217 J212:K212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="457" operator="containsText" id="{05cac14b-a236-486f-ac1e-a4917396c163}">
+          <x14:cfRule type="containsText" priority="461" operator="containsText" id="{525aa60f-6a04-4428-9c4b-5b6967babde7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21315,7 +21385,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="458" operator="containsText" id="{81aab1b8-0ccd-425f-93c6-0b3596fe9abb}">
+          <x14:cfRule type="containsText" priority="462" operator="containsText" id="{022e0544-77d4-481a-a63e-4ce7e85fbf27}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21333,7 +21403,7 @@
           <xm:sqref>A224 H224 C224:F224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="465" operator="containsText" id="{c9a06d59-cab6-4170-9bca-3e7bdae58cff}">
+          <x14:cfRule type="containsText" priority="469" operator="containsText" id="{4597b861-0b24-4031-970d-72b321821480}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21348,7 +21418,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="466" operator="containsText" id="{433d55b1-88f8-4c66-aa83-f721e8660fa2}">
+          <x14:cfRule type="containsText" priority="470" operator="containsText" id="{5f458447-16d2-4485-b2e0-21093e332f7e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21366,7 +21436,7 @@
           <xm:sqref>C225:D225 F225 H225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="407" operator="containsText" id="{b54f8b71-5506-4668-94cd-855b0baffa6b}">
+          <x14:cfRule type="containsText" priority="411" operator="containsText" id="{35b8699f-49d4-4910-9c1d-5392bc460cf8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21381,7 +21451,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="408" operator="containsText" id="{fa2ad938-ef6d-459f-9225-05dc2d6036dd}">
+          <x14:cfRule type="containsText" priority="412" operator="containsText" id="{fc6909f5-65aa-4dcf-9767-73d045cdd51e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21399,7 +21469,7 @@
           <xm:sqref>A226:A237 A239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="409" operator="containsText" id="{b90fc184-3c84-44a6-b774-810953ea0d4f}">
+          <x14:cfRule type="containsText" priority="413" operator="containsText" id="{c2647412-0db5-40b5-b53c-68c2bae49a1e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21414,7 +21484,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="410" operator="containsText" id="{02b69b6d-732b-4e1d-b449-4414dec11e94}">
+          <x14:cfRule type="containsText" priority="414" operator="containsText" id="{7b3c2aef-74b6-4dd3-a6ac-1235b240e742}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21432,7 +21502,7 @@
           <xm:sqref>E226:F226 J237 M237 J232:M236 J231 J238:M239 C227:F233 C235:F236 C234:D234 F234 C237:D237 J228:M230 H226:H237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="411" operator="containsText" id="{b9a40df3-7fc4-4e68-8c0b-c9101d076f28}">
+          <x14:cfRule type="containsText" priority="415" operator="containsText" id="{6549dec5-0d4f-4a11-9dd0-a3bd5aafae19}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21447,7 +21517,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="412" operator="containsText" id="{90322813-924d-4c93-9e34-6e0fb546241d}">
+          <x14:cfRule type="containsText" priority="416" operator="containsText" id="{91364cb4-f835-4637-9d3f-656043bc15a4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21465,7 +21535,7 @@
           <xm:sqref>M226 M231 J226:K226</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="405" operator="containsText" id="{7fef209b-5a25-4310-b7ac-918d0dbbdc1e}">
+          <x14:cfRule type="containsText" priority="409" operator="containsText" id="{aef664ec-8041-4425-b235-6e68153663a0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21480,7 +21550,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="406" operator="containsText" id="{ebdf1c81-f2d7-44e5-8a50-9a8741c2172e}">
+          <x14:cfRule type="containsText" priority="410" operator="containsText" id="{e2d776a6-c2bd-4dbf-be4f-13cf75120af5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21498,7 +21568,7 @@
           <xm:sqref>A238 H238 C238:F238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="413" operator="containsText" id="{420ea98a-9f5e-48e6-8ea6-061832f933d9}">
+          <x14:cfRule type="containsText" priority="417" operator="containsText" id="{edf73d65-13cf-402a-9ae6-40c3d1d27789}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21513,7 +21583,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="414" operator="containsText" id="{0fe1ebb8-7f67-4a82-adbb-4f099d41ee99}">
+          <x14:cfRule type="containsText" priority="418" operator="containsText" id="{727a91ec-a7ce-48a2-bb06-df22e02c753d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21531,7 +21601,7 @@
           <xm:sqref>C239:D239 F239 H239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="349" operator="containsText" id="{bfddf03c-f276-42b4-9eec-24f371b954fc}">
+          <x14:cfRule type="containsText" priority="353" operator="containsText" id="{a932dcac-9a18-4502-92e3-1c0797c5706b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21546,7 +21616,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="350" operator="containsText" id="{cf700a28-84c0-4656-a7e4-2ba4aafe35fa}">
+          <x14:cfRule type="containsText" priority="354" operator="containsText" id="{4b0e0466-e46d-4b2d-bfd7-6f11d975db25}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21564,7 +21634,7 @@
           <xm:sqref>A240:A251 A253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="351" operator="containsText" id="{9111b34a-8c60-4677-883e-e8e0e8163fc3}">
+          <x14:cfRule type="containsText" priority="355" operator="containsText" id="{cc0141c9-70a6-4022-8e13-8126b4101772}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21579,7 +21649,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="352" operator="containsText" id="{cd884360-ce98-45f1-84d6-cddd94d13eba}">
+          <x14:cfRule type="containsText" priority="356" operator="containsText" id="{f797b493-93e7-4599-9ac5-fcc534edb881}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21597,7 +21667,7 @@
           <xm:sqref>E240:F240 J251 M251 J246:M250 J245 J252:M253 C241:F246 C249:F250 C251:D251 J242:M244 C247:D248 F248 H240:H251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="353" operator="containsText" id="{f7545e56-5c38-44bd-89c4-f7acd421c150}">
+          <x14:cfRule type="containsText" priority="357" operator="containsText" id="{27a69071-0435-4343-ae77-52eb427ba2f4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21612,7 +21682,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="354" operator="containsText" id="{11d4b51e-74b2-4908-bedb-6537035449b1}">
+          <x14:cfRule type="containsText" priority="358" operator="containsText" id="{228e54a5-dd18-4038-b296-7b6f415017fa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21630,7 +21700,7 @@
           <xm:sqref>M240 M245 J240:K240 K245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="347" operator="containsText" id="{c83830aa-de1b-4ee3-a0eb-6d61bb5e7ebd}">
+          <x14:cfRule type="containsText" priority="351" operator="containsText" id="{10d38ff1-6df5-45e6-8729-b3950ef5216f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21645,7 +21715,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="348" operator="containsText" id="{622ba56e-b5f2-489c-a2ce-daa0396fb9c5}">
+          <x14:cfRule type="containsText" priority="352" operator="containsText" id="{9bee7cf6-a961-47db-b409-1f10e78e63aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21663,7 +21733,7 @@
           <xm:sqref>A252 H252 C252:F252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="355" operator="containsText" id="{7bcd31ec-0c92-4e99-809b-d8438ab2f9bf}">
+          <x14:cfRule type="containsText" priority="359" operator="containsText" id="{0e1e505d-dfe3-47cf-b68b-5710656d298e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21678,7 +21748,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="356" operator="containsText" id="{654fa216-5758-4329-b6e4-5aee117913e4}">
+          <x14:cfRule type="containsText" priority="360" operator="containsText" id="{982ee74a-d696-4cd8-9984-db64b9738720}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21696,7 +21766,7 @@
           <xm:sqref>C253:D253 F253 H253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="291" operator="containsText" id="{d6a39eaa-eb23-4efc-a21b-12166317fe50}">
+          <x14:cfRule type="containsText" priority="295" operator="containsText" id="{d51701bf-3a3f-46d3-9bc5-a32e5df2c0ef}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21711,7 +21781,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="292" operator="containsText" id="{29c2dd03-dc39-48b2-9129-2f886d0e90ad}">
+          <x14:cfRule type="containsText" priority="296" operator="containsText" id="{20901ab3-c327-499c-ab2b-9464eab8b1be}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21729,7 +21799,7 @@
           <xm:sqref>A254:A265 A267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="293" operator="containsText" id="{061ef632-597b-4eba-8f6f-ebb70592861e}">
+          <x14:cfRule type="containsText" priority="297" operator="containsText" id="{98c92527-e369-4218-9aff-445ddfae8070}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21744,7 +21814,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="294" operator="containsText" id="{a26e7046-ea75-47dd-b96e-1d7d113ab240}">
+          <x14:cfRule type="containsText" priority="298" operator="containsText" id="{559823e9-2422-4927-92a5-05d837eac5cb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21762,7 +21832,7 @@
           <xm:sqref>E254:F254 J260:M263 J259 J266:M266 C255:F261 C264:F264 C265:D265 J256:M258 J264:J265 M264:M265 C262:D263 F262 H254:H265 K267:M267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="295" operator="containsText" id="{5fe58241-5cf7-4001-9d0d-3131a446e306}">
+          <x14:cfRule type="containsText" priority="299" operator="containsText" id="{4618fce3-c85c-4cc8-b450-5c406e6a4d7c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21777,7 +21847,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="296" operator="containsText" id="{aa50feb2-611a-4e68-875d-e3f05f651ccd}">
+          <x14:cfRule type="containsText" priority="300" operator="containsText" id="{755bbfe2-6d97-41f0-9923-b2d3a0546b67}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21795,7 +21865,7 @@
           <xm:sqref>M254 M259 J254:K254 K259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="289" operator="containsText" id="{91da9422-c26f-4bef-b6c8-8c8a443e0836}">
+          <x14:cfRule type="containsText" priority="293" operator="containsText" id="{2eb893d5-dd07-4696-84c1-31d15b7e66c8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21810,7 +21880,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="290" operator="containsText" id="{613cbe48-1366-4170-9cbd-88d994ad4b8c}">
+          <x14:cfRule type="containsText" priority="294" operator="containsText" id="{e77ead4f-ea18-47b5-939f-7f67fe4e0b10}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21828,7 +21898,7 @@
           <xm:sqref>A266 H266 C266:F266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="297" operator="containsText" id="{64b0b951-39a3-4b65-b8c5-2d9b55a31edd}">
+          <x14:cfRule type="containsText" priority="301" operator="containsText" id="{5a721dc9-f646-4b69-8b26-e5a109509d6c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21843,7 +21913,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="298" operator="containsText" id="{ce80f4d0-3050-478b-9d38-b9f1cd11aeb7}">
+          <x14:cfRule type="containsText" priority="302" operator="containsText" id="{3dc3f04d-9cbf-40ac-988b-06d7460ca89d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21861,7 +21931,7 @@
           <xm:sqref>C267:D267 F267 H267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="62" operator="containsText" id="{34ef45a7-165b-40bf-a624-164872ef1920}">
+          <x14:cfRule type="containsText" priority="66" operator="containsText" id="{0147f190-a361-431f-8b2a-65f08155c3c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A268)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21876,7 +21946,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="61" operator="containsText" id="{f7776ebc-c8d3-4f50-8636-4107185e5497}">
+          <x14:cfRule type="containsText" priority="65" operator="containsText" id="{d342d11c-7f8d-4a8f-8423-bb562b8106c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A268)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21894,7 +21964,7 @@
           <xm:sqref>A268:A279 A281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="55" operator="containsText" id="{e8ba8ce0-1fd0-4f87-a158-cbdb9d19fec3}">
+          <x14:cfRule type="containsText" priority="59" operator="containsText" id="{cc6f8da2-ae95-4ca4-bca6-246f08dac93a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E268)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21909,7 +21979,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="56" operator="containsText" id="{2c59d97e-0acf-4661-9df5-48355f5559f5}">
+          <x14:cfRule type="containsText" priority="60" operator="containsText" id="{ae02f434-d775-42bb-a158-ac7991109d6d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E268)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE DIARIO" sheetId="1" r:id="rId1"/>
@@ -9870,7 +9870,7 @@
         <v>503</v>
       </c>
       <c r="G269" s="57">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H269" s="74"/>
       <c r="I269" s="74"/>
@@ -9900,7 +9900,7 @@
         <v>505</v>
       </c>
       <c r="G270" s="57">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H270" s="74"/>
       <c r="I270" s="74"/>
@@ -9984,7 +9984,7 @@
         <v>275</v>
       </c>
       <c r="G273" s="57">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="H273" s="74"/>
       <c r="I273" s="74"/>
@@ -10348,7 +10348,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="165" operator="containsText" id="{7e43147d-4fe2-453f-9f78-53ab33426ffb}">
+          <x14:cfRule type="containsText" priority="165" operator="containsText" id="{180437bf-8204-4688-8316-d4f0bf0a06a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G28)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10363,7 +10363,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="166" operator="containsText" id="{995923e3-9648-4c91-a190-aa9a9b04d2cb}">
+          <x14:cfRule type="containsText" priority="166" operator="containsText" id="{6eb48be5-c8ef-4d62-b2e5-9e778e8c773c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G28)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10381,7 +10381,7 @@
           <xm:sqref>G28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="163" operator="containsText" id="{1f455e5d-6282-400a-b0a2-dc779e3c1d20}">
+          <x14:cfRule type="containsText" priority="163" operator="containsText" id="{bea229b1-54c3-4fcc-a8b4-41b6bdaaf2dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G42)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10396,7 +10396,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="164" operator="containsText" id="{bed370d5-e130-49c2-84ad-59d797eb4b9c}">
+          <x14:cfRule type="containsText" priority="164" operator="containsText" id="{77d843cd-c70a-40f9-b3f6-8456ab45c981}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G42)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10414,7 +10414,7 @@
           <xm:sqref>G42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="161" operator="containsText" id="{649d1852-a581-412c-af32-5963293949d1}">
+          <x14:cfRule type="containsText" priority="161" operator="containsText" id="{97a85a0b-8390-42bd-9590-05949ab37dae}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G56)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10429,7 +10429,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="162" operator="containsText" id="{16230fe5-cb09-4f3b-b548-2245b630af2b}">
+          <x14:cfRule type="containsText" priority="162" operator="containsText" id="{aef80459-572a-4ff3-8792-5f403f3271f9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G56)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10447,7 +10447,7 @@
           <xm:sqref>G56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="159" operator="containsText" id="{58c1c179-fef8-4e46-b2c1-b23b756995f1}">
+          <x14:cfRule type="containsText" priority="159" operator="containsText" id="{7e3793f6-8436-4d93-8935-ce482a7815da}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G70)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10462,7 +10462,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="160" operator="containsText" id="{0712cccb-8e61-4e40-9b78-6e14dceb2b3d}">
+          <x14:cfRule type="containsText" priority="160" operator="containsText" id="{d6766479-1205-41e2-bfcd-8ba4264a80e1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G70)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10480,7 +10480,7 @@
           <xm:sqref>G70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="835" operator="containsText" id="{01c48221-10f6-4245-919e-a061d5af5a68}">
+          <x14:cfRule type="containsText" priority="835" operator="containsText" id="{0bcb817f-cbd3-4289-9f57-c021dc286db4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K73)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10495,7 +10495,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="836" operator="containsText" id="{64b61c07-6296-42b9-84fa-660d0b217dc5}">
+          <x14:cfRule type="containsText" priority="836" operator="containsText" id="{d5c6756b-cad2-475e-9392-fb964cb20115}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K73)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10513,7 +10513,7 @@
           <xm:sqref>K73</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="833" operator="containsText" id="{d515be14-c903-4a2a-a49d-cf96eac66961}">
+          <x14:cfRule type="containsText" priority="833" operator="containsText" id="{f1f2acde-5597-450f-ab72-6940b4cc3408}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K83)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10528,7 +10528,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="834" operator="containsText" id="{1ddfdf96-7f8b-44bd-b741-8e79bf721dc5}">
+          <x14:cfRule type="containsText" priority="834" operator="containsText" id="{cff4896e-e2a7-4a03-87fa-f8f6c66a15b8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K83)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10546,7 +10546,7 @@
           <xm:sqref>K83</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="831" operator="containsText" id="{1680db68-4163-4085-9e7d-a96f9f6f4e07}">
+          <x14:cfRule type="containsText" priority="831" operator="containsText" id="{e47d97a1-ae23-40a5-ad07-0c563cc451b4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K84)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10561,7 +10561,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="832" operator="containsText" id="{464a12ad-7731-433e-a0b7-18807400b0a9}">
+          <x14:cfRule type="containsText" priority="832" operator="containsText" id="{a6d15a23-26b7-4a83-bd55-c0257d1db74e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K84)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10579,7 +10579,7 @@
           <xm:sqref>K84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="859" operator="containsText" id="{f3250457-73a5-4429-8a54-12d1e5ca392e}">
+          <x14:cfRule type="containsText" priority="859" operator="containsText" id="{b5702ca8-d308-4d74-9b01-930923fa8018}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L87)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10594,7 +10594,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="860" operator="containsText" id="{bd25bbba-4037-47b9-bcc8-4968b083db2d}">
+          <x14:cfRule type="containsText" priority="860" operator="containsText" id="{c63f85a2-a22e-467c-a6a8-58f0b4feff98}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L87)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10612,7 +10612,7 @@
           <xm:sqref>L87</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="857" operator="containsText" id="{1d5a4d62-64fd-4ce7-a4b2-057c5d81a869}">
+          <x14:cfRule type="containsText" priority="857" operator="containsText" id="{f4f251e5-2a17-4865-ba90-8ea9b87a33de}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I92)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10627,7 +10627,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="858" operator="containsText" id="{6f5f8ad8-1322-4f6d-8541-1ad3142d2a88}">
+          <x14:cfRule type="containsText" priority="858" operator="containsText" id="{3dba22ed-52c3-4400-9f8e-798407ce43fb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I92)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10645,7 +10645,7 @@
           <xm:sqref>I92</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="863" operator="containsText" id="{1556e9bc-bc12-49cd-8d95-a563bd14238a}">
+          <x14:cfRule type="containsText" priority="863" operator="containsText" id="{490517fa-0bb1-4e93-ace8-41a15c04b3a8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I93)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10660,7 +10660,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="864" operator="containsText" id="{d4b8003d-926b-476d-928d-5365d0e24db8}">
+          <x14:cfRule type="containsText" priority="864" operator="containsText" id="{681854f7-3886-48f3-9cad-8c85ca1b6650}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I93)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10678,7 +10678,7 @@
           <xm:sqref>I93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="861" operator="containsText" id="{3bcfae40-f3c9-42a9-b3fd-e3f578bbc2e2}">
+          <x14:cfRule type="containsText" priority="861" operator="containsText" id="{4d5e84ff-5cd9-4506-b27e-ed63aec4a0c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I96)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10693,7 +10693,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="862" operator="containsText" id="{430a2ed9-44a1-43a4-a4c6-b2f130a2779d}">
+          <x14:cfRule type="containsText" priority="862" operator="containsText" id="{7b093de9-3686-4a11-87cb-5346f34cb4c5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I96)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10711,7 +10711,7 @@
           <xm:sqref>I96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="829" operator="containsText" id="{7f550a7f-fc4c-4504-a16c-1666def0eaa9}">
+          <x14:cfRule type="containsText" priority="829" operator="containsText" id="{58e18258-9aad-40ab-873d-fe0e59661efc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K96)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10726,7 +10726,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="830" operator="containsText" id="{a37a34e9-a3be-4da3-94d0-a6d9516e2717}">
+          <x14:cfRule type="containsText" priority="830" operator="containsText" id="{c05d1f08-f3d5-490c-99c1-098921f6504a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K96)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10744,7 +10744,7 @@
           <xm:sqref>K96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="867" operator="containsText" id="{63cbd2a1-cd86-44e8-9ba3-169b8d58d54f}">
+          <x14:cfRule type="containsText" priority="867" operator="containsText" id="{83c91f87-43bb-46ba-9b09-8fc71e15bb88}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10759,7 +10759,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="868" operator="containsText" id="{6f05766b-7125-4375-bf6f-44b8cfdc9ffe}">
+          <x14:cfRule type="containsText" priority="868" operator="containsText" id="{f0f38f8c-28b4-48d7-b9d7-a446e77faf32}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10777,7 +10777,7 @@
           <xm:sqref>I97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="827" operator="containsText" id="{76101755-1cd9-4181-ba10-0e4e78177bf1}">
+          <x14:cfRule type="containsText" priority="827" operator="containsText" id="{ad8c5b4e-23ea-4823-95a6-4004f21a426a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10792,7 +10792,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="828" operator="containsText" id="{52628e9c-45ff-442f-9da2-c0502037bf7f}">
+          <x14:cfRule type="containsText" priority="828" operator="containsText" id="{d9b4d739-bdc4-4990-af8b-9b016f19e0ef}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10810,7 +10810,7 @@
           <xm:sqref>K97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="865" operator="containsText" id="{a2a3c3ae-2467-4857-8d5b-8dce8ef72e2c}">
+          <x14:cfRule type="containsText" priority="865" operator="containsText" id="{7613dc6f-281e-4184-99e8-a7057e3dae30}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L97)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10825,7 +10825,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="866" operator="containsText" id="{3de49a0b-191e-45bb-a11a-615681a7e7d5}">
+          <x14:cfRule type="containsText" priority="866" operator="containsText" id="{928e3566-aacd-4445-92b0-89f9f0f2ff8f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L97)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10843,7 +10843,7 @@
           <xm:sqref>L97</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="155" operator="containsText" id="{40956c1f-07c4-4da4-8ace-9b2c0af9e549}">
+          <x14:cfRule type="containsText" priority="155" operator="containsText" id="{9afb1699-82d6-41c5-b3d3-d32360c42127}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G98)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10858,7 +10858,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="156" operator="containsText" id="{f861a684-3889-41e7-a905-3b010b29d300}">
+          <x14:cfRule type="containsText" priority="156" operator="containsText" id="{21eaf7a4-93cb-483f-b31b-3ec4d642fb15}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G98)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10876,7 +10876,7 @@
           <xm:sqref>G98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="841" operator="containsText" id="{ccba35ad-f6f5-41fa-888d-a06cf6704dba}">
+          <x14:cfRule type="containsText" priority="841" operator="containsText" id="{0649ef9a-3451-48ea-bb2b-f093ce1ab4be}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L101)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10891,7 +10891,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="842" operator="containsText" id="{f37f096d-9a88-4c18-81b1-a4189a85510a}">
+          <x14:cfRule type="containsText" priority="842" operator="containsText" id="{3a2140dd-c7d4-4031-880a-d44889947bf2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L101)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10909,7 +10909,7 @@
           <xm:sqref>L101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="813" operator="containsText" id="{821a930d-64cd-4a6b-ad76-d74c295dd347}">
+          <x14:cfRule type="containsText" priority="813" operator="containsText" id="{4b19721d-50da-4a88-922c-fbe68869aa9b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I102)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10924,7 +10924,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="814" operator="containsText" id="{d5afe392-e8af-40a3-b1ac-2cdc0013e4fd}">
+          <x14:cfRule type="containsText" priority="814" operator="containsText" id="{b99f4d2d-b917-44e9-a370-3e0f211fb83d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I102)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10942,7 +10942,7 @@
           <xm:sqref>I102</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="817" operator="containsText" id="{e023e743-abc2-4d89-9bd2-cbbf6caaed0e}">
+          <x14:cfRule type="containsText" priority="817" operator="containsText" id="{f875d034-e6aa-4490-a8b9-15a32fbb0ca8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I106)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10957,7 +10957,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="818" operator="containsText" id="{e65b42c1-4477-4b0f-9cd3-c693abb09878}">
+          <x14:cfRule type="containsText" priority="818" operator="containsText" id="{6dd5ae95-ed46-4b8a-aba5-7f43f92cb0fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I106)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -10975,7 +10975,7 @@
           <xm:sqref>I106</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="815" operator="containsText" id="{ce1f8500-b81b-438f-9b80-aba8bdf9a166}">
+          <x14:cfRule type="containsText" priority="815" operator="containsText" id="{04884286-12d6-47b2-b36f-30aad69c65be}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I107)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -10990,7 +10990,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="816" operator="containsText" id="{11359b0e-f677-4ff0-8727-7e4c93ddb156}">
+          <x14:cfRule type="containsText" priority="816" operator="containsText" id="{fdb84b0c-5e3a-4a01-bb45-9a8b6309109f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I107)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11008,7 +11008,7 @@
           <xm:sqref>I107</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="819" operator="containsText" id="{59d2c37a-7a1f-4a67-9690-4414d76c2950}">
+          <x14:cfRule type="containsText" priority="819" operator="containsText" id="{2779e6d2-6ea6-4431-a6b4-9cfaf2284b3d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I110)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11023,7 +11023,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="820" operator="containsText" id="{678b6d51-af5f-497d-85db-06347db154dd}">
+          <x14:cfRule type="containsText" priority="820" operator="containsText" id="{85f62948-88b6-46af-aa65-070251adb835}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I110)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11041,7 +11041,7 @@
           <xm:sqref>I110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="837" operator="containsText" id="{1f25ff6a-e63f-441a-8f34-d2667106ff4f}">
+          <x14:cfRule type="containsText" priority="837" operator="containsText" id="{81a95039-169f-46ce-937f-5114688ce531}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11056,7 +11056,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="838" operator="containsText" id="{9e2f6e82-76ec-4e5e-a0c9-fffcd5ec4e58}">
+          <x14:cfRule type="containsText" priority="838" operator="containsText" id="{fa59fc2f-fb30-43a0-b8a4-ea3befcb5bd8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11074,7 +11074,7 @@
           <xm:sqref>I111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="825" operator="containsText" id="{801c6ddd-db1e-4267-9683-2f7955480241}">
+          <x14:cfRule type="containsText" priority="825" operator="containsText" id="{ffaae333-4871-43a1-958d-555a4938af64}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11089,7 +11089,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="826" operator="containsText" id="{1e449b38-f305-4a84-8d26-1f702339761e}">
+          <x14:cfRule type="containsText" priority="826" operator="containsText" id="{993ace73-cc24-4133-9e04-950926f96275}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11107,7 +11107,7 @@
           <xm:sqref>K111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="823" operator="containsText" id="{9e192cb4-c0e5-4d7b-8efd-d99bfdbc3087}">
+          <x14:cfRule type="containsText" priority="823" operator="containsText" id="{bc9953bf-05d1-46cf-89c6-13448a735916}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L111)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11122,7 +11122,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="824" operator="containsText" id="{a102dbf5-c4ba-450d-a64d-16d0be44c333}">
+          <x14:cfRule type="containsText" priority="824" operator="containsText" id="{b305aff8-3ae3-483a-a8a8-c90fd86d9579}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L111)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11140,7 +11140,7 @@
           <xm:sqref>L111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="151" operator="containsText" id="{b99bd2f6-7fc0-4be4-b477-a03ef2bb6ed4}">
+          <x14:cfRule type="containsText" priority="151" operator="containsText" id="{dc3a2ce3-7d36-4372-b5f9-b81aebe23582}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11155,7 +11155,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="152" operator="containsText" id="{cfb7d3ea-e601-46df-aa31-e68c618820d1}">
+          <x14:cfRule type="containsText" priority="152" operator="containsText" id="{f49fd0b3-9dd7-432d-a839-4ed1fc77fa8d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11173,7 +11173,7 @@
           <xm:sqref>G112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="821" operator="containsText" id="{738d6050-0184-47d1-a901-0d691ecb6e9a}">
+          <x14:cfRule type="containsText" priority="821" operator="containsText" id="{f2b7b615-6bcc-41c8-aec2-d907d5595676}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11188,7 +11188,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="822" operator="containsText" id="{ca821c41-33c5-4c59-ba8d-33fb88da4aec}">
+          <x14:cfRule type="containsText" priority="822" operator="containsText" id="{f44c7a4d-5eb4-42f6-a710-9dc8ce3d10cf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11206,7 +11206,7 @@
           <xm:sqref>I112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="787" operator="containsText" id="{480b0bff-31cf-47d3-b505-cf92dfb1db77}">
+          <x14:cfRule type="containsText" priority="787" operator="containsText" id="{c0ba0ff6-feea-42a2-9007-eaafdf95dc58}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11221,7 +11221,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="788" operator="containsText" id="{cf0ce3a6-2248-4ff9-9435-f2817269cb60}">
+          <x14:cfRule type="containsText" priority="788" operator="containsText" id="{ecd1df7d-ad02-400d-a9a5-e1d0b6739f47}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11239,7 +11239,7 @@
           <xm:sqref>I114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="805" operator="containsText" id="{0aafb8c9-b8c7-4eba-a307-c54c962eea32}">
+          <x14:cfRule type="containsText" priority="805" operator="containsText" id="{af7ac385-67e1-45fa-9189-9e822dd4e749}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L115)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11254,7 +11254,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="806" operator="containsText" id="{6b52d5aa-4263-43aa-a5e6-4bbc9d576ec7}">
+          <x14:cfRule type="containsText" priority="806" operator="containsText" id="{c313c0da-86d6-48b6-926a-6dd724548fbc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L115)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11272,7 +11272,7 @@
           <xm:sqref>L115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="789" operator="containsText" id="{81c4f33b-53ea-474c-93bd-ffdce96ef4c3}">
+          <x14:cfRule type="containsText" priority="789" operator="containsText" id="{2f169d32-3cf1-4853-a78f-d69578a9dcd9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I116)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11287,7 +11287,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="790" operator="containsText" id="{e96a2b3d-5b34-41fd-a0fe-3694478b29a7}">
+          <x14:cfRule type="containsText" priority="790" operator="containsText" id="{687b892e-0282-4c95-b081-09816ca87a44}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I116)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11305,7 +11305,7 @@
           <xm:sqref>I116</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="781" operator="containsText" id="{a8940fc9-a333-4df6-95ee-4545323493dc}">
+          <x14:cfRule type="containsText" priority="781" operator="containsText" id="{b379fb1d-ae1b-4549-b70f-6c9d4f64a650}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I120)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11320,7 +11320,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="782" operator="containsText" id="{3369de4f-11da-4b26-8c83-a7e184e1ef5e}">
+          <x14:cfRule type="containsText" priority="782" operator="containsText" id="{fc3794f5-2a2c-4551-a7e0-25a05032e653}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I120)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11338,7 +11338,7 @@
           <xm:sqref>I120</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="777" operator="containsText" id="{93c37f72-d514-4cb4-8caa-df371bbcd40f}">
+          <x14:cfRule type="containsText" priority="777" operator="containsText" id="{af2f3d29-cec1-4b6a-8a79-567c8b6c3dc3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I121)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11353,7 +11353,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="778" operator="containsText" id="{f333d75a-1fb1-42eb-a8f1-61a514acf6cd}">
+          <x14:cfRule type="containsText" priority="778" operator="containsText" id="{7f8efcc1-aebc-4731-9970-f54f3df0b0e3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I121)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11371,7 +11371,7 @@
           <xm:sqref>I121</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="779" operator="containsText" id="{d90482bc-4d51-403d-a160-d39e6cbbb83a}">
+          <x14:cfRule type="containsText" priority="779" operator="containsText" id="{729f2174-8a12-43d5-a452-b7d84aa539d7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I122)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11386,7 +11386,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="780" operator="containsText" id="{6678aa6d-9b2d-419f-aa5a-091da2a72286}">
+          <x14:cfRule type="containsText" priority="780" operator="containsText" id="{0f21489f-5671-485b-9391-8caa4183bb9b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I122)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11404,7 +11404,7 @@
           <xm:sqref>I122</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="773" operator="containsText" id="{d626748e-2ebe-47cb-9520-9cc7de221d05}">
+          <x14:cfRule type="containsText" priority="773" operator="containsText" id="{128344e7-261f-475f-a854-0274eb9e8e06}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I123)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11419,7 +11419,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="774" operator="containsText" id="{9ce86512-1f24-401e-af2e-865701cacc95}">
+          <x14:cfRule type="containsText" priority="774" operator="containsText" id="{afdcecd9-6b6b-4e5c-94da-ef919bc6a343}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I123)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11437,7 +11437,7 @@
           <xm:sqref>I123</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="795" operator="containsText" id="{32f03339-324a-4802-a1ec-f68fd9a9b391}">
+          <x14:cfRule type="containsText" priority="795" operator="containsText" id="{d909e21b-2860-47d6-8959-9260bdc31f4d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I124)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11452,7 +11452,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="796" operator="containsText" id="{eb1d4105-48e5-4668-bce7-5d8c514f01bb}">
+          <x14:cfRule type="containsText" priority="796" operator="containsText" id="{4331ad18-e014-47a0-a007-4678bb1f5cae}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I124)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11470,7 +11470,7 @@
           <xm:sqref>I124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="785" operator="containsText" id="{b3f717ab-3e79-47f9-95c0-36c3fd2a5f54}">
+          <x14:cfRule type="containsText" priority="785" operator="containsText" id="{07e5cb16-7741-4fa0-9d1b-a2815b152851}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11485,7 +11485,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="786" operator="containsText" id="{94f87c30-d519-4a5e-b121-163fd3af85cf}">
+          <x14:cfRule type="containsText" priority="786" operator="containsText" id="{c69aad58-cecd-4b28-8ef9-730c5aa99661}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11503,7 +11503,7 @@
           <xm:sqref>I125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="801" operator="containsText" id="{7bf56905-84e2-486e-bfc9-4ed959633b3d}">
+          <x14:cfRule type="containsText" priority="801" operator="containsText" id="{b22b27f0-ebc2-4a8d-9799-20aa711eae82}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11518,7 +11518,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="802" operator="containsText" id="{1beea190-824d-4af6-916c-b7b748dc82ba}">
+          <x14:cfRule type="containsText" priority="802" operator="containsText" id="{a7d23cba-8a60-443b-b082-edeaff16e539}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11536,7 +11536,7 @@
           <xm:sqref>K125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="783" operator="containsText" id="{deab5508-945d-4404-97fd-fbe8e082cf62}">
+          <x14:cfRule type="containsText" priority="783" operator="containsText" id="{6163d43d-9157-474f-b701-21d41dd8fba8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L125)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11551,7 +11551,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="784" operator="containsText" id="{b4e3c12f-5b3b-453d-9ed8-ae10695c737b}">
+          <x14:cfRule type="containsText" priority="784" operator="containsText" id="{f9624812-5b25-49b7-8344-bce3dc3fe643}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L125)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11569,7 +11569,7 @@
           <xm:sqref>L125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="147" operator="containsText" id="{6d293715-cebd-4264-baa7-15e53d329f44}">
+          <x14:cfRule type="containsText" priority="147" operator="containsText" id="{408ab733-84c3-4c3c-a359-eb21f2c8dcfd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11584,7 +11584,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="148" operator="containsText" id="{646728e0-9ec8-4b9c-b78a-70f6e3e8035d}">
+          <x14:cfRule type="containsText" priority="148" operator="containsText" id="{416ce1da-64da-4b51-a0b7-6ea3b55ce8fa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11602,7 +11602,7 @@
           <xm:sqref>G126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="775" operator="containsText" id="{87be6d60-fc90-4211-8f43-ad165b8419ab}">
+          <x14:cfRule type="containsText" priority="775" operator="containsText" id="{cd1f9712-e004-41ff-9b3d-4faf0b3034ff}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11617,7 +11617,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="776" operator="containsText" id="{0eebaded-a634-409f-9c3b-36baa5a98a12}">
+          <x14:cfRule type="containsText" priority="776" operator="containsText" id="{f4c50b9d-ebc1-4058-86f1-7afe48f03f70}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11635,7 +11635,7 @@
           <xm:sqref>I126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="757" operator="containsText" id="{a9b52c19-c387-4398-8479-df2776774437}">
+          <x14:cfRule type="containsText" priority="757" operator="containsText" id="{e70d1a40-dbe8-413f-88d7-73df7aaa8663}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11650,7 +11650,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="758" operator="containsText" id="{1bddb6dd-09da-4f71-9c17-b415664e741c}">
+          <x14:cfRule type="containsText" priority="758" operator="containsText" id="{45d1718f-07a0-4878-957c-f8b1b14ebe29}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11668,7 +11668,7 @@
           <xm:sqref>I128</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="733" operator="containsText" id="{6af42e14-986d-42ea-916c-fa7063d7174a}">
+          <x14:cfRule type="containsText" priority="733" operator="containsText" id="{4c58df52-b5f3-4163-83f4-2dabee52f0aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I129)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11683,7 +11683,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="734" operator="containsText" id="{a6bbdfbf-debb-4dd0-ae61-a34bbb9bd94a}">
+          <x14:cfRule type="containsText" priority="734" operator="containsText" id="{5663c168-d539-4f12-a922-513d3c526a16}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I129)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11701,7 +11701,7 @@
           <xm:sqref>I129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="765" operator="containsText" id="{5f87015e-28a5-4d84-bba5-9160348955d2}">
+          <x14:cfRule type="containsText" priority="765" operator="containsText" id="{2e1e3a33-1cd7-4546-a562-74dbdd902093}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L129)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11716,7 +11716,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="766" operator="containsText" id="{c8aad775-b0ab-4de7-86c4-d8f15f8e6d2b}">
+          <x14:cfRule type="containsText" priority="766" operator="containsText" id="{781e6731-e013-4cf1-bc26-ca65f7500344}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L129)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11734,7 +11734,7 @@
           <xm:sqref>L129</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="759" operator="containsText" id="{10905b8c-d593-4635-bc12-a0554abe593f}">
+          <x14:cfRule type="containsText" priority="759" operator="containsText" id="{99315df2-734a-4a86-8867-524d4a62c376}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I130)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11749,7 +11749,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="760" operator="containsText" id="{edd8d910-73e4-4eb3-b5c8-8e28bd5eb9e6}">
+          <x14:cfRule type="containsText" priority="760" operator="containsText" id="{b519ee91-4370-4cb6-ab09-dfeadb7a7e0d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I130)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11767,7 +11767,7 @@
           <xm:sqref>I130</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="737" operator="containsText" id="{8ec90d1c-fb78-429b-b0e6-327c4f386c2e}">
+          <x14:cfRule type="containsText" priority="737" operator="containsText" id="{ffa5bc72-e659-4262-b528-8ff999e76da9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11782,7 +11782,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="738" operator="containsText" id="{5a199fb9-e485-4108-90fb-23eb90fc39cb}">
+          <x14:cfRule type="containsText" priority="738" operator="containsText" id="{8d84c51c-71f3-4fc7-bcae-15c389d1ca35}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11800,7 +11800,7 @@
           <xm:sqref>I133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="677" operator="containsText" id="{e0a93478-4d03-4a2c-a700-efafb700049e}">
+          <x14:cfRule type="containsText" priority="677" operator="containsText" id="{1c5855a3-1fbf-4c81-91bf-c20dd3d2fc5b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11815,7 +11815,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="678" operator="containsText" id="{c573a633-d330-4f98-b56c-a805c0d10579}">
+          <x14:cfRule type="containsText" priority="678" operator="containsText" id="{bd7b2262-d25e-4a82-b7f8-2711ba83f9bf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11833,7 +11833,7 @@
           <xm:sqref>K133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="735" operator="containsText" id="{9c92ace1-9cfa-4ba2-a124-ea907f4be73a}">
+          <x14:cfRule type="containsText" priority="735" operator="containsText" id="{45625ca9-38c3-4246-9ff0-b9c94728c044}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L133)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11848,7 +11848,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="736" operator="containsText" id="{fff9bea7-5193-4a81-94ff-20d43edc9971}">
+          <x14:cfRule type="containsText" priority="736" operator="containsText" id="{3f1ae627-7832-439b-87bb-5680ae94d853}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L133)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11866,7 +11866,7 @@
           <xm:sqref>L133</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="729" operator="containsText" id="{9bf2d572-a5c2-484e-a487-491852437638}">
+          <x14:cfRule type="containsText" priority="729" operator="containsText" id="{bbb58489-50db-4f69-9767-e5d79705f48d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I134)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11881,7 +11881,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="730" operator="containsText" id="{ca657395-ffc7-41cb-bffc-cdb1e156af75}">
+          <x14:cfRule type="containsText" priority="730" operator="containsText" id="{d48a1c10-b54a-45e9-8268-42384f3e0167}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I134)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11899,7 +11899,7 @@
           <xm:sqref>I134</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="731" operator="containsText" id="{d43621b8-b2b6-46b5-b3c6-3e0ec54a1208}">
+          <x14:cfRule type="containsText" priority="731" operator="containsText" id="{7a63df57-3105-4b02-8a2f-e428d9562783}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I135)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11914,7 +11914,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="732" operator="containsText" id="{5f6f3bad-ce82-4684-9352-528370163a18}">
+          <x14:cfRule type="containsText" priority="732" operator="containsText" id="{5b191af3-3539-4067-822f-4da42ded6891}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I135)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11932,7 +11932,7 @@
           <xm:sqref>I135</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="743" operator="containsText" id="{d76b0c6f-52f7-44dc-b7f2-697ea486fc86}">
+          <x14:cfRule type="containsText" priority="743" operator="containsText" id="{0bdcce92-b960-4bd1-93d7-dad451097289}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I137)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11947,7 +11947,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="744" operator="containsText" id="{105a0b99-17ba-41f5-9470-6603bd42d3bb}">
+          <x14:cfRule type="containsText" priority="744" operator="containsText" id="{4cff16e2-715c-4898-bb55-5dcedba1c620}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I137)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11965,7 +11965,7 @@
           <xm:sqref>I137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="761" operator="containsText" id="{977a957c-8855-493c-aa16-c173348df503}">
+          <x14:cfRule type="containsText" priority="761" operator="containsText" id="{056351b6-1576-4e3a-a041-a73dcd416e6f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I138)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -11980,7 +11980,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="762" operator="containsText" id="{8aa05739-56a5-40e8-869f-668f9dd3e7be}">
+          <x14:cfRule type="containsText" priority="762" operator="containsText" id="{0ce407c8-93a7-4cda-ba73-01519feeaf6a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I138)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -11998,7 +11998,7 @@
           <xm:sqref>I138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="741" operator="containsText" id="{cb6affa2-1c69-4dcc-ad9e-5e4351f58c49}">
+          <x14:cfRule type="containsText" priority="741" operator="containsText" id="{d7714c43-8557-4562-86e7-8544a7e2181e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12013,7 +12013,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="742" operator="containsText" id="{f6756949-6c2e-4847-b5a7-0b1d3b4fb786}">
+          <x14:cfRule type="containsText" priority="742" operator="containsText" id="{9e05fc6b-5774-4500-88a2-9bc4285495c6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12031,7 +12031,7 @@
           <xm:sqref>I139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="691" operator="containsText" id="{1debb3a1-202c-47f6-ab4e-b5451065f194}">
+          <x14:cfRule type="containsText" priority="691" operator="containsText" id="{d14d8685-e2c7-4359-9314-82f1642f7608}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12046,7 +12046,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="692" operator="containsText" id="{fbad31be-4280-49b3-87ec-7c7a65367b24}">
+          <x14:cfRule type="containsText" priority="692" operator="containsText" id="{2ae3189f-bef4-4d35-b96e-98223da71255}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12064,7 +12064,7 @@
           <xm:sqref>K139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="739" operator="containsText" id="{ae20c341-d8b2-4ba7-b6ca-3f1bf8ba3349}">
+          <x14:cfRule type="containsText" priority="739" operator="containsText" id="{ac6ff766-f107-4637-854e-665bb0ddc23b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L139)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12079,7 +12079,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="740" operator="containsText" id="{cf97498a-93a3-45e0-a588-6d3a35a3bfbf}">
+          <x14:cfRule type="containsText" priority="740" operator="containsText" id="{cb19a5ce-2d15-4a3c-b829-327b1cb159d2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L139)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12097,7 +12097,7 @@
           <xm:sqref>L139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="143" operator="containsText" id="{56dfa5ac-08da-4545-91e6-41422bf8e737}">
+          <x14:cfRule type="containsText" priority="143" operator="containsText" id="{32cc8647-368e-43a7-a4b0-08fb881dd5f5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12112,7 +12112,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="144" operator="containsText" id="{30d58cb3-9421-4aeb-bccf-7bbfda925b78}">
+          <x14:cfRule type="containsText" priority="144" operator="containsText" id="{36274a5a-f79a-4591-8df7-22672fcfeb50}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12130,7 +12130,7 @@
           <xm:sqref>G140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="745" operator="containsText" id="{e6b5434e-286b-4407-b58e-66146b224b87}">
+          <x14:cfRule type="containsText" priority="745" operator="containsText" id="{2e02e68b-024e-49e7-ae42-3a7f26da3349}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12145,7 +12145,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="746" operator="containsText" id="{1628d202-c1be-4bf1-9ae6-0343fc4fa990}">
+          <x14:cfRule type="containsText" priority="746" operator="containsText" id="{820433c5-a9cf-4c78-b915-56e8a986c6a8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12163,7 +12163,7 @@
           <xm:sqref>I140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="713" operator="containsText" id="{14da99ea-a210-4859-a508-fa56e9c0616d}">
+          <x14:cfRule type="containsText" priority="713" operator="containsText" id="{b8fe8d51-10b6-4641-9f85-212398eaa791}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12178,7 +12178,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="714" operator="containsText" id="{9852ff2d-7847-4099-999d-455ce1bdd529}">
+          <x14:cfRule type="containsText" priority="714" operator="containsText" id="{8786f37c-0fe8-40ef-9dcf-505c10d6e58a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12196,7 +12196,7 @@
           <xm:sqref>I142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="693" operator="containsText" id="{b1873d6b-9754-445d-ae70-9df72b5a0350}">
+          <x14:cfRule type="containsText" priority="693" operator="containsText" id="{ab5b6362-fe2a-4c31-a64f-4f0810925904}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12211,7 +12211,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="694" operator="containsText" id="{ce0609cf-8fe7-434b-981e-23227f966ab4}">
+          <x14:cfRule type="containsText" priority="694" operator="containsText" id="{51034eee-fc1a-44ec-b62b-5bdd1bd1586c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12229,7 +12229,7 @@
           <xm:sqref>L142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="715" operator="containsText" id="{2c2ba472-9c16-4615-9b6f-4c1bdafe554b}">
+          <x14:cfRule type="containsText" priority="715" operator="containsText" id="{d357ad82-5b90-41d0-a74d-1aafd291b53c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I144)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12244,7 +12244,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="716" operator="containsText" id="{65ab8045-01f6-4b61-912e-3af69429014a}">
+          <x14:cfRule type="containsText" priority="716" operator="containsText" id="{22823afa-4284-4015-ac10-11083f8aed4e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I144)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12262,7 +12262,7 @@
           <xm:sqref>I144</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="681" operator="containsText" id="{e8c614cc-24e0-4043-b344-30adce1b1fb2}">
+          <x14:cfRule type="containsText" priority="681" operator="containsText" id="{d6c64eec-fea8-42b2-8391-f4b67f296cdc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I146)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12277,7 +12277,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="682" operator="containsText" id="{e5a40cd5-3fa9-4c56-9cc6-c7262bbfc072}">
+          <x14:cfRule type="containsText" priority="682" operator="containsText" id="{8f80af18-46c5-4312-afda-12c7923f3950}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I146)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12295,7 +12295,7 @@
           <xm:sqref>I146</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="679" operator="containsText" id="{7fbfbdff-d26a-4a01-8c83-292d70d07ecd}">
+          <x14:cfRule type="containsText" priority="679" operator="containsText" id="{0370322d-bc73-4bc1-be3e-ea55b9958f4a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I147)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12310,7 +12310,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="680" operator="containsText" id="{3c42fd32-6ff4-40b1-bf75-0d762f7e1251}">
+          <x14:cfRule type="containsText" priority="680" operator="containsText" id="{bb5c3474-340f-42d5-9d8c-106f98fae5da}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I147)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12328,7 +12328,7 @@
           <xm:sqref>I147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="685" operator="containsText" id="{1b0f0b24-c430-4df7-be84-278f7acf0a2c}">
+          <x14:cfRule type="containsText" priority="685" operator="containsText" id="{d660901a-9809-4676-ae09-8b341bd0f218}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L147)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12343,7 +12343,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="686" operator="containsText" id="{2af754c9-73ed-4822-81b8-187a491a64e7}">
+          <x14:cfRule type="containsText" priority="686" operator="containsText" id="{85dc309a-9e29-4a8d-a26b-29c0d8c92f6d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L147)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12361,7 +12361,7 @@
           <xm:sqref>L147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="683" operator="containsText" id="{16909bc2-3ad5-4f39-898e-460279ccb30a}">
+          <x14:cfRule type="containsText" priority="683" operator="containsText" id="{914f6d7d-04c6-4b90-bc7a-0d3381287129}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I148)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12376,7 +12376,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="684" operator="containsText" id="{e1c8813d-96c8-4c97-8a7d-57beb730d074}">
+          <x14:cfRule type="containsText" priority="684" operator="containsText" id="{3df6c991-bdaf-49b0-ac29-f72c628e1a5a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I148)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12394,7 +12394,7 @@
           <xm:sqref>I148</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="687" operator="containsText" id="{7a56c603-cc67-46ce-8c7e-5fab1ed260d7}">
+          <x14:cfRule type="containsText" priority="687" operator="containsText" id="{db5b4628-41c6-4e28-b27c-ff53e88bc8a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I149)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12409,7 +12409,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="688" operator="containsText" id="{6f2fdf32-2e1f-4281-a635-bbeafaa2ba0b}">
+          <x14:cfRule type="containsText" priority="688" operator="containsText" id="{3f1321bc-c758-4480-8e3c-8ec24e33ee16}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I149)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12427,7 +12427,7 @@
           <xm:sqref>I149</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="709" operator="containsText" id="{91077e60-37d0-41f0-94ec-983f67f701b2}">
+          <x14:cfRule type="containsText" priority="709" operator="containsText" id="{33c8f1ef-41c3-40da-a0ac-0f6a6828e58d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I151)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12442,7 +12442,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="710" operator="containsText" id="{f5b91b6c-4ae1-4721-bf10-f8f04f8ffc58}">
+          <x14:cfRule type="containsText" priority="710" operator="containsText" id="{41039016-09ae-4669-88f9-ca8907b64297}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I151)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12460,7 +12460,7 @@
           <xm:sqref>I151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="717" operator="containsText" id="{1c8bbd67-dbe3-4c09-852a-653f672c5ca7}">
+          <x14:cfRule type="containsText" priority="717" operator="containsText" id="{7d3386fe-25af-4456-86d4-b101123aa56d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I152)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12475,7 +12475,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="718" operator="containsText" id="{31a1a5ad-4add-480a-9c81-b17b782c0aad}">
+          <x14:cfRule type="containsText" priority="718" operator="containsText" id="{85ed67ec-0ea1-4657-a980-2df541aea86e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I152)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12493,7 +12493,7 @@
           <xm:sqref>I152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="707" operator="containsText" id="{050cf5c9-e45e-4fc8-a248-4db41aa20f97}">
+          <x14:cfRule type="containsText" priority="707" operator="containsText" id="{86565c68-e115-46f2-85e3-b3d195dc834b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12508,7 +12508,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="708" operator="containsText" id="{7ee1a027-4245-48ac-bb5a-201baf38e9f7}">
+          <x14:cfRule type="containsText" priority="708" operator="containsText" id="{58d69646-4eae-4538-9857-e607659c21e6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12526,7 +12526,7 @@
           <xm:sqref>I153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="719" operator="containsText" id="{5cd60511-964b-4913-b830-8c3c8edc203f}">
+          <x14:cfRule type="containsText" priority="719" operator="containsText" id="{41ecc027-d704-4518-a59d-932836f352b7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12541,7 +12541,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="720" operator="containsText" id="{8eae5917-1694-49f6-b173-8f86c9fd28bc}">
+          <x14:cfRule type="containsText" priority="720" operator="containsText" id="{20f47b41-6976-42b0-b1ec-f0b718b255ee}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12559,7 +12559,7 @@
           <xm:sqref>K153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="705" operator="containsText" id="{26c146fb-5f5d-4ebb-82da-08d5aa11351c}">
+          <x14:cfRule type="containsText" priority="705" operator="containsText" id="{1affb2db-4a06-4bb8-82d4-d35ab215a353}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L153)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12574,7 +12574,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="706" operator="containsText" id="{facbce47-8d3a-4ec0-bb6e-81f3409f0678}">
+          <x14:cfRule type="containsText" priority="706" operator="containsText" id="{ceef8699-6b33-4d98-8ae7-824f52899eb3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L153)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12592,7 +12592,7 @@
           <xm:sqref>L153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="139" operator="containsText" id="{87b9edd5-1945-49cc-a4d6-61809b2ab77d}">
+          <x14:cfRule type="containsText" priority="139" operator="containsText" id="{0ba6809a-b506-469a-997b-09af279f6c33}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12607,7 +12607,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="140" operator="containsText" id="{709bdb2b-8801-4da2-8899-0967369c388e}">
+          <x14:cfRule type="containsText" priority="140" operator="containsText" id="{83950c4f-7f7d-4717-bfab-c9912ef8e3e4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12625,7 +12625,7 @@
           <xm:sqref>G154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="711" operator="containsText" id="{5eb58d26-4034-4c2c-aefa-a50a7883cc23}">
+          <x14:cfRule type="containsText" priority="711" operator="containsText" id="{76d75496-1197-4dee-aed3-d4e96cecd6b2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12640,7 +12640,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="712" operator="containsText" id="{6500745a-f5e8-4395-857b-c7466487e5d6}">
+          <x14:cfRule type="containsText" priority="712" operator="containsText" id="{316b388f-4a7b-4e37-9169-8a324b8eba67}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12658,7 +12658,7 @@
           <xm:sqref>I154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="689" operator="containsText" id="{168cef30-36bb-4a63-a306-68f48256d862}">
+          <x14:cfRule type="containsText" priority="689" operator="containsText" id="{1413840d-1c5f-4a01-8a8e-98324b405eb8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I155)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12673,7 +12673,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="690" operator="containsText" id="{763f584e-3d10-421f-a2f5-63c807b29480}">
+          <x14:cfRule type="containsText" priority="690" operator="containsText" id="{523abf77-7fb1-47da-96dc-d675fdb8656f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I155)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12691,7 +12691,7 @@
           <xm:sqref>I155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="661" operator="containsText" id="{f54c40bc-2870-45e6-9b97-0eca0a9089d0}">
+          <x14:cfRule type="containsText" priority="661" operator="containsText" id="{8dae1b4f-6b98-4b0e-9f68-967b6742174d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12706,7 +12706,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="662" operator="containsText" id="{00f45b74-c2bf-447e-b839-2ea3f410c19c}">
+          <x14:cfRule type="containsText" priority="662" operator="containsText" id="{f2a25a1d-1b2e-4122-a015-e70de8a03a01}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12724,7 +12724,7 @@
           <xm:sqref>I156</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="651" operator="containsText" id="{59194be3-6d38-45e8-8f98-8f406cc1476b}">
+          <x14:cfRule type="containsText" priority="651" operator="containsText" id="{d4d20848-ed1c-4771-9a95-c63eb403ad5d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12739,7 +12739,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="652" operator="containsText" id="{1ed14ae9-1da7-4c9c-8133-97d174f04e38}">
+          <x14:cfRule type="containsText" priority="652" operator="containsText" id="{5a4937a2-2ffc-4b70-a501-280cc64ebe7d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12757,7 +12757,7 @@
           <xm:sqref>L156</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="663" operator="containsText" id="{4851811c-ad76-484b-a7da-92f8f4de1a6c}">
+          <x14:cfRule type="containsText" priority="663" operator="containsText" id="{d4927174-2a7c-4e9c-a351-21481cd6d7c9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I158)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12772,7 +12772,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="664" operator="containsText" id="{288a9513-7cca-45fa-8327-baaa9a0ff861}">
+          <x14:cfRule type="containsText" priority="664" operator="containsText" id="{6d5b891d-0909-4bc9-a13d-0e4dc3dbcef7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I158)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12790,7 +12790,7 @@
           <xm:sqref>I158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="641" operator="containsText" id="{339ef32e-6959-4ae7-a9f1-b2c3594565b5}">
+          <x14:cfRule type="containsText" priority="641" operator="containsText" id="{ecf2dbe6-3dca-45df-90bc-6bcc4ef32f95}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I160)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12805,7 +12805,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="642" operator="containsText" id="{05589ec1-348a-44b2-a2ff-b5e9d4e5ca17}">
+          <x14:cfRule type="containsText" priority="642" operator="containsText" id="{95d99c72-6939-4a7b-ad62-2f4c3df38489}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I160)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12823,7 +12823,7 @@
           <xm:sqref>I160</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="639" operator="containsText" id="{942416ee-8d06-47cb-a92d-d9ca9e284ee9}">
+          <x14:cfRule type="containsText" priority="639" operator="containsText" id="{be49a676-5167-43f5-a1a2-c6a1b9fe7ed3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I161)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12838,7 +12838,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="640" operator="containsText" id="{d588fe28-64b7-4d63-8bb8-c851ed82c23a}">
+          <x14:cfRule type="containsText" priority="640" operator="containsText" id="{5bf8066d-1633-4d27-aa7c-14b3392a1e57}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I161)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12856,7 +12856,7 @@
           <xm:sqref>I161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="645" operator="containsText" id="{705d6538-684d-4349-a1f1-c7301f17b14a}">
+          <x14:cfRule type="containsText" priority="645" operator="containsText" id="{d19c3fea-35cf-4775-8364-4d96abdd0a32}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L161)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12871,7 +12871,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="646" operator="containsText" id="{1a4c1f46-2925-4507-8a92-c17cbf4b9c13}">
+          <x14:cfRule type="containsText" priority="646" operator="containsText" id="{4806b8c8-b9bb-46d9-bab9-7a4796af7ecf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L161)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12889,7 +12889,7 @@
           <xm:sqref>L161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="631" operator="containsText" id="{6f855ae2-4fc8-42a2-bfa0-84ebe71c11a1}">
+          <x14:cfRule type="containsText" priority="631" operator="containsText" id="{daa0644e-86e4-4604-a1c6-85e4cf4c1552}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I162)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12904,7 +12904,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="632" operator="containsText" id="{9567272a-116d-41a0-a87e-d955eceba593}">
+          <x14:cfRule type="containsText" priority="632" operator="containsText" id="{ff95d65b-e5f8-4adf-823a-3d7fd888e51a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I162)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12922,7 +12922,7 @@
           <xm:sqref>I162</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="633" operator="containsText" id="{2c8ebddc-829c-4b81-a582-14f1491a094b}">
+          <x14:cfRule type="containsText" priority="633" operator="containsText" id="{23e4ac11-1787-4a28-860d-d9efe919a0ee}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I163)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12937,7 +12937,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="634" operator="containsText" id="{04aa567b-9a17-42b4-b679-2805b8012d8d}">
+          <x14:cfRule type="containsText" priority="634" operator="containsText" id="{cb2b40bc-72db-40cc-802e-6db5a3795b5c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I163)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12955,7 +12955,7 @@
           <xm:sqref>I163</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="657" operator="containsText" id="{d65f5e13-3f34-42dd-9819-f08eeb91d53b}">
+          <x14:cfRule type="containsText" priority="657" operator="containsText" id="{ccccf86e-f576-4bff-8e86-c67adc404c3f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I165)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -12970,7 +12970,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="658" operator="containsText" id="{62b6a08d-942f-4c17-a2b9-eed49993ebc1}">
+          <x14:cfRule type="containsText" priority="658" operator="containsText" id="{8cd6eb8f-c4a6-45a1-b324-cdb77aed51c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I165)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -12988,7 +12988,7 @@
           <xm:sqref>I165</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="665" operator="containsText" id="{6299d295-0c60-4ec1-8e2e-ed8714a5da53}">
+          <x14:cfRule type="containsText" priority="665" operator="containsText" id="{22e1da3b-4123-44e0-b856-cfaa61b1c639}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I166)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13003,7 +13003,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="666" operator="containsText" id="{eea03c8f-4810-4b51-be83-3e4aabc13c59}">
+          <x14:cfRule type="containsText" priority="666" operator="containsText" id="{2db554a2-e61c-4608-988b-f13716c00b9b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I166)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13021,7 +13021,7 @@
           <xm:sqref>I166</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="637" operator="containsText" id="{f1a81c02-557f-45de-b911-a419c1c524ca}">
+          <x14:cfRule type="containsText" priority="637" operator="containsText" id="{3036c091-0325-4807-a633-60cfbc1aded0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13036,7 +13036,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="638" operator="containsText" id="{f937609b-bc52-4b3e-8cf4-e76dd5175092}">
+          <x14:cfRule type="containsText" priority="638" operator="containsText" id="{0273274e-c5d9-4b96-9cd6-e9d906cb33ea}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13054,7 +13054,7 @@
           <xm:sqref>I167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="667" operator="containsText" id="{70742a24-1376-4438-b0fc-4ee191d96c5a}">
+          <x14:cfRule type="containsText" priority="667" operator="containsText" id="{4bd2a6be-0933-4b71-9556-bbb54e33a68f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13069,7 +13069,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="668" operator="containsText" id="{373fb17d-8ea0-40db-868b-ed0f4b6a5cf3}">
+          <x14:cfRule type="containsText" priority="668" operator="containsText" id="{4c6fc226-f409-4ab2-bb6e-6a1bf6bf27a6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13087,7 +13087,7 @@
           <xm:sqref>K167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="635" operator="containsText" id="{dd24a093-036c-4806-a3b9-078ebcf3367c}">
+          <x14:cfRule type="containsText" priority="635" operator="containsText" id="{8711c179-cb26-40b0-abb0-03bd20bcc507}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L167)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13102,7 +13102,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="636" operator="containsText" id="{91fa7669-08cd-4580-8223-6940de825003}">
+          <x14:cfRule type="containsText" priority="636" operator="containsText" id="{3e6c7adb-25d9-4698-a8fa-c50304f7ce22}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L167)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13120,7 +13120,7 @@
           <xm:sqref>L167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="135" operator="containsText" id="{d8e89015-0b5a-4787-a528-0a6ff6a3f344}">
+          <x14:cfRule type="containsText" priority="135" operator="containsText" id="{476dff0f-cf51-4ede-b871-de2e02857106}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13135,7 +13135,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="136" operator="containsText" id="{4e0f3b09-0e57-412c-b38c-b77b6b9a38d1}">
+          <x14:cfRule type="containsText" priority="136" operator="containsText" id="{61a4ce70-d23c-40aa-941c-270a881d063c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13153,7 +13153,7 @@
           <xm:sqref>G168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="659" operator="containsText" id="{d40d3b10-3569-433b-b519-8d4ddd93fe79}">
+          <x14:cfRule type="containsText" priority="659" operator="containsText" id="{856fc85c-cd09-41b8-a0cd-74b0a7f602c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13168,7 +13168,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="660" operator="containsText" id="{886ee901-cdee-4a4d-9c27-5329448c2025}">
+          <x14:cfRule type="containsText" priority="660" operator="containsText" id="{588c990b-5619-45d2-99eb-9b6991749fff}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13186,7 +13186,7 @@
           <xm:sqref>I168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="649" operator="containsText" id="{7b16fdf3-0bf2-4e6e-999b-eb69ad288daf}">
+          <x14:cfRule type="containsText" priority="649" operator="containsText" id="{b181f233-03c6-49d9-81b4-421d2bc04b4a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I169)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13201,7 +13201,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="650" operator="containsText" id="{8699d35b-433e-4180-b6be-d7b59ffe0c44}">
+          <x14:cfRule type="containsText" priority="650" operator="containsText" id="{167b04cb-813d-4f50-a93d-c5632f1cc934}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I169)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13219,7 +13219,7 @@
           <xm:sqref>I169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="615" operator="containsText" id="{a99bc9e5-6343-4994-ac71-6caffb406ca1}">
+          <x14:cfRule type="containsText" priority="615" operator="containsText" id="{9a7918e8-27fc-484d-89e9-0f057799a3d0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13234,7 +13234,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="616" operator="containsText" id="{22706584-b34a-41db-af88-88b3c819775c}">
+          <x14:cfRule type="containsText" priority="616" operator="containsText" id="{35865e2a-29b9-4768-b4cb-990bc7fcc3da}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13252,7 +13252,7 @@
           <xm:sqref>I170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="609" operator="containsText" id="{17ef0ff9-5a1f-40ed-b785-a024ce008dc6}">
+          <x14:cfRule type="containsText" priority="609" operator="containsText" id="{39f0ccdf-80ac-4bb2-ae97-1411a9ff5864}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13267,7 +13267,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="610" operator="containsText" id="{d706fc80-491a-40cf-bd70-7ccb90af79f3}">
+          <x14:cfRule type="containsText" priority="610" operator="containsText" id="{dfae622e-04a4-44d0-bf8c-a9bd88424295}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13285,7 +13285,7 @@
           <xm:sqref>L170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="585" operator="containsText" id="{bc2c930c-2d42-45c1-b2b4-63e451c6292b}">
+          <x14:cfRule type="containsText" priority="585" operator="containsText" id="{0cb3feec-da56-4484-a922-555a09471fb8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13300,7 +13300,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="586" operator="containsText" id="{8257bb3d-ba60-47f8-9e77-0715bfff648e}">
+          <x14:cfRule type="containsText" priority="586" operator="containsText" id="{8ac5ae1d-daec-49ae-8399-cc2286a9d9c7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13318,7 +13318,7 @@
           <xm:sqref>I171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="169" operator="containsText" id="{72eed64b-d84a-4791-b2e8-4af74b9d2785}">
+          <x14:cfRule type="containsText" priority="169" operator="containsText" id="{78982128-2598-483f-867d-e8f02407bee0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13333,7 +13333,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="170" operator="containsText" id="{4e4d382c-73f4-4b96-9189-ce5295e3d722}">
+          <x14:cfRule type="containsText" priority="170" operator="containsText" id="{702411e5-4008-49ae-aaee-3b32b987bf3b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13351,7 +13351,7 @@
           <xm:sqref>K171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="583" operator="containsText" id="{acd7ab71-a2e6-4bb4-bb1b-ad436604eaf1}">
+          <x14:cfRule type="containsText" priority="583" operator="containsText" id="{4c3acbfa-c9e7-4e3b-a757-85b22382b627}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L171)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13366,7 +13366,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="584" operator="containsText" id="{48c6bb50-9e14-41fa-a8dc-d2256595887e}">
+          <x14:cfRule type="containsText" priority="584" operator="containsText" id="{00904f1f-8994-4e60-a17d-e412d2bc98b6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L171)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13384,7 +13384,7 @@
           <xm:sqref>L171</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="617" operator="containsText" id="{4a3d9aeb-7bf6-4c32-9c3a-10a4abae569a}">
+          <x14:cfRule type="containsText" priority="617" operator="containsText" id="{88eab696-3f7b-43a5-889d-125732fa1fcd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I172)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13399,7 +13399,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="618" operator="containsText" id="{e8c2e97d-85f7-49d1-bf10-9e5a970690b5}">
+          <x14:cfRule type="containsText" priority="618" operator="containsText" id="{452b5ad1-51ba-4006-b428-8ccd57077173}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I172)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13417,7 +13417,7 @@
           <xm:sqref>I172</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="603" operator="containsText" id="{fe062484-28c3-46f6-9c7e-c5fff1da949b}">
+          <x14:cfRule type="containsText" priority="603" operator="containsText" id="{3af459b6-642b-4ac9-ad2f-f9c8caf9cb05}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I174)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13432,7 +13432,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="604" operator="containsText" id="{1ec4441d-b6a7-4a94-bec2-e2895e4c1477}">
+          <x14:cfRule type="containsText" priority="604" operator="containsText" id="{5a283d67-7f7d-4c77-ac11-4ed9f05c9f9e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I174)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13450,7 +13450,7 @@
           <xm:sqref>I174</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="601" operator="containsText" id="{82251464-571e-4312-a37c-45ab3efdfdbc}">
+          <x14:cfRule type="containsText" priority="601" operator="containsText" id="{6194fc2a-d2e0-4d8e-942d-ce9d36133f2f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13465,7 +13465,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="602" operator="containsText" id="{fb91e405-f92d-49aa-bf4e-34bcc3eb8763}">
+          <x14:cfRule type="containsText" priority="602" operator="containsText" id="{b7848796-1621-432b-bfef-2cb990047e30}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13483,7 +13483,7 @@
           <xm:sqref>I175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="525" operator="containsText" id="{f0786853-a5b2-46a3-9db3-b9c76e598b40}">
+          <x14:cfRule type="containsText" priority="525" operator="containsText" id="{0f0b1a35-a30d-4e7a-8c7f-b6c093136665}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13498,7 +13498,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="526" operator="containsText" id="{9479d8ab-dc31-4cb0-a707-6fe7f80e2e7b}">
+          <x14:cfRule type="containsText" priority="526" operator="containsText" id="{fe99a7c5-f789-4ff8-b307-666978249899}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13516,7 +13516,7 @@
           <xm:sqref>K175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="577" operator="containsText" id="{ca0acf9a-7e6a-4d37-8610-44a32ad17228}">
+          <x14:cfRule type="containsText" priority="577" operator="containsText" id="{752408b6-9119-48d4-a461-55f0fbe2fd80}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L175)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13531,7 +13531,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="578" operator="containsText" id="{ca3c154c-6568-4505-91ee-aca041f928ae}">
+          <x14:cfRule type="containsText" priority="578" operator="containsText" id="{47bb0804-0f8b-4ca3-b9f4-8571cd169817}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L175)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13549,7 +13549,7 @@
           <xm:sqref>L175</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="579" operator="containsText" id="{8e87ff89-9b77-4d1c-a199-b7f493058a84}">
+          <x14:cfRule type="containsText" priority="579" operator="containsText" id="{dcc2e86a-d38f-4ded-ac5f-fa956e78c48e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I176)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13564,7 +13564,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="580" operator="containsText" id="{feac389e-1d0b-4875-9aa6-0a86509efbc6}">
+          <x14:cfRule type="containsText" priority="580" operator="containsText" id="{67fa5b6b-ec7f-4110-a3c7-61911268f4cf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I176)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13582,7 +13582,7 @@
           <xm:sqref>I176</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="581" operator="containsText" id="{801365e4-7e7b-447b-bf95-e285d656a795}">
+          <x14:cfRule type="containsText" priority="581" operator="containsText" id="{c588e484-649c-4512-9bdf-1942b1f745f7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I177)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13597,7 +13597,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="582" operator="containsText" id="{93128d1d-16a8-48ee-8b97-a0b7703b353e}">
+          <x14:cfRule type="containsText" priority="582" operator="containsText" id="{cb89e197-7fa6-444c-99bf-8c4a69b6994b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I177)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13615,7 +13615,7 @@
           <xm:sqref>I177</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="611" operator="containsText" id="{61e2f26b-d03c-460f-9352-9459d894c6f7}">
+          <x14:cfRule type="containsText" priority="611" operator="containsText" id="{1a3b9501-9d26-4ef5-843f-0d44912d5f5a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I179)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13630,7 +13630,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="612" operator="containsText" id="{ae7a18ff-8bf2-4477-98ed-2257148b6dbb}">
+          <x14:cfRule type="containsText" priority="612" operator="containsText" id="{54d79705-b645-4b73-9e11-3a1821e192e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I179)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13648,7 +13648,7 @@
           <xm:sqref>I179</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="619" operator="containsText" id="{3cfd65e8-16cf-4395-aae3-2e61c6a342d2}">
+          <x14:cfRule type="containsText" priority="619" operator="containsText" id="{6e603b3c-d244-48a8-887f-51955b3b99fa}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I180)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13663,7 +13663,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="620" operator="containsText" id="{3049c8f9-9c62-4679-aacd-516f0b23c6d4}">
+          <x14:cfRule type="containsText" priority="620" operator="containsText" id="{f64da00f-a085-4537-a9b0-1b0050d66f72}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I180)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13681,7 +13681,7 @@
           <xm:sqref>I180</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="589" operator="containsText" id="{522ad13a-9683-4bef-9542-4db88fe9b3ab}">
+          <x14:cfRule type="containsText" priority="589" operator="containsText" id="{57ebb902-1c55-4bd3-80d7-861b1a3b3566}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13696,7 +13696,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="590" operator="containsText" id="{ea232405-791f-4dce-8b87-7244cdb6f9a9}">
+          <x14:cfRule type="containsText" priority="590" operator="containsText" id="{f3c34089-d8b0-469e-9470-f0b205ca89f9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13714,7 +13714,7 @@
           <xm:sqref>I181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="621" operator="containsText" id="{457cb0cd-dc06-4322-aee9-63f18e9f43a9}">
+          <x14:cfRule type="containsText" priority="621" operator="containsText" id="{693b3dd2-9f9b-4d4b-9695-eee327d2b6d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13729,7 +13729,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="622" operator="containsText" id="{88bd5252-2d38-4dcf-97a1-dfddb64725c5}">
+          <x14:cfRule type="containsText" priority="622" operator="containsText" id="{c56cf708-bbe5-4c1a-ba85-6082282c1b60}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13747,7 +13747,7 @@
           <xm:sqref>K181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="587" operator="containsText" id="{3794af57-ed10-4f79-80cd-ab2750ce88ae}">
+          <x14:cfRule type="containsText" priority="587" operator="containsText" id="{d42e7236-6b9c-44ef-9826-8dc508dae43b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L181)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13762,7 +13762,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="588" operator="containsText" id="{77268c3e-23a5-429a-91cd-aeede501264c}">
+          <x14:cfRule type="containsText" priority="588" operator="containsText" id="{2be6079e-5930-45ce-bde9-8193966f81c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L181)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13780,7 +13780,7 @@
           <xm:sqref>L181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="131" operator="containsText" id="{ab27fc92-dbd5-4d48-9fad-c139d70489db}">
+          <x14:cfRule type="containsText" priority="131" operator="containsText" id="{24372c1e-4330-4cd0-924d-cc4ed3dbf356}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13795,7 +13795,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="132" operator="containsText" id="{22ae9cec-09c8-4599-9ac5-f158a3bd2afa}">
+          <x14:cfRule type="containsText" priority="132" operator="containsText" id="{f714f75d-f7f3-48b9-a45d-dcdab1d8466a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13813,7 +13813,7 @@
           <xm:sqref>G182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="613" operator="containsText" id="{ab33aad0-4d57-4511-b8a5-78f6af9ccf37}">
+          <x14:cfRule type="containsText" priority="613" operator="containsText" id="{07a1178c-c449-497e-948a-fce10cdb8ca8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13828,7 +13828,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="614" operator="containsText" id="{8724bb6a-7f41-408d-8fdb-395c9ad298ef}">
+          <x14:cfRule type="containsText" priority="614" operator="containsText" id="{0407c5aa-e942-47da-971e-6133c9576934}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13846,7 +13846,7 @@
           <xm:sqref>I182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="591" operator="containsText" id="{4ed206cc-d004-4089-9214-57dfd6d1a1cb}">
+          <x14:cfRule type="containsText" priority="591" operator="containsText" id="{143e3d53-fdc4-49f6-8bf1-3bb389779844}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I183)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13861,7 +13861,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="592" operator="containsText" id="{40c02543-4a04-4aa7-8471-b086729073b4}">
+          <x14:cfRule type="containsText" priority="592" operator="containsText" id="{a8090564-6dc7-4319-b07d-8700d58f637d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I183)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13879,7 +13879,7 @@
           <xm:sqref>I183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="561" operator="containsText" id="{9d28a55b-a1b6-4452-aa2b-819263dc3af7}">
+          <x14:cfRule type="containsText" priority="561" operator="containsText" id="{8a83242a-fd90-4743-b81b-e7e9c20ebb7b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13894,7 +13894,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="562" operator="containsText" id="{899e3732-5a12-48f2-ad66-de6ffe8a902c}">
+          <x14:cfRule type="containsText" priority="562" operator="containsText" id="{4a07b724-ec28-40b1-bcac-26081dbc0f02}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13912,7 +13912,7 @@
           <xm:sqref>I184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="555" operator="containsText" id="{9781c74c-667a-4a6e-b88a-e67823e39fb3}">
+          <x14:cfRule type="containsText" priority="555" operator="containsText" id="{7c087ae9-c812-4199-92af-4cf6d0b55fa4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13927,7 +13927,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="556" operator="containsText" id="{606ff761-452b-450a-8566-a5d1cd91d661}">
+          <x14:cfRule type="containsText" priority="556" operator="containsText" id="{888ad8db-241c-44ac-aea7-d4e7b96c4068}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13945,7 +13945,7 @@
           <xm:sqref>L184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="543" operator="containsText" id="{f062e32d-b24d-4720-bb3b-366f5f9655bc}">
+          <x14:cfRule type="containsText" priority="543" operator="containsText" id="{5d1c002b-1680-49b6-9907-5c40d7c310b6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I185)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13960,7 +13960,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="544" operator="containsText" id="{141c285d-5c66-4cd8-955d-b949bf738045}">
+          <x14:cfRule type="containsText" priority="544" operator="containsText" id="{bd89bf70-8a2f-4723-ae6d-26e5dda9ee2b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I185)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -13978,7 +13978,7 @@
           <xm:sqref>I185</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="541" operator="containsText" id="{27b96349-30b1-4431-ac48-b8524b3ff280}">
+          <x14:cfRule type="containsText" priority="541" operator="containsText" id="{4f25fa2d-c982-4424-9815-f907b2162720}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L185)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -13993,7 +13993,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="542" operator="containsText" id="{22937210-f71a-449c-8d14-866bc08f0886}">
+          <x14:cfRule type="containsText" priority="542" operator="containsText" id="{3fb791a9-830e-482d-870a-51b6035e63a6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L185)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14011,7 +14011,7 @@
           <xm:sqref>L185</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="563" operator="containsText" id="{3c1149dc-20b4-4ca0-be31-a0ed3c76ea2c}">
+          <x14:cfRule type="containsText" priority="563" operator="containsText" id="{f5eaf1b2-f036-46d5-8787-24077e3bc52c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I186)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14026,7 +14026,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="564" operator="containsText" id="{42a632d4-398b-4ef6-a29e-e9a46608eeab}">
+          <x14:cfRule type="containsText" priority="564" operator="containsText" id="{69594431-296a-4412-90c8-d1e2e4b0917f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I186)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14044,7 +14044,7 @@
           <xm:sqref>I186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="553" operator="containsText" id="{cb318a82-f4fe-4f63-b197-1156213664d1}">
+          <x14:cfRule type="containsText" priority="553" operator="containsText" id="{15d8edd3-b60a-47fe-808f-cc52e6442ef4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I188)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14059,7 +14059,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="554" operator="containsText" id="{a1b96868-aada-4b69-a711-478fea43ae4e}">
+          <x14:cfRule type="containsText" priority="554" operator="containsText" id="{edb14a1a-7f4e-42e1-b2fa-17e5efd2da85}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I188)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14077,7 +14077,7 @@
           <xm:sqref>I188</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="551" operator="containsText" id="{003cf212-ed62-4e63-9217-dc2050647a92}">
+          <x14:cfRule type="containsText" priority="551" operator="containsText" id="{8b7c7d9a-5d2c-4f08-98d8-772a472578d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14092,7 +14092,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="552" operator="containsText" id="{4ebef25b-6e52-42c8-9fa1-b27939d25ea7}">
+          <x14:cfRule type="containsText" priority="552" operator="containsText" id="{13cdac2d-f459-4ab8-b9cd-05cc9b8c8c89}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14110,7 +14110,7 @@
           <xm:sqref>I189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="197" operator="containsText" id="{8168bdaa-4699-460a-b87e-29a4797137bd}">
+          <x14:cfRule type="containsText" priority="197" operator="containsText" id="{cdb692e2-ff98-4086-8049-c342be6ee4cd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14125,7 +14125,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="198" operator="containsText" id="{85ea8c9f-fcd5-473b-860a-40430b79c714}">
+          <x14:cfRule type="containsText" priority="198" operator="containsText" id="{cb54e224-419e-4f3d-add9-c8b287a09576}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14143,7 +14143,7 @@
           <xm:sqref>K189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="529" operator="containsText" id="{c30f68c7-955f-492d-9dcb-d3912b05d575}">
+          <x14:cfRule type="containsText" priority="529" operator="containsText" id="{83e23995-5990-4957-a4a5-aad91774957d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L189)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14158,7 +14158,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="530" operator="containsText" id="{fcc84951-6fa7-451d-bb51-f255d59f022c}">
+          <x14:cfRule type="containsText" priority="530" operator="containsText" id="{8a4c72f4-579d-45a3-9856-3604cc107466}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L189)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14176,7 +14176,7 @@
           <xm:sqref>L189</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="527" operator="containsText" id="{8e706633-1e2f-4310-bd83-04d29591f90d}">
+          <x14:cfRule type="containsText" priority="527" operator="containsText" id="{b60a500c-7e4f-44a2-8383-fc2a2e9d561b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I190)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14191,7 +14191,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="528" operator="containsText" id="{b55ad885-00b8-4f97-90ee-09447736f865}">
+          <x14:cfRule type="containsText" priority="528" operator="containsText" id="{9fac1249-39e9-49b1-896b-afa4aa747523}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I190)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14209,7 +14209,7 @@
           <xm:sqref>I190</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="539" operator="containsText" id="{f2ccd662-db5e-4a0b-99ac-dfbaed78c1d6}">
+          <x14:cfRule type="containsText" priority="539" operator="containsText" id="{f887e634-2beb-42b1-999a-183dfbcc4051}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I191)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14224,7 +14224,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="540" operator="containsText" id="{33136aed-380a-4cb3-bd4d-884e906e3653}">
+          <x14:cfRule type="containsText" priority="540" operator="containsText" id="{6058f6c0-a505-4e44-af40-4f7d8301fb96}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I191)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14242,7 +14242,7 @@
           <xm:sqref>I191</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="557" operator="containsText" id="{ead7313b-2684-4730-b1b5-787dec4ccdff}">
+          <x14:cfRule type="containsText" priority="557" operator="containsText" id="{1e0613c9-46c2-40e8-b0d1-0bcf3a3f630f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I193)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14257,7 +14257,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="558" operator="containsText" id="{a1a09dee-7185-468a-8894-90acf469ed54}">
+          <x14:cfRule type="containsText" priority="558" operator="containsText" id="{b4994a4c-7926-4e14-ad17-ca3b932fb673}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I193)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14275,7 +14275,7 @@
           <xm:sqref>I193</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="565" operator="containsText" id="{0dcec330-5d3f-4d45-b92c-e83da4e59427}">
+          <x14:cfRule type="containsText" priority="565" operator="containsText" id="{55be9149-1c0e-41c1-8f5d-bff3e6a6f65a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I194)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14290,7 +14290,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="566" operator="containsText" id="{a6b78553-3860-4bd6-ad76-35ad311417e4}">
+          <x14:cfRule type="containsText" priority="566" operator="containsText" id="{6df38c89-03a2-468f-ad97-8698eb2043dc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I194)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14308,7 +14308,7 @@
           <xm:sqref>I194</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="533" operator="containsText" id="{6d99bca6-0b8a-434c-a89f-280b870e1dcb}">
+          <x14:cfRule type="containsText" priority="533" operator="containsText" id="{3970bd1e-bf30-4146-9929-1a46d36498b5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14323,7 +14323,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="534" operator="containsText" id="{2cc7fd00-7e87-47e0-bdef-94cae5942981}">
+          <x14:cfRule type="containsText" priority="534" operator="containsText" id="{5a756ef6-d0f8-481e-8657-10e51a89585a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14341,7 +14341,7 @@
           <xm:sqref>I195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="195" operator="containsText" id="{1c78a6c4-74ca-40df-95f1-c9de4ccb7b32}">
+          <x14:cfRule type="containsText" priority="195" operator="containsText" id="{c5599225-38ee-44d9-8ea0-17155c74741f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14356,7 +14356,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="196" operator="containsText" id="{6c817f29-f7db-49ed-b100-cb4513d57c48}">
+          <x14:cfRule type="containsText" priority="196" operator="containsText" id="{813f4057-b4a6-4b50-845f-f5642a476158}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14374,7 +14374,7 @@
           <xm:sqref>K195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="531" operator="containsText" id="{d0473a1f-8bca-4b0a-8825-41f820bc5e37}">
+          <x14:cfRule type="containsText" priority="531" operator="containsText" id="{3db2fbad-dca2-4b93-a949-f95c7dda7e9c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L195)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14389,7 +14389,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="532" operator="containsText" id="{1954573d-46f4-4bf1-a314-cfe9f0903b56}">
+          <x14:cfRule type="containsText" priority="532" operator="containsText" id="{a77d2f50-f348-4030-b936-d62eceabfab7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L195)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14407,7 +14407,7 @@
           <xm:sqref>L195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="127" operator="containsText" id="{b7475e8d-e37c-4dfd-94e5-a52ac6efd36a}">
+          <x14:cfRule type="containsText" priority="127" operator="containsText" id="{f3d57e9b-0f37-46b2-8b5c-118d40f2a937}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14422,7 +14422,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="128" operator="containsText" id="{92742e0a-c0e7-467d-822b-84800b46d0ac}">
+          <x14:cfRule type="containsText" priority="128" operator="containsText" id="{4525db8b-37a4-4a7f-8b73-29cefdaab824}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14440,7 +14440,7 @@
           <xm:sqref>G196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="559" operator="containsText" id="{217ab5ca-e0d4-433f-a1a4-632e473b0c06}">
+          <x14:cfRule type="containsText" priority="559" operator="containsText" id="{4eec0be0-2e25-4581-bcd9-e6abaf949fff}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14455,7 +14455,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="560" operator="containsText" id="{48d5e071-18cb-4e33-a06f-49cee11d6c06}">
+          <x14:cfRule type="containsText" priority="560" operator="containsText" id="{48de1e4f-51f1-4e03-897a-51050b6f45d0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14473,7 +14473,7 @@
           <xm:sqref>I196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="549" operator="containsText" id="{5db8d270-f975-4ea9-8835-1b2f2cf7f885}">
+          <x14:cfRule type="containsText" priority="549" operator="containsText" id="{b5f0a136-98f7-4fde-8381-a74cc17e9bb2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I197)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14488,7 +14488,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="550" operator="containsText" id="{2c5b27f9-c5ac-4e41-a271-d7b28a1cfe3c}">
+          <x14:cfRule type="containsText" priority="550" operator="containsText" id="{2559fed8-47e8-4efc-b461-defa95750de3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I197)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14506,7 +14506,7 @@
           <xm:sqref>I197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="507" operator="containsText" id="{f5f56b7a-4196-4d7c-97b9-3e752ced3ab2}">
+          <x14:cfRule type="containsText" priority="507" operator="containsText" id="{2b98cc90-9be8-462c-9ed1-94b02e58dadf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14521,7 +14521,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="508" operator="containsText" id="{c584374c-6964-4f93-807b-9a516de15c1a}">
+          <x14:cfRule type="containsText" priority="508" operator="containsText" id="{84f755a7-3d3a-4585-9ceb-d0b5e7dfa1a4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14539,7 +14539,7 @@
           <xm:sqref>I198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="501" operator="containsText" id="{9f64e0be-d59d-4eca-ad6b-99543191e874}">
+          <x14:cfRule type="containsText" priority="501" operator="containsText" id="{52b49979-d8bf-4451-bfeb-1877b50dbfac}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14554,7 +14554,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="502" operator="containsText" id="{4c772447-43d1-474e-bd8b-e9d2f27da5d4}">
+          <x14:cfRule type="containsText" priority="502" operator="containsText" id="{e657c6f1-b726-44d2-803c-507b9b778e6d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14572,7 +14572,7 @@
           <xm:sqref>L198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="493" operator="containsText" id="{6e6ca853-a125-409a-a16e-7f22c2234b72}">
+          <x14:cfRule type="containsText" priority="493" operator="containsText" id="{36ba3708-4e63-438d-8758-82e9b7560791}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14587,7 +14587,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="494" operator="containsText" id="{3d9a75b9-48c2-47f9-80d2-d4e563306c2b}">
+          <x14:cfRule type="containsText" priority="494" operator="containsText" id="{6657caf4-16d9-44ba-97e4-c44a56f9ecc3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14605,7 +14605,7 @@
           <xm:sqref>I199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="193" operator="containsText" id="{5458daed-cb40-4ff1-914f-9b0f02af789d}">
+          <x14:cfRule type="containsText" priority="193" operator="containsText" id="{67d72225-d9ce-466e-9948-3858a94e4bc7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14620,7 +14620,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="194" operator="containsText" id="{23ad668e-2c32-431c-a6e7-2de3beac4091}">
+          <x14:cfRule type="containsText" priority="194" operator="containsText" id="{d72430f8-6116-4804-be70-c51d839cedff}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14638,7 +14638,7 @@
           <xm:sqref>K199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="473" operator="containsText" id="{65dcbbf2-9ba5-4141-a343-d839d752c5b4}">
+          <x14:cfRule type="containsText" priority="473" operator="containsText" id="{636a2e13-46e0-474f-9f90-084ce3f70d7b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L199)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14653,7 +14653,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="474" operator="containsText" id="{b5caa2a0-38c4-486b-9dc0-e02d6af474f0}">
+          <x14:cfRule type="containsText" priority="474" operator="containsText" id="{3b898d4b-06e4-43ff-a801-6de898c73891}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L199)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14671,7 +14671,7 @@
           <xm:sqref>L199</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="509" operator="containsText" id="{5107fdc3-f60d-4597-8c27-c85ef4e103d7}">
+          <x14:cfRule type="containsText" priority="509" operator="containsText" id="{49d49fd4-8b7a-45c5-becf-df4caab1651b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I200)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14686,7 +14686,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="510" operator="containsText" id="{dc117160-6f6a-40e3-9ac1-1cc220535966}">
+          <x14:cfRule type="containsText" priority="510" operator="containsText" id="{31a6b282-aa50-446f-b49c-c25095083ceb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I200)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14704,7 +14704,7 @@
           <xm:sqref>I200</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="499" operator="containsText" id="{41552385-7d7d-45d0-87e1-848c6d8f1466}">
+          <x14:cfRule type="containsText" priority="499" operator="containsText" id="{49d2d28b-634c-492e-bc97-4c6c36f2205d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I202)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14719,7 +14719,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="500" operator="containsText" id="{b297b497-8da2-4182-ade5-029690d49d18}">
+          <x14:cfRule type="containsText" priority="500" operator="containsText" id="{b2cd5080-1ffc-4d57-a2d2-e6384cf1bae3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I202)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14737,7 +14737,7 @@
           <xm:sqref>I202</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="497" operator="containsText" id="{63234021-04db-48da-bce7-f96e1d0ead00}">
+          <x14:cfRule type="containsText" priority="497" operator="containsText" id="{2636fc8a-38d6-47a0-938a-833d10b9296f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14752,7 +14752,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="498" operator="containsText" id="{a84c91eb-6731-48ad-8c33-a71891a2cacc}">
+          <x14:cfRule type="containsText" priority="498" operator="containsText" id="{b79a5be8-d7bb-4790-a9ee-25cc51dfe84f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14770,7 +14770,7 @@
           <xm:sqref>I203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="191" operator="containsText" id="{228045c3-7a56-4a60-97a1-f971ce93fea7}">
+          <x14:cfRule type="containsText" priority="191" operator="containsText" id="{843161c5-5ffb-4864-8448-f540cb81c769}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14785,7 +14785,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="192" operator="containsText" id="{e00085e0-e97f-47a0-954e-ea4f593a2e1e}">
+          <x14:cfRule type="containsText" priority="192" operator="containsText" id="{8d077de5-72d4-48ac-b070-f96ee33906aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14803,7 +14803,7 @@
           <xm:sqref>K203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="479" operator="containsText" id="{f55d9101-309f-4ac1-8ea7-51c8dcf51cd6}">
+          <x14:cfRule type="containsText" priority="479" operator="containsText" id="{c835b2fb-14b2-403f-8ef2-5f6e844588eb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L203)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14818,7 +14818,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="480" operator="containsText" id="{7f8fb459-3144-4da2-ba18-31543de4e9e2}">
+          <x14:cfRule type="containsText" priority="480" operator="containsText" id="{fa823650-4821-4552-8a6d-122a360980ed}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L203)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14836,7 +14836,7 @@
           <xm:sqref>L203</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="481" operator="containsText" id="{7e102ad1-d861-4666-8763-a3178b38c1e3}">
+          <x14:cfRule type="containsText" priority="481" operator="containsText" id="{c703efba-422e-4559-8258-9594204fc2ec}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I204)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14851,7 +14851,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="482" operator="containsText" id="{e7937902-cb63-427d-9489-cd1a79690628}">
+          <x14:cfRule type="containsText" priority="482" operator="containsText" id="{64489140-3072-4e45-a5c8-3571d8c03ec8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I204)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14869,7 +14869,7 @@
           <xm:sqref>I204</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="471" operator="containsText" id="{30f396ff-b0dc-44f2-a996-9efff5221695}">
+          <x14:cfRule type="containsText" priority="471" operator="containsText" id="{fbb642f9-78be-44ce-90c7-7adc4bf09638}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I205)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14884,7 +14884,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="472" operator="containsText" id="{b7730a22-96cf-4a68-8670-ecfa2b0448ae}">
+          <x14:cfRule type="containsText" priority="472" operator="containsText" id="{3ec51ad4-73cb-4d5a-9417-6ccf2a78135c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I205)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14902,7 +14902,7 @@
           <xm:sqref>I205</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="503" operator="containsText" id="{d2565371-de26-402c-a0d7-9bbfa07f872d}">
+          <x14:cfRule type="containsText" priority="503" operator="containsText" id="{35312687-0418-45fc-ad9c-f523ee41cdc5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I207)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14917,7 +14917,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="504" operator="containsText" id="{9420980b-51da-4d05-b16a-9dae03be8e28}">
+          <x14:cfRule type="containsText" priority="504" operator="containsText" id="{f69b7788-a378-4362-9120-f0f8b07a1121}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I207)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14935,7 +14935,7 @@
           <xm:sqref>I207</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="511" operator="containsText" id="{44808e3c-9c96-4698-b205-26d26e9eaab2}">
+          <x14:cfRule type="containsText" priority="511" operator="containsText" id="{72a4d0b5-1a51-4025-989a-7a56c5eac143}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I208)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14950,7 +14950,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="512" operator="containsText" id="{e75c4ed9-45de-4c4d-86b6-3a6646ef9b78}">
+          <x14:cfRule type="containsText" priority="512" operator="containsText" id="{5320806d-9ab1-4d8c-8b86-10572d6553ed}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I208)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -14968,7 +14968,7 @@
           <xm:sqref>I208</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="477" operator="containsText" id="{adf8825e-3058-464a-aabd-c40a51f5db39}">
+          <x14:cfRule type="containsText" priority="477" operator="containsText" id="{320b4feb-da03-4cf1-b733-973cc77f1ddb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -14983,7 +14983,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="478" operator="containsText" id="{4f395a5b-f6a9-4dd1-83cc-631a96c311ab}">
+          <x14:cfRule type="containsText" priority="478" operator="containsText" id="{989de735-8605-4ef3-a2ac-75aee8bc3398}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15001,7 +15001,7 @@
           <xm:sqref>I209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="189" operator="containsText" id="{77797935-38c4-4ffd-91cb-8ee9531569e2}">
+          <x14:cfRule type="containsText" priority="189" operator="containsText" id="{f808a8b9-4c55-4bfa-97d6-e65c25fd8d04}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15016,7 +15016,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="190" operator="containsText" id="{6dd76db5-6bcc-4f5d-bf1e-c13ae79e01e0}">
+          <x14:cfRule type="containsText" priority="190" operator="containsText" id="{360e08cc-3106-4105-8379-97bb78e9811d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15034,7 +15034,7 @@
           <xm:sqref>K209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="475" operator="containsText" id="{030f550a-147e-40ab-b9b7-fe41c009ae18}">
+          <x14:cfRule type="containsText" priority="475" operator="containsText" id="{829c6cc5-2712-444d-93ef-e2b6c9ca3049}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L209)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15049,7 +15049,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="476" operator="containsText" id="{5be02b10-caf1-4e40-82be-c5689eb4f0e8}">
+          <x14:cfRule type="containsText" priority="476" operator="containsText" id="{71935368-be4c-49c9-8e24-92729a10d60e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L209)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15067,7 +15067,7 @@
           <xm:sqref>L209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="121" operator="containsText" id="{62276a20-eac1-4a65-b40d-e2020e6d354b}">
+          <x14:cfRule type="containsText" priority="121" operator="containsText" id="{16538624-4fc7-40b3-a368-6e936d681ec3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15082,7 +15082,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="122" operator="containsText" id="{45a80e83-f5fd-4ace-8051-0c958a0b9647}">
+          <x14:cfRule type="containsText" priority="122" operator="containsText" id="{4d1064b6-1111-48d1-91e4-054ecc928638}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15100,7 +15100,7 @@
           <xm:sqref>G210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="505" operator="containsText" id="{3ce27e2a-d5bd-4265-9227-de4bf1e0ade6}">
+          <x14:cfRule type="containsText" priority="505" operator="containsText" id="{9b92df30-a950-4b11-8ea1-2114865afef7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15115,7 +15115,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="506" operator="containsText" id="{7861c9fb-570b-4e0e-9b6b-3cfe24a6364b}">
+          <x14:cfRule type="containsText" priority="506" operator="containsText" id="{451c76ad-4939-4f28-94f9-dd855b791fa7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15133,7 +15133,7 @@
           <xm:sqref>I210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="125" operator="containsText" id="{9055d412-4b5c-4912-b25e-5455ba94b03b}">
+          <x14:cfRule type="containsText" priority="125" operator="containsText" id="{b7592293-d1f9-4db2-9211-ba44fc28ddd4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15148,7 +15148,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="126" operator="containsText" id="{5c574cf1-8638-4567-8f4b-9010923a07a7}">
+          <x14:cfRule type="containsText" priority="126" operator="containsText" id="{d439a712-abff-4a26-9379-cbf8b509c70c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15166,7 +15166,7 @@
           <xm:sqref>G211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="495" operator="containsText" id="{5e3d1c88-3b9a-4876-8393-36f64ec5e175}">
+          <x14:cfRule type="containsText" priority="495" operator="containsText" id="{b3368051-d97a-446f-acce-a558971eb792}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15181,7 +15181,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="496" operator="containsText" id="{ecf76981-ff9f-488e-8a5d-885d4665399f}">
+          <x14:cfRule type="containsText" priority="496" operator="containsText" id="{fc63f834-5d9c-46d6-b3cc-eb0ed92e9d96}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15199,7 +15199,7 @@
           <xm:sqref>I211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="453" operator="containsText" id="{342fd05e-8e53-469b-a5b7-993ae176cec8}">
+          <x14:cfRule type="containsText" priority="453" operator="containsText" id="{1194383e-820c-4a7b-9138-fcb7e2c286a5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15214,7 +15214,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="454" operator="containsText" id="{4d53f335-0e88-4f89-91f7-e6b17f20635a}">
+          <x14:cfRule type="containsText" priority="454" operator="containsText" id="{ed3d943e-a97f-4303-8c0d-8b876042f127}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15232,7 +15232,7 @@
           <xm:sqref>I212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="447" operator="containsText" id="{6ef08daa-5646-415d-b59e-e9d80c7d4207}">
+          <x14:cfRule type="containsText" priority="447" operator="containsText" id="{bbfb1456-e092-48c1-9e68-67be624fab97}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15247,7 +15247,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="448" operator="containsText" id="{b1001647-5ce9-4686-85c6-a3c8c8f031a7}">
+          <x14:cfRule type="containsText" priority="448" operator="containsText" id="{99774656-27db-45e8-998f-1d9447482651}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15265,7 +15265,7 @@
           <xm:sqref>L212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="439" operator="containsText" id="{322c6696-a9c2-4252-8acf-73a52fa5ea9f}">
+          <x14:cfRule type="containsText" priority="439" operator="containsText" id="{b0fd5f9b-a798-4d9a-bad5-3530eab213a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I213)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15280,7 +15280,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="440" operator="containsText" id="{316cb8a9-c971-4476-870e-606ec8609607}">
+          <x14:cfRule type="containsText" priority="440" operator="containsText" id="{865bdc44-e71b-4a9d-bfe5-bd975c22f2f4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I213)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15298,7 +15298,7 @@
           <xm:sqref>I213</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="429" operator="containsText" id="{a92b5d18-2ac2-4527-9687-d36b12c1e53e}">
+          <x14:cfRule type="containsText" priority="429" operator="containsText" id="{813ae299-2202-4cba-b845-4aad72e22afc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L213)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15313,7 +15313,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="430" operator="containsText" id="{19270182-523b-46d3-bc9f-94be3b95e8eb}">
+          <x14:cfRule type="containsText" priority="430" operator="containsText" id="{29794974-9ca3-461b-8225-bfbb02c5f310}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L213)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15331,7 +15331,7 @@
           <xm:sqref>L213</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="455" operator="containsText" id="{d74bfda3-90d3-4761-8857-592e1ea10d79}">
+          <x14:cfRule type="containsText" priority="455" operator="containsText" id="{fc730b02-c874-45cc-9be8-6ce4fa9872ff}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I214)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15346,7 +15346,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="456" operator="containsText" id="{ada7bd54-7b24-4dc6-8774-94f529fcf0bb}">
+          <x14:cfRule type="containsText" priority="456" operator="containsText" id="{7b19a058-8bb4-46d9-86e9-58945f73d6ec}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I214)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15364,7 +15364,7 @@
           <xm:sqref>I214</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="445" operator="containsText" id="{a15a7e82-fa85-46b9-ae60-7ce6b45a0d73}">
+          <x14:cfRule type="containsText" priority="445" operator="containsText" id="{7bf0b094-7b65-4614-b3cb-2bedf16590ad}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I216)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15379,7 +15379,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="446" operator="containsText" id="{3e1c6db6-5c2c-4bc6-b4c9-0407a8fa17bb}">
+          <x14:cfRule type="containsText" priority="446" operator="containsText" id="{5bc4eb35-2cf1-41e7-b877-a55591aedc88}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I216)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15397,7 +15397,7 @@
           <xm:sqref>I216</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="419" operator="containsText" id="{32727733-b887-445f-bed2-73c7b92aab5e}">
+          <x14:cfRule type="containsText" priority="419" operator="containsText" id="{c492f300-c09e-4498-89f1-0439981c2a96}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15412,7 +15412,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="420" operator="containsText" id="{b3bb4ee2-e408-41ab-b508-cf87da67f88d}">
+          <x14:cfRule type="containsText" priority="420" operator="containsText" id="{55910382-6372-4402-994e-da6ce1b25605}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15430,7 +15430,7 @@
           <xm:sqref>I217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="187" operator="containsText" id="{0d3b0b91-2759-441a-9adf-36e3117e4615}">
+          <x14:cfRule type="containsText" priority="187" operator="containsText" id="{b79928ef-e775-441f-8e00-e4022a290369}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15445,7 +15445,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="188" operator="containsText" id="{c9994dbb-80f4-4741-b70b-a022512cc81e}">
+          <x14:cfRule type="containsText" priority="188" operator="containsText" id="{466342b7-0484-4d03-a502-bb28b969d89a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15463,7 +15463,7 @@
           <xm:sqref>K217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="421" operator="containsText" id="{b5cbd911-1a8f-4246-8128-bd1293ab3b48}">
+          <x14:cfRule type="containsText" priority="421" operator="containsText" id="{a59d1f1b-efed-4b68-a983-644c122c5e46}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L217)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15478,7 +15478,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="422" operator="containsText" id="{4222ba67-4eeb-4a71-8c2a-847de1c5b758}">
+          <x14:cfRule type="containsText" priority="422" operator="containsText" id="{775a2776-5542-4d1f-8c56-80c2d6a24160}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L217)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15496,7 +15496,7 @@
           <xm:sqref>L217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="437" operator="containsText" id="{02443ff4-cdb7-4d62-bb56-950c4cf10117}">
+          <x14:cfRule type="containsText" priority="437" operator="containsText" id="{b7edfca8-0c7e-4850-b52c-21a62492e96c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I218)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15511,7 +15511,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="438" operator="containsText" id="{b3cf0c21-8d90-4cad-a5df-c96283f2cb16}">
+          <x14:cfRule type="containsText" priority="438" operator="containsText" id="{0906f5d7-52bd-49d1-9a54-a05ec06f36c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I218)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15529,7 +15529,7 @@
           <xm:sqref>I218</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="373" operator="containsText" id="{a0840775-cd0e-44bd-b5ca-ad51175bc576}">
+          <x14:cfRule type="containsText" priority="373" operator="containsText" id="{fb619c86-e8ca-450b-9c1d-3ceff61ad8a4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I219)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15544,7 +15544,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="374" operator="containsText" id="{d7cc6cd0-447d-4488-bea2-6e45a6ba0d63}">
+          <x14:cfRule type="containsText" priority="374" operator="containsText" id="{06552812-7c46-416f-a710-50417f95bb45}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I219)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15562,7 +15562,7 @@
           <xm:sqref>I219</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="449" operator="containsText" id="{0a09f3d3-2ec0-475d-bb00-ba2083272902}">
+          <x14:cfRule type="containsText" priority="449" operator="containsText" id="{6f772356-1354-4147-b5de-9bf507e45545}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I221)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15577,7 +15577,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="450" operator="containsText" id="{9b46b73f-c28c-4a31-8dfc-83d74df92f10}">
+          <x14:cfRule type="containsText" priority="450" operator="containsText" id="{f895512f-2670-4241-8851-ce6428337092}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I221)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15595,7 +15595,7 @@
           <xm:sqref>I221</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="457" operator="containsText" id="{6a252371-09c6-49af-83ff-7224ce735c69}">
+          <x14:cfRule type="containsText" priority="457" operator="containsText" id="{7e27b69a-7556-4439-bfa9-57813eaaf6ff}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I222)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15610,7 +15610,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="458" operator="containsText" id="{3ad56b3e-2f92-465d-8b9a-4a7fbb8d8104}">
+          <x14:cfRule type="containsText" priority="458" operator="containsText" id="{e6d945a7-7614-41db-a68e-d4b10a449d93}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I222)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15628,7 +15628,7 @@
           <xm:sqref>I222</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="425" operator="containsText" id="{3e9ad81b-e0f4-4450-8d12-4a93e40ab523}">
+          <x14:cfRule type="containsText" priority="425" operator="containsText" id="{f894598f-a874-4a5b-9992-61937dc572e5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15643,7 +15643,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="426" operator="containsText" id="{ae10160c-5a1c-46e8-bffd-ca29ff857d01}">
+          <x14:cfRule type="containsText" priority="426" operator="containsText" id="{7afe395e-8383-4c56-ab52-e87149097d68}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15661,7 +15661,7 @@
           <xm:sqref>I223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="185" operator="containsText" id="{09c51489-9a24-41e3-a8a3-a5e2d4cdbdda}">
+          <x14:cfRule type="containsText" priority="185" operator="containsText" id="{d686e553-5ec4-4630-aca5-e98e6c7df5a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15676,7 +15676,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="186" operator="containsText" id="{a0a091ef-806e-4ac0-80cd-2d197e746b92}">
+          <x14:cfRule type="containsText" priority="186" operator="containsText" id="{bc8bcf23-e5e8-4b10-88c7-a87ab835e09d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15694,7 +15694,7 @@
           <xm:sqref>K223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="423" operator="containsText" id="{7d1b0d46-215d-4f0a-84d7-c4334378b794}">
+          <x14:cfRule type="containsText" priority="423" operator="containsText" id="{d289d4c5-ed71-4a1a-9a6b-b3737cc6ea65}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L223)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15709,7 +15709,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="424" operator="containsText" id="{1b84e5e1-5fec-4680-89b3-04691983efc4}">
+          <x14:cfRule type="containsText" priority="424" operator="containsText" id="{070f75dc-c3f3-4a58-83ff-c4f66502be00}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L223)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15727,7 +15727,7 @@
           <xm:sqref>L223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="115" operator="containsText" id="{9edf96bd-1f85-4bfb-90ee-92523ca3db12}">
+          <x14:cfRule type="containsText" priority="115" operator="containsText" id="{625b57b2-9ea5-4df8-a751-dc8e19bc3415}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15742,7 +15742,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="116" operator="containsText" id="{54f172fc-7d9a-43a4-b4f2-b2f8e094f339}">
+          <x14:cfRule type="containsText" priority="116" operator="containsText" id="{b16e60c2-a7b7-4429-9a8a-59c69ca2be17}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15760,7 +15760,7 @@
           <xm:sqref>G224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="451" operator="containsText" id="{ce52a766-ec74-4db0-ba9c-c81b12962345}">
+          <x14:cfRule type="containsText" priority="451" operator="containsText" id="{215a513f-f011-431b-8791-cf5c9a19e4fe}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15775,7 +15775,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="452" operator="containsText" id="{ea994c35-b909-4809-a8a9-93ad6d1902e0}">
+          <x14:cfRule type="containsText" priority="452" operator="containsText" id="{a505cb1f-75c4-451b-9d7a-f9429943c1e1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15793,7 +15793,7 @@
           <xm:sqref>I224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="119" operator="containsText" id="{741a0013-7235-40c7-b842-8967b4e6a74b}">
+          <x14:cfRule type="containsText" priority="119" operator="containsText" id="{6a6b6081-e681-4ea9-ad5d-476864c5b6cf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15808,7 +15808,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="120" operator="containsText" id="{afc6c2f1-63f1-40b8-bbc7-c5030ef35f75}">
+          <x14:cfRule type="containsText" priority="120" operator="containsText" id="{a6ffd844-441b-4bab-bd3e-38e969baa27d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15826,7 +15826,7 @@
           <xm:sqref>G225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="441" operator="containsText" id="{c2fc2abb-1c19-4b97-b5a4-fbbcf0140c6c}">
+          <x14:cfRule type="containsText" priority="441" operator="containsText" id="{09ec7f52-bb13-4e75-a9f5-1ce4a8f75d9c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15841,7 +15841,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="442" operator="containsText" id="{f12d1f36-2ca6-4070-a023-662468c8d10f}">
+          <x14:cfRule type="containsText" priority="442" operator="containsText" id="{0701fe0d-c121-49ec-a74c-58fc6d1767e1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15859,7 +15859,7 @@
           <xm:sqref>I225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="395" operator="containsText" id="{67f46371-5c4f-4d71-9f03-a98402f53531}">
+          <x14:cfRule type="containsText" priority="395" operator="containsText" id="{de1e2771-f8c9-407d-a0f9-7569fdeb5514}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15874,7 +15874,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="396" operator="containsText" id="{04ed9e8a-2faf-454d-8bbf-085d98318635}">
+          <x14:cfRule type="containsText" priority="396" operator="containsText" id="{27db4b59-108e-4271-98f1-0b715fef8036}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15892,7 +15892,7 @@
           <xm:sqref>L226</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="389" operator="containsText" id="{5355b66b-5de9-45ea-a91b-1f6ccfbc2c3d}">
+          <x14:cfRule type="containsText" priority="389" operator="containsText" id="{28ea630f-a696-4a33-ade8-77ea60599a72}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I227)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15907,7 +15907,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="390" operator="containsText" id="{0127f0a8-a361-450c-9b0c-4f662fca3082}">
+          <x14:cfRule type="containsText" priority="390" operator="containsText" id="{7527cfd4-bc6e-46e4-9e3b-34e5e5e9e749}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I227)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15925,7 +15925,7 @@
           <xm:sqref>I227</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="385" operator="containsText" id="{0ebefbdb-4fa0-444a-8b6f-73b2ba8ed63c}">
+          <x14:cfRule type="containsText" priority="385" operator="containsText" id="{d0b18786-f334-4a67-a8fb-d7e2cc86ee1d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L227)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15940,7 +15940,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="386" operator="containsText" id="{214601d3-f0b6-45f6-8fb9-f73d279996a3}">
+          <x14:cfRule type="containsText" priority="386" operator="containsText" id="{b9c8b417-e965-4e30-a48b-aab865230c17}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L227)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15958,7 +15958,7 @@
           <xm:sqref>L227</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="403" operator="containsText" id="{f255b9d9-9c07-4efa-ad1a-36a28c2b1cce}">
+          <x14:cfRule type="containsText" priority="403" operator="containsText" id="{078fdec3-5be9-432b-80a3-12cf253bb965}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I228)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -15973,7 +15973,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="404" operator="containsText" id="{57010cd6-9820-472a-b0f8-c4592b95da0c}">
+          <x14:cfRule type="containsText" priority="404" operator="containsText" id="{e5970374-4b0c-47d1-9542-cdbfb9368f1a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I228)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -15991,7 +15991,7 @@
           <xm:sqref>I228</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="367" operator="containsText" id="{0de76176-2d3f-4c8c-9d36-691500aa7b71}">
+          <x14:cfRule type="containsText" priority="367" operator="containsText" id="{38305c13-9772-420d-9b75-bdbd4ad023a9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I229)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16006,7 +16006,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="368" operator="containsText" id="{7ea20c5c-984f-4f19-b490-d5aab365f240}">
+          <x14:cfRule type="containsText" priority="368" operator="containsText" id="{9a8c2d80-7e32-42b0-be6b-6c847fc8cc5f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I229)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16024,7 +16024,7 @@
           <xm:sqref>I229</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="393" operator="containsText" id="{a55dc327-9408-4a6a-b062-a11b4773b20d}">
+          <x14:cfRule type="containsText" priority="393" operator="containsText" id="{393b8d3a-d074-43d9-a818-22a27612c7f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I230)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16039,7 +16039,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="394" operator="containsText" id="{741f13be-7fc2-4630-b9b7-20c844ef6587}">
+          <x14:cfRule type="containsText" priority="394" operator="containsText" id="{81d1bd1c-f714-4e2c-905d-39b8c243a188}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I230)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16057,7 +16057,7 @@
           <xm:sqref>I230</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="375" operator="containsText" id="{c3e41b6c-40d3-40be-a38b-e46a740f66fb}">
+          <x14:cfRule type="containsText" priority="375" operator="containsText" id="{e85d494b-2ccf-4385-8313-49c62cc0a6d7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16072,7 +16072,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="376" operator="containsText" id="{7b07cff6-2442-40d9-9f5b-1833d6ab6973}">
+          <x14:cfRule type="containsText" priority="376" operator="containsText" id="{4e8e8002-6ad5-47c5-9c86-b790ced97dcb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16090,7 +16090,7 @@
           <xm:sqref>I231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="183" operator="containsText" id="{6a4790ae-7fe0-4a74-8053-ae2c35319f8e}">
+          <x14:cfRule type="containsText" priority="183" operator="containsText" id="{63f33406-a9a7-4160-8e05-bfd95829e2f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16105,7 +16105,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="184" operator="containsText" id="{62a2688b-3b45-4f0e-8b50-d7704927c52b}">
+          <x14:cfRule type="containsText" priority="184" operator="containsText" id="{73011e24-2c4a-4099-8bd5-956934ce382d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16123,7 +16123,7 @@
           <xm:sqref>K231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="365" operator="containsText" id="{78e32408-668f-40d8-98c6-64d481b96190}">
+          <x14:cfRule type="containsText" priority="365" operator="containsText" id="{8c9f476e-e146-4d7c-864b-fd059cfebe3b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L231)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16138,7 +16138,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="366" operator="containsText" id="{fa8a355a-c972-4d2b-931c-490a1d4d6aaf}">
+          <x14:cfRule type="containsText" priority="366" operator="containsText" id="{fd74ffa4-3c73-479c-9464-99f079620aaa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L231)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16156,7 +16156,7 @@
           <xm:sqref>L231</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="387" operator="containsText" id="{8a1d93ed-eb0f-40ad-8cda-6db4e08b803e}">
+          <x14:cfRule type="containsText" priority="387" operator="containsText" id="{5d9bc351-3d47-4445-aed5-c864fb0f5801}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I232)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16171,7 +16171,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="388" operator="containsText" id="{b32768b5-78c6-4d0e-95c8-448f468cc773}">
+          <x14:cfRule type="containsText" priority="388" operator="containsText" id="{2141c39a-4402-40cb-9906-fa92d6ddd73a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I232)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16189,7 +16189,7 @@
           <xm:sqref>I232</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="363" operator="containsText" id="{c4b7bc3a-1696-49cd-bfe0-ae5a75280af7}">
+          <x14:cfRule type="containsText" priority="363" operator="containsText" id="{11d39987-843d-4ac0-b0cc-2f59bfac9de4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I233)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16204,7 +16204,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="364" operator="containsText" id="{f24b6e20-f55f-45b9-8085-13fe8fe79ff0}">
+          <x14:cfRule type="containsText" priority="364" operator="containsText" id="{0ad9b452-89b0-4db6-91ad-93c735bdba57}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I233)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16222,7 +16222,7 @@
           <xm:sqref>I233</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="397" operator="containsText" id="{e99331d7-a78c-416d-b953-3c636f043244}">
+          <x14:cfRule type="containsText" priority="397" operator="containsText" id="{29de49b7-39df-4a52-9fe6-f2f09b6b08ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I235)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16237,7 +16237,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="398" operator="containsText" id="{d4a3a6a5-cf67-4033-a2b0-5a8351ab5b63}">
+          <x14:cfRule type="containsText" priority="398" operator="containsText" id="{7c2b89ad-7821-4960-9bcb-c4d214ecf917}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I235)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16255,7 +16255,7 @@
           <xm:sqref>I235</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="405" operator="containsText" id="{4a017250-a589-4fbe-99cb-0c36ed464292}">
+          <x14:cfRule type="containsText" priority="405" operator="containsText" id="{1317882e-654b-42cd-bb5e-af7c1c0f19f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I236)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16270,7 +16270,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="406" operator="containsText" id="{90dd0610-b617-4244-a66e-8849c28988aa}">
+          <x14:cfRule type="containsText" priority="406" operator="containsText" id="{a73ee5a9-cbfd-403f-a35b-4de5fbbec31a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I236)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16288,7 +16288,7 @@
           <xm:sqref>I236</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="371" operator="containsText" id="{75b29738-57fb-4e6c-9f1a-3f01c6776aea}">
+          <x14:cfRule type="containsText" priority="371" operator="containsText" id="{a3afabb4-40e2-4946-a3d3-4f1e0144cd10}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16303,7 +16303,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="372" operator="containsText" id="{5061fabf-2cd0-425d-8e02-89547d50bf49}">
+          <x14:cfRule type="containsText" priority="372" operator="containsText" id="{2d5f1e66-9ffa-487b-bdba-04e56238daf9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16321,7 +16321,7 @@
           <xm:sqref>I237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="181" operator="containsText" id="{a390f8d0-ed16-49aa-b110-da2e9604593c}">
+          <x14:cfRule type="containsText" priority="181" operator="containsText" id="{9a6c6e1b-2613-47d0-a8e5-71e1afeadd0a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16336,7 +16336,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="182" operator="containsText" id="{110fecfd-7c5c-469e-bf93-fb3f830bbaeb}">
+          <x14:cfRule type="containsText" priority="182" operator="containsText" id="{ffc3b7ef-9360-41ab-a54b-ae5047e9f744}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16354,7 +16354,7 @@
           <xm:sqref>K237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="369" operator="containsText" id="{524f00f4-88d9-49ff-aa3f-52cf482ef748}">
+          <x14:cfRule type="containsText" priority="369" operator="containsText" id="{4b96f706-8f49-419e-9b26-1712a26dafac}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L237)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16369,7 +16369,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="370" operator="containsText" id="{044aea91-c325-4b8a-b85e-57b83213176c}">
+          <x14:cfRule type="containsText" priority="370" operator="containsText" id="{3dd71922-725f-4c29-8bfd-dfba016f10d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L237)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16387,7 +16387,7 @@
           <xm:sqref>L237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{a6c1ec6a-8ecf-4983-87a1-f8ba1e804906}">
+          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{b00f8d8c-b227-4318-a8ca-57690fc5b1e1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16402,7 +16402,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{8dcd1f5b-c41d-4577-bd33-7d73f5638dea}">
+          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{68144af8-398d-406b-a62d-6ba1e6c16797}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16420,7 +16420,7 @@
           <xm:sqref>G238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="361" operator="containsText" id="{845f0550-b58a-4c5c-ae62-7b66ae5762fb}">
+          <x14:cfRule type="containsText" priority="361" operator="containsText" id="{149eae4a-1960-4f59-a2d3-8576ed7e4760}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16435,7 +16435,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="362" operator="containsText" id="{05b62bab-b7cd-49a5-8434-e04cce444aef}">
+          <x14:cfRule type="containsText" priority="362" operator="containsText" id="{29dd5e8f-e749-400a-a80c-2f234ec84774}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16453,7 +16453,7 @@
           <xm:sqref>I238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="113" operator="containsText" id="{3bc87748-6ed0-47ad-86f8-36dfc8a69b14}">
+          <x14:cfRule type="containsText" priority="113" operator="containsText" id="{a75df7f2-66c7-4b78-84f5-043920910892}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16468,7 +16468,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="114" operator="containsText" id="{6a80f14d-7b3c-4de2-91a9-fb87d0635b5a}">
+          <x14:cfRule type="containsText" priority="114" operator="containsText" id="{30f71dbd-16e6-4b54-9975-404f28eb71b8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16486,7 +16486,7 @@
           <xm:sqref>G239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="391" operator="containsText" id="{946ef5fa-bb2e-4e15-9ad9-0dabed2f8851}">
+          <x14:cfRule type="containsText" priority="391" operator="containsText" id="{3f7e33ab-830a-4387-af00-b2891eb88ee6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16501,7 +16501,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="392" operator="containsText" id="{0ffe183e-7d59-45a2-9a6f-b4f44e347be0}">
+          <x14:cfRule type="containsText" priority="392" operator="containsText" id="{40e1f93b-e3a7-4de8-9c9f-c2d588f45c7d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16519,7 +16519,7 @@
           <xm:sqref>I239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="311" operator="containsText" id="{d878e98d-6c93-457b-abc4-f87f19c490a7}">
+          <x14:cfRule type="containsText" priority="311" operator="containsText" id="{29ff843d-1653-4edd-b732-c685c73e3cb9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16534,7 +16534,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="312" operator="containsText" id="{d287b3bf-a4e4-4fbc-9a7c-6bcc672fec71}">
+          <x14:cfRule type="containsText" priority="312" operator="containsText" id="{01d7d6c9-9b56-45c2-b9c4-c992b98efdd4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16552,7 +16552,7 @@
           <xm:sqref>I240</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="341" operator="containsText" id="{ec6d0fb2-0cfb-443e-b131-fe057b266a30}">
+          <x14:cfRule type="containsText" priority="341" operator="containsText" id="{a6abec2e-7fb4-4b9c-b3c5-4636761d343d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16567,7 +16567,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="342" operator="containsText" id="{67f5c876-a726-42ba-a158-01057bbe1a2a}">
+          <x14:cfRule type="containsText" priority="342" operator="containsText" id="{13a5301e-a6ea-4ed7-87af-8992f43167d8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16585,7 +16585,7 @@
           <xm:sqref>L240</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="335" operator="containsText" id="{93faae9c-e5fd-4c0f-96a9-b45ed7f31b45}">
+          <x14:cfRule type="containsText" priority="335" operator="containsText" id="{d59afae2-f27c-4872-be42-ff7ac54ae8c5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16600,7 +16600,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="336" operator="containsText" id="{97918213-eef8-44ef-918c-e0d11a6b0567}">
+          <x14:cfRule type="containsText" priority="336" operator="containsText" id="{b0d0d7ee-5bf2-461e-857c-3e22c1314ab7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16618,7 +16618,7 @@
           <xm:sqref>I241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="179" operator="containsText" id="{879ea46c-03a5-45e3-9142-68d297e6065e}">
+          <x14:cfRule type="containsText" priority="179" operator="containsText" id="{1578ec06-de44-4145-89f9-61535e1ad88c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16633,7 +16633,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="180" operator="containsText" id="{d60aeae9-d5d1-4407-9d89-960348f1716c}">
+          <x14:cfRule type="containsText" priority="180" operator="containsText" id="{611cc526-2476-4c3f-a887-8dc9f2aef3d9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16651,7 +16651,7 @@
           <xm:sqref>K241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="309" operator="containsText" id="{47637354-0110-419a-b41f-1047c0187f9e}">
+          <x14:cfRule type="containsText" priority="309" operator="containsText" id="{0bea2a75-afaf-49c5-bc09-8f9f515285c6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L241)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16666,7 +16666,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="310" operator="containsText" id="{4e0c7d9d-10d5-4445-8518-6a2281270f0a}">
+          <x14:cfRule type="containsText" priority="310" operator="containsText" id="{1897fc82-e8cd-4d05-8ef2-a19e4e523b25}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L241)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16684,7 +16684,7 @@
           <xm:sqref>L241</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="305" operator="containsText" id="{e2b49e49-dad7-4031-8dc3-7fefd205314e}">
+          <x14:cfRule type="containsText" priority="305" operator="containsText" id="{98a58fa0-23ae-4992-916a-3cf261aa96e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I242)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16699,7 +16699,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="306" operator="containsText" id="{7324bc5f-de5a-4907-a48d-d76b4c8e0bfd}">
+          <x14:cfRule type="containsText" priority="306" operator="containsText" id="{d05a3166-a998-44b3-9eb3-190026224c3c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I242)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16717,7 +16717,7 @@
           <xm:sqref>I242</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="323" operator="containsText" id="{25eac937-96a8-487d-b9a0-85ac678939b2}">
+          <x14:cfRule type="containsText" priority="323" operator="containsText" id="{9c14fe4d-e991-4fb7-a0d3-d75689d480c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I243)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16732,7 +16732,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="324" operator="containsText" id="{ddabc77b-894c-4467-817e-6e91c0d0a34d}">
+          <x14:cfRule type="containsText" priority="324" operator="containsText" id="{19558745-eded-44a4-b0e6-cd1e53a181b9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I243)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16750,7 +16750,7 @@
           <xm:sqref>I243</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="339" operator="containsText" id="{0f320392-b056-4d8d-a4cf-deae490a6cf6}">
+          <x14:cfRule type="containsText" priority="339" operator="containsText" id="{260b841d-7504-470d-8a14-9a8cec7eba4f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I244)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16765,7 +16765,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="340" operator="containsText" id="{f983004f-f38a-4e87-b99c-ef5c208524d9}">
+          <x14:cfRule type="containsText" priority="340" operator="containsText" id="{c53f2444-1471-42ff-a4f1-212c6bceb5ee}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I244)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16783,7 +16783,7 @@
           <xm:sqref>I244</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="329" operator="containsText" id="{25d95939-c95c-4366-a991-8fdf5146d085}">
+          <x14:cfRule type="containsText" priority="329" operator="containsText" id="{ea741674-628a-47a2-89b6-0aca489e0aa8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I245)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16798,7 +16798,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="330" operator="containsText" id="{c6dd0946-8266-474e-94e5-339b9c311268}">
+          <x14:cfRule type="containsText" priority="330" operator="containsText" id="{74a2a029-daa3-4108-bc10-8f16f4ce4d8d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I245)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16816,7 +16816,7 @@
           <xm:sqref>I245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="321" operator="containsText" id="{d4b02767-bd13-4c52-9db3-4bd31fa6bb82}">
+          <x14:cfRule type="containsText" priority="321" operator="containsText" id="{78a3ad8c-ed51-438f-ad23-3a8997a902d8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L245)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16831,7 +16831,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="322" operator="containsText" id="{27a10059-c40e-452d-8054-3fe5a7d1597a}">
+          <x14:cfRule type="containsText" priority="322" operator="containsText" id="{b3e6f129-dc67-469c-a544-175fc2907c8f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L245)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16849,7 +16849,7 @@
           <xm:sqref>L245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="333" operator="containsText" id="{cb9c9d59-d60f-4fc7-bc26-5def0bacc965}">
+          <x14:cfRule type="containsText" priority="333" operator="containsText" id="{af0b1792-7184-4616-bd0e-1cfc738ae2c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I246)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16864,7 +16864,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="334" operator="containsText" id="{8ef6e34c-4f9b-4769-be46-ceef9f3a7165}">
+          <x14:cfRule type="containsText" priority="334" operator="containsText" id="{1983dbb7-13a1-4a56-9882-d4d3c0737d6d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I246)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16882,7 +16882,7 @@
           <xm:sqref>I246</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="307" operator="containsText" id="{3ac52106-e619-4e6b-931c-c0af81ee68c7}">
+          <x14:cfRule type="containsText" priority="307" operator="containsText" id="{aab8b5d8-8d9d-4b35-b1bd-54899d677f4c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I247)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16897,7 +16897,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="308" operator="containsText" id="{80292fbe-3ebe-4ac5-90c7-8de04baa686c}">
+          <x14:cfRule type="containsText" priority="308" operator="containsText" id="{cc88cfd7-bd97-4788-a2f7-f2e9b7ec7067}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I247)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16915,7 +16915,7 @@
           <xm:sqref>I247</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="343" operator="containsText" id="{42bffc50-f959-4b47-aa73-1d0fb8515398}">
+          <x14:cfRule type="containsText" priority="343" operator="containsText" id="{4b3cec74-a4bd-4dd6-b4b4-8b6a94d9cb55}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I249)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16930,7 +16930,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="344" operator="containsText" id="{92b3df69-cfe5-4eca-8c1e-2a4cbddaeda3}">
+          <x14:cfRule type="containsText" priority="344" operator="containsText" id="{eefea656-af9e-4f59-8ba1-03d8d90df754}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I249)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16948,7 +16948,7 @@
           <xm:sqref>I249</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="303" operator="containsText" id="{8cda39fc-8abc-491f-85e0-ef5364e55962}">
+          <x14:cfRule type="containsText" priority="303" operator="containsText" id="{f756ed6e-a6c0-45f1-98e3-1a70eb58b19e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I250)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16963,7 +16963,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="304" operator="containsText" id="{f0d41ce4-4014-4b85-9c86-4cf8a59a0ee8}">
+          <x14:cfRule type="containsText" priority="304" operator="containsText" id="{8af6c515-6818-4ab1-a288-53909f1f3e81}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I250)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -16981,7 +16981,7 @@
           <xm:sqref>I250</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="315" operator="containsText" id="{fcd6c067-2a8d-40be-9b4a-684ea8e04efd}">
+          <x14:cfRule type="containsText" priority="315" operator="containsText" id="{e58cee34-2c2f-43c5-9467-96bf1df073eb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -16996,7 +16996,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="316" operator="containsText" id="{62b90f1c-6358-4513-a1cc-6b1f28a84ac0}">
+          <x14:cfRule type="containsText" priority="316" operator="containsText" id="{3af83618-051a-4fdf-b419-296358106ce1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17014,7 +17014,7 @@
           <xm:sqref>I251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="177" operator="containsText" id="{06c181ce-ab74-4ff2-b260-328f96328db6}">
+          <x14:cfRule type="containsText" priority="177" operator="containsText" id="{b1c7fc59-0e5a-4b1f-b8f0-f8e88cc663c1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17029,7 +17029,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="178" operator="containsText" id="{34878dde-57d2-4168-a9ac-976e6c027bc1}">
+          <x14:cfRule type="containsText" priority="178" operator="containsText" id="{c70fafc9-a896-4406-bee4-31bc233b3b9e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17047,7 +17047,7 @@
           <xm:sqref>K251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="313" operator="containsText" id="{bc169476-81d8-413d-9127-7f4fe760cd10}">
+          <x14:cfRule type="containsText" priority="313" operator="containsText" id="{be7976fe-b9b6-4f7b-9701-f0ae3cdba4de}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L251)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17062,7 +17062,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="314" operator="containsText" id="{815fa8b9-36fb-4edd-9dc0-1124e7480e0d}">
+          <x14:cfRule type="containsText" priority="314" operator="containsText" id="{4448846a-0fc6-4f5b-8ac1-406f0ec54c0e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L251)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17080,7 +17080,7 @@
           <xm:sqref>L251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="103" operator="containsText" id="{174a6dc8-65c3-4e42-9a1f-073994fbef9c}">
+          <x14:cfRule type="containsText" priority="103" operator="containsText" id="{e2fb62c7-2c56-4c83-afee-37529abc5a25}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17095,7 +17095,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="104" operator="containsText" id="{c4ec1aa0-51f0-42f1-ae2a-be3d53bc77f0}">
+          <x14:cfRule type="containsText" priority="104" operator="containsText" id="{a3a97255-929d-4bed-8f85-cc9c62597d9e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17113,7 +17113,7 @@
           <xm:sqref>G252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="211" operator="containsText" id="{06afff89-7f24-4191-81a2-66011e506b67}">
+          <x14:cfRule type="containsText" priority="211" operator="containsText" id="{e8e78617-5ae5-45e9-a1ba-75d5f1f5bd59}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17128,7 +17128,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="212" operator="containsText" id="{d632f8a4-4b7d-4446-8965-a7ac6714b025}">
+          <x14:cfRule type="containsText" priority="212" operator="containsText" id="{c785abc4-08ce-4dba-bcdf-44d8e15aa084}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17146,7 +17146,7 @@
           <xm:sqref>I252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="107" operator="containsText" id="{be061586-a85d-4987-9575-33356e375bd9}">
+          <x14:cfRule type="containsText" priority="107" operator="containsText" id="{49d38b90-6d5e-4b25-b62e-421ad7b23381}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17161,7 +17161,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{5070072a-2bdf-4c43-bf7b-b65297f36d77}">
+          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{60c4c369-830c-4364-bc4b-1374cc77187a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17179,7 +17179,7 @@
           <xm:sqref>G253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="337" operator="containsText" id="{4c1a76dd-a39d-49c8-a5c1-67312db59985}">
+          <x14:cfRule type="containsText" priority="337" operator="containsText" id="{c1c78714-3779-4c58-a91d-c4f296d1e32a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17194,7 +17194,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="338" operator="containsText" id="{9165838b-a7e9-46da-8d63-0756557ab6a3}">
+          <x14:cfRule type="containsText" priority="338" operator="containsText" id="{3718399a-2e8c-4753-9645-a339037ad83e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17212,7 +17212,7 @@
           <xm:sqref>I253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="203" operator="containsText" id="{0521ef64-6842-4e2b-ad42-6954e19ca75d}">
+          <x14:cfRule type="containsText" priority="203" operator="containsText" id="{9ffc1e5e-485c-41af-b991-9ca62cbf4528}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17227,7 +17227,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="204" operator="containsText" id="{7cea0b57-da61-4a58-8273-fe670af5e383}">
+          <x14:cfRule type="containsText" priority="204" operator="containsText" id="{bb8a7a8c-6818-45ff-a5b8-ae923910fda5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17245,7 +17245,7 @@
           <xm:sqref>I254</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="283" operator="containsText" id="{c4709827-e280-46d4-8294-ca2f11e26208}">
+          <x14:cfRule type="containsText" priority="283" operator="containsText" id="{8619bb07-ca8e-49e1-8cfb-2d6fd45a1a3f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17260,7 +17260,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="284" operator="containsText" id="{8bf86a23-d53a-4c66-bd6f-98363b586127}">
+          <x14:cfRule type="containsText" priority="284" operator="containsText" id="{6975b0a7-cc97-4cd6-b29f-4082b46ca56b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17278,7 +17278,7 @@
           <xm:sqref>L254</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="277" operator="containsText" id="{fd0b3f7b-9ee6-4bd7-9673-f05890112f9e}">
+          <x14:cfRule type="containsText" priority="277" operator="containsText" id="{0284bf6b-a528-47ea-bdd7-83d040f1fa8b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17293,7 +17293,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="278" operator="containsText" id="{6dba8172-8281-4e5a-8b50-614ffc08be05}">
+          <x14:cfRule type="containsText" priority="278" operator="containsText" id="{359b5ab7-aae1-46d9-83fc-dab7cfd07d0b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17311,7 +17311,7 @@
           <xm:sqref>I255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="175" operator="containsText" id="{accaaea4-bc77-429e-9688-6840e06e17c2}">
+          <x14:cfRule type="containsText" priority="175" operator="containsText" id="{028c2b28-323f-423a-a74f-709049f0413f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17326,7 +17326,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="176" operator="containsText" id="{c398fdfb-7bf0-4314-8a56-4a44d9607145}">
+          <x14:cfRule type="containsText" priority="176" operator="containsText" id="{ca04c9b5-3676-44d5-aa80-1b44ef5cbe1a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17344,7 +17344,7 @@
           <xm:sqref>K255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="201" operator="containsText" id="{a866c8fd-2194-495d-ae70-26e459ac4849}">
+          <x14:cfRule type="containsText" priority="201" operator="containsText" id="{163e229f-9f3c-4b1b-be26-91d44eea54c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L255)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17359,7 +17359,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="202" operator="containsText" id="{2f13eee5-e4ed-425f-8a85-4a1a8cbefb65}">
+          <x14:cfRule type="containsText" priority="202" operator="containsText" id="{555718a5-ff37-48e0-9d19-7a036ce38a6e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L255)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17377,7 +17377,7 @@
           <xm:sqref>L255</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="287" operator="containsText" id="{2e9b1b6b-1cd0-4e10-b264-431778cfc6e0}">
+          <x14:cfRule type="containsText" priority="287" operator="containsText" id="{eb862f54-6c04-40bb-97b5-e24ba5865c4c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I256)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17392,7 +17392,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="288" operator="containsText" id="{85a20ff2-d686-41ef-a011-aba9d9bb4de3}">
+          <x14:cfRule type="containsText" priority="288" operator="containsText" id="{5ae104b6-0e56-46d0-b251-049fffd40993}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I256)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17410,7 +17410,7 @@
           <xm:sqref>I256</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="265" operator="containsText" id="{a20b5415-1f92-47aa-81ff-d27233522cd4}">
+          <x14:cfRule type="containsText" priority="265" operator="containsText" id="{334a39b4-15a3-4c96-aa0a-3d73d72af418}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I257)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17425,7 +17425,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="266" operator="containsText" id="{6bcbf0c2-4595-4060-831f-95f01611da0b}">
+          <x14:cfRule type="containsText" priority="266" operator="containsText" id="{a6a4921b-6dd8-4154-9d62-67c51d591596}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I257)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17443,7 +17443,7 @@
           <xm:sqref>I257</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="281" operator="containsText" id="{68272c03-66c2-418f-aceb-3263db0e2634}">
+          <x14:cfRule type="containsText" priority="281" operator="containsText" id="{030919f3-3632-4988-b7f5-0d63c6e25f6a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I258)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17458,7 +17458,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="282" operator="containsText" id="{304aca95-74c3-4c6c-b0b2-686fb1b7c886}">
+          <x14:cfRule type="containsText" priority="282" operator="containsText" id="{50342859-b566-4d89-8058-e1383c2020a2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I258)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17476,7 +17476,7 @@
           <xm:sqref>I258</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="271" operator="containsText" id="{aa45bdba-5e2d-4bf3-bb1c-5d6a50a2163f}">
+          <x14:cfRule type="containsText" priority="271" operator="containsText" id="{b4ac1723-866a-4e01-9f3e-514a685b8edc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I259)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17491,7 +17491,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="272" operator="containsText" id="{e4af479f-bd70-4b08-91bc-f6a516d2412f}">
+          <x14:cfRule type="containsText" priority="272" operator="containsText" id="{4af59886-f9dc-4bd0-b007-7f98e04a7ef7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I259)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17509,7 +17509,7 @@
           <xm:sqref>I259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="263" operator="containsText" id="{7a3d9d08-7202-4148-b078-decea23ca4a6}">
+          <x14:cfRule type="containsText" priority="263" operator="containsText" id="{2e1d505b-d95b-4df3-b1b9-2d41c042fa5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L259)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17524,7 +17524,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="264" operator="containsText" id="{33692436-ca8a-45af-98df-2601b0afa2bb}">
+          <x14:cfRule type="containsText" priority="264" operator="containsText" id="{2684b4d5-f3c1-4203-a893-8a2e22f4fed2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L259)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17542,7 +17542,7 @@
           <xm:sqref>L259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="275" operator="containsText" id="{ecb48943-ac01-437b-a4b4-fff390874a79}">
+          <x14:cfRule type="containsText" priority="275" operator="containsText" id="{e9806e96-8948-4c27-bc9d-eee9fbb603ec}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I260)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17557,7 +17557,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="276" operator="containsText" id="{f6e60aa8-a6f3-4289-a792-1c3644087176}">
+          <x14:cfRule type="containsText" priority="276" operator="containsText" id="{ce364436-cfab-4c2a-b299-278ce80a5081}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I260)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17575,7 +17575,7 @@
           <xm:sqref>I260</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="261" operator="containsText" id="{bea838c5-70ff-414c-ab5a-64d57878bee7}">
+          <x14:cfRule type="containsText" priority="261" operator="containsText" id="{60319bf7-7de4-49f5-97ee-17bb29611e8b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I261)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17590,7 +17590,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="262" operator="containsText" id="{b1bee444-5843-4f85-828e-a5e99e7a857f}">
+          <x14:cfRule type="containsText" priority="262" operator="containsText" id="{5d5b0fb5-451a-468a-aa77-a2b6844f45cd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I261)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17608,7 +17608,7 @@
           <xm:sqref>I261</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="199" operator="containsText" id="{382da7fc-f7be-41c5-a565-3426e718f3d6}">
+          <x14:cfRule type="containsText" priority="199" operator="containsText" id="{a21fa0f1-1042-4c77-a538-ddcd325294b9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I263)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17623,7 +17623,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="200" operator="containsText" id="{28e24f35-da40-488b-a03d-c5aab248d14b}">
+          <x14:cfRule type="containsText" priority="200" operator="containsText" id="{65d1454a-768e-4296-a864-ca1d41c05473}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I263)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17641,7 +17641,7 @@
           <xm:sqref>I263</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="289" operator="containsText" id="{e2b8236c-63ed-484e-9b4f-c509bc35be24}">
+          <x14:cfRule type="containsText" priority="289" operator="containsText" id="{52187351-c407-4366-81c6-45a66429a1ca}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17656,7 +17656,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="290" operator="containsText" id="{a4e29131-34d9-46f4-ae51-6557d1500a86}">
+          <x14:cfRule type="containsText" priority="290" operator="containsText" id="{b6439f71-b706-47d4-97e1-085d95a69537}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17674,7 +17674,7 @@
           <xm:sqref>I264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="173" operator="containsText" id="{e93118d6-4f13-4e0a-b393-0f66cbc1bad0}">
+          <x14:cfRule type="containsText" priority="173" operator="containsText" id="{e73ac6fd-b339-4dbf-af9c-32e8cce53af6}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17689,7 +17689,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="174" operator="containsText" id="{589fed5e-7f9d-497b-9e93-0a80d94b9226}">
+          <x14:cfRule type="containsText" priority="174" operator="containsText" id="{1c087a32-4eeb-425d-9ea0-2ad5eb11a6a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17707,7 +17707,7 @@
           <xm:sqref>K264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="205" operator="containsText" id="{ff69bee0-7da8-4fda-bd61-c2c8858751ea}">
+          <x14:cfRule type="containsText" priority="205" operator="containsText" id="{87287ad2-2cd8-47a3-afd8-39f1e40292af}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L264)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17722,7 +17722,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="206" operator="containsText" id="{f0668e30-dd4f-4d24-a1c4-5e66dfb26b75}">
+          <x14:cfRule type="containsText" priority="206" operator="containsText" id="{4104ca6f-ef40-465d-8983-49ff5308331a}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L264)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17740,7 +17740,7 @@
           <xm:sqref>L264</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="209" operator="containsText" id="{e0db1969-614e-457f-ab65-cdbd62779c23}">
+          <x14:cfRule type="containsText" priority="209" operator="containsText" id="{3f215627-db74-4ec3-be73-a308649a3bd3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17755,7 +17755,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="210" operator="containsText" id="{71fa146f-60e0-49ca-ba05-2e527be37290}">
+          <x14:cfRule type="containsText" priority="210" operator="containsText" id="{545c696d-bd5f-4c44-9390-a105d4b29a2e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17773,7 +17773,7 @@
           <xm:sqref>I265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="171" operator="containsText" id="{7d670334-89bb-4634-8bab-eadf1755bfa5}">
+          <x14:cfRule type="containsText" priority="171" operator="containsText" id="{61f14e2a-b53a-4342-9aa5-b6da0c4782b2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17788,7 +17788,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="172" operator="containsText" id="{f2797330-2bb5-466e-a860-ca894d10989e}">
+          <x14:cfRule type="containsText" priority="172" operator="containsText" id="{b811b01c-07a8-485f-9101-29b724d75f63}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17806,7 +17806,7 @@
           <xm:sqref>K265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="207" operator="containsText" id="{ddc4c8c5-1659-49ec-9e41-0bfabb1f3308}">
+          <x14:cfRule type="containsText" priority="207" operator="containsText" id="{0a23c316-9e83-4369-be27-54ac5b3f7a79}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,L265)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17821,7 +17821,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="208" operator="containsText" id="{8e50916e-7116-4884-8c1a-0fae478bb4f3}">
+          <x14:cfRule type="containsText" priority="208" operator="containsText" id="{fb8859f0-8fc3-42f2-ab0c-7474aee2c710}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,L265)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17839,7 +17839,7 @@
           <xm:sqref>L265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="97" operator="containsText" id="{542ec13c-24a8-493a-a468-157d2d518155}">
+          <x14:cfRule type="containsText" priority="97" operator="containsText" id="{718e2895-89e2-4396-a796-b74949f07d8d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17854,7 +17854,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="98" operator="containsText" id="{f36b013e-dec5-4b3b-8b96-123690914cbd}">
+          <x14:cfRule type="containsText" priority="98" operator="containsText" id="{5225f1fb-4b2c-47f8-8f44-2033d33cf4a9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17872,7 +17872,7 @@
           <xm:sqref>G266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="259" operator="containsText" id="{08f593b4-907a-4a43-b990-f3b7b857b2bd}">
+          <x14:cfRule type="containsText" priority="259" operator="containsText" id="{b7411305-8f99-463c-ad61-072b307f5a33}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17887,7 +17887,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="260" operator="containsText" id="{1a3e6696-49f7-4075-826b-1bdc7b7bfc64}">
+          <x14:cfRule type="containsText" priority="260" operator="containsText" id="{ea1d763c-0cc4-4b1e-a73d-513f2f6bb8fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17905,7 +17905,7 @@
           <xm:sqref>I266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="101" operator="containsText" id="{6f536437-c19e-4c16-ab4e-39bcb042a377}">
+          <x14:cfRule type="containsText" priority="101" operator="containsText" id="{a64d6321-2520-49a4-b003-0ba6efafba3f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17920,7 +17920,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="102" operator="containsText" id="{7b05600b-9ebc-4f03-8187-be830c02b30c}">
+          <x14:cfRule type="containsText" priority="102" operator="containsText" id="{279805f2-253c-4143-bf5b-ea0169d2f1c3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17938,7 +17938,7 @@
           <xm:sqref>G267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="279" operator="containsText" id="{4d050d65-ac0e-432f-8560-f3b6701933b7}">
+          <x14:cfRule type="containsText" priority="279" operator="containsText" id="{f8ce71f1-3b1a-4c55-810d-5f4d7e8682e8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,I267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -17953,7 +17953,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="280" operator="containsText" id="{b6e8dfdc-cee4-4ecd-9bd2-71e90bdd9d1f}">
+          <x14:cfRule type="containsText" priority="280" operator="containsText" id="{c392df3a-06d7-466d-9aa8-7d6e2b6a6d9c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,I267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17971,7 +17971,7 @@
           <xm:sqref>I267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{7ec6a4de-f3c5-4860-8f1e-b1b00865c975}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{c62429ff-0f68-4f7e-9d49-1d2d623fe037}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G268)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -17986,7 +17986,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{f7c0e50a-3ac2-4959-9974-8aef476509c5}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{42a2c91d-39bc-4eca-adfc-124fcdda8e88}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G268)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18004,7 +18004,7 @@
           <xm:sqref>G268</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="55" operator="containsText" id="{12a3fae9-208e-4264-be45-f42fa995c8e7}">
+          <x14:cfRule type="containsText" priority="55" operator="containsText" id="{f6f7224c-489e-41f2-beb1-08c9a6dc2201}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18019,7 +18019,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="56" operator="containsText" id="{a96f752d-3829-41e4-9de3-34b22ac69484}">
+          <x14:cfRule type="containsText" priority="56" operator="containsText" id="{0619a51d-87a3-47ea-a308-46c346773103}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18037,7 +18037,7 @@
           <xm:sqref>F269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{c0ce0155-55f2-4921-8d93-1cc9cf355104}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{98dd0c45-9498-491e-af62-ee8bfdf7030b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18052,7 +18052,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{cf4843b2-83a3-48a3-8b38-2cd4cbce205a}">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{856106e7-5fce-4e85-9b8b-815eacd903ee}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18070,7 +18070,7 @@
           <xm:sqref>G269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{13590551-a5ea-4b12-8194-7213e5e185b3}">
+          <x14:cfRule type="containsText" priority="32" operator="containsText" id="{65d3fe86-a0e3-4b38-a1db-b6eccd4b4d0c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18085,7 +18085,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="31" operator="containsText" id="{79f1ec33-bb37-4b2b-acc1-4bd121a9624e}">
+          <x14:cfRule type="containsText" priority="31" operator="containsText" id="{c53b2dae-4827-4f56-b656-c306cf51b707}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18103,7 +18103,7 @@
           <xm:sqref>J269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{150b8d53-1864-4a03-98ac-ef2354f8c471}">
+          <x14:cfRule type="containsText" priority="18" operator="containsText" id="{f8af98be-5864-481c-9e3e-a07399a1516d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K269)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18118,7 +18118,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{fbee82d2-4fba-4f95-ab2d-3e6a1f359567}">
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{16b31e71-43ee-4d5f-a309-884bdb870186}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K269)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18136,7 +18136,7 @@
           <xm:sqref>K269</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{4f22903b-51d3-4c2d-b1ea-26c6819486dd}">
+          <x14:cfRule type="containsText" priority="53" operator="containsText" id="{1bc54ed2-3e25-4267-9bdd-c097e1f8dfe2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F270)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18151,7 +18151,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{392f0e95-608f-4534-9483-43e65c534032}">
+          <x14:cfRule type="containsText" priority="54" operator="containsText" id="{9bf27cf6-8580-4370-bd12-99c04353bc70}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F270)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18169,7 +18169,7 @@
           <xm:sqref>F270</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="51" operator="containsText" id="{5b8c6c08-74de-4a2d-b2d9-f0755aaa79fa}">
+          <x14:cfRule type="containsText" priority="51" operator="containsText" id="{2ceddbe0-4235-4532-900c-2faf788fe255}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G270)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18184,7 +18184,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="52" operator="containsText" id="{13a9ef32-1b5f-420d-94e0-9f32ea07a1df}">
+          <x14:cfRule type="containsText" priority="52" operator="containsText" id="{1a4547df-9fe4-42d9-b5e2-fda729c5b986}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G270)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18202,7 +18202,7 @@
           <xm:sqref>G270</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="30" operator="containsText" id="{bb23b3a8-8e74-451a-81ba-3b039e56e8c2}">
+          <x14:cfRule type="containsText" priority="30" operator="containsText" id="{e2d677e2-4dde-4954-8776-8360b1ddaad0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J271)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18217,7 +18217,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{14e30bca-4053-4970-ba3f-0d512d921723}">
+          <x14:cfRule type="containsText" priority="29" operator="containsText" id="{675b7990-79b4-4165-a633-c44ae709b0f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J271)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18235,7 +18235,7 @@
           <xm:sqref>J271</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{25194452-42c5-4cba-b19f-e5ab44980eea}">
+          <x14:cfRule type="containsText" priority="16" operator="containsText" id="{7853c0ad-2fe2-4764-9e63-a07aa1821596}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K271)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18250,7 +18250,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{4e67eb27-e3f8-4c19-8ab8-ef606aafd321}">
+          <x14:cfRule type="containsText" priority="15" operator="containsText" id="{fb10db36-4080-4d11-83e4-8a906e3741a3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K271)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18268,7 +18268,7 @@
           <xm:sqref>K271</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{4d5c2d10-0ae9-41ae-aeda-907cad0c1186}">
+          <x14:cfRule type="containsText" priority="49" operator="containsText" id="{f3858192-6bff-40a2-a83e-3796ed37a137}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18283,7 +18283,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="50" operator="containsText" id="{1b3e2fba-21db-47a6-8b90-aa98edfb9e3f}">
+          <x14:cfRule type="containsText" priority="50" operator="containsText" id="{d07990fb-f4a3-42ce-9b1a-1c849e404662}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18301,7 +18301,7 @@
           <xm:sqref>G272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{bb49e5ad-ec4f-42ed-a72d-4e5bfcc8b65b}">
+          <x14:cfRule type="containsText" priority="28" operator="containsText" id="{1dddbb94-9af5-4081-b595-ab9a370f56e7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18316,7 +18316,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="27" operator="containsText" id="{3ae8ee18-6554-45a1-9b84-0c4d4bd9f491}">
+          <x14:cfRule type="containsText" priority="27" operator="containsText" id="{4792e47f-7340-4dd4-8f28-b86d887d8dfb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18334,7 +18334,7 @@
           <xm:sqref>J272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{0eeedb5c-b9e7-42e4-a864-28e97f48a9d8}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{52ccd17b-966f-4cf3-9f9b-f23ea0867832}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K272)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18349,7 +18349,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{502f985d-1b3d-478a-8984-17105151c3e3}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{7cda7979-3f7e-464a-b4f6-83e84a6609d3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K272)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18367,7 +18367,7 @@
           <xm:sqref>K272</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="45" operator="containsText" id="{24dce0cc-514c-4fe2-85bf-607e54464918}">
+          <x14:cfRule type="containsText" priority="45" operator="containsText" id="{5d7ec725-8ec3-47af-91bc-6d345a1ae366}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18382,7 +18382,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="46" operator="containsText" id="{43f465bd-6fb7-40fd-bd17-10b4ccaacfb2}">
+          <x14:cfRule type="containsText" priority="46" operator="containsText" id="{c2cc87e6-0db3-4f00-a511-5f3154f1bb11}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18400,7 +18400,7 @@
           <xm:sqref>F273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{298dc70d-7205-41f5-8030-76688e205155}">
+          <x14:cfRule type="containsText" priority="47" operator="containsText" id="{e9961e19-6334-40d6-9db1-bbdce8c79394}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18415,7 +18415,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="48" operator="containsText" id="{5795fdc3-661f-4a5e-a678-1e0550248464}">
+          <x14:cfRule type="containsText" priority="48" operator="containsText" id="{ec92906b-d06b-4ff2-908c-d139f76e977b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18433,7 +18433,7 @@
           <xm:sqref>G273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{2e4ef911-09af-45bb-bb01-0f7ea0a043b9}">
+          <x14:cfRule type="containsText" priority="26" operator="containsText" id="{8c399e25-392f-4d25-a800-5920becf0c5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18448,7 +18448,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="25" operator="containsText" id="{adb6da43-ec37-4e1a-ae91-36ca5ef70c81}">
+          <x14:cfRule type="containsText" priority="25" operator="containsText" id="{e14e9f87-f0e7-4b7b-94eb-8b0ea60b562d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18466,7 +18466,7 @@
           <xm:sqref>J273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{3649d75e-85d9-468e-8cf6-4a3acb3b3669}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{6082a6ac-71ca-4f9f-adba-2d40a51a1833}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K273)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18481,7 +18481,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{73fa19f9-997f-4211-bdc6-b412585e2715}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{a2d91062-8704-4449-96f5-5738a0742242}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K273)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18499,7 +18499,7 @@
           <xm:sqref>K273</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{0f14c9aa-42c5-42a3-ba53-62c02e2120bd}">
+          <x14:cfRule type="containsText" priority="41" operator="containsText" id="{8616bf28-4267-4520-8797-f0d9d21f5463}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18514,7 +18514,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="42" operator="containsText" id="{65b0fa8b-2b77-47f9-b2ca-e4a8a3257fa6}">
+          <x14:cfRule type="containsText" priority="42" operator="containsText" id="{6261cd32-2e68-4cc6-986b-baeb5d36f4ce}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18532,7 +18532,7 @@
           <xm:sqref>F274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="43" operator="containsText" id="{84aa3e53-b6ca-400d-86d1-f0f5944c81e2}">
+          <x14:cfRule type="containsText" priority="43" operator="containsText" id="{bea47732-94e8-4f3f-a79d-40bf64bf22bf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18547,7 +18547,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{adbc6e29-2cf0-4ace-a705-72997c668855}">
+          <x14:cfRule type="containsText" priority="44" operator="containsText" id="{ed8cb1ac-8284-4806-b94d-dbc70b066268}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18565,7 +18565,7 @@
           <xm:sqref>G274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{f308146a-5c1e-4975-b0cb-c407774e8c98}">
+          <x14:cfRule type="containsText" priority="24" operator="containsText" id="{6a5e18f9-b63b-45cb-86ce-92297a9c4c35}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18580,7 +18580,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="23" operator="containsText" id="{d98e49a4-672b-415d-b45b-4e634acc90db}">
+          <x14:cfRule type="containsText" priority="23" operator="containsText" id="{278d6fd8-98b3-427a-8572-c8d7fb4726e5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18598,7 +18598,7 @@
           <xm:sqref>J274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{0eee3764-8018-43dc-a7f9-1d2dbbf473bb}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{324e4c23-3037-4eb5-905c-364011562ce3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K274)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18613,7 +18613,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{8484ebb4-602d-4dec-a965-e321fb7de60e}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{1c1c624c-4fe7-4114-9a4d-37b7697b6cfc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K274)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18631,7 +18631,7 @@
           <xm:sqref>K274</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{c1b22c4c-c2f8-4d3e-acde-fedc3dfec777}">
+          <x14:cfRule type="containsText" priority="39" operator="containsText" id="{ef8d4f7d-b9f9-409d-953a-c7b9426fc881}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G275)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18646,7 +18646,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="40" operator="containsText" id="{e4bddf99-a3ca-417c-a211-7c10cf7121c3}">
+          <x14:cfRule type="containsText" priority="40" operator="containsText" id="{55a8759f-8e96-4f7a-9b6e-eea8acd0855f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G275)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18664,7 +18664,7 @@
           <xm:sqref>G275</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{a77d2b53-b87d-409a-871b-ce68458ff0d1}">
+          <x14:cfRule type="containsText" priority="22" operator="containsText" id="{0f3f504a-275c-4ec3-a42f-c5e2a514ab77}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J278)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18679,7 +18679,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="21" operator="containsText" id="{2a20ee2e-50cb-4f71-8c47-2512f3e4d3b7}">
+          <x14:cfRule type="containsText" priority="21" operator="containsText" id="{393f91ce-072f-46f9-b868-894a0062ed08}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J278)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18697,7 +18697,7 @@
           <xm:sqref>J278</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{0c8cf9ea-c968-45e6-9715-859e2f6456da}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{fbfe8415-86f9-4a48-9433-3eecd39d81f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K278)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18712,7 +18712,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{63eb3aa3-e5e8-499f-887c-b7a56710b972}">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{6a0bd044-bd7f-4355-9e00-a4dd7d4d7de3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K278)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18730,7 +18730,7 @@
           <xm:sqref>K278</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{4e08b522-fdef-47c9-af2f-357f403eb05b}">
+          <x14:cfRule type="containsText" priority="35" operator="containsText" id="{d3f69399-3d1e-43be-bf7e-637a56065d2b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,F279)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18745,7 +18745,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="36" operator="containsText" id="{54281ddc-39a0-44d5-8442-db80f3c8043a}">
+          <x14:cfRule type="containsText" priority="36" operator="containsText" id="{55e3d151-650b-473a-9375-46ad9f564f05}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,F279)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18763,7 +18763,7 @@
           <xm:sqref>F279</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{eb2aa9fc-1726-40ce-8a30-7a42283a4884}">
+          <x14:cfRule type="containsText" priority="37" operator="containsText" id="{55a53e92-c61a-4777-844b-57b1dd95eb80}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G279)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18778,7 +18778,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{becc3c42-36d6-43b5-8709-6c95ae7bd207}">
+          <x14:cfRule type="containsText" priority="38" operator="containsText" id="{dafb9fc2-9170-435f-b40c-1c9799e40167}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G279)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18796,7 +18796,7 @@
           <xm:sqref>G279</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="64" operator="containsText" id="{bcc0caa1-d0df-4fa5-87c8-6b357f1665ae}">
+          <x14:cfRule type="containsText" priority="64" operator="containsText" id="{411433c7-7ba0-496c-98b1-143229fc96dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18811,7 +18811,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="63" operator="containsText" id="{fa4bc2bd-1218-4f25-b581-c76c00c86aba}">
+          <x14:cfRule type="containsText" priority="63" operator="containsText" id="{aca0f3b7-2615-4066-8341-f7f42d566318}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18829,7 +18829,7 @@
           <xm:sqref>A280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="57" operator="containsText" id="{16bea4b2-c8a5-4936-a80c-7af013f5a492}">
+          <x14:cfRule type="containsText" priority="57" operator="containsText" id="{35ed6006-a6be-4e38-8ddc-165239810f53}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18844,7 +18844,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="58" operator="containsText" id="{90ceae64-d22a-465e-b80c-5e41455c2fb1}">
+          <x14:cfRule type="containsText" priority="58" operator="containsText" id="{002be3c1-53b7-475d-b784-ecefa2b1c1be}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18862,7 +18862,7 @@
           <xm:sqref>E280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{7ae55da5-ad64-4cd8-b672-cd458ef68e4a}">
+          <x14:cfRule type="containsText" priority="20" operator="containsText" id="{18827ef1-9aaf-4db2-badc-b96e8e3e3434}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18877,7 +18877,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="19" operator="containsText" id="{994c0ca7-34a4-44ee-8373-36e0a366d71f}">
+          <x14:cfRule type="containsText" priority="19" operator="containsText" id="{5b9aa18f-1942-4cc0-a46f-7794dbeccc4c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18895,7 +18895,7 @@
           <xm:sqref>J280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{befd1658-0d06-47dd-b95a-198f55cab72f}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{7503d15c-170b-4663-9e8f-5ebd85fae8ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K280)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18910,7 +18910,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{e5755096-6072-472b-aaa3-550a1ecc169a}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{b6771a38-f74a-4234-978f-7e9277470042}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K280)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18928,7 +18928,7 @@
           <xm:sqref>K280</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="61" operator="containsText" id="{06802901-c55b-404b-b9c5-fcc2a6bc63e8}">
+          <x14:cfRule type="containsText" priority="61" operator="containsText" id="{dda9c076-15b1-45c2-a791-66933c8b85ad}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E281)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18943,7 +18943,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="62" operator="containsText" id="{6caf97c1-b4b3-4117-9b5f-86ca55fafd0c}">
+          <x14:cfRule type="containsText" priority="62" operator="containsText" id="{b3d9c4c3-7fbd-4459-b544-173960297a54}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E281)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18961,7 +18961,7 @@
           <xm:sqref>E281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{f806374a-07c6-431c-aa66-2454325af19b}">
+          <x14:cfRule type="containsText" priority="33" operator="containsText" id="{087e13c0-0f2f-4119-90fd-8b8ffb1b5ea1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G281)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -18976,7 +18976,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{3e8cf20e-397b-4702-934b-f73057ee8b98}">
+          <x14:cfRule type="containsText" priority="34" operator="containsText" id="{3bab864d-f63a-4849-812d-4e173281713e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G281)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -18994,7 +18994,7 @@
           <xm:sqref>G281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="93" operator="containsText" id="{80ed6341-0d3f-4566-9931-4e989820ab3b}">
+          <x14:cfRule type="containsText" priority="93" operator="containsText" id="{907cd6f9-54eb-45c8-91eb-524fc907f73e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19009,7 +19009,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="94" operator="containsText" id="{74860fd8-9ef3-4871-a23a-f03b86bf460e}">
+          <x14:cfRule type="containsText" priority="94" operator="containsText" id="{5c7fa60f-9a5b-4c98-8fda-5d013eb6fffd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19027,7 +19027,7 @@
           <xm:sqref>B86:B99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="91" operator="containsText" id="{bd1aabe3-8e6c-4d28-a93a-04b851fbe726}">
+          <x14:cfRule type="containsText" priority="91" operator="containsText" id="{e519a425-0fa5-43bd-a5ca-31c699a1a15e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19042,7 +19042,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="92" operator="containsText" id="{869f9878-2cd8-4965-bdeb-54ff69be23f3}">
+          <x14:cfRule type="containsText" priority="92" operator="containsText" id="{185fb8a7-ca09-4250-86ce-ab9a223dc9e8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19060,7 +19060,7 @@
           <xm:sqref>B100:B113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="89" operator="containsText" id="{37ac2321-8f66-43e5-8036-0c45d63f9485}">
+          <x14:cfRule type="containsText" priority="89" operator="containsText" id="{52bf15be-1322-4413-974c-4af01f47e1ac}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19075,7 +19075,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="90" operator="containsText" id="{28693bb0-3a75-4600-aacd-fbcb01ab80b5}">
+          <x14:cfRule type="containsText" priority="90" operator="containsText" id="{26243723-0248-41b2-929b-be6f1acb66ab}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19093,7 +19093,7 @@
           <xm:sqref>B114:B127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="87" operator="containsText" id="{5641189c-58fa-444e-8f83-d1f244dabf08}">
+          <x14:cfRule type="containsText" priority="87" operator="containsText" id="{2b289228-8af1-4cd2-81dd-4e5b3fddf76c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19108,7 +19108,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="88" operator="containsText" id="{9bcc5ff2-60cc-4e24-aaa1-57046df821bf}">
+          <x14:cfRule type="containsText" priority="88" operator="containsText" id="{0a5e405a-4246-4f8c-9be0-6418027cc3a8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19126,7 +19126,7 @@
           <xm:sqref>B128:B141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="85" operator="containsText" id="{bde77a6d-5735-40f5-b54e-a6a7b7fea616}">
+          <x14:cfRule type="containsText" priority="85" operator="containsText" id="{d8baf9df-dfda-49ed-9e32-6b75d50e575c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19141,7 +19141,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="86" operator="containsText" id="{b88bba71-b606-4523-8a59-b3f6523c18ca}">
+          <x14:cfRule type="containsText" priority="86" operator="containsText" id="{46fb4cea-d34b-43a4-ab40-0646a2bc93f3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19159,7 +19159,7 @@
           <xm:sqref>B142:B155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="83" operator="containsText" id="{93674b2a-289b-4fd5-acb9-e4cabd380c7f}">
+          <x14:cfRule type="containsText" priority="83" operator="containsText" id="{a00f6341-d41b-40c6-84d5-c691451650c4}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19174,7 +19174,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="84" operator="containsText" id="{b909b3c9-dc1b-4229-9b9f-60e7638979e3}">
+          <x14:cfRule type="containsText" priority="84" operator="containsText" id="{ccd0c9ba-151b-4444-a0e9-2834fdde8da8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19192,7 +19192,7 @@
           <xm:sqref>B156:B169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="81" operator="containsText" id="{20e9c70f-5082-46ef-8a0b-0593c959cdf6}">
+          <x14:cfRule type="containsText" priority="81" operator="containsText" id="{0187dcf3-0de0-4cb0-8ec2-df2962d24b22}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19207,7 +19207,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="82" operator="containsText" id="{b01b5613-f3b4-4afd-b23b-7e61466075b2}">
+          <x14:cfRule type="containsText" priority="82" operator="containsText" id="{5b95ce43-b5f1-4f4b-a073-c7027b271244}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19225,7 +19225,7 @@
           <xm:sqref>B170:B183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="79" operator="containsText" id="{694c9df4-fb47-4cb4-9d5b-c70440309a18}">
+          <x14:cfRule type="containsText" priority="79" operator="containsText" id="{62f065fb-b874-434c-a058-8a61658d927b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19240,7 +19240,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="80" operator="containsText" id="{da27927c-b2b3-4365-8eef-6f8a2237d768}">
+          <x14:cfRule type="containsText" priority="80" operator="containsText" id="{ba08502d-955c-482b-ab33-324572666fd4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19258,7 +19258,7 @@
           <xm:sqref>B184:B197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="77" operator="containsText" id="{962e5900-9e22-400f-9bbe-057dd2567e4d}">
+          <x14:cfRule type="containsText" priority="77" operator="containsText" id="{ad9d8249-ff05-4c36-851f-36a7df53101e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19273,7 +19273,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="78" operator="containsText" id="{f39ba5bf-48ca-4ab6-908f-bcfb50aa1469}">
+          <x14:cfRule type="containsText" priority="78" operator="containsText" id="{2b4cd99b-c839-43ea-9846-156c600f4167}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19291,7 +19291,7 @@
           <xm:sqref>B198:B211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="75" operator="containsText" id="{6c34f78a-4fe3-47bc-b1b7-125afcdcfa1d}">
+          <x14:cfRule type="containsText" priority="75" operator="containsText" id="{727c6c31-cb0f-48fe-966e-c630288195b9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19306,7 +19306,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="76" operator="containsText" id="{17c9f006-413c-4b8e-9114-6b8d86a09732}">
+          <x14:cfRule type="containsText" priority="76" operator="containsText" id="{832dc435-8568-430e-b99d-00832aed7a3d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19324,7 +19324,7 @@
           <xm:sqref>B212:B225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="73" operator="containsText" id="{ea7b90e9-ddef-44b8-8e36-8d2c54abc997}">
+          <x14:cfRule type="containsText" priority="73" operator="containsText" id="{a920eeb8-8754-4ebe-aef1-089e78edfe96}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19339,7 +19339,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="74" operator="containsText" id="{7ef0ffb4-0559-4f78-b717-f07b176810ef}">
+          <x14:cfRule type="containsText" priority="74" operator="containsText" id="{6c32c270-795f-4d51-b25a-934fd1b04443}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19357,7 +19357,7 @@
           <xm:sqref>B226:B239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="71" operator="containsText" id="{b8bf2f7f-06f9-4ff2-8805-145ee4b3b95b}">
+          <x14:cfRule type="containsText" priority="71" operator="containsText" id="{b788a62e-d22b-4fe0-94a2-8c2db9f1ad68}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19372,7 +19372,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="72" operator="containsText" id="{259bbf91-e300-4c96-92db-879592bb2888}">
+          <x14:cfRule type="containsText" priority="72" operator="containsText" id="{2cdfa758-0073-4bb8-bc50-fa64b11ff3c8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19390,7 +19390,7 @@
           <xm:sqref>B240:B253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="69" operator="containsText" id="{9c2a86f0-a45b-4767-a98a-e6c2623954d4}">
+          <x14:cfRule type="containsText" priority="69" operator="containsText" id="{bcafda37-b8bf-4554-a718-1636f977c884}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19405,7 +19405,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="70" operator="containsText" id="{246b71c4-7e2d-485a-a78a-6c47bda0f325}">
+          <x14:cfRule type="containsText" priority="70" operator="containsText" id="{616fdaa9-5181-4d2a-9589-05f3411350a4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19423,7 +19423,7 @@
           <xm:sqref>B254:B267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="129" operator="containsText" id="{c7f830ed-79d8-476f-965a-4451eecbcd90}">
+          <x14:cfRule type="containsText" priority="129" operator="containsText" id="{ca50bbc4-81ad-40ad-907b-cad41c0462c5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19438,7 +19438,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="130" operator="containsText" id="{3a966e2c-f54a-4048-ace1-7e960cb345d3}">
+          <x14:cfRule type="containsText" priority="130" operator="containsText" id="{324caf4d-cf38-4d64-bfa6-f93faa514ce2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19456,7 +19456,7 @@
           <xm:sqref>G184:G195</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="123" operator="containsText" id="{d36a0901-85be-4c22-a37a-631a78917666}">
+          <x14:cfRule type="containsText" priority="123" operator="containsText" id="{6675f08d-deaf-4d13-b42b-20d2626a4d53}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19471,7 +19471,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="124" operator="containsText" id="{dce9b944-e4a8-4402-ad84-debd5ff1066d}">
+          <x14:cfRule type="containsText" priority="124" operator="containsText" id="{00a1612d-d097-43eb-a9b0-4eab0b1673dd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19489,7 +19489,7 @@
           <xm:sqref>G198:G209</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="117" operator="containsText" id="{522a90e3-e4c9-44fd-b2e3-acaf4587cd4e}">
+          <x14:cfRule type="containsText" priority="117" operator="containsText" id="{5147f0cf-5103-4abc-9b0e-8db400c4cc7f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19504,7 +19504,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="118" operator="containsText" id="{09768b02-2c41-47a5-a99b-07b2778ba704}">
+          <x14:cfRule type="containsText" priority="118" operator="containsText" id="{3898d795-f2ab-4bd7-9444-e3a74874975b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19522,7 +19522,7 @@
           <xm:sqref>G212:G223</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{15498f82-b6c4-41a1-91cb-4484033d32d5}">
+          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{234aa7b4-0d65-4066-bd84-5cbf249ead15}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19537,7 +19537,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="112" operator="containsText" id="{c303b1d8-643b-4210-a4bc-766f7172de93}">
+          <x14:cfRule type="containsText" priority="112" operator="containsText" id="{5535fe40-f1f6-4b37-bbb5-539dd57220b9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19555,7 +19555,7 @@
           <xm:sqref>G226:G237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="105" operator="containsText" id="{81f89ffa-1522-406e-be18-60beccb74bad}">
+          <x14:cfRule type="containsText" priority="105" operator="containsText" id="{17782842-ff7b-4488-b517-b67f15607494}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19570,7 +19570,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="106" operator="containsText" id="{2872d686-8568-406a-97fc-5fbb279bf124}">
+          <x14:cfRule type="containsText" priority="106" operator="containsText" id="{7ab5e1ad-f931-4378-8416-2b881e72355d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19588,7 +19588,7 @@
           <xm:sqref>G240:G251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="99" operator="containsText" id="{f4595b9f-9497-4c23-bb94-4a30b904426d}">
+          <x14:cfRule type="containsText" priority="99" operator="containsText" id="{6940a29f-55c8-44df-bac4-594a90092510}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19603,7 +19603,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="100" operator="containsText" id="{19794811-44a3-45d6-9d0e-d69156c32b54}">
+          <x14:cfRule type="containsText" priority="100" operator="containsText" id="{2ce7d8d8-6d1a-4ccf-886f-7dd6abb279ae}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19621,7 +19621,7 @@
           <xm:sqref>G254:G265</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="887" operator="containsText" id="{e2d98991-4739-446a-9125-538f6b44200a}">
+          <x14:cfRule type="containsText" priority="887" operator="containsText" id="{013d2cc7-690f-4d4f-b465-b576f60cf767}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,K69)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19636,7 +19636,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="888" operator="containsText" id="{6fdec2f8-26d3-488b-9e26-c11b5dc65dc9}">
+          <x14:cfRule type="containsText" priority="888" operator="containsText" id="{b8b4d40c-b053-4fbc-9586-867234b62111}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,K69)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19654,7 +19654,7 @@
           <xm:sqref>K69:K70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="889" operator="containsText" id="{a0ae69b8-3b66-4bd9-90ba-e3e8c09a9c1c}">
+          <x14:cfRule type="containsText" priority="889" operator="containsText" id="{d603b9d1-8b39-414f-b46a-db661b525370}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19669,7 +19669,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="894" operator="containsText" id="{ed582c2f-61ca-497f-bc5c-e430025e466c}">
+          <x14:cfRule type="containsText" priority="894" operator="containsText" id="{6687d19e-c8e9-4a12-93cc-92ceeb70cbd5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19687,7 +19687,7 @@
           <xm:sqref>L22:M22 M36 J38:M38 K21:M21 J31:M32 A29:A41 L58:M58 L67:M67 A71 L69:M70 A1:A27 E72:F72 J28:M28 A43:A55 J42:M42 A57:A69 J56:M56 J70 C85:F85 L73:M73 C73:F83 L83:M84 J84 L96:M96 J96:J97 M142 M147 C134:F134 J142:K142 K147 A284:F1048576 C197:D197 F197 E195 H197 H284:M1048576 H83:J83 H73:J73 H74:M82 H85:M85 H57:M57 H43:M55 H69:J69 H71:M72 H68:M68 H67:J67 H59:M66 H58:J58 H39:M41 H33:M35 H38 H37:M37 H36:K36 H21 H23:M27 H22:J22 H29:M29 H31:H32 H1:M20 C57:F69 C43:F55 C71:F71 C31:F41 C29:F29 C1:F27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="95" operator="containsText" id="{fed4ec08-b2f2-45fc-8703-d16394e6b66b}">
+          <x14:cfRule type="containsText" priority="95" operator="containsText" id="{c488effa-0e63-4e4c-9b2e-25487bc29396}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19702,7 +19702,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="96" operator="containsText" id="{de87173e-94ea-42f6-899a-c66a07f9a233}">
+          <x14:cfRule type="containsText" priority="96" operator="containsText" id="{3c8a472c-3409-4a70-94f8-59fb9244c794}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19720,7 +19720,7 @@
           <xm:sqref>B1:B2 B4 B6 B8 B10 B12 B14 B16:B85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="167" operator="containsText" id="{db7c03a4-d33e-4268-8d74-9d8a181cf84a}">
+          <x14:cfRule type="containsText" priority="167" operator="containsText" id="{c8148542-c236-479e-8151-73d168d0cf29}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G1)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19735,7 +19735,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="168" operator="containsText" id="{e657ab6d-7cfb-42d9-a3c4-6ceeeffeba14}">
+          <x14:cfRule type="containsText" priority="168" operator="containsText" id="{29524c6f-d619-45e0-ac84-a84bfec8daf6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G1)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19753,7 +19753,7 @@
           <xm:sqref>G31 G29 G33:G41 G1:G27 G57:G69 G71:G85 G96:G97 G284:G1048576 G197 G43:G55</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="67" operator="containsText" id="{4807ce80-b5ac-4f1a-9ddc-ac04f847aba0}">
+          <x14:cfRule type="containsText" priority="67" operator="containsText" id="{a9bb793b-bc0a-413e-bde6-d3851480ba93}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,B3)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19768,7 +19768,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="68" operator="containsText" id="{635c63b0-5036-4e41-bf1a-139f194331fd}">
+          <x14:cfRule type="containsText" priority="68" operator="containsText" id="{b63e9996-3b11-4939-a1ac-c46f50ab5fd3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,B3)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19786,7 +19786,7 @@
           <xm:sqref>B3 B5 B7 B9 B11 B13 B15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="883" operator="containsText" id="{50a856b7-0178-4f71-b5bb-bcf11837f985}">
+          <x14:cfRule type="containsText" priority="883" operator="containsText" id="{c72ffc55-4fc0-4cc5-a95d-da5144deed5e}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A28)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19801,7 +19801,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="884" operator="containsText" id="{665abc23-5892-47a0-8f08-45e770041cec}">
+          <x14:cfRule type="containsText" priority="884" operator="containsText" id="{dff8b59a-0836-4b27-bb5a-34b731a2a1aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A28)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19819,7 +19819,7 @@
           <xm:sqref>A28 H28:I28 C28:F28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="881" operator="containsText" id="{bbdd4d6b-58ef-4b3b-83b3-125659ce3c9c}">
+          <x14:cfRule type="containsText" priority="881" operator="containsText" id="{bd62eb32-fd5d-4723-bb08-764089aafcae}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A42)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19834,7 +19834,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="882" operator="containsText" id="{0e93222e-9a52-43e5-b356-943a8c18bac7}">
+          <x14:cfRule type="containsText" priority="882" operator="containsText" id="{28ea28b4-861f-48c8-929e-71d24e866bd8}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A42)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19852,7 +19852,7 @@
           <xm:sqref>A42 H42:I42 C42:F42</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="879" operator="containsText" id="{a3982c2a-59ba-4fea-badb-7acfd739310b}">
+          <x14:cfRule type="containsText" priority="879" operator="containsText" id="{79e940d7-101e-4042-824c-6a8a1acd128c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A56)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19867,7 +19867,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="880" operator="containsText" id="{a53d5a0a-31a3-487c-8059-33b34e0a5b8e}">
+          <x14:cfRule type="containsText" priority="880" operator="containsText" id="{6313d09a-41da-4481-b792-71302f78288b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A56)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19885,7 +19885,7 @@
           <xm:sqref>A56 H56:I56 C56:F56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="877" operator="containsText" id="{bb43d91f-541f-4730-8437-d6f13911523b}">
+          <x14:cfRule type="containsText" priority="877" operator="containsText" id="{01c265ee-7e8a-4ae1-b671-ebec866a53fb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A70)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19900,7 +19900,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="878" operator="containsText" id="{df838723-9db5-4ea6-bac1-9ed3978c247c}">
+          <x14:cfRule type="containsText" priority="878" operator="containsText" id="{cb4d3765-352f-49ca-9ac8-9e01c68bac13}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A70)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19918,7 +19918,7 @@
           <xm:sqref>A70 H70:I70 C70:F70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="885" operator="containsText" id="{c73be821-df78-484d-a87f-5603b0493391}">
+          <x14:cfRule type="containsText" priority="885" operator="containsText" id="{58e06b8b-b399-46d8-9539-3b145376fa32}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A72)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19933,7 +19933,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="886" operator="containsText" id="{4ee43f24-498a-4ae2-b1c6-f0a48c00a0d2}">
+          <x14:cfRule type="containsText" priority="886" operator="containsText" id="{08cc2d5f-1807-4d77-bdb5-d02f9fd053d3}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A72)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19951,7 +19951,7 @@
           <xm:sqref>A72:A83 A85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="875" operator="containsText" id="{113cd0a6-5a30-4fb1-aed3-e86b8699b27d}">
+          <x14:cfRule type="containsText" priority="875" operator="containsText" id="{c68d24eb-8ba2-4c41-81a1-539076f63665}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A84)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19966,7 +19966,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="876" operator="containsText" id="{159e4d62-5f05-4c30-82f4-3aff768b5a6e}">
+          <x14:cfRule type="containsText" priority="876" operator="containsText" id="{4acc40ef-2ff5-4b9a-917f-8279194fcd99}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A84)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -19984,7 +19984,7 @@
           <xm:sqref>A84 H84:I84 C84:F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="871" operator="containsText" id="{37a976df-70e0-4ac9-8bf8-3972adcf4f62}">
+          <x14:cfRule type="containsText" priority="871" operator="containsText" id="{39e9866c-cd89-46e9-b521-2fa21f76b8e3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -19999,7 +19999,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="872" operator="containsText" id="{84c40a44-1288-4004-af66-7a107eff5d80}">
+          <x14:cfRule type="containsText" priority="872" operator="containsText" id="{634bc224-8a17-45d2-9386-0c24e8392b95}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20017,7 +20017,7 @@
           <xm:sqref>A86:A97 A99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="873" operator="containsText" id="{2af20f61-25d1-464e-b1c3-c60459d22b0c}">
+          <x14:cfRule type="containsText" priority="873" operator="containsText" id="{93c2484d-2ed4-4ec5-834a-2d38c1862c22}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20032,7 +20032,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="874" operator="containsText" id="{f649de5e-7d45-4c48-b067-3f2d4b1fe9df}">
+          <x14:cfRule type="containsText" priority="874" operator="containsText" id="{931d43e9-100d-4209-8c35-f33edf5e637f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20050,7 +20050,7 @@
           <xm:sqref>E86:F86 C99:F99 J98:M98 M97 M87 J92:M93 C87:F97 H96:H97 H92:H93 H87:K87 H88:M91 H94:M95 H99:M99 H86:M86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="157" operator="containsText" id="{5788f371-28f1-4759-abab-a780f9c4bc45}">
+          <x14:cfRule type="containsText" priority="157" operator="containsText" id="{723d7b49-64a6-476f-8093-f7e4c919ca98}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G86)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20065,7 +20065,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="158" operator="containsText" id="{8845b73b-a409-4366-b9b0-c0a4cbb47bb7}">
+          <x14:cfRule type="containsText" priority="158" operator="containsText" id="{e682914b-4957-4b9b-babf-43641413a3c7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G86)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20083,7 +20083,7 @@
           <xm:sqref>G99 G86:G95</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="869" operator="containsText" id="{ad06bfa6-c6e2-4a92-932a-e7edfec145d3}">
+          <x14:cfRule type="containsText" priority="869" operator="containsText" id="{c456aef4-294c-4b1f-b361-0301dcd18609}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A98)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20098,7 +20098,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="870" operator="containsText" id="{64735b89-7c8b-4e55-896e-6611edda3731}">
+          <x14:cfRule type="containsText" priority="870" operator="containsText" id="{adf16c7c-47ee-4181-b387-0c9f5e502b0b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A98)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20116,7 +20116,7 @@
           <xm:sqref>A98 H98:I98 C98:F98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="853" operator="containsText" id="{ee18761b-7d15-45eb-b0f9-b6fcc4fae749}">
+          <x14:cfRule type="containsText" priority="853" operator="containsText" id="{d017487c-4c53-420d-bafe-6a844a182cbf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20131,7 +20131,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="854" operator="containsText" id="{61b81a55-240f-4a72-a8f1-2c94613bb34f}">
+          <x14:cfRule type="containsText" priority="854" operator="containsText" id="{352b3758-7f9b-433a-8127-4a94186a09da}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20149,7 +20149,7 @@
           <xm:sqref>A100:A111 A113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="855" operator="containsText" id="{89aaf2f5-2193-4760-a925-d0125e4e85a0}">
+          <x14:cfRule type="containsText" priority="855" operator="containsText" id="{ac588dbe-f22d-4fca-853e-b28996174d9a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20164,7 +20164,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="856" operator="containsText" id="{6e173993-3d22-4755-a21b-7c135baa6cf9}">
+          <x14:cfRule type="containsText" priority="856" operator="containsText" id="{263cdc00-9e76-4baf-9bb7-b86c9d4cb49c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20182,7 +20182,7 @@
           <xm:sqref>E100:F100 C113:F113 J112:M112 J111 M111 J110:M110 M101 J106:M107 C101:F111 J102:M102 H102 H106:H107 H101:K101 H103:M105 H110:H111 H108:M109 H113:M113 H100:M100</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="153" operator="containsText" id="{d2eeec47-a1eb-480e-9b28-dce4aed135fc}">
+          <x14:cfRule type="containsText" priority="153" operator="containsText" id="{d058b626-9d6a-49df-bc4d-f79bc26e8eb3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G100)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20197,7 +20197,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="154" operator="containsText" id="{c78ddee1-8858-4471-b0db-69c325e975b5}">
+          <x14:cfRule type="containsText" priority="154" operator="containsText" id="{c84c8ad4-d142-4927-b73a-98e152699a6d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G100)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20215,7 +20215,7 @@
           <xm:sqref>G113 G100:G111</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="851" operator="containsText" id="{ff091134-6877-4943-ad43-a105604314a2}">
+          <x14:cfRule type="containsText" priority="851" operator="containsText" id="{4d0bcfee-5ea4-4fb3-ba36-aed13d417d1a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A112)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20230,7 +20230,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="852" operator="containsText" id="{ac6d76da-3744-405e-b8f7-aa3545e41fbe}">
+          <x14:cfRule type="containsText" priority="852" operator="containsText" id="{8fd21ace-12ae-434c-8545-04181a341e89}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A112)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20248,7 +20248,7 @@
           <xm:sqref>A112 H112 C112:F112</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="809" operator="containsText" id="{ced1d119-f3ab-432f-8442-b2e9d3c082b2}">
+          <x14:cfRule type="containsText" priority="809" operator="containsText" id="{b6fbdf15-b464-44ad-9c6a-0ecc6c097966}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20263,7 +20263,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="810" operator="containsText" id="{427fc127-f33e-46dc-aa69-57e1ab8befb1}">
+          <x14:cfRule type="containsText" priority="810" operator="containsText" id="{355e044d-42db-4a1e-b943-4ff76768c1b5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20281,7 +20281,7 @@
           <xm:sqref>A114:A125 A127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="811" operator="containsText" id="{494f474b-a962-4656-a364-09f4e0ac138f}">
+          <x14:cfRule type="containsText" priority="811" operator="containsText" id="{c8b1484c-9b53-4739-979b-61293038ff63}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20296,7 +20296,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="812" operator="containsText" id="{84527ada-2eb5-4ea4-a97c-2022a91093e8}">
+          <x14:cfRule type="containsText" priority="812" operator="containsText" id="{b978c29a-eba4-4c0c-853a-e32a8e84fffb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20314,7 +20314,7 @@
           <xm:sqref>E114:F114 C127:F127 J126:M126 J125 M125 M115 J116:M116 J114:M114 C115:F125 J120:M124 H120:H125 H116 H115:K115 H117:M119 H127:M127 H114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="149" operator="containsText" id="{00d7c7eb-b057-4a76-a710-b3137419460e}">
+          <x14:cfRule type="containsText" priority="149" operator="containsText" id="{b6ab858c-9309-436f-8301-cce0e63c4fdc}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G114)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20329,7 +20329,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="150" operator="containsText" id="{3982a6d4-4e8d-409d-8dd1-19f69aca815f}">
+          <x14:cfRule type="containsText" priority="150" operator="containsText" id="{6d29d138-091c-4737-9ae4-1ae93ccd1168}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G114)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20347,7 +20347,7 @@
           <xm:sqref>G127 G114:G125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="807" operator="containsText" id="{b364f66d-61bb-4a09-8b49-3a470c5dd8c0}">
+          <x14:cfRule type="containsText" priority="807" operator="containsText" id="{70e5ba90-195b-40db-8688-3bf032308da3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A126)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20362,7 +20362,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="808" operator="containsText" id="{3eb5667b-c4c8-42a5-9dcd-e15752c47092}">
+          <x14:cfRule type="containsText" priority="808" operator="containsText" id="{d66b33e7-891f-4d3c-949e-5f950e1b746f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A126)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20380,7 +20380,7 @@
           <xm:sqref>A126 H126 C126:F126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="769" operator="containsText" id="{28c1121d-1cc9-4a75-9007-e96b3b06905c}">
+          <x14:cfRule type="containsText" priority="769" operator="containsText" id="{4d7f7c7f-192d-4b90-b979-62d90868474d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20395,7 +20395,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="770" operator="containsText" id="{a29328cd-57ff-44ad-a8b6-f959ef101c32}">
+          <x14:cfRule type="containsText" priority="770" operator="containsText" id="{c680846e-d06f-4025-bc31-fc52249708d0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20413,7 +20413,7 @@
           <xm:sqref>A128:A139 A141</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="771" operator="containsText" id="{f1df021e-9250-463e-a809-0609b15bbdbe}">
+          <x14:cfRule type="containsText" priority="771" operator="containsText" id="{25f6c10a-7ff0-4510-8713-65e86e9dd327}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20428,7 +20428,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="772" operator="containsText" id="{45363826-fd0f-425a-90f4-02a71e0424d3}">
+          <x14:cfRule type="containsText" priority="772" operator="containsText" id="{11b511df-b774-447f-8484-468b44135fcf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20446,7 +20446,7 @@
           <xm:sqref>E128:F128 C141:F141 J140:M140 J139 M139 M129 J130:M130 J128:M128 C129:F133 J134:M138 J133 M133 J129:K129 C135:F139 H133:H139 H131:M132 H141:M141 H128:H130</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="145" operator="containsText" id="{cffc2c02-9866-4808-a22f-2e4418ca5a7f}">
+          <x14:cfRule type="containsText" priority="145" operator="containsText" id="{3c18bf78-c24b-48f0-aed4-78c3f0b6eb7a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G128)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20461,7 +20461,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="146" operator="containsText" id="{f25ef0b3-3f5f-4994-a753-3286d05c75b6}">
+          <x14:cfRule type="containsText" priority="146" operator="containsText" id="{14088e07-cf8a-47db-ad82-8350db70f541}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G128)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20479,7 +20479,7 @@
           <xm:sqref>G141 G128:G139</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="767" operator="containsText" id="{e3c254fb-b489-4e91-877a-ce7e827b32ad}">
+          <x14:cfRule type="containsText" priority="767" operator="containsText" id="{5b6db322-471b-46dd-bf83-8d81b54a14eb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A140)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20494,7 +20494,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="768" operator="containsText" id="{dd8f774c-aa19-4d47-a961-0bd46e6a1d0a}">
+          <x14:cfRule type="containsText" priority="768" operator="containsText" id="{5591c556-a1af-476b-a215-e44910e277c1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A140)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20512,7 +20512,7 @@
           <xm:sqref>A140 H140 C140:F140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="725" operator="containsText" id="{84324c1e-4732-4dca-a0b9-9dea26f39ca9}">
+          <x14:cfRule type="containsText" priority="725" operator="containsText" id="{fb77d433-03c9-4f85-8c5f-9a59a680d165}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20527,7 +20527,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="726" operator="containsText" id="{86116256-a3bf-4d9c-9b36-c1511512c493}">
+          <x14:cfRule type="containsText" priority="726" operator="containsText" id="{196b0fa2-f81c-4490-be45-8836b524dafd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20545,7 +20545,7 @@
           <xm:sqref>A142:A153 A155</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="727" operator="containsText" id="{53478697-26f4-4e56-8606-0ebde2f1de87}">
+          <x14:cfRule type="containsText" priority="727" operator="containsText" id="{c4324e8b-7fa4-4c81-86d7-455f3e8e21d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20560,7 +20560,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="728" operator="containsText" id="{e9be80ea-9cc5-4a70-a845-e222fe006ace}">
+          <x14:cfRule type="containsText" priority="728" operator="containsText" id="{d79ef911-2a5a-45a7-adef-57a7af6cf9e4}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20578,7 +20578,7 @@
           <xm:sqref>E142:F142 C155:F155 J153 M153 J144:M144 J148:M152 J147 J154:M155 C143:F153 J146:M146 H146:H153 H145:M145 H155 H142:H144</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="141" operator="containsText" id="{580650eb-058e-4a9b-adb4-8b3640c7b6fc}">
+          <x14:cfRule type="containsText" priority="141" operator="containsText" id="{2844293e-0a39-44b3-9dc7-2a7fffa30533}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G142)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20593,7 +20593,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="142" operator="containsText" id="{a0b31e18-fd55-4023-ad64-4d9b68f9bc7f}">
+          <x14:cfRule type="containsText" priority="142" operator="containsText" id="{24216c42-c49c-444a-a4a7-e3c7b751cd31}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G142)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20611,7 +20611,7 @@
           <xm:sqref>G155 G142:G153</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="723" operator="containsText" id="{6f09e35d-69bd-4c93-953d-25872d6ca131}">
+          <x14:cfRule type="containsText" priority="723" operator="containsText" id="{297e7707-f434-49df-a3cd-676148107fca}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A154)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20626,7 +20626,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="724" operator="containsText" id="{ad0fba92-37f7-4e4b-b9eb-98130ff1a401}">
+          <x14:cfRule type="containsText" priority="724" operator="containsText" id="{c895ecb0-9b14-43b4-a007-78265b6d0a3e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A154)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20644,7 +20644,7 @@
           <xm:sqref>A154 H154 C154:F154</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="671" operator="containsText" id="{caa635c5-86e9-4d8e-9423-db6d74fd1989}">
+          <x14:cfRule type="containsText" priority="671" operator="containsText" id="{89c29555-ed3f-442c-9fb4-0cdaeecff417}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20659,7 +20659,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="672" operator="containsText" id="{046c21e6-d1ef-4631-b173-4f0539578194}">
+          <x14:cfRule type="containsText" priority="672" operator="containsText" id="{90271f2c-9114-4265-b337-a3c8cae1468f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20677,7 +20677,7 @@
           <xm:sqref>A156:A167 A169</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="673" operator="containsText" id="{966cca24-eb9d-4e15-a08a-318978aff2ac}">
+          <x14:cfRule type="containsText" priority="673" operator="containsText" id="{3bafae63-0029-4c44-8190-b350ecb0bb8a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20692,7 +20692,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="674" operator="containsText" id="{db70bc40-6c61-441a-9c7c-f652b9fab7a1}">
+          <x14:cfRule type="containsText" priority="674" operator="containsText" id="{bb67d19c-9a04-419d-89c9-f323b8d4fdf6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20710,7 +20710,7 @@
           <xm:sqref>E156:F156 C169:F169 J167 M167 J158:M158 J162:M166 J161 J168:M169 C157:F167 J160:M160 H160:H167 H159:M159 H169 H156:H158</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="137" operator="containsText" id="{b3b91a03-3f74-4a58-88a1-a0b3746bce63}">
+          <x14:cfRule type="containsText" priority="137" operator="containsText" id="{8bae3597-6dd2-4390-9d55-e1040735c504}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20725,7 +20725,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="138" operator="containsText" id="{2189249d-114b-4bbe-b418-4a91ec7b4a50}">
+          <x14:cfRule type="containsText" priority="138" operator="containsText" id="{251424c1-9d08-4748-8bce-33ec2f491967}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20743,7 +20743,7 @@
           <xm:sqref>G169 G156:G167</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="675" operator="containsText" id="{886ba147-83b3-4827-940d-0eea08bd9f20}">
+          <x14:cfRule type="containsText" priority="675" operator="containsText" id="{0ae7da48-9569-4c77-885b-ab8efca2e9bf}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J156)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20758,7 +20758,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="676" operator="containsText" id="{2c5c1d16-c30c-4c8f-b073-6b7dbf1a218a}">
+          <x14:cfRule type="containsText" priority="676" operator="containsText" id="{e30280ac-465f-44ba-81a4-0142c57918dc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J156)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20776,7 +20776,7 @@
           <xm:sqref>M156 M161 J156:K156 K161</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="669" operator="containsText" id="{55aba8e2-d985-42de-8a56-4a330dc4abc3}">
+          <x14:cfRule type="containsText" priority="669" operator="containsText" id="{98dc9209-c995-4c42-9682-9b156f8b51f0}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A168)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20791,7 +20791,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="670" operator="containsText" id="{60e59a9b-5fdd-434a-a6e4-5e06e006d152}">
+          <x14:cfRule type="containsText" priority="670" operator="containsText" id="{4c335612-073b-4a45-a15c-9c36921f43ba}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A168)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20809,7 +20809,7 @@
           <xm:sqref>A168 H168 C168:F168</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="625" operator="containsText" id="{b462e88d-9775-441e-aa04-b2fb3d7e83a5}">
+          <x14:cfRule type="containsText" priority="625" operator="containsText" id="{fbe06f65-9e6d-4cb1-b9fc-66494a6167ad}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20824,7 +20824,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="626" operator="containsText" id="{da99a171-05a2-4578-b31a-75528e8d39e7}">
+          <x14:cfRule type="containsText" priority="626" operator="containsText" id="{2d0daef1-0c0c-4f9c-9dd3-6c67b86aa6fa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20842,7 +20842,7 @@
           <xm:sqref>A170:A181 A183</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="627" operator="containsText" id="{ce299645-2851-4a23-b6a4-b4a9a6a75f54}">
+          <x14:cfRule type="containsText" priority="627" operator="containsText" id="{61b9a491-eeda-44a2-a1ba-35fa984ca86c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20857,7 +20857,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="628" operator="containsText" id="{b86dd520-9ae4-4caf-9715-c28433699c6e}">
+          <x14:cfRule type="containsText" priority="628" operator="containsText" id="{fd992dc8-30b9-4615-9a94-f539e6abcf89}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20875,7 +20875,7 @@
           <xm:sqref>E170:F170 C183:F183 J181 M181 J172:M172 J176:M180 J175 J182:M183 C171:F181 J174:M174 H174:H181 H173:M173 H183 H170:H172</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="133" operator="containsText" id="{1cee3b70-c0ab-4940-b299-b93abbd948f3}">
+          <x14:cfRule type="containsText" priority="133" operator="containsText" id="{f48201ee-5dfc-4aec-934f-2a24ac9eee7c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,G170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20890,7 +20890,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="134" operator="containsText" id="{3d3756b2-3556-4b21-aeaa-dcd0b513cf60}">
+          <x14:cfRule type="containsText" priority="134" operator="containsText" id="{6d8001fb-c8b1-421a-a038-8bf4d1123f13}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,G170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20908,7 +20908,7 @@
           <xm:sqref>G183 G170:G181</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="629" operator="containsText" id="{eb34074c-79e4-4870-806b-73ac2cb04a58}">
+          <x14:cfRule type="containsText" priority="629" operator="containsText" id="{bfbc51a4-13df-45da-ba0b-6873ece275fd}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J170)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20923,7 +20923,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="630" operator="containsText" id="{e9228857-0d4f-4d1f-ad4f-f0b5725a02a3}">
+          <x14:cfRule type="containsText" priority="630" operator="containsText" id="{f1e133f5-7f3f-4065-a44e-adc60d9e0435}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J170)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20941,7 +20941,7 @@
           <xm:sqref>M170 M175 J170:K170</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="623" operator="containsText" id="{e8da05eb-33b9-44ee-b18b-607aa00e1293}">
+          <x14:cfRule type="containsText" priority="623" operator="containsText" id="{6c4f0278-1474-4f07-9c14-0803e67c942c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A182)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20956,7 +20956,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="624" operator="containsText" id="{67977d46-d38a-4171-a5f5-62a10ca0322d}">
+          <x14:cfRule type="containsText" priority="624" operator="containsText" id="{2e494e97-645d-4fb8-9ad1-f309be7687d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A182)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -20974,7 +20974,7 @@
           <xm:sqref>A182 H182 C182:F182</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="571" operator="containsText" id="{1dc67001-463b-4842-9aea-e3a6e27b9913}">
+          <x14:cfRule type="containsText" priority="571" operator="containsText" id="{ad496f45-f257-486b-a744-b4b5fc1f7cb8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -20989,7 +20989,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="572" operator="containsText" id="{13c8cb87-ed64-4ac9-9bcf-1558a616bb9b}">
+          <x14:cfRule type="containsText" priority="572" operator="containsText" id="{fb7d8d86-30bd-4e24-827c-82f48d40570e}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21007,7 +21007,7 @@
           <xm:sqref>A184:A195 A197</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="573" operator="containsText" id="{e52debce-b1c1-4f24-aad6-e79039155720}">
+          <x14:cfRule type="containsText" priority="573" operator="containsText" id="{acb76931-067a-4e0e-aea5-eb344ba9f310}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21022,7 +21022,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="574" operator="containsText" id="{625b5ed1-59ed-4706-9ac2-3c3b704c6a17}">
+          <x14:cfRule type="containsText" priority="574" operator="containsText" id="{0eea754d-7ce2-45c2-bd1d-77c7205fd6ea}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21040,7 +21040,7 @@
           <xm:sqref>E184:F184 J195 M195 J186:M186 J190:M194 J189 J196:M197 C185:F191 J188:M188 C193:F194 C192:D192 F192 C195:D195 F195 H188:H195 H187:M187 H184:H186</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="575" operator="containsText" id="{3c28f92c-6406-4f73-81e9-8c1fa0ecd983}">
+          <x14:cfRule type="containsText" priority="575" operator="containsText" id="{7feea145-92f4-4993-b034-3134be1f9fdb}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J184)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21055,7 +21055,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="576" operator="containsText" id="{47128c5a-90fe-4413-ba0b-77381a308757}">
+          <x14:cfRule type="containsText" priority="576" operator="containsText" id="{4b300951-2a4b-4b0c-ba94-59cd6efa57d6}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J184)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21073,7 +21073,7 @@
           <xm:sqref>M184 M189 J184:K184</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="569" operator="containsText" id="{fc9decec-800a-4e36-96cd-f89fdf09d7a8}">
+          <x14:cfRule type="containsText" priority="569" operator="containsText" id="{911a3883-b817-4b5c-9364-0160d01db6a2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A196)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21088,7 +21088,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="570" operator="containsText" id="{ab616c6b-ab6c-4119-918a-29946c176bf3}">
+          <x14:cfRule type="containsText" priority="570" operator="containsText" id="{a97f129f-0b67-432e-99c2-b51e9213d3a7}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A196)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21106,7 +21106,7 @@
           <xm:sqref>A196 H196 C196:F196</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="517" operator="containsText" id="{48f64060-77e6-428a-a2db-e70fce00dab3}">
+          <x14:cfRule type="containsText" priority="517" operator="containsText" id="{c5cd763f-7327-430c-8e30-a4a2cd305794}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21121,7 +21121,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="518" operator="containsText" id="{ae145444-6ca5-4597-8553-93194ef88953}">
+          <x14:cfRule type="containsText" priority="518" operator="containsText" id="{a638d5a8-8db2-424f-a3bc-f2f88c78eb28}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21139,7 +21139,7 @@
           <xm:sqref>A198:A209 A211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="519" operator="containsText" id="{c5d1b229-b282-4e85-b13c-8415ad58c97f}">
+          <x14:cfRule type="containsText" priority="519" operator="containsText" id="{334e2aad-4a6a-46ca-8508-7f79c1d508e9}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21154,7 +21154,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="520" operator="containsText" id="{8c4a91f6-e374-4831-9d8b-d91e57df32c0}">
+          <x14:cfRule type="containsText" priority="520" operator="containsText" id="{f2b6c29e-152d-40c7-a419-f642aa355107}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21172,7 +21172,7 @@
           <xm:sqref>E198:F198 J209 M209 J200:M200 J204:M208 J203 J210:M211 C199:F204 J202:M202 C207:F208 C209:D209 C205:D206 F206 H202:H209 H201:M201 H198:H200</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="521" operator="containsText" id="{86c0d695-4a2f-4ee0-843a-049d2ab0cf7d}">
+          <x14:cfRule type="containsText" priority="521" operator="containsText" id="{eec29207-5f39-4e56-993e-0609ebfad173}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J198)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21187,7 +21187,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="522" operator="containsText" id="{19f84bc2-44c9-4043-8fc2-77d9f973ff80}">
+          <x14:cfRule type="containsText" priority="522" operator="containsText" id="{75e7a320-794e-45a6-ac67-48f6f9d5ecb9}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J198)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21205,7 +21205,7 @@
           <xm:sqref>M198 M203 J198:K198</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="515" operator="containsText" id="{c3573588-b472-4eee-9701-e7c6c678ce46}">
+          <x14:cfRule type="containsText" priority="515" operator="containsText" id="{4d2e4978-8b7f-4f70-a187-38deeaf9ec66}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A210)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21220,7 +21220,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="516" operator="containsText" id="{f9b5bb94-b345-4f7f-b5a1-392f21a4ead6}">
+          <x14:cfRule type="containsText" priority="516" operator="containsText" id="{665f2e4b-a6ad-4137-890a-6b10b6c0b19f}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A210)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21238,7 +21238,7 @@
           <xm:sqref>A210 H210 C210:F210</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="523" operator="containsText" id="{661f79f3-607a-448a-a0d1-f02f0a695b9f}">
+          <x14:cfRule type="containsText" priority="523" operator="containsText" id="{dc45072c-96a0-4487-b18a-eb38940c471a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C211)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21253,7 +21253,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="524" operator="containsText" id="{8bcea746-2bee-442d-9529-5d80d97104b4}">
+          <x14:cfRule type="containsText" priority="524" operator="containsText" id="{4a17afb6-f295-47f5-8e0e-980f12a2a9aa}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C211)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21271,7 +21271,7 @@
           <xm:sqref>C211:D211 F211 H211</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="463" operator="containsText" id="{41f103a0-f538-42e4-a9ad-453700e453a4}">
+          <x14:cfRule type="containsText" priority="463" operator="containsText" id="{fd40cd6c-5a73-4439-9f5a-494d2396d398}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21286,7 +21286,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="464" operator="containsText" id="{91e05480-7bd9-4c61-a265-8761f9b12424}">
+          <x14:cfRule type="containsText" priority="464" operator="containsText" id="{88d350bb-1829-4fbe-91b0-96e146139669}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21304,7 +21304,7 @@
           <xm:sqref>A212:A223 A225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="465" operator="containsText" id="{016124af-b3fb-4ac1-8389-86f6379028ff}">
+          <x14:cfRule type="containsText" priority="465" operator="containsText" id="{539d54bf-ad6c-4b4d-a991-01463a32d577}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21319,7 +21319,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="466" operator="containsText" id="{0ac4c39f-5fe2-4f7a-81cc-65985d781b0d}">
+          <x14:cfRule type="containsText" priority="466" operator="containsText" id="{d1189196-e7b5-49ad-9fc3-59ed20821e44}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21337,7 +21337,7 @@
           <xm:sqref>E212:F212 J223 M223 J214:M214 J218:M222 J217 J224:M225 C213:F218 J216:M216 C221:F222 C223:D223 C219:D220 F220 H216:H223 H215:M215 H212:H214</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="467" operator="containsText" id="{569cf088-a36c-4a34-bb76-5a661725968b}">
+          <x14:cfRule type="containsText" priority="467" operator="containsText" id="{620004a4-3223-4a3d-bca1-91a82a010cd1}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J212)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21352,7 +21352,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="468" operator="containsText" id="{4745cc2a-7d67-49d3-90e8-37be69749acc}">
+          <x14:cfRule type="containsText" priority="468" operator="containsText" id="{723767b9-0477-4447-acac-ba24472d9af1}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J212)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21370,7 +21370,7 @@
           <xm:sqref>M212 M217 J212:K212</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="461" operator="containsText" id="{525aa60f-6a04-4428-9c4b-5b6967babde7}">
+          <x14:cfRule type="containsText" priority="461" operator="containsText" id="{f49f7e32-ce5a-402d-ba59-7d0f4ab07b70}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A224)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21385,7 +21385,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="462" operator="containsText" id="{022e0544-77d4-481a-a63e-4ce7e85fbf27}">
+          <x14:cfRule type="containsText" priority="462" operator="containsText" id="{f2140efc-0d61-4e63-9e1a-533c72a2bb2b}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A224)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21403,7 +21403,7 @@
           <xm:sqref>A224 H224 C224:F224</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="469" operator="containsText" id="{4597b861-0b24-4031-970d-72b321821480}">
+          <x14:cfRule type="containsText" priority="469" operator="containsText" id="{41b1ddaa-d6d1-44d8-946f-fbdf6189d9f2}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C225)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21418,7 +21418,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="470" operator="containsText" id="{5f458447-16d2-4485-b2e0-21093e332f7e}">
+          <x14:cfRule type="containsText" priority="470" operator="containsText" id="{c11b303e-5d87-4402-a0ad-88a98588dbe2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C225)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21436,7 +21436,7 @@
           <xm:sqref>C225:D225 F225 H225</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="411" operator="containsText" id="{35b8699f-49d4-4910-9c1d-5392bc460cf8}">
+          <x14:cfRule type="containsText" priority="411" operator="containsText" id="{39e28922-d33e-4b98-bc60-adac1c110467}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21451,7 +21451,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="412" operator="containsText" id="{fc6909f5-65aa-4dcf-9767-73d045cdd51e}">
+          <x14:cfRule type="containsText" priority="412" operator="containsText" id="{15c10570-f392-4918-8ece-6688a343f2bc}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21469,7 +21469,7 @@
           <xm:sqref>A226:A237 A239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="413" operator="containsText" id="{c2647412-0db5-40b5-b53c-68c2bae49a1e}">
+          <x14:cfRule type="containsText" priority="413" operator="containsText" id="{d91d8285-5f12-4a8c-8e1d-fd78ff3c619b}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21484,7 +21484,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="414" operator="containsText" id="{7b3c2aef-74b6-4dd3-a6ac-1235b240e742}">
+          <x14:cfRule type="containsText" priority="414" operator="containsText" id="{eec9c68e-5aac-4e24-aa5c-b38357dbe40d}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21502,7 +21502,7 @@
           <xm:sqref>E226:F226 J237 M237 J232:M236 J231 J238:M239 C227:F233 C235:F236 C234:D234 F234 C237:D237 J228:M230 H226:H237</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="415" operator="containsText" id="{6549dec5-0d4f-4a11-9dd0-a3bd5aafae19}">
+          <x14:cfRule type="containsText" priority="415" operator="containsText" id="{9d41a017-cd88-4de2-b9c3-afa87c5da20f}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J226)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21517,7 +21517,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="416" operator="containsText" id="{91364cb4-f835-4637-9d3f-656043bc15a4}">
+          <x14:cfRule type="containsText" priority="416" operator="containsText" id="{49f443b2-8cdc-450a-b106-06205d7f95bf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J226)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21535,7 +21535,7 @@
           <xm:sqref>M226 M231 J226:K226</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="409" operator="containsText" id="{aef664ec-8041-4425-b235-6e68153663a0}">
+          <x14:cfRule type="containsText" priority="409" operator="containsText" id="{2650f644-1281-47f9-ac0f-ae57f3e85082}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A238)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21550,7 +21550,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="410" operator="containsText" id="{e2d776a6-c2bd-4dbf-be4f-13cf75120af5}">
+          <x14:cfRule type="containsText" priority="410" operator="containsText" id="{11e83114-0aa3-4251-b116-f10cbc6d5418}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A238)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21568,7 +21568,7 @@
           <xm:sqref>A238 H238 C238:F238</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="417" operator="containsText" id="{edf73d65-13cf-402a-9ae6-40c3d1d27789}">
+          <x14:cfRule type="containsText" priority="417" operator="containsText" id="{7697e808-e1ce-4d1b-8b9b-1603010a2535}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C239)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21583,7 +21583,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="418" operator="containsText" id="{727a91ec-a7ce-48a2-bb06-df22e02c753d}">
+          <x14:cfRule type="containsText" priority="418" operator="containsText" id="{3681949a-fcc4-4436-933b-50c9b88765bd}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C239)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21601,7 +21601,7 @@
           <xm:sqref>C239:D239 F239 H239</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="353" operator="containsText" id="{a932dcac-9a18-4502-92e3-1c0797c5706b}">
+          <x14:cfRule type="containsText" priority="353" operator="containsText" id="{bd8e5d75-ae7a-4a36-bfd7-3efb2a8a2422}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21616,7 +21616,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="354" operator="containsText" id="{4b0e0466-e46d-4b2d-bfd7-6f11d975db25}">
+          <x14:cfRule type="containsText" priority="354" operator="containsText" id="{c3e0e426-a94c-4bb7-808f-57abedcc68c2}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21634,7 +21634,7 @@
           <xm:sqref>A240:A251 A253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="355" operator="containsText" id="{cc0141c9-70a6-4022-8e13-8126b4101772}">
+          <x14:cfRule type="containsText" priority="355" operator="containsText" id="{8e835668-8f7f-4d48-b23c-c54d24c06a37}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21649,7 +21649,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="356" operator="containsText" id="{f797b493-93e7-4599-9ac5-fcc534edb881}">
+          <x14:cfRule type="containsText" priority="356" operator="containsText" id="{992eb45d-69b2-47e6-97de-5333383ed80c}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21667,7 +21667,7 @@
           <xm:sqref>E240:F240 J251 M251 J246:M250 J245 J252:M253 C241:F246 C249:F250 C251:D251 J242:M244 C247:D248 F248 H240:H251</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="357" operator="containsText" id="{27a69071-0435-4343-ae77-52eb427ba2f4}">
+          <x14:cfRule type="containsText" priority="357" operator="containsText" id="{b30bc944-e915-4ad3-9b39-94d663d49e2d}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J240)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21682,7 +21682,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="358" operator="containsText" id="{228e54a5-dd18-4038-b296-7b6f415017fa}">
+          <x14:cfRule type="containsText" priority="358" operator="containsText" id="{d1104064-6976-417c-be02-bb4f18924faf}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J240)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21700,7 +21700,7 @@
           <xm:sqref>M240 M245 J240:K240 K245</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="351" operator="containsText" id="{10d38ff1-6df5-45e6-8729-b3950ef5216f}">
+          <x14:cfRule type="containsText" priority="351" operator="containsText" id="{f82482a2-5af0-4116-a759-10ebe2af21d8}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A252)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21715,7 +21715,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="352" operator="containsText" id="{9bee7cf6-a961-47db-b409-1f10e78e63aa}">
+          <x14:cfRule type="containsText" priority="352" operator="containsText" id="{cd9f4f6a-ace6-4d1a-8324-bd80ec2f28eb}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A252)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21733,7 +21733,7 @@
           <xm:sqref>A252 H252 C252:F252</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="359" operator="containsText" id="{0e1e505d-dfe3-47cf-b68b-5710656d298e}">
+          <x14:cfRule type="containsText" priority="359" operator="containsText" id="{297225b3-7c28-4f74-9269-e976382781f5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C253)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21748,7 +21748,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="360" operator="containsText" id="{982ee74a-d696-4cd8-9984-db64b9738720}">
+          <x14:cfRule type="containsText" priority="360" operator="containsText" id="{469f342e-485c-4cbf-b6d6-7c4238181911}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C253)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21766,7 +21766,7 @@
           <xm:sqref>C253:D253 F253 H253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="295" operator="containsText" id="{d51701bf-3a3f-46d3-9bc5-a32e5df2c0ef}">
+          <x14:cfRule type="containsText" priority="295" operator="containsText" id="{4d740311-64fa-4667-b735-4c32b6a8554c}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21781,7 +21781,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="296" operator="containsText" id="{20901ab3-c327-499c-ab2b-9464eab8b1be}">
+          <x14:cfRule type="containsText" priority="296" operator="containsText" id="{2ca4f064-2c9c-40d2-8bce-729c18ca9830}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21799,7 +21799,7 @@
           <xm:sqref>A254:A265 A267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="297" operator="containsText" id="{98c92527-e369-4218-9aff-445ddfae8070}">
+          <x14:cfRule type="containsText" priority="297" operator="containsText" id="{9e17f703-8470-404a-bf57-4a7ce95eba65}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21814,7 +21814,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="298" operator="containsText" id="{559823e9-2422-4927-92a5-05d837eac5cb}">
+          <x14:cfRule type="containsText" priority="298" operator="containsText" id="{eb13c0c5-8ec7-4dee-8c15-1e7323669696}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21832,7 +21832,7 @@
           <xm:sqref>E254:F254 J260:M263 J259 J266:M266 C255:F261 C264:F264 C265:D265 J256:M258 J264:J265 M264:M265 C262:D263 F262 H254:H265 K267:M267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="299" operator="containsText" id="{4618fce3-c85c-4cc8-b450-5c406e6a4d7c}">
+          <x14:cfRule type="containsText" priority="299" operator="containsText" id="{152dadc0-0a9f-4848-ba04-af092ac6574a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,J254)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21847,7 +21847,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="300" operator="containsText" id="{755bbfe2-6d97-41f0-9923-b2d3a0546b67}">
+          <x14:cfRule type="containsText" priority="300" operator="containsText" id="{59fac83c-e597-46d8-8292-8a7f62d33121}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,J254)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21865,7 +21865,7 @@
           <xm:sqref>M254 M259 J254:K254 K259</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="293" operator="containsText" id="{2eb893d5-dd07-4696-84c1-31d15b7e66c8}">
+          <x14:cfRule type="containsText" priority="293" operator="containsText" id="{7a4852dd-1626-4a5b-abf4-7383789e4eaa}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A266)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21880,7 +21880,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="294" operator="containsText" id="{e77ead4f-ea18-47b5-939f-7f67fe4e0b10}">
+          <x14:cfRule type="containsText" priority="294" operator="containsText" id="{7f803495-9f36-4809-b5cb-3ebe7e289387}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A266)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21898,7 +21898,7 @@
           <xm:sqref>A266 H266 C266:F266</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="301" operator="containsText" id="{5a721dc9-f646-4b69-8b26-e5a109509d6c}">
+          <x14:cfRule type="containsText" priority="301" operator="containsText" id="{a71f9dd6-3138-4d85-aa46-d9d06bb43ed3}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,C267)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21913,7 +21913,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="302" operator="containsText" id="{3dc3f04d-9cbf-40ac-988b-06d7460ca89d}">
+          <x14:cfRule type="containsText" priority="302" operator="containsText" id="{4ace3e65-6ace-4a43-a41c-520014442b35}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,C267)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21931,7 +21931,7 @@
           <xm:sqref>C267:D267 F267 H267</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="66" operator="containsText" id="{0147f190-a361-431f-8b2a-65f08155c3c2}">
+          <x14:cfRule type="containsText" priority="66" operator="containsText" id="{a2fd18e2-9f82-4fbb-a3c3-5fc0439f44d0}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,A268)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>
@@ -21946,7 +21946,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="65" operator="containsText" id="{d342d11c-7f8d-4a8f-8423-bb562b8106c3}">
+          <x14:cfRule type="containsText" priority="65" operator="containsText" id="{d03ecee4-01e7-434a-aaf9-add717fc93d5}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,A268)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21964,7 +21964,7 @@
           <xm:sqref>A268:A279 A281</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="59" operator="containsText" id="{cc6f8da2-ae95-4ca4-bca6-246f08dac93a}">
+          <x14:cfRule type="containsText" priority="59" operator="containsText" id="{80408eee-8167-4ca8-8011-194ef930cb1a}">
             <xm:f>NOT(ISERROR(SEARCH($A$15,E268)))</xm:f>
             <xm:f>$A$15</xm:f>
             <x14:dxf>
@@ -21979,7 +21979,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="60" operator="containsText" id="{ae02f434-d775-42bb-a158-ac7991109d6d}">
+          <x14:cfRule type="containsText" priority="60" operator="containsText" id="{01b67697-6461-44b1-8029-a5035f08b937}">
             <xm:f>NOT(ISERROR(SEARCH($A$2,E268)))</xm:f>
             <xm:f>$A$2</xm:f>
             <x14:dxf>

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -9965,7 +9965,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>625928</xdr:colOff>
+      <xdr:colOff>625929</xdr:colOff>
       <xdr:row>237</xdr:row>
       <xdr:rowOff>1782913</xdr:rowOff>
     </xdr:to>
@@ -10298,8 +10298,8 @@
   <cols>
     <col min="1" max="1" width="53.42578125" style="8" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="53.85546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" style="8" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="53.85546875" style="8" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="28.85546875" style="8" customWidth="1"/>
     <col min="6" max="6" width="41.42578125" style="8" customWidth="1"/>
     <col min="7" max="7" width="43.85546875" style="9" customWidth="1"/>
@@ -17078,12 +17078,18 @@
       <c r="E269" s="57"/>
       <c r="F269" s="74"/>
       <c r="G269" s="57">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H269" s="74"/>
-      <c r="I269" s="74"/>
-      <c r="J269" s="63" t="s">
-        <v>502</v>
+      <c r="I269" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 8 códigos del tramo Loja - Catamayo. Las 21 limpiadas de julio ya superan los códigos del tramo (13 sin código en la fila del 07/07), por eso 0 adicionales. Km ya cubiertos en julio.</t>
+        </is>
+      </c>
+      <c r="J269" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3861, 3876, 3965, 3994, 3996, 4036, 4095, 4252</t>
+        </is>
       </c>
       <c r="K269" s="18" t="s">
         <v>302</v>
@@ -17101,19 +17107,29 @@
       </c>
       <c r="C270" s="74"/>
       <c r="D270" s="74"/>
-      <c r="E270" s="57" t="s">
-        <v>171</v>
-      </c>
-      <c r="F270" s="57" t="s">
-        <v>503</v>
+      <c r="E270" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13+256</t>
+        </is>
+      </c>
+      <c r="F270" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38+100</t>
+        </is>
       </c>
       <c r="G270" s="57">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H270" s="74"/>
-      <c r="I270" s="74"/>
-      <c r="J270" s="63" t="s">
-        <v>504</v>
+      <c r="I270" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 11 códigos del tramo Oña - Saraguro; total micro 25 alcantarillas (16 julio + 9 consolidado). Km nuevos 24.84 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 38.1 km). Se agregaron 4388, 4373 (del tramo, estaban en julio en otra micro).</t>
+        </is>
+      </c>
+      <c r="J270" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18, 341, 4324, 4340, 4368, 4517, 4565, 4638, 4710, 4388, 4373</t>
+        </is>
       </c>
       <c r="K270" s="18" t="s">
         <v>302</v>
@@ -17131,19 +17147,29 @@
       </c>
       <c r="C271" s="74"/>
       <c r="D271" s="74"/>
-      <c r="E271" s="57" t="s">
-        <v>484</v>
-      </c>
-      <c r="F271" s="57" t="s">
-        <v>505</v>
+      <c r="E271" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3+620</t>
+        </is>
+      </c>
+      <c r="F271" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28+300</t>
+        </is>
       </c>
       <c r="G271" s="57">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H271" s="74"/>
-      <c r="I271" s="74"/>
-      <c r="J271" s="63" t="s">
-        <v>506</v>
+      <c r="I271" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 54 códigos del tramo San Pedro de la Bendita - Velacruz; total micro 54 alcantarillas (1 julio + 53 consolidado). Km nuevos 24.68 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 28.3 km).</t>
+        </is>
+      </c>
+      <c r="J271" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7, 10, 3437, 3447, 3448, 3449, 3450, 3451, 3452, 3453, 3468, 3472, 3474, 3475, 3477, 3483, 3486, 3488, 3505, 3512, 3517, 3526, 3531, 3539, 3541, 3543, 3547, 3549, 3553, 3560, 3565, 3566, 3567, 3579, 3583, 3584, 3590, 3594, 3595, 3597, 3599, 3604, 3605, 3607, 3608, 3612, 3621, 3629, 3638, 3639, 3643, 3647, 3662, 3666</t>
+        </is>
       </c>
       <c r="K271" s="18" t="s">
         <v>302</v>
@@ -17161,15 +17187,29 @@
       </c>
       <c r="C272" s="74"/>
       <c r="D272" s="74"/>
-      <c r="E272" s="57" t="s">
-        <v>486</v>
-      </c>
-      <c r="F272" s="74"/>
-      <c r="G272" s="76"/>
+      <c r="E272" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10+500</t>
+        </is>
+      </c>
+      <c r="F272" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29+400</t>
+        </is>
+      </c>
+      <c r="G272" s="76">
+        <v>5</v>
+      </c>
       <c r="H272" s="74"/>
-      <c r="I272" s="74"/>
-      <c r="J272" s="63" t="s">
-        <v>507</v>
+      <c r="I272" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 7 códigos del tramo Catamayo - Gonzanamá; total micro 7 alcantarillas (2 julio + 5 consolidado). Km nuevos 18.90 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 29.4 km).</t>
+        </is>
+      </c>
+      <c r="J272" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3656, 3692, 3724, 3764, 3772, 3809, 3850</t>
+        </is>
       </c>
       <c r="K272" s="18" t="s">
         <v>302</v>
@@ -17187,17 +17227,21 @@
       </c>
       <c r="C273" s="74"/>
       <c r="D273" s="74"/>
-      <c r="E273" s="57" t="s">
-        <v>487</v>
-      </c>
+      <c r="E273" s="57"/>
       <c r="F273" s="74"/>
       <c r="G273" s="57">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H273" s="74"/>
-      <c r="I273" s="74"/>
-      <c r="J273" s="63" t="s">
-        <v>508</v>
+      <c r="I273" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 104 códigos del tramo Catacocha - El Empalme; total micro 104 alcantarillas (0 julio + 104 consolidado). Sin km adicionales: las filas de julio ya suman 34.7 km (tramo 32.9 km).</t>
+        </is>
+      </c>
+      <c r="J273" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1746, 1790, 1799, 1810, 1816, 1820, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1906, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2032, 2045, 2054, 2059, 2133, 2166, 2193, 2202, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2359, 2364, 2372, 2382, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2649, 2671, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
+        </is>
       </c>
       <c r="K273" s="18" t="s">
         <v>302</v>
@@ -17214,20 +17258,32 @@
         <v>46303</v>
       </c>
       <c r="C274" s="74"/>
-      <c r="D274" s="74"/>
-      <c r="E274" s="57" t="s">
-        <v>488</v>
-      </c>
-      <c r="F274" s="57" t="s">
-        <v>275</v>
+      <c r="D274" s="74">
+        <v>214</v>
+      </c>
+      <c r="E274" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24+414</t>
+        </is>
+      </c>
+      <c r="F274" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42+000</t>
+        </is>
       </c>
       <c r="G274" s="57">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="H274" s="74"/>
-      <c r="I274" s="74"/>
-      <c r="J274" s="63" t="s">
-        <v>509</v>
+      <c r="I274" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 138 códigos del tramo San Lucas - Loja; total micro 155 alcantarillas (21 julio + 134 consolidado). Km nuevos 17.59 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 42 km). Se quitaron 17 códigos repetidos con julio.</t>
+        </is>
+      </c>
+      <c r="J274" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3, 15, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3914, 3915, 3917, 3918, 3920, 3923, 3925, 3928, 3929, 3931, 3933, 3934, 3937, 3938, 3939, 3940, 3943, 3944, 3946, 3947, 3951, 3953, 3961, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4029, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4201, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4230, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
+        </is>
       </c>
       <c r="K274" s="18" t="s">
         <v>302</v>
@@ -17245,19 +17301,29 @@
       </c>
       <c r="C275" s="74"/>
       <c r="D275" s="74"/>
-      <c r="E275" s="55" t="s">
-        <v>229</v>
-      </c>
-      <c r="F275" s="57" t="s">
-        <v>183</v>
+      <c r="E275" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0+000</t>
+        </is>
+      </c>
+      <c r="F275" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5+000</t>
+        </is>
       </c>
       <c r="G275" s="57">
         <v>20</v>
       </c>
       <c r="H275" s="74"/>
-      <c r="I275" s="74"/>
-      <c r="J275" s="63" t="s">
-        <v>510</v>
+      <c r="I275" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 20 códigos del tramo Redondel de Carigán - Capulí; total micro 20 alcantarillas (0 julio + 20 consolidado).</t>
+        </is>
+      </c>
+      <c r="J275" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000, 10002, 10005, 10006, 10007, 10008, 10009, 10010, 10013, 10014, 10015, 10016, 10019, 10021, 10022, 10024, 10026, 10028, 10031, 10032</t>
+        </is>
       </c>
       <c r="K275" s="18" t="s">
         <v>302</v>
@@ -17275,15 +17341,29 @@
       </c>
       <c r="C276" s="74"/>
       <c r="D276" s="74"/>
-      <c r="E276" s="55"/>
-      <c r="F276" s="74"/>
+      <c r="E276" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0+000</t>
+        </is>
+      </c>
+      <c r="F276" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19+529</t>
+        </is>
+      </c>
       <c r="G276" s="57">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H276" s="74"/>
-      <c r="I276" s="74"/>
-      <c r="J276" s="63" t="s">
-        <v>511</v>
+      <c r="I276" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 76 códigos del tramo Loja - Vilcabamba; total micro 76 alcantarillas (0 julio + 76 consolidado). Km nuevos 19.53 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39.5 km).</t>
+        </is>
+      </c>
+      <c r="J276" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333, 335, 4238, 4240, 4255, 4269, 4272, 4274, 4276, 4283, 4289, 4290, 4295, 4298, 4302, 4303, 4311, 4312, 4316, 4327, 4330, 4336, 4341, 4345, 4350, 4352, 4353, 4370, 4375, 4387, 4393, 4394, 4395, 4400, 4406, 4421, 4422, 4433, 4435, 4436, 4437, 4440, 4443, 4444, 4449, 4454, 4456, 4458, 4459, 4460, 4461, 4464, 4466, 4467, 4471, 4474, 4478, 4481, 4484, 4487, 4491, 4492, 4498, 4508, 4510, 4522, 4524, 4531, 4533, 4536, 4540, 4544, 4545, 4548, 4549, 4552</t>
+        </is>
       </c>
       <c r="K276" s="18" t="s">
         <v>302</v>
@@ -17301,15 +17381,29 @@
       </c>
       <c r="C277" s="74"/>
       <c r="D277" s="74"/>
-      <c r="E277" s="57" t="s">
-        <v>490</v>
-      </c>
-      <c r="F277" s="74"/>
-      <c r="G277" s="76"/>
+      <c r="E277" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7+320</t>
+        </is>
+      </c>
+      <c r="F277" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21+400</t>
+        </is>
+      </c>
+      <c r="G277" s="76">
+        <v>39</v>
+      </c>
       <c r="H277" s="74"/>
-      <c r="I277" s="74"/>
-      <c r="J277" s="63" t="s">
-        <v>512</v>
+      <c r="I277" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 39 códigos del tramo Célica - El Empalme; total micro 39 alcantarillas (0 julio + 39 consolidado). Km nuevos 14.08 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 21.4 km). Se agregaron 1660 (del tramo, estaban en julio en otra micro).</t>
+        </is>
+      </c>
+      <c r="J277" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1245, 1262, 1268, 1289, 1290, 1296, 1297, 1304, 1307, 1314, 1325, 1332, 1342, 1377, 1392, 1393, 1397, 1404, 1405, 1407, 1408, 1413, 1416, 1423, 1424, 1427, 1436, 1440, 1456, 1466, 1472, 1496, 1499, 1526, 1532, 1537, 1553, 1632, 1660</t>
+        </is>
       </c>
       <c r="K277" s="18" t="s">
         <v>302</v>
@@ -17327,15 +17421,21 @@
       </c>
       <c r="C278" s="74"/>
       <c r="D278" s="74"/>
-      <c r="E278" s="55" t="s">
-        <v>492</v>
-      </c>
+      <c r="E278" s="55"/>
       <c r="F278" s="74"/>
-      <c r="G278" s="76"/>
+      <c r="G278" s="76">
+        <v>19</v>
+      </c>
       <c r="H278" s="74"/>
-      <c r="I278" s="74"/>
-      <c r="J278" s="63" t="s">
-        <v>513</v>
+      <c r="I278" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 19 códigos del tramo Cariamanga - Sozoranga; total micro 19 alcantarillas (0 julio + 19 consolidado). Sin km adicionales: las filas de julio ya suman 43.49 km (tramo 46.3 km).</t>
+        </is>
+      </c>
+      <c r="J278" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2186, 2194, 2198, 2212, 2219, 2225, 2241, 2244, 2417, 2450, 2462, 2536, 2758, 2797, 2803, 2813, 2934, 3416, 3428</t>
+        </is>
       </c>
       <c r="K278" s="18" t="s">
         <v>302</v>
@@ -17353,13 +17453,29 @@
       </c>
       <c r="C279" s="74"/>
       <c r="D279" s="74"/>
-      <c r="E279" s="57"/>
-      <c r="F279" s="74"/>
-      <c r="G279" s="76"/>
+      <c r="E279" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7+000</t>
+        </is>
+      </c>
+      <c r="F279" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21+000</t>
+        </is>
+      </c>
+      <c r="G279" s="76">
+        <v>12</v>
+      </c>
       <c r="H279" s="74"/>
-      <c r="I279" s="74"/>
-      <c r="J279" s="63" t="s">
-        <v>514</v>
+      <c r="I279" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 18 códigos del tramo El Empalme - Macará; total micro 19 alcantarillas (7 julio + 12 consolidado). Km nuevos 14.00 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39.6 km).</t>
+        </is>
+      </c>
+      <c r="J279" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271, 1273, 1276, 1279, 1280, 1339, 1362, 1363, 1371, 1420, 1449, 1479, 1560, 1598, 1603, 1606, 1611, 1625</t>
+        </is>
       </c>
       <c r="K279" s="18" t="s">
         <v>302</v>
@@ -17377,19 +17493,23 @@
       </c>
       <c r="C280" s="74"/>
       <c r="D280" s="74"/>
-      <c r="E280" s="55" t="s">
-        <v>496</v>
-      </c>
-      <c r="F280" s="57" t="s">
-        <v>515</v>
-      </c>
+      <c r="E280" s="55"/>
+      <c r="F280" s="57"/>
       <c r="G280" s="57">
-        <v>92</v>
-      </c>
-      <c r="H280" s="74"/>
-      <c r="I280" s="74"/>
-      <c r="J280" s="63" t="s">
-        <v>516</v>
+        <v>58</v>
+      </c>
+      <c r="H280" s="74">
+        <v>32.2</v>
+      </c>
+      <c r="I280" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 69 códigos del tramo Río Pindo - Chaguarpamba; total micro 104 alcantarillas (46 julio + 58 consolidado). Sin km adicionales: las filas de julio ya suman 64.05 km (tramo 32.2 km). Se quitaron 35 códigos repetidos con julio.</t>
+        </is>
+      </c>
+      <c r="J280" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288, 2173, 2181, 2206, 2215, 2276, 2281, 2288, 2305, 2317, 2332, 2354, 2355, 2361, 2367, 2368, 2385, 2389, 2395, 2408, 2428, 2440, 2445, 2446, 2452, 2468, 2469, 2475, 2479, 2484, 2495, 2577, 2578, 2605, 2615, 2617, 2628, 2636, 2640, 2647, 2651, 2653, 2654, 2657, 2661, 2665, 2676, 2677, 2692, 2701, 2714, 2745, 2755, 2764, 2772, 2835, 2850, 2870, 2894, 2898, 2941, 3015, 3031, 3064, 3081, 3097, 3104, 3108, 3112</t>
+        </is>
       </c>
       <c r="K280" s="18" t="s">
         <v>302</v>
@@ -17407,13 +17527,31 @@
       </c>
       <c r="C281" s="74"/>
       <c r="D281" s="74"/>
-      <c r="E281" s="18"/>
-      <c r="F281" s="74"/>
-      <c r="G281" s="76"/>
-      <c r="H281" s="74"/>
-      <c r="I281" s="74"/>
-      <c r="J281" s="63" t="s">
-        <v>517</v>
+      <c r="E281" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2+000</t>
+        </is>
+      </c>
+      <c r="F281" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9+000</t>
+        </is>
+      </c>
+      <c r="G281" s="76">
+        <v>10</v>
+      </c>
+      <c r="H281" s="74">
+        <v>33.2</v>
+      </c>
+      <c r="I281" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 11 códigos del tramo Sozoranga - Macará; total micro 11 alcantarillas (1 julio + 10 consolidado). Km nuevos 7.00 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 33.2 km).</t>
+        </is>
+      </c>
+      <c r="J281" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1394, 1845, 2042, 2047, 2052, 2060, 2063, 2087, 2112, 2113, 2144</t>
+        </is>
       </c>
       <c r="K281" s="18" t="s">
         <v>302</v>
@@ -17431,15 +17569,23 @@
       </c>
       <c r="C282" s="74"/>
       <c r="D282" s="74"/>
-      <c r="E282" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="F282" s="74" t="s">
-        <v>521</v>
+      <c r="E282" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0+000</t>
+        </is>
+      </c>
+      <c r="F282" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10+100</t>
+        </is>
       </c>
       <c r="G282" s="76"/>
       <c r="H282" s="74"/>
-      <c r="I282" s="74"/>
+      <c r="I282" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: sin códigos de alcantarillas registrados para el tramo; se conservan las abscisas del usuario.</t>
+        </is>
+      </c>
       <c r="J282" s="63"/>
       <c r="K282" s="18"/>
       <c r="L282" s="74"/>
@@ -17455,19 +17601,29 @@
       </c>
       <c r="C283" s="74"/>
       <c r="D283" s="74"/>
-      <c r="E283" s="57" t="s">
-        <v>501</v>
-      </c>
-      <c r="F283" s="74" t="s">
-        <v>518</v>
+      <c r="E283" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20+930</t>
+        </is>
+      </c>
+      <c r="F283" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39+000</t>
+        </is>
       </c>
       <c r="G283" s="57">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="H283" s="74"/>
-      <c r="I283" s="74"/>
-      <c r="J283" s="63" t="s">
-        <v>519</v>
+      <c r="I283" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidado 08/10: 107 códigos del tramo Y de Alamor - Pindal - Zapotillo; total micro 107 alcantarillas (44 julio + 63 consolidado). Km nuevos 18.07 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39 km).</t>
+        </is>
+      </c>
+      <c r="J283" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80, 105, 522, 569, 571, 575, 577, 578, 579, 580, 581, 583, 584, 586, 590, 593, 595, 596, 600, 601, 602, 603, 604, 605, 606, 610, 614, 615, 616, 617, 618, 623, 625, 628, 632, 633, 634, 636, 639, 640, 642, 643, 644, 645, 646, 647, 648, 649, 650, 653, 654, 656, 660, 661, 664, 666, 670, 671, 673, 675, 677, 680, 682, 683, 686, 687, 690, 696, 705, 707, 711, 721, 729, 730, 731, 732, 745, 755, 758, 760, 761, 770, 772, 777, 779, 782, 784, 791, 803, 807, 813, 816, 821, 824, 837, 839, 861, 863, 864, 867, 868, 879, 882, 903, 943, 944, 949</t>
+        </is>
       </c>
       <c r="K283" s="18" t="s">
         <v>302</v>

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="547">
   <si>
     <t>MICROEMPRESA</t>
   </si>
@@ -1575,18 +1575,6 @@
     <t>30+900</t>
   </si>
   <si>
-    <t>3861, 3876, 3965, 3994, 3996, 4036, 4095, 4252</t>
-  </si>
-  <si>
-    <t>40+000</t>
-  </si>
-  <si>
-    <t>18, 341, 4324, 4340, 4368, 4517, 4565, 4638, 4710</t>
-  </si>
-  <si>
-    <t>118+340</t>
-  </si>
-  <si>
     <t>7, 10, 3437, 3447, 3448, 3449, 3450, 3451, 3452, 3453, 3468, 3472, 3474, 3475, 3477, 3483, 3486, 3488, 3505, 3512, 3517, 3526, 3531, 3539, 3541, 3543, 3547, 3549, 3553, 3560, 3565, 3566, 3567, 3579, 3583, 3584, 3590, 3594, 3595, 3597, 3599, 3604, 3605, 3607, 3608, 3612, 3621, 3629, 3638, 3639, 3643, 3647, 3662, 3666</t>
   </si>
   <si>
@@ -1596,36 +1584,21 @@
     <t>1746, 1790, 1799, 1810, 1816, 1820, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1906, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2032, 2045, 2054, 2059, 2133, 2166, 2193, 2202, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2359, 2364, 2372, 2382, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2649, 2671, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
   </si>
   <si>
-    <t>3, 4, 15, 304, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3912, 3914, 3915, 3916, 3917, 3918, 3920, 3922, 3923, 3924, 3925, 3926, 3928, 3929, 3931, 3932, 3933, 3934, 3936, 3937, 3938, 3939, 3940, 3943, 3944, 3945, 3946, 3947, 3948, 3951, 3952, 3953, 3954, 3958, 3961, 3962, 3963, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4013, 4029, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4201, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4230, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
-  </si>
-  <si>
     <t>1000, 10002, 10005, 10006, 10007, 10008, 10009, 10010, 10013, 10014, 10015, 10016, 10019, 10021, 10022, 10024, 10026, 10028, 10031, 10032</t>
   </si>
   <si>
     <t>333, 335, 4238, 4240, 4255, 4269, 4272, 4274, 4276, 4283, 4289, 4290, 4295, 4298, 4302, 4303, 4311, 4312, 4316, 4327, 4330, 4336, 4341, 4345, 4350, 4352, 4353, 4370, 4375, 4387, 4393, 4394, 4395, 4400, 4406, 4421, 4422, 4433, 4435, 4436, 4437, 4440, 4443, 4444, 4449, 4454, 4456, 4458, 4459, 4460, 4461, 4464, 4466, 4467, 4471, 4474, 4478, 4481, 4484, 4487, 4491, 4492, 4498, 4508, 4510, 4522, 4524, 4531, 4533, 4536, 4540, 4544, 4545, 4548, 4549, 4552</t>
   </si>
   <si>
-    <t>1245, 1262, 1268, 1289, 1290, 1296, 1297, 1304, 1307, 1314, 1325, 1332, 1342, 1377, 1392, 1393, 1397, 1404, 1405, 1407, 1408, 1413, 1416, 1423, 1424, 1427, 1436, 1440, 1456, 1466, 1472, 1496, 1499, 1526, 1532, 1537, 1553, 1632</t>
-  </si>
-  <si>
     <t>2186, 2194, 2198, 2212, 2219, 2225, 2241, 2244, 2417, 2450, 2462, 2536, 2758, 2797, 2803, 2813, 2934, 3416, 3428</t>
   </si>
   <si>
     <t>1271, 1273, 1276, 1279, 1280, 1339, 1362, 1363, 1371, 1420, 1449, 1479, 1560, 1598, 1603, 1606, 1611, 1625</t>
   </si>
   <si>
-    <t>35+000</t>
-  </si>
-  <si>
-    <t>288, 2173, 2181, 2206, 2215, 2276, 2281, 2288, 2305, 2317, 2332, 2354, 2355, 2361, 2367, 2368, 2385, 2389, 2395, 2408, 2428, 2440, 2445, 2446, 2452, 2468, 2469, 2475, 2479, 2484, 2495, 2577, 2578, 2590, 2597, 2605, 2615, 2617, 2628, 2636, 2640, 2647, 2651, 2653, 2654, 2657, 2661, 2665, 2676, 2677, 2692, 2701, 2714, 2733, 2745, 2751, 2753, 2755, 2759, 2764, 2766, 2771, 2772, 2780, 2784, 2791, 2798, 2806, 2811, 2819, 2835, 2838, 2846, 2850, 2852, 2857, 2861, 2866, 2870, 2872, 2876, 2880, 2883, 2887, 2889, 2890, 2894, 2898, 2916, 2941, 2951, 2966, 2972, 2993, 3015, 3031, 3035, 3044, 3064, 3081, 3097, 3104, 3108, 3112</t>
-  </si>
-  <si>
     <t>1394, 1845, 2042, 2047, 2052, 2060, 2063, 2087, 2112, 2113, 2144</t>
   </si>
   <si>
-    <t>48+000</t>
-  </si>
-  <si>
     <t>80, 105, 522, 569, 571, 575, 577, 578, 579, 580, 581, 583, 584, 586, 590, 593, 595, 596, 600, 601, 602, 603, 604, 605, 606, 610, 614, 615, 616, 617, 618, 623, 625, 628, 632, 633, 634, 636, 639, 640, 642, 643, 644, 645, 646, 647, 648, 649, 650, 653, 654, 656, 660, 661, 664, 666, 670, 671, 673, 675, 677, 680, 682, 683, 686, 687, 690, 696, 705, 707, 711, 721, 729, 730, 731, 732, 745, 755, 758, 760, 761, 770, 772, 777, 779, 782, 784, 791, 803, 807, 813, 816, 821, 824, 837, 839, 861, 863, 864, 867, 868, 879, 882, 903, 943, 944, 949</t>
   </si>
   <si>
@@ -1636,6 +1609,105 @@
   </si>
   <si>
     <t>Vilcabamba - Yangana - Limite Provincial Loja/ Zamora Chinchipe</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 21 códigos del tramo Loja - Catamayo (8 registrados + 13 agregados en la auditoría de fotos del 18/10, ubicados por la marca de agua de las fotos del grupo). Coincide con las 21 limpiadas de julio, por eso 0 adicionales. Km ya cubiertos en julio.</t>
+  </si>
+  <si>
+    <t>3861, 3876, 3965, 3994, 3996, 4036, 4095, 4252, 3864, 3866, 3867, 3868, 3869, 3870, 3871, 3877, 3881, 3882, 3883, 3885, 3886</t>
+  </si>
+  <si>
+    <t>13+256</t>
+  </si>
+  <si>
+    <t>38+100</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 11 códigos del tramo Oña - Saraguro; total micro 25 alcantarillas (16 julio + 9 consolidado). Km nuevos 24.84 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 38.1 km). Se agregaron 4388, 4373 (del tramo, estaban en julio en otra micro).</t>
+  </si>
+  <si>
+    <t>18, 341, 4324, 4340, 4368, 4517, 4565, 4638, 4710, 4388, 4373</t>
+  </si>
+  <si>
+    <t>3+620</t>
+  </si>
+  <si>
+    <t>28+300</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 54 códigos del tramo San Pedro de la Bendita - Velacruz; total micro 54 alcantarillas (1 julio + 53 consolidado). Km nuevos 24.68 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 28.3 km).</t>
+  </si>
+  <si>
+    <t>29+400</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 7 códigos del tramo Catamayo - Gonzanamá; total micro 7 alcantarillas (2 julio + 5 consolidado). Km nuevos 18.90 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 29.4 km).</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 104 códigos del tramo Catacocha - El Empalme; total micro 104 alcantarillas (0 julio + 104 consolidado). Sin km adicionales: las filas de julio ya suman 34.7 km (tramo 32.9 km).</t>
+  </si>
+  <si>
+    <t>24+414</t>
+  </si>
+  <si>
+    <t>42+000</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 138 códigos del tramo San Lucas - Loja; total micro 155 alcantarillas (21 julio + 134 consolidado). Km nuevos 17.59 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 42 km). Se quitaron 17 códigos repetidos con julio.</t>
+  </si>
+  <si>
+    <t>3, 15, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3914, 3915, 3917, 3918, 3920, 3923, 3925, 3928, 3929, 3931, 3933, 3934, 3937, 3938, 3939, 3940, 3943, 3944, 3946, 3947, 3951, 3953, 3961, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4029, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4201, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4230, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 20 códigos del tramo Redondel de Carigán - Capulí; total micro 20 alcantarillas (0 julio + 20 consolidado).</t>
+  </si>
+  <si>
+    <t>19+529</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 76 códigos del tramo Loja - Vilcabamba; total micro 76 alcantarillas (0 julio + 76 consolidado). Km nuevos 19.53 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39.5 km).</t>
+  </si>
+  <si>
+    <t>7+320</t>
+  </si>
+  <si>
+    <t>21+400</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 39 códigos del tramo Célica - El Empalme; total micro 39 alcantarillas (0 julio + 39 consolidado). Km nuevos 14.08 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 21.4 km). Se agregaron 1660 (del tramo, estaban en julio en otra micro).</t>
+  </si>
+  <si>
+    <t>1245, 1262, 1268, 1289, 1290, 1296, 1297, 1304, 1307, 1314, 1325, 1332, 1342, 1377, 1392, 1393, 1397, 1404, 1405, 1407, 1408, 1413, 1416, 1423, 1424, 1427, 1436, 1440, 1456, 1466, 1472, 1496, 1499, 1526, 1532, 1537, 1553, 1632, 1660</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 19 códigos del tramo Cariamanga - Sozoranga; total micro 19 alcantarillas (0 julio + 19 consolidado). Sin km adicionales: las filas de julio ya suman 43.49 km (tramo 46.3 km).</t>
+  </si>
+  <si>
+    <t>7+000</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 18 códigos del tramo El Empalme - Macará; total micro 19 alcantarillas (7 julio + 12 consolidado). Km nuevos 14.00 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39.6 km).</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 69 códigos del tramo Río Pindo - Chaguarpamba; total micro 104 alcantarillas (46 julio + 58 consolidado). Sin km adicionales: las filas de julio ya suman 64.05 km (tramo 32.2 km). Se quitaron 35 códigos repetidos con julio.</t>
+  </si>
+  <si>
+    <t>288, 2173, 2181, 2206, 2215, 2276, 2281, 2288, 2305, 2317, 2332, 2354, 2355, 2361, 2367, 2368, 2385, 2389, 2395, 2408, 2428, 2440, 2445, 2446, 2452, 2468, 2469, 2475, 2479, 2484, 2495, 2577, 2578, 2605, 2615, 2617, 2628, 2636, 2640, 2647, 2651, 2653, 2654, 2657, 2661, 2665, 2676, 2677, 2692, 2701, 2714, 2745, 2755, 2764, 2772, 2835, 2850, 2870, 2894, 2898, 2941, 3015, 3031, 3064, 3081, 3097, 3104, 3108, 3112</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 11 códigos del tramo Sozoranga - Macará; total micro 11 alcantarillas (1 julio + 10 consolidado). Km nuevos 7.00 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 33.2 km).</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: sin códigos de alcantarillas registrados para el tramo; se conservan las abscisas del usuario.</t>
+  </si>
+  <si>
+    <t>20+930</t>
+  </si>
+  <si>
+    <t>39+000</t>
+  </si>
+  <si>
+    <t>Consolidado 08/10: 107 códigos del tramo Y de Alamor - Pindal - Zapotillo; total micro 107 alcantarillas (44 julio + 63 consolidado). Km nuevos 18.07 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39 km).</t>
   </si>
 </sst>
 </file>
@@ -1814,7 +1886,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1969,17 +2041,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2019,6 +2085,42 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10304,7 +10406,7 @@
     <col min="6" max="6" width="41.42578125" style="8" customWidth="1"/>
     <col min="7" max="7" width="43.85546875" style="9" customWidth="1"/>
     <col min="8" max="8" width="27.7109375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="75" style="10" customWidth="1"/>
+    <col min="9" max="9" width="75" style="87" customWidth="1"/>
     <col min="10" max="10" width="46.7109375" style="10" customWidth="1"/>
     <col min="11" max="11" width="36.7109375" style="10" customWidth="1"/>
     <col min="12" max="12" width="37.85546875" style="10" customWidth="1"/>
@@ -10337,7 +10439,7 @@
       <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="78" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -10376,7 +10478,7 @@
       <c r="H2" s="18">
         <v>35.299999999999997</v>
       </c>
-      <c r="I2" s="20"/>
+      <c r="I2" s="79"/>
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
       <c r="L2" s="21"/>
@@ -10452,7 +10554,7 @@
       <c r="H4" s="18">
         <v>28.3</v>
       </c>
-      <c r="I4" s="20"/>
+      <c r="I4" s="79"/>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
@@ -10485,7 +10587,7 @@
       <c r="H5" s="18">
         <v>29.4</v>
       </c>
-      <c r="I5" s="20"/>
+      <c r="I5" s="79"/>
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
       <c r="L5" s="21"/>
@@ -10518,7 +10620,7 @@
       <c r="H6" s="18">
         <v>32.9</v>
       </c>
-      <c r="I6" s="20"/>
+      <c r="I6" s="79"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20"/>
       <c r="L6" s="21"/>
@@ -10551,7 +10653,7 @@
       <c r="H7" s="18">
         <v>42</v>
       </c>
-      <c r="I7" s="20"/>
+      <c r="I7" s="79"/>
       <c r="J7" s="20"/>
       <c r="K7" s="20"/>
       <c r="L7" s="17"/>
@@ -10584,7 +10686,7 @@
       <c r="H8" s="18">
         <v>14.9</v>
       </c>
-      <c r="I8" s="20"/>
+      <c r="I8" s="79"/>
       <c r="J8" s="20"/>
       <c r="K8" s="20"/>
       <c r="L8" s="21"/>
@@ -10613,7 +10715,7 @@
       <c r="H9" s="18">
         <v>39.5</v>
       </c>
-      <c r="I9" s="20"/>
+      <c r="I9" s="79"/>
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
       <c r="L9" s="21"/>
@@ -10646,7 +10748,7 @@
       <c r="H10" s="18">
         <v>21.4</v>
       </c>
-      <c r="I10" s="20"/>
+      <c r="I10" s="79"/>
       <c r="J10" s="20"/>
       <c r="K10" s="20"/>
       <c r="L10" s="21"/>
@@ -10679,7 +10781,7 @@
       <c r="H11" s="18">
         <v>46.3</v>
       </c>
-      <c r="I11" s="20"/>
+      <c r="I11" s="79"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
       <c r="L11" s="21"/>
@@ -10708,7 +10810,7 @@
       <c r="H12" s="18">
         <v>39.6</v>
       </c>
-      <c r="I12" s="20"/>
+      <c r="I12" s="79"/>
       <c r="J12" s="20"/>
       <c r="K12" s="20"/>
       <c r="L12" s="21"/>
@@ -10737,7 +10839,7 @@
       <c r="H13" s="18">
         <v>148</v>
       </c>
-      <c r="I13" s="20"/>
+      <c r="I13" s="79"/>
       <c r="J13" s="20"/>
       <c r="K13" s="20"/>
       <c r="L13" s="21"/>
@@ -10764,7 +10866,7 @@
       <c r="F14" s="18"/>
       <c r="G14" s="19"/>
       <c r="H14" s="18"/>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="24" t="s">
         <v>59</v>
       </c>
       <c r="J14" s="20"/>
@@ -10778,13 +10880,13 @@
     </row>
     <row r="15" spans="1:17" s="1" customFormat="1" ht="33" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="B15" s="15">
         <v>46210</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D15" s="17">
         <v>205</v>
@@ -10795,7 +10897,7 @@
       <c r="H15" s="18">
         <v>40</v>
       </c>
-      <c r="I15" s="18"/>
+      <c r="I15" s="24"/>
       <c r="J15" s="20"/>
       <c r="K15" s="20"/>
       <c r="L15" s="21"/>
@@ -10828,7 +10930,7 @@
       <c r="H16" s="18">
         <v>39</v>
       </c>
-      <c r="I16" s="20"/>
+      <c r="I16" s="79"/>
       <c r="J16" s="20"/>
       <c r="K16" s="20"/>
       <c r="L16" s="21"/>
@@ -10950,7 +11052,7 @@
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="18"/>
-      <c r="I20" s="21"/>
+      <c r="I20" s="80"/>
       <c r="J20" s="20"/>
       <c r="K20" s="20"/>
       <c r="L20" s="21"/>
@@ -10977,7 +11079,7 @@
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="18"/>
-      <c r="I21" s="21"/>
+      <c r="I21" s="80"/>
       <c r="J21" s="20"/>
       <c r="K21" s="20"/>
       <c r="L21" s="21"/>
@@ -11006,7 +11108,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="18"/>
-      <c r="I22" s="33"/>
+      <c r="I22" s="81"/>
       <c r="J22" s="34">
         <v>3952</v>
       </c>
@@ -11094,7 +11196,7 @@
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="18"/>
-      <c r="I25" s="21"/>
+      <c r="I25" s="80"/>
       <c r="J25" s="20"/>
       <c r="K25" s="20"/>
       <c r="L25" s="21"/>
@@ -11117,7 +11219,7 @@
       <c r="F26" s="18"/>
       <c r="G26" s="19"/>
       <c r="H26" s="18"/>
-      <c r="I26" s="21"/>
+      <c r="I26" s="80"/>
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
       <c r="L26" s="21"/>
@@ -11140,7 +11242,7 @@
       <c r="F27" s="18"/>
       <c r="G27" s="19"/>
       <c r="H27" s="18"/>
-      <c r="I27" s="20"/>
+      <c r="I27" s="79"/>
       <c r="J27" s="20"/>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
@@ -11196,7 +11298,7 @@
       <c r="F29" s="18"/>
       <c r="G29" s="19"/>
       <c r="H29" s="18"/>
-      <c r="I29" s="18" t="s">
+      <c r="I29" s="24" t="s">
         <v>59</v>
       </c>
       <c r="J29" s="18"/>
@@ -11221,7 +11323,7 @@
       </c>
       <c r="G30" s="19"/>
       <c r="H30" s="18"/>
-      <c r="I30" s="20"/>
+      <c r="I30" s="79"/>
       <c r="J30" s="20"/>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
@@ -11244,6 +11346,7 @@
       </c>
       <c r="G31" s="45"/>
       <c r="H31" s="33"/>
+      <c r="I31" s="82"/>
       <c r="J31" s="33"/>
       <c r="K31" s="33"/>
       <c r="L31" s="33"/>
@@ -11268,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="18"/>
-      <c r="I32" s="34" t="s">
+      <c r="I32" s="83" t="s">
         <v>91</v>
       </c>
       <c r="J32" s="18">
@@ -11299,7 +11402,7 @@
       </c>
       <c r="G33" s="46"/>
       <c r="H33" s="18"/>
-      <c r="I33" s="34" t="s">
+      <c r="I33" s="83" t="s">
         <v>95</v>
       </c>
       <c r="J33" s="20"/>
@@ -11324,7 +11427,7 @@
       </c>
       <c r="G34" s="19"/>
       <c r="H34" s="18"/>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="25" t="s">
         <v>97</v>
       </c>
       <c r="J34" s="47"/>
@@ -11349,7 +11452,7 @@
       </c>
       <c r="G35" s="19"/>
       <c r="H35" s="18"/>
-      <c r="I35" s="21"/>
+      <c r="I35" s="80"/>
       <c r="J35" s="47"/>
       <c r="K35" s="47"/>
       <c r="L35" s="47"/>
@@ -11374,7 +11477,7 @@
         <v>3</v>
       </c>
       <c r="H36" s="18"/>
-      <c r="I36" s="21"/>
+      <c r="I36" s="80"/>
       <c r="J36" s="48" t="s">
         <v>101</v>
       </c>
@@ -11423,7 +11526,7 @@
       <c r="F38" s="18"/>
       <c r="G38" s="19"/>
       <c r="H38" s="18"/>
-      <c r="I38" s="21"/>
+      <c r="I38" s="80"/>
       <c r="J38" s="49"/>
       <c r="K38" s="49"/>
       <c r="L38" s="49"/>
@@ -11446,6 +11549,7 @@
       </c>
       <c r="G39" s="19"/>
       <c r="H39" s="18"/>
+      <c r="I39" s="82"/>
       <c r="J39" s="20"/>
       <c r="K39" s="20"/>
       <c r="L39" s="20"/>
@@ -11468,7 +11572,7 @@
       </c>
       <c r="G40" s="19"/>
       <c r="H40" s="18"/>
-      <c r="I40" s="21"/>
+      <c r="I40" s="80"/>
       <c r="J40" s="20"/>
       <c r="K40" s="20"/>
       <c r="L40" s="20"/>
@@ -11545,7 +11649,7 @@
       <c r="F43" s="18"/>
       <c r="G43" s="19"/>
       <c r="H43" s="18"/>
-      <c r="I43" s="18" t="s">
+      <c r="I43" s="24" t="s">
         <v>59</v>
       </c>
       <c r="J43" s="18"/>
@@ -11647,7 +11751,7 @@
       </c>
       <c r="G47" s="19"/>
       <c r="H47" s="18"/>
-      <c r="I47" s="21"/>
+      <c r="I47" s="80"/>
       <c r="J47" s="20"/>
       <c r="K47" s="20"/>
       <c r="L47" s="20"/>
@@ -11697,7 +11801,7 @@
       </c>
       <c r="G49" s="19"/>
       <c r="H49" s="18"/>
-      <c r="I49" s="17" t="s">
+      <c r="I49" s="25" t="s">
         <v>124</v>
       </c>
       <c r="J49" s="20"/>
@@ -11718,7 +11822,7 @@
       <c r="F50" s="18"/>
       <c r="G50" s="19"/>
       <c r="H50" s="18"/>
-      <c r="I50" s="21"/>
+      <c r="I50" s="80"/>
       <c r="J50" s="20"/>
       <c r="K50" s="20"/>
       <c r="L50" s="20"/>
@@ -11791,7 +11895,7 @@
       </c>
       <c r="G53" s="19"/>
       <c r="H53" s="18"/>
-      <c r="I53" s="21"/>
+      <c r="I53" s="80"/>
       <c r="J53" s="20"/>
       <c r="K53" s="20"/>
       <c r="L53" s="20"/>
@@ -11889,7 +11993,7 @@
       <c r="F57" s="18"/>
       <c r="G57" s="19"/>
       <c r="H57" s="18"/>
-      <c r="I57" s="18" t="s">
+      <c r="I57" s="24" t="s">
         <v>59</v>
       </c>
       <c r="J57" s="20"/>
@@ -12048,7 +12152,7 @@
       </c>
       <c r="G63" s="19"/>
       <c r="H63" s="58"/>
-      <c r="I63" s="58"/>
+      <c r="I63" s="84"/>
       <c r="J63" s="58"/>
       <c r="K63" s="58"/>
       <c r="L63" s="58"/>
@@ -12140,7 +12244,7 @@
       </c>
       <c r="G67" s="19"/>
       <c r="H67" s="58"/>
-      <c r="I67" s="57" t="s">
+      <c r="I67" s="62" t="s">
         <v>159</v>
       </c>
       <c r="J67" s="58"/>
@@ -12187,7 +12291,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="58"/>
-      <c r="I69" s="62" t="s">
+      <c r="I69" s="56" t="s">
         <v>163</v>
       </c>
       <c r="J69" s="57">
@@ -12251,7 +12355,7 @@
       <c r="F71" s="18"/>
       <c r="G71" s="19"/>
       <c r="H71" s="18"/>
-      <c r="I71" s="18" t="s">
+      <c r="I71" s="24" t="s">
         <v>59</v>
       </c>
       <c r="J71" s="57"/>
@@ -12276,7 +12380,7 @@
       </c>
       <c r="G72" s="19"/>
       <c r="H72" s="58"/>
-      <c r="I72" s="58"/>
+      <c r="I72" s="84"/>
       <c r="J72" s="58"/>
       <c r="K72" s="58"/>
       <c r="L72" s="58"/>
@@ -12297,7 +12401,7 @@
       </c>
       <c r="G73" s="19"/>
       <c r="H73" s="58"/>
-      <c r="I73" s="63" t="s">
+      <c r="I73" s="62" t="s">
         <v>66</v>
       </c>
       <c r="J73" s="58"/>
@@ -12324,7 +12428,7 @@
         <v>2</v>
       </c>
       <c r="H74" s="58"/>
-      <c r="I74" s="63" t="s">
+      <c r="I74" s="62" t="s">
         <v>174</v>
       </c>
       <c r="J74" s="57" t="s">
@@ -12355,7 +12459,7 @@
       </c>
       <c r="G75" s="19"/>
       <c r="H75" s="58"/>
-      <c r="I75" s="57" t="s">
+      <c r="I75" s="62" t="s">
         <v>179</v>
       </c>
       <c r="J75" s="58"/>
@@ -12380,7 +12484,7 @@
       </c>
       <c r="G76" s="19"/>
       <c r="H76" s="58"/>
-      <c r="I76" s="58"/>
+      <c r="I76" s="84"/>
       <c r="J76" s="58"/>
       <c r="K76" s="58"/>
       <c r="L76" s="58"/>
@@ -12403,7 +12507,7 @@
       </c>
       <c r="G77" s="19"/>
       <c r="H77" s="58"/>
-      <c r="I77" s="58"/>
+      <c r="I77" s="84"/>
       <c r="J77" s="58"/>
       <c r="K77" s="58"/>
       <c r="L77" s="58"/>
@@ -12426,7 +12530,7 @@
       </c>
       <c r="G78" s="19"/>
       <c r="H78" s="58"/>
-      <c r="I78" s="58"/>
+      <c r="I78" s="84"/>
       <c r="J78" s="58"/>
       <c r="K78" s="58"/>
       <c r="L78" s="58"/>
@@ -12466,10 +12570,10 @@
       </c>
       <c r="C80" s="57"/>
       <c r="D80" s="57"/>
-      <c r="E80" s="64" t="s">
+      <c r="E80" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="F80" s="64" t="s">
+      <c r="F80" s="63" t="s">
         <v>189</v>
       </c>
       <c r="G80" s="19"/>
@@ -12499,7 +12603,7 @@
       </c>
       <c r="G81" s="19"/>
       <c r="H81" s="58"/>
-      <c r="I81" s="65"/>
+      <c r="I81" s="85"/>
       <c r="J81" s="58"/>
       <c r="K81" s="58"/>
       <c r="L81" s="58"/>
@@ -12522,7 +12626,7 @@
       </c>
       <c r="G82" s="19"/>
       <c r="H82" s="58"/>
-      <c r="I82" s="65"/>
+      <c r="I82" s="85"/>
       <c r="J82" s="58"/>
       <c r="K82" s="58"/>
       <c r="L82" s="58"/>
@@ -12537,7 +12641,7 @@
       </c>
       <c r="C83" s="57"/>
       <c r="D83" s="57"/>
-      <c r="E83" s="64" t="s">
+      <c r="E83" s="63" t="s">
         <v>194</v>
       </c>
       <c r="F83" s="57" t="s">
@@ -12564,10 +12668,10 @@
       </c>
       <c r="C84" s="57"/>
       <c r="D84" s="57"/>
-      <c r="E84" s="64" t="s">
+      <c r="E84" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="F84" s="64" t="s">
+      <c r="F84" s="63" t="s">
         <v>198</v>
       </c>
       <c r="G84" s="19">
@@ -12607,7 +12711,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="18"/>
-      <c r="I85" s="18" t="s">
+      <c r="I85" s="24" t="s">
         <v>202</v>
       </c>
       <c r="J85" s="58"/>
@@ -12632,7 +12736,7 @@
       </c>
       <c r="G86" s="19"/>
       <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
+      <c r="I86" s="84"/>
       <c r="J86" s="58"/>
       <c r="K86" s="58"/>
       <c r="L86" s="58"/>
@@ -12653,7 +12757,7 @@
       </c>
       <c r="G87" s="19"/>
       <c r="H87" s="58"/>
-      <c r="I87" s="63" t="s">
+      <c r="I87" s="62" t="s">
         <v>66</v>
       </c>
       <c r="J87" s="58"/>
@@ -12680,7 +12784,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="58"/>
-      <c r="I88" s="66" t="s">
+      <c r="I88" s="64" t="s">
         <v>206</v>
       </c>
       <c r="J88" s="57">
@@ -12711,7 +12815,7 @@
       </c>
       <c r="G89" s="19"/>
       <c r="H89" s="58"/>
-      <c r="I89" s="57"/>
+      <c r="I89" s="62"/>
       <c r="J89" s="58"/>
       <c r="K89" s="58"/>
       <c r="L89" s="58"/>
@@ -12734,7 +12838,7 @@
       </c>
       <c r="G90" s="19"/>
       <c r="H90" s="58"/>
-      <c r="I90" s="58"/>
+      <c r="I90" s="84"/>
       <c r="J90" s="58"/>
       <c r="K90" s="58"/>
       <c r="L90" s="58"/>
@@ -12757,7 +12861,7 @@
       </c>
       <c r="G91" s="19"/>
       <c r="H91" s="58"/>
-      <c r="I91" s="58"/>
+      <c r="I91" s="84"/>
       <c r="J91" s="58"/>
       <c r="K91" s="58"/>
       <c r="L91" s="58"/>
@@ -12779,12 +12883,12 @@
         <v>211</v>
       </c>
       <c r="G92" s="19"/>
-      <c r="H92" s="67"/>
-      <c r="I92" s="67"/>
-      <c r="J92" s="67"/>
-      <c r="K92" s="67"/>
-      <c r="L92" s="67"/>
-      <c r="M92" s="67"/>
+      <c r="H92" s="65"/>
+      <c r="I92" s="86"/>
+      <c r="J92" s="65"/>
+      <c r="K92" s="65"/>
+      <c r="L92" s="65"/>
+      <c r="M92" s="65"/>
     </row>
     <row r="93" spans="1:13" ht="51" customHeight="1">
       <c r="A93" s="50" t="s">
@@ -12853,7 +12957,7 @@
       </c>
       <c r="G95" s="19"/>
       <c r="H95" s="58"/>
-      <c r="I95" s="58"/>
+      <c r="I95" s="84"/>
       <c r="J95" s="58"/>
       <c r="K95" s="58"/>
       <c r="L95" s="58"/>
@@ -12876,7 +12980,7 @@
       </c>
       <c r="G96" s="19"/>
       <c r="H96" s="58"/>
-      <c r="I96" s="58"/>
+      <c r="I96" s="84"/>
       <c r="J96" s="58"/>
       <c r="K96" s="58"/>
       <c r="L96" s="58"/>
@@ -12897,7 +13001,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="58"/>
-      <c r="I97" s="18" t="s">
+      <c r="I97" s="24" t="s">
         <v>220</v>
       </c>
       <c r="J97" s="58"/>
@@ -12955,7 +13059,7 @@
       <c r="F99" s="18"/>
       <c r="G99" s="19"/>
       <c r="H99" s="18"/>
-      <c r="I99" s="18" t="s">
+      <c r="I99" s="24" t="s">
         <v>220</v>
       </c>
       <c r="J99" s="58"/>
@@ -12980,7 +13084,7 @@
       </c>
       <c r="G100" s="19"/>
       <c r="H100" s="58"/>
-      <c r="I100" s="58"/>
+      <c r="I100" s="84"/>
       <c r="J100" s="58"/>
       <c r="K100" s="58"/>
       <c r="L100" s="58"/>
@@ -13001,7 +13105,7 @@
       </c>
       <c r="G101" s="19"/>
       <c r="H101" s="58"/>
-      <c r="I101" s="63" t="s">
+      <c r="I101" s="62" t="s">
         <v>66</v>
       </c>
       <c r="J101" s="58"/>
@@ -13026,7 +13130,7 @@
       </c>
       <c r="G102" s="19"/>
       <c r="H102" s="58"/>
-      <c r="I102" s="66"/>
+      <c r="I102" s="64"/>
       <c r="J102" s="58"/>
       <c r="K102" s="57"/>
       <c r="L102" s="25"/>
@@ -13049,7 +13153,7 @@
       </c>
       <c r="G103" s="19"/>
       <c r="H103" s="58"/>
-      <c r="I103" s="68" t="s">
+      <c r="I103" s="66" t="s">
         <v>233</v>
       </c>
       <c r="J103" s="58"/>
@@ -13074,7 +13178,7 @@
       </c>
       <c r="G104" s="19"/>
       <c r="H104" s="58"/>
-      <c r="I104" s="58"/>
+      <c r="I104" s="84"/>
       <c r="J104" s="58"/>
       <c r="K104" s="58"/>
       <c r="L104" s="58"/>
@@ -13097,7 +13201,7 @@
       </c>
       <c r="G105" s="19"/>
       <c r="H105" s="58"/>
-      <c r="I105" s="58"/>
+      <c r="I105" s="84"/>
       <c r="J105" s="58"/>
       <c r="K105" s="58"/>
       <c r="L105" s="58"/>
@@ -13119,12 +13223,12 @@
         <v>119</v>
       </c>
       <c r="G106" s="19"/>
-      <c r="H106" s="67"/>
-      <c r="I106" s="67"/>
-      <c r="J106" s="67"/>
-      <c r="K106" s="67"/>
-      <c r="L106" s="67"/>
-      <c r="M106" s="67"/>
+      <c r="H106" s="65"/>
+      <c r="I106" s="86"/>
+      <c r="J106" s="65"/>
+      <c r="K106" s="65"/>
+      <c r="L106" s="65"/>
+      <c r="M106" s="65"/>
     </row>
     <row r="107" spans="1:13" ht="62.25" customHeight="1">
       <c r="A107" s="50" t="s">
@@ -13193,7 +13297,7 @@
       </c>
       <c r="G109" s="19"/>
       <c r="H109" s="58"/>
-      <c r="I109" s="58"/>
+      <c r="I109" s="84"/>
       <c r="J109" s="58"/>
       <c r="K109" s="58"/>
       <c r="L109" s="58"/>
@@ -13216,7 +13320,7 @@
       </c>
       <c r="G110" s="19"/>
       <c r="H110" s="58"/>
-      <c r="I110" s="58"/>
+      <c r="I110" s="84"/>
       <c r="J110" s="58"/>
       <c r="K110" s="58"/>
       <c r="L110" s="58"/>
@@ -13235,7 +13339,7 @@
       <c r="F111" s="57"/>
       <c r="G111" s="19"/>
       <c r="H111" s="58"/>
-      <c r="I111" s="68" t="s">
+      <c r="I111" s="66" t="s">
         <v>243</v>
       </c>
       <c r="J111" s="58"/>
@@ -13293,7 +13397,7 @@
       <c r="F113" s="18"/>
       <c r="G113" s="19"/>
       <c r="H113" s="18"/>
-      <c r="I113" s="68" t="s">
+      <c r="I113" s="66" t="s">
         <v>248</v>
       </c>
       <c r="J113" s="58"/>
@@ -13318,7 +13422,7 @@
       </c>
       <c r="G114" s="19"/>
       <c r="H114" s="58"/>
-      <c r="I114" s="58"/>
+      <c r="I114" s="84"/>
       <c r="J114" s="58"/>
       <c r="K114" s="58"/>
       <c r="L114" s="58"/>
@@ -13339,7 +13443,7 @@
       </c>
       <c r="G115" s="19"/>
       <c r="H115" s="58"/>
-      <c r="I115" s="68" t="s">
+      <c r="I115" s="66" t="s">
         <v>252</v>
       </c>
       <c r="J115" s="58"/>
@@ -13364,7 +13468,7 @@
       </c>
       <c r="G116" s="19"/>
       <c r="H116" s="58"/>
-      <c r="I116" s="66"/>
+      <c r="I116" s="64"/>
       <c r="J116" s="58"/>
       <c r="K116" s="57"/>
       <c r="L116" s="25"/>
@@ -13387,7 +13491,7 @@
       </c>
       <c r="G117" s="19"/>
       <c r="H117" s="58"/>
-      <c r="I117" s="68" t="s">
+      <c r="I117" s="66" t="s">
         <v>233</v>
       </c>
       <c r="J117" s="58"/>
@@ -13412,7 +13516,7 @@
       </c>
       <c r="G118" s="19"/>
       <c r="H118" s="58"/>
-      <c r="I118" s="58"/>
+      <c r="I118" s="84"/>
       <c r="J118" s="58"/>
       <c r="K118" s="58"/>
       <c r="L118" s="58"/>
@@ -13435,7 +13539,7 @@
       </c>
       <c r="G119" s="19"/>
       <c r="H119" s="58"/>
-      <c r="I119" s="58"/>
+      <c r="I119" s="84"/>
       <c r="J119" s="58"/>
       <c r="K119" s="58"/>
       <c r="L119" s="58"/>
@@ -13457,12 +13561,12 @@
         <v>257</v>
       </c>
       <c r="G120" s="19"/>
-      <c r="H120" s="67"/>
-      <c r="I120" s="67"/>
-      <c r="J120" s="67"/>
-      <c r="K120" s="67"/>
-      <c r="L120" s="67"/>
-      <c r="M120" s="67"/>
+      <c r="H120" s="65"/>
+      <c r="I120" s="86"/>
+      <c r="J120" s="65"/>
+      <c r="K120" s="65"/>
+      <c r="L120" s="65"/>
+      <c r="M120" s="65"/>
     </row>
     <row r="121" spans="1:13" ht="70.5" customHeight="1">
       <c r="A121" s="50" t="s">
@@ -13554,7 +13658,7 @@
       </c>
       <c r="G124" s="19"/>
       <c r="H124" s="58"/>
-      <c r="I124" s="68" t="s">
+      <c r="I124" s="66" t="s">
         <v>267</v>
       </c>
       <c r="J124" s="58"/>
@@ -13575,7 +13679,7 @@
       <c r="F125" s="57"/>
       <c r="G125" s="19"/>
       <c r="H125" s="58"/>
-      <c r="I125" s="68" t="s">
+      <c r="I125" s="66" t="s">
         <v>268</v>
       </c>
       <c r="J125" s="58"/>
@@ -13595,7 +13699,7 @@
       <c r="E126" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="F126" s="69" t="s">
+      <c r="F126" s="67" t="s">
         <v>270</v>
       </c>
       <c r="G126" s="19">
@@ -13633,7 +13737,7 @@
       <c r="F127" s="18"/>
       <c r="G127" s="19"/>
       <c r="H127" s="18"/>
-      <c r="I127" s="68" t="s">
+      <c r="I127" s="66" t="s">
         <v>243</v>
       </c>
       <c r="J127" s="58"/>
@@ -13658,7 +13762,7 @@
       </c>
       <c r="G128" s="19"/>
       <c r="H128" s="58"/>
-      <c r="I128" s="58"/>
+      <c r="I128" s="84"/>
       <c r="J128" s="58"/>
       <c r="K128" s="58"/>
       <c r="L128" s="58"/>
@@ -13679,7 +13783,7 @@
       </c>
       <c r="G129" s="19"/>
       <c r="H129" s="58"/>
-      <c r="I129" s="68" t="s">
+      <c r="I129" s="66" t="s">
         <v>277</v>
       </c>
       <c r="J129" s="58"/>
@@ -13729,7 +13833,7 @@
       </c>
       <c r="G131" s="19"/>
       <c r="H131" s="58"/>
-      <c r="I131" s="68"/>
+      <c r="I131" s="66"/>
       <c r="J131" s="58"/>
       <c r="K131" s="58"/>
       <c r="L131" s="58"/>
@@ -13752,7 +13856,7 @@
       </c>
       <c r="G132" s="19"/>
       <c r="H132" s="58"/>
-      <c r="I132" s="58"/>
+      <c r="I132" s="84"/>
       <c r="J132" s="58"/>
       <c r="K132" s="58"/>
       <c r="L132" s="58"/>
@@ -13775,7 +13879,7 @@
       </c>
       <c r="G133" s="19"/>
       <c r="H133" s="58"/>
-      <c r="I133" s="58"/>
+      <c r="I133" s="84"/>
       <c r="J133" s="58"/>
       <c r="K133" s="58"/>
       <c r="L133" s="58"/>
@@ -13799,8 +13903,8 @@
       <c r="G134" s="19">
         <v>1</v>
       </c>
-      <c r="H134" s="67"/>
-      <c r="I134" s="68" t="s">
+      <c r="H134" s="65"/>
+      <c r="I134" s="66" t="s">
         <v>287</v>
       </c>
       <c r="J134" s="57">
@@ -13812,7 +13916,7 @@
       <c r="L134" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="M134" s="67"/>
+      <c r="M134" s="65"/>
     </row>
     <row r="135" spans="1:13" ht="60.75" customHeight="1">
       <c r="A135" s="50" t="s">
@@ -13899,7 +14003,7 @@
       <c r="F138" s="57"/>
       <c r="G138" s="19"/>
       <c r="H138" s="58"/>
-      <c r="I138" s="68" t="s">
+      <c r="I138" s="66" t="s">
         <v>296</v>
       </c>
       <c r="J138" s="58"/>
@@ -13920,7 +14024,7 @@
       <c r="F139" s="57"/>
       <c r="G139" s="19"/>
       <c r="H139" s="58"/>
-      <c r="I139" s="68" t="s">
+      <c r="I139" s="66" t="s">
         <v>297</v>
       </c>
       <c r="J139" s="58"/>
@@ -13978,7 +14082,7 @@
       <c r="F141" s="18"/>
       <c r="G141" s="19"/>
       <c r="H141" s="18"/>
-      <c r="I141" s="68" t="s">
+      <c r="I141" s="66" t="s">
         <v>268</v>
       </c>
       <c r="J141" s="58"/>
@@ -14003,7 +14107,7 @@
       </c>
       <c r="G142" s="19"/>
       <c r="H142" s="58"/>
-      <c r="I142" s="58"/>
+      <c r="I142" s="84"/>
       <c r="J142" s="58"/>
       <c r="K142" s="58"/>
       <c r="L142" s="58"/>
@@ -14026,7 +14130,7 @@
         <v>2</v>
       </c>
       <c r="H143" s="58"/>
-      <c r="I143" s="68" t="s">
+      <c r="I143" s="66" t="s">
         <v>306</v>
       </c>
       <c r="J143" s="57" t="s">
@@ -14057,7 +14161,7 @@
       </c>
       <c r="G144" s="19"/>
       <c r="H144" s="58"/>
-      <c r="I144" s="58"/>
+      <c r="I144" s="84"/>
       <c r="J144" s="58"/>
       <c r="K144" s="58"/>
       <c r="L144" s="58"/>
@@ -14080,7 +14184,7 @@
       </c>
       <c r="G145" s="19"/>
       <c r="H145" s="58"/>
-      <c r="I145" s="68"/>
+      <c r="I145" s="66"/>
       <c r="J145" s="58"/>
       <c r="K145" s="58"/>
       <c r="L145" s="58"/>
@@ -14103,7 +14207,7 @@
       </c>
       <c r="G146" s="19"/>
       <c r="H146" s="58"/>
-      <c r="I146" s="58"/>
+      <c r="I146" s="84"/>
       <c r="J146" s="58"/>
       <c r="K146" s="58"/>
       <c r="L146" s="58"/>
@@ -14122,7 +14226,7 @@
       <c r="F147" s="57"/>
       <c r="G147" s="19"/>
       <c r="H147" s="58"/>
-      <c r="I147" s="68" t="s">
+      <c r="I147" s="66" t="s">
         <v>59</v>
       </c>
       <c r="J147" s="58"/>
@@ -14148,7 +14252,7 @@
       <c r="G148" s="19">
         <v>1</v>
       </c>
-      <c r="H148" s="67"/>
+      <c r="H148" s="65"/>
       <c r="I148" s="42" t="s">
         <v>313</v>
       </c>
@@ -14252,7 +14356,7 @@
       </c>
       <c r="G152" s="19"/>
       <c r="H152" s="58"/>
-      <c r="I152" s="68"/>
+      <c r="I152" s="66"/>
       <c r="J152" s="58"/>
       <c r="K152" s="58"/>
       <c r="L152" s="58"/>
@@ -14271,7 +14375,7 @@
       <c r="F153" s="57"/>
       <c r="G153" s="19"/>
       <c r="H153" s="58"/>
-      <c r="I153" s="68" t="s">
+      <c r="I153" s="66" t="s">
         <v>323</v>
       </c>
       <c r="J153" s="58"/>
@@ -14289,7 +14393,7 @@
       <c r="C154" s="57"/>
       <c r="D154" s="57"/>
       <c r="E154" s="55"/>
-      <c r="F154" s="69"/>
+      <c r="F154" s="67"/>
       <c r="G154" s="19"/>
       <c r="H154" s="58"/>
       <c r="I154" s="42"/>
@@ -14315,7 +14419,7 @@
       <c r="F155" s="18"/>
       <c r="G155" s="19"/>
       <c r="H155" s="18"/>
-      <c r="I155" s="68"/>
+      <c r="I155" s="66"/>
       <c r="J155" s="58"/>
       <c r="K155" s="57"/>
       <c r="L155" s="25"/>
@@ -14336,7 +14440,7 @@
         <v>14</v>
       </c>
       <c r="H156" s="58"/>
-      <c r="I156" s="68" t="s">
+      <c r="I156" s="66" t="s">
         <v>324</v>
       </c>
       <c r="J156" s="58"/>
@@ -14359,7 +14463,7 @@
       </c>
       <c r="G157" s="19"/>
       <c r="H157" s="58"/>
-      <c r="I157" s="68" t="s">
+      <c r="I157" s="66" t="s">
         <v>326</v>
       </c>
       <c r="J157" s="57"/>
@@ -14384,7 +14488,7 @@
       </c>
       <c r="G158" s="19"/>
       <c r="H158" s="58"/>
-      <c r="I158" s="58"/>
+      <c r="I158" s="84"/>
       <c r="J158" s="58"/>
       <c r="K158" s="58"/>
       <c r="L158" s="58"/>
@@ -14407,7 +14511,7 @@
       </c>
       <c r="G159" s="19"/>
       <c r="H159" s="58"/>
-      <c r="I159" s="68"/>
+      <c r="I159" s="66"/>
       <c r="J159" s="58"/>
       <c r="K159" s="58"/>
       <c r="L159" s="58"/>
@@ -14430,7 +14534,7 @@
       </c>
       <c r="G160" s="19"/>
       <c r="H160" s="58"/>
-      <c r="I160" s="58"/>
+      <c r="I160" s="84"/>
       <c r="J160" s="58"/>
       <c r="K160" s="58"/>
       <c r="L160" s="58"/>
@@ -14453,7 +14557,7 @@
       </c>
       <c r="G161" s="19"/>
       <c r="H161" s="58"/>
-      <c r="I161" s="68"/>
+      <c r="I161" s="66"/>
       <c r="J161" s="58"/>
       <c r="K161" s="58"/>
       <c r="L161" s="58"/>
@@ -14475,7 +14579,7 @@
         <v>333</v>
       </c>
       <c r="G162" s="19"/>
-      <c r="H162" s="67"/>
+      <c r="H162" s="65"/>
       <c r="I162" s="42"/>
       <c r="J162" s="57"/>
       <c r="K162" s="57"/>
@@ -14549,7 +14653,7 @@
       </c>
       <c r="G165" s="19"/>
       <c r="H165" s="58"/>
-      <c r="I165" s="70"/>
+      <c r="I165" s="68"/>
       <c r="J165" s="58"/>
       <c r="K165" s="58"/>
       <c r="L165" s="58"/>
@@ -14568,7 +14672,7 @@
       <c r="F166" s="57"/>
       <c r="G166" s="19"/>
       <c r="H166" s="58"/>
-      <c r="I166" s="68" t="s">
+      <c r="I166" s="66" t="s">
         <v>339</v>
       </c>
       <c r="J166" s="58"/>
@@ -14589,7 +14693,7 @@
       <c r="F167" s="57"/>
       <c r="G167" s="19"/>
       <c r="H167" s="58"/>
-      <c r="I167" s="68" t="s">
+      <c r="I167" s="66" t="s">
         <v>340</v>
       </c>
       <c r="J167" s="58"/>
@@ -14647,7 +14751,7 @@
       <c r="F169" s="18"/>
       <c r="G169" s="19"/>
       <c r="H169" s="18"/>
-      <c r="I169" s="68"/>
+      <c r="I169" s="66"/>
       <c r="J169" s="58"/>
       <c r="K169" s="57"/>
       <c r="L169" s="25"/>
@@ -14668,7 +14772,7 @@
         <v>14</v>
       </c>
       <c r="H170" s="58"/>
-      <c r="I170" s="68" t="s">
+      <c r="I170" s="66" t="s">
         <v>346</v>
       </c>
       <c r="J170" s="58"/>
@@ -14691,7 +14795,7 @@
       </c>
       <c r="G171" s="19"/>
       <c r="H171" s="58"/>
-      <c r="I171" s="68" t="s">
+      <c r="I171" s="66" t="s">
         <v>347</v>
       </c>
       <c r="J171" s="57"/>
@@ -14718,7 +14822,7 @@
         <v>2</v>
       </c>
       <c r="H172" s="58"/>
-      <c r="I172" s="68" t="s">
+      <c r="I172" s="66" t="s">
         <v>349</v>
       </c>
       <c r="J172" s="57" t="s">
@@ -14751,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="H173" s="58"/>
-      <c r="I173" s="68" t="s">
+      <c r="I173" s="66" t="s">
         <v>354</v>
       </c>
       <c r="J173" s="58"/>
@@ -14776,7 +14880,7 @@
       </c>
       <c r="G174" s="19"/>
       <c r="H174" s="58"/>
-      <c r="I174" s="58"/>
+      <c r="I174" s="84"/>
       <c r="J174" s="58"/>
       <c r="K174" s="58"/>
       <c r="L174" s="58"/>
@@ -14799,7 +14903,7 @@
       </c>
       <c r="G175" s="19"/>
       <c r="H175" s="58"/>
-      <c r="I175" s="68"/>
+      <c r="I175" s="66"/>
       <c r="J175" s="58"/>
       <c r="K175" s="58"/>
       <c r="L175" s="58"/>
@@ -14823,7 +14927,7 @@
       <c r="G176" s="19">
         <v>3</v>
       </c>
-      <c r="H176" s="67"/>
+      <c r="H176" s="65"/>
       <c r="I176" s="42"/>
       <c r="J176" s="57" t="s">
         <v>359</v>
@@ -14903,7 +15007,7 @@
       </c>
       <c r="G179" s="19"/>
       <c r="H179" s="58"/>
-      <c r="I179" s="70"/>
+      <c r="I179" s="68"/>
       <c r="J179" s="58"/>
       <c r="K179" s="58"/>
       <c r="L179" s="58"/>
@@ -14922,7 +15026,7 @@
       <c r="F180" s="57"/>
       <c r="G180" s="19"/>
       <c r="H180" s="58"/>
-      <c r="I180" s="68"/>
+      <c r="I180" s="66"/>
       <c r="J180" s="58"/>
       <c r="K180" s="58"/>
       <c r="L180" s="58"/>
@@ -14941,7 +15045,7 @@
       <c r="F181" s="57"/>
       <c r="G181" s="19"/>
       <c r="H181" s="58"/>
-      <c r="I181" s="68" t="s">
+      <c r="I181" s="66" t="s">
         <v>323</v>
       </c>
       <c r="J181" s="58"/>
@@ -14999,7 +15103,7 @@
       <c r="F183" s="18"/>
       <c r="G183" s="19"/>
       <c r="H183" s="18"/>
-      <c r="I183" s="68"/>
+      <c r="I183" s="66"/>
       <c r="J183" s="58"/>
       <c r="K183" s="57"/>
       <c r="L183" s="25"/>
@@ -15018,7 +15122,7 @@
       <c r="F184" s="57"/>
       <c r="G184" s="19"/>
       <c r="H184" s="58"/>
-      <c r="I184" s="68" t="s">
+      <c r="I184" s="66" t="s">
         <v>373</v>
       </c>
       <c r="J184" s="58"/>
@@ -15041,7 +15145,7 @@
       </c>
       <c r="G185" s="19"/>
       <c r="H185" s="58"/>
-      <c r="I185" s="68"/>
+      <c r="I185" s="66"/>
       <c r="J185" s="57"/>
       <c r="K185" s="57"/>
       <c r="L185" s="25"/>
@@ -15064,7 +15168,7 @@
       </c>
       <c r="G186" s="19"/>
       <c r="H186" s="58"/>
-      <c r="I186" s="68" t="s">
+      <c r="I186" s="66" t="s">
         <v>377</v>
       </c>
       <c r="J186" s="58"/>
@@ -15089,7 +15193,7 @@
       </c>
       <c r="G187" s="19"/>
       <c r="H187" s="58"/>
-      <c r="I187" s="68"/>
+      <c r="I187" s="66"/>
       <c r="J187" s="58"/>
       <c r="K187" s="58"/>
       <c r="L187" s="58"/>
@@ -15112,7 +15216,7 @@
       </c>
       <c r="G188" s="19"/>
       <c r="H188" s="58"/>
-      <c r="I188" s="58"/>
+      <c r="I188" s="84"/>
       <c r="J188" s="58"/>
       <c r="K188" s="58"/>
       <c r="L188" s="58"/>
@@ -15135,7 +15239,7 @@
       </c>
       <c r="G189" s="19"/>
       <c r="H189" s="58"/>
-      <c r="I189" s="68"/>
+      <c r="I189" s="66"/>
       <c r="J189" s="58"/>
       <c r="K189" s="58"/>
       <c r="L189" s="58"/>
@@ -15159,7 +15263,7 @@
       <c r="G190" s="19">
         <v>6</v>
       </c>
-      <c r="H190" s="67"/>
+      <c r="H190" s="65"/>
       <c r="I190" s="42"/>
       <c r="J190" s="57" t="s">
         <v>381</v>
@@ -15210,7 +15314,7 @@
       <c r="F192" s="55"/>
       <c r="G192" s="19"/>
       <c r="H192" s="58"/>
-      <c r="I192" s="68" t="s">
+      <c r="I192" s="66" t="s">
         <v>386</v>
       </c>
       <c r="J192" s="58"/>
@@ -15227,7 +15331,7 @@
       </c>
       <c r="C193" s="57"/>
       <c r="D193" s="57"/>
-      <c r="E193" s="70" t="s">
+      <c r="E193" s="68" t="s">
         <v>367</v>
       </c>
       <c r="F193" s="57" t="s">
@@ -15253,7 +15357,7 @@
       <c r="F194" s="57"/>
       <c r="G194" s="19"/>
       <c r="H194" s="58"/>
-      <c r="I194" s="68" t="s">
+      <c r="I194" s="66" t="s">
         <v>388</v>
       </c>
       <c r="J194" s="58"/>
@@ -15274,7 +15378,7 @@
       <c r="F195" s="57"/>
       <c r="G195" s="19"/>
       <c r="H195" s="58"/>
-      <c r="I195" s="68"/>
+      <c r="I195" s="66"/>
       <c r="J195" s="58"/>
       <c r="K195" s="57"/>
       <c r="L195" s="58"/>
@@ -15330,7 +15434,7 @@
       <c r="F197" s="18"/>
       <c r="G197" s="19"/>
       <c r="H197" s="18"/>
-      <c r="I197" s="68" t="s">
+      <c r="I197" s="66" t="s">
         <v>268</v>
       </c>
       <c r="J197" s="58"/>
@@ -15350,7 +15454,7 @@
       <c r="F198" s="57"/>
       <c r="G198" s="19"/>
       <c r="H198" s="58"/>
-      <c r="I198" s="68" t="s">
+      <c r="I198" s="66" t="s">
         <v>394</v>
       </c>
       <c r="J198" s="58"/>
@@ -15373,7 +15477,7 @@
       </c>
       <c r="G199" s="19"/>
       <c r="H199" s="58"/>
-      <c r="I199" s="68" t="s">
+      <c r="I199" s="66" t="s">
         <v>396</v>
       </c>
       <c r="J199" s="57"/>
@@ -15400,7 +15504,7 @@
         <v>1</v>
       </c>
       <c r="H200" s="58"/>
-      <c r="I200" s="68" t="s">
+      <c r="I200" s="66" t="s">
         <v>398</v>
       </c>
       <c r="J200" s="57">
@@ -15431,7 +15535,7 @@
       </c>
       <c r="G201" s="19"/>
       <c r="H201" s="58"/>
-      <c r="I201" s="68"/>
+      <c r="I201" s="66"/>
       <c r="J201" s="58"/>
       <c r="K201" s="58"/>
       <c r="L201" s="58"/>
@@ -15454,7 +15558,7 @@
       </c>
       <c r="G202" s="19"/>
       <c r="H202" s="58"/>
-      <c r="I202" s="58"/>
+      <c r="I202" s="84"/>
       <c r="J202" s="58"/>
       <c r="K202" s="58"/>
       <c r="L202" s="58"/>
@@ -15477,7 +15581,7 @@
       </c>
       <c r="G203" s="19"/>
       <c r="H203" s="58"/>
-      <c r="I203" s="68"/>
+      <c r="I203" s="66"/>
       <c r="J203" s="58"/>
       <c r="K203" s="58"/>
       <c r="L203" s="58"/>
@@ -15501,7 +15605,7 @@
       <c r="G204" s="19">
         <v>4</v>
       </c>
-      <c r="H204" s="67"/>
+      <c r="H204" s="65"/>
       <c r="I204" s="42"/>
       <c r="J204" s="57" t="s">
         <v>404</v>
@@ -15527,7 +15631,7 @@
       <c r="F205" s="55"/>
       <c r="G205" s="19"/>
       <c r="H205" s="58"/>
-      <c r="I205" s="68" t="s">
+      <c r="I205" s="66" t="s">
         <v>268</v>
       </c>
       <c r="J205" s="58"/>
@@ -15569,7 +15673,7 @@
       </c>
       <c r="C207" s="57"/>
       <c r="D207" s="57"/>
-      <c r="E207" s="71" t="s">
+      <c r="E207" s="69" t="s">
         <v>387</v>
       </c>
       <c r="F207" s="57" t="s">
@@ -15599,7 +15703,7 @@
       </c>
       <c r="G208" s="19"/>
       <c r="H208" s="58"/>
-      <c r="I208" s="68"/>
+      <c r="I208" s="66"/>
       <c r="J208" s="58"/>
       <c r="K208" s="58"/>
       <c r="L208" s="58"/>
@@ -15618,7 +15722,7 @@
       <c r="F209" s="57"/>
       <c r="G209" s="19"/>
       <c r="H209" s="58"/>
-      <c r="I209" s="68" t="s">
+      <c r="I209" s="66" t="s">
         <v>411</v>
       </c>
       <c r="J209" s="58"/>
@@ -15676,7 +15780,7 @@
       <c r="F211" s="18"/>
       <c r="G211" s="19"/>
       <c r="H211" s="18"/>
-      <c r="I211" s="68" t="s">
+      <c r="I211" s="66" t="s">
         <v>417</v>
       </c>
       <c r="J211" s="58"/>
@@ -15701,7 +15805,7 @@
       </c>
       <c r="G212" s="19"/>
       <c r="H212" s="58"/>
-      <c r="I212" s="68" t="s">
+      <c r="I212" s="66" t="s">
         <v>418</v>
       </c>
       <c r="J212" s="58"/>
@@ -15724,7 +15828,7 @@
       </c>
       <c r="G213" s="19"/>
       <c r="H213" s="58"/>
-      <c r="I213" s="68" t="s">
+      <c r="I213" s="66" t="s">
         <v>420</v>
       </c>
       <c r="J213" s="57"/>
@@ -15749,7 +15853,7 @@
       </c>
       <c r="G214" s="19"/>
       <c r="H214" s="58"/>
-      <c r="I214" s="68" t="s">
+      <c r="I214" s="66" t="s">
         <v>422</v>
       </c>
       <c r="J214" s="58"/>
@@ -15774,7 +15878,7 @@
       </c>
       <c r="G215" s="19"/>
       <c r="H215" s="58"/>
-      <c r="I215" s="68"/>
+      <c r="I215" s="66"/>
       <c r="J215" s="58"/>
       <c r="K215" s="58"/>
       <c r="L215" s="58"/>
@@ -15797,7 +15901,7 @@
       </c>
       <c r="G216" s="19"/>
       <c r="H216" s="58"/>
-      <c r="I216" s="58"/>
+      <c r="I216" s="84"/>
       <c r="J216" s="58"/>
       <c r="K216" s="58"/>
       <c r="L216" s="58"/>
@@ -15820,7 +15924,7 @@
       </c>
       <c r="G217" s="19"/>
       <c r="H217" s="58"/>
-      <c r="I217" s="68"/>
+      <c r="I217" s="66"/>
       <c r="J217" s="58"/>
       <c r="K217" s="58"/>
       <c r="L217" s="58"/>
@@ -15844,8 +15948,8 @@
       <c r="G218" s="19">
         <v>1</v>
       </c>
-      <c r="H218" s="67"/>
-      <c r="I218" s="68" t="s">
+      <c r="H218" s="65"/>
+      <c r="I218" s="66" t="s">
         <v>426</v>
       </c>
       <c r="J218" s="57">
@@ -15872,7 +15976,7 @@
       <c r="F219" s="55"/>
       <c r="G219" s="19"/>
       <c r="H219" s="58"/>
-      <c r="I219" s="68" t="s">
+      <c r="I219" s="66" t="s">
         <v>428</v>
       </c>
       <c r="J219" s="58"/>
@@ -15914,7 +16018,7 @@
       </c>
       <c r="C221" s="57"/>
       <c r="D221" s="57"/>
-      <c r="E221" s="71" t="s">
+      <c r="E221" s="69" t="s">
         <v>409</v>
       </c>
       <c r="F221" s="57" t="s">
@@ -15944,7 +16048,7 @@
       </c>
       <c r="G222" s="19"/>
       <c r="H222" s="58"/>
-      <c r="I222" s="68"/>
+      <c r="I222" s="66"/>
       <c r="J222" s="58"/>
       <c r="K222" s="58"/>
       <c r="L222" s="58"/>
@@ -15963,7 +16067,7 @@
       <c r="F223" s="57"/>
       <c r="G223" s="19"/>
       <c r="H223" s="58"/>
-      <c r="I223" s="68" t="s">
+      <c r="I223" s="66" t="s">
         <v>434</v>
       </c>
       <c r="J223" s="58"/>
@@ -16021,7 +16125,7 @@
       <c r="F225" s="18"/>
       <c r="G225" s="19"/>
       <c r="H225" s="18"/>
-      <c r="I225" s="68" t="s">
+      <c r="I225" s="66" t="s">
         <v>440</v>
       </c>
       <c r="J225" s="58"/>
@@ -16046,7 +16150,7 @@
       </c>
       <c r="G226" s="19"/>
       <c r="H226" s="58"/>
-      <c r="I226" s="68" t="s">
+      <c r="I226" s="66" t="s">
         <v>420</v>
       </c>
       <c r="J226" s="58"/>
@@ -16091,7 +16195,7 @@
       </c>
       <c r="G228" s="19"/>
       <c r="H228" s="58"/>
-      <c r="I228" s="68"/>
+      <c r="I228" s="66"/>
       <c r="J228" s="58"/>
       <c r="K228" s="58"/>
       <c r="L228" s="25"/>
@@ -16114,7 +16218,7 @@
       </c>
       <c r="G229" s="19"/>
       <c r="H229" s="58"/>
-      <c r="I229" s="68"/>
+      <c r="I229" s="66"/>
       <c r="J229" s="58"/>
       <c r="K229" s="58"/>
       <c r="L229" s="58"/>
@@ -16137,7 +16241,7 @@
       </c>
       <c r="G230" s="19"/>
       <c r="H230" s="58"/>
-      <c r="I230" s="68" t="s">
+      <c r="I230" s="66" t="s">
         <v>446</v>
       </c>
       <c r="J230" s="58"/>
@@ -16162,7 +16266,7 @@
       </c>
       <c r="G231" s="19"/>
       <c r="H231" s="58"/>
-      <c r="I231" s="68"/>
+      <c r="I231" s="66"/>
       <c r="J231" s="58"/>
       <c r="K231" s="58"/>
       <c r="L231" s="58"/>
@@ -16186,8 +16290,8 @@
       <c r="G232" s="19">
         <v>1</v>
       </c>
-      <c r="H232" s="67"/>
-      <c r="I232" s="68" t="s">
+      <c r="H232" s="65"/>
+      <c r="I232" s="66" t="s">
         <v>449</v>
       </c>
       <c r="J232" s="57">
@@ -16214,7 +16318,7 @@
       <c r="F233" s="55"/>
       <c r="G233" s="19"/>
       <c r="H233" s="58"/>
-      <c r="I233" s="68"/>
+      <c r="I233" s="66"/>
       <c r="J233" s="58"/>
       <c r="K233" s="58"/>
       <c r="L233" s="58"/>
@@ -16233,7 +16337,7 @@
       <c r="F234" s="55"/>
       <c r="G234" s="19"/>
       <c r="H234" s="58"/>
-      <c r="I234" s="68" t="s">
+      <c r="I234" s="66" t="s">
         <v>451</v>
       </c>
       <c r="J234" s="58"/>
@@ -16250,7 +16354,7 @@
       </c>
       <c r="C235" s="57"/>
       <c r="D235" s="57"/>
-      <c r="E235" s="71" t="s">
+      <c r="E235" s="69" t="s">
         <v>432</v>
       </c>
       <c r="F235" s="57" t="s">
@@ -16280,7 +16384,7 @@
       </c>
       <c r="G236" s="19"/>
       <c r="H236" s="58"/>
-      <c r="I236" s="68"/>
+      <c r="I236" s="66"/>
       <c r="J236" s="58"/>
       <c r="K236" s="58"/>
       <c r="L236" s="58"/>
@@ -16299,7 +16403,7 @@
       <c r="F237" s="57"/>
       <c r="G237" s="19"/>
       <c r="H237" s="58"/>
-      <c r="I237" s="68" t="s">
+      <c r="I237" s="66" t="s">
         <v>454</v>
       </c>
       <c r="J237" s="58"/>
@@ -16357,7 +16461,7 @@
       <c r="F239" s="18"/>
       <c r="G239" s="19"/>
       <c r="H239" s="18"/>
-      <c r="I239" s="68" t="s">
+      <c r="I239" s="66" t="s">
         <v>454</v>
       </c>
       <c r="J239" s="58"/>
@@ -16382,7 +16486,7 @@
       </c>
       <c r="G240" s="19"/>
       <c r="H240" s="58"/>
-      <c r="I240" s="68"/>
+      <c r="I240" s="66"/>
       <c r="J240" s="58"/>
       <c r="K240" s="58"/>
       <c r="L240" s="58"/>
@@ -16403,7 +16507,7 @@
       </c>
       <c r="G241" s="19"/>
       <c r="H241" s="58"/>
-      <c r="I241" s="68" t="s">
+      <c r="I241" s="66" t="s">
         <v>396</v>
       </c>
       <c r="J241" s="57"/>
@@ -16430,7 +16534,7 @@
         <v>2</v>
       </c>
       <c r="H242" s="58"/>
-      <c r="I242" s="68" t="s">
+      <c r="I242" s="66" t="s">
         <v>463</v>
       </c>
       <c r="J242" s="57" t="s">
@@ -16457,7 +16561,7 @@
       <c r="F243" s="57"/>
       <c r="G243" s="19"/>
       <c r="H243" s="58"/>
-      <c r="I243" s="68" t="s">
+      <c r="I243" s="66" t="s">
         <v>454</v>
       </c>
       <c r="J243" s="58"/>
@@ -16482,7 +16586,7 @@
       </c>
       <c r="G244" s="19"/>
       <c r="H244" s="58"/>
-      <c r="I244" s="68"/>
+      <c r="I244" s="66"/>
       <c r="J244" s="58"/>
       <c r="K244" s="58"/>
       <c r="L244" s="58"/>
@@ -16505,7 +16609,7 @@
       </c>
       <c r="G245" s="19"/>
       <c r="H245" s="58"/>
-      <c r="I245" s="68"/>
+      <c r="I245" s="66"/>
       <c r="J245" s="58"/>
       <c r="K245" s="58"/>
       <c r="L245" s="58"/>
@@ -16527,8 +16631,8 @@
         <v>448</v>
       </c>
       <c r="G246" s="19"/>
-      <c r="H246" s="67"/>
-      <c r="I246" s="68" t="s">
+      <c r="H246" s="65"/>
+      <c r="I246" s="66" t="s">
         <v>467</v>
       </c>
       <c r="J246" s="57"/>
@@ -16549,7 +16653,7 @@
       <c r="F247" s="55"/>
       <c r="G247" s="19"/>
       <c r="H247" s="58"/>
-      <c r="I247" s="68"/>
+      <c r="I247" s="66"/>
       <c r="J247" s="58"/>
       <c r="K247" s="58"/>
       <c r="L247" s="58"/>
@@ -16589,7 +16693,7 @@
       </c>
       <c r="C249" s="57"/>
       <c r="D249" s="57"/>
-      <c r="E249" s="71" t="s">
+      <c r="E249" s="69" t="s">
         <v>452</v>
       </c>
       <c r="F249" s="57" t="s">
@@ -16619,7 +16723,7 @@
       </c>
       <c r="G250" s="19"/>
       <c r="H250" s="58"/>
-      <c r="I250" s="68"/>
+      <c r="I250" s="66"/>
       <c r="J250" s="58"/>
       <c r="K250" s="58"/>
       <c r="L250" s="58"/>
@@ -16638,7 +16742,7 @@
       <c r="F251" s="57"/>
       <c r="G251" s="19"/>
       <c r="H251" s="58"/>
-      <c r="I251" s="68" t="s">
+      <c r="I251" s="66" t="s">
         <v>454</v>
       </c>
       <c r="J251" s="58"/>
@@ -16696,7 +16800,7 @@
       <c r="F253" s="18"/>
       <c r="G253" s="19"/>
       <c r="H253" s="18"/>
-      <c r="I253" s="68" t="s">
+      <c r="I253" s="66" t="s">
         <v>478</v>
       </c>
       <c r="J253" s="58"/>
@@ -16721,7 +16825,7 @@
       </c>
       <c r="G254" s="19"/>
       <c r="H254" s="58"/>
-      <c r="I254" s="68"/>
+      <c r="I254" s="66"/>
       <c r="J254" s="58"/>
       <c r="K254" s="58"/>
       <c r="L254" s="58"/>
@@ -16738,7 +16842,7 @@
       <c r="F255" s="57"/>
       <c r="G255" s="19"/>
       <c r="H255" s="58"/>
-      <c r="I255" s="68" t="s">
+      <c r="I255" s="66" t="s">
         <v>480</v>
       </c>
       <c r="J255" s="57"/>
@@ -16765,7 +16869,7 @@
         <v>1</v>
       </c>
       <c r="H256" s="58"/>
-      <c r="I256" s="68" t="s">
+      <c r="I256" s="66" t="s">
         <v>481</v>
       </c>
       <c r="J256" s="57">
@@ -16796,7 +16900,7 @@
       </c>
       <c r="G257" s="19"/>
       <c r="H257" s="58"/>
-      <c r="I257" s="68" t="s">
+      <c r="I257" s="66" t="s">
         <v>485</v>
       </c>
       <c r="J257" s="58"/>
@@ -16821,7 +16925,7 @@
       </c>
       <c r="G258" s="19"/>
       <c r="H258" s="58"/>
-      <c r="I258" s="68"/>
+      <c r="I258" s="66"/>
       <c r="J258" s="58"/>
       <c r="K258" s="58"/>
       <c r="L258" s="58"/>
@@ -16844,7 +16948,7 @@
       </c>
       <c r="G259" s="19"/>
       <c r="H259" s="58"/>
-      <c r="I259" s="68"/>
+      <c r="I259" s="66"/>
       <c r="J259" s="58"/>
       <c r="K259" s="58"/>
       <c r="L259" s="58"/>
@@ -16866,8 +16970,8 @@
         <v>488</v>
       </c>
       <c r="G260" s="19"/>
-      <c r="H260" s="67"/>
-      <c r="I260" s="68"/>
+      <c r="H260" s="65"/>
+      <c r="I260" s="66"/>
       <c r="J260" s="57"/>
       <c r="K260" s="57"/>
       <c r="L260" s="25"/>
@@ -16886,7 +16990,7 @@
       <c r="F261" s="55"/>
       <c r="G261" s="19"/>
       <c r="H261" s="58"/>
-      <c r="I261" s="68"/>
+      <c r="I261" s="66"/>
       <c r="J261" s="58"/>
       <c r="K261" s="58"/>
       <c r="L261" s="58"/>
@@ -16905,7 +17009,7 @@
       <c r="F262" s="55"/>
       <c r="G262" s="19"/>
       <c r="H262" s="58"/>
-      <c r="I262" s="68"/>
+      <c r="I262" s="66"/>
       <c r="J262" s="58"/>
       <c r="K262" s="58"/>
       <c r="L262" s="58"/>
@@ -16920,7 +17024,7 @@
       </c>
       <c r="C263" s="57"/>
       <c r="D263" s="57"/>
-      <c r="E263" s="71" t="s">
+      <c r="E263" s="69" t="s">
         <v>489</v>
       </c>
       <c r="F263" s="57" t="s">
@@ -16973,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="H265" s="58"/>
-      <c r="I265" s="68"/>
+      <c r="I265" s="66"/>
       <c r="J265" s="57">
         <v>1475</v>
       </c>
@@ -17035,7 +17139,7 @@
       <c r="F267" s="18"/>
       <c r="G267" s="19"/>
       <c r="H267" s="18"/>
-      <c r="I267" s="68" t="s">
+      <c r="I267" s="66" t="s">
         <v>500</v>
       </c>
       <c r="J267" s="58"/>
@@ -17060,8 +17164,8 @@
       </c>
       <c r="G268" s="19"/>
       <c r="H268" s="58"/>
-      <c r="I268" s="68"/>
-      <c r="J268" s="72"/>
+      <c r="I268" s="66"/>
+      <c r="J268" s="70"/>
       <c r="K268" s="58"/>
       <c r="L268" s="58"/>
       <c r="M268" s="58"/>
@@ -17070,692 +17174,590 @@
       <c r="A269" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B269" s="73">
+      <c r="B269" s="71">
         <v>46303</v>
       </c>
-      <c r="C269" s="74"/>
-      <c r="D269" s="74"/>
+      <c r="C269" s="72"/>
+      <c r="D269" s="72"/>
       <c r="E269" s="57"/>
-      <c r="F269" s="74"/>
+      <c r="F269" s="72"/>
       <c r="G269" s="57">
         <v>0</v>
       </c>
-      <c r="H269" s="74"/>
-      <c r="I269" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 8 códigos del tramo Loja - Catamayo. Las 21 limpiadas de julio ya superan los códigos del tramo (13 sin código en la fila del 07/07), por eso 0 adicionales. Km ya cubiertos en julio.</t>
-        </is>
-      </c>
-      <c r="J269" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3861, 3876, 3965, 3994, 3996, 4036, 4095, 4252</t>
-        </is>
+      <c r="H269" s="72"/>
+      <c r="I269" s="77" t="s">
+        <v>514</v>
+      </c>
+      <c r="J269" s="62" t="s">
+        <v>515</v>
       </c>
       <c r="K269" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L269" s="74"/>
-      <c r="M269" s="74"/>
-      <c r="N269" s="75"/>
+      <c r="L269" s="72"/>
+      <c r="M269" s="72"/>
+      <c r="N269" s="73"/>
     </row>
     <row r="270" spans="1:14" ht="141" customHeight="1">
       <c r="A270" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B270" s="73">
+      <c r="B270" s="71">
         <v>46303</v>
       </c>
-      <c r="C270" s="74"/>
-      <c r="D270" s="74"/>
-      <c r="E270" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13+256</t>
-        </is>
-      </c>
-      <c r="F270" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38+100</t>
-        </is>
+      <c r="C270" s="72"/>
+      <c r="D270" s="72"/>
+      <c r="E270" s="57" t="s">
+        <v>516</v>
+      </c>
+      <c r="F270" s="57" t="s">
+        <v>517</v>
       </c>
       <c r="G270" s="57">
         <v>9</v>
       </c>
-      <c r="H270" s="74"/>
-      <c r="I270" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 11 códigos del tramo Oña - Saraguro; total micro 25 alcantarillas (16 julio + 9 consolidado). Km nuevos 24.84 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 38.1 km). Se agregaron 4388, 4373 (del tramo, estaban en julio en otra micro).</t>
-        </is>
-      </c>
-      <c r="J270" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18, 341, 4324, 4340, 4368, 4517, 4565, 4638, 4710, 4388, 4373</t>
-        </is>
+      <c r="H270" s="72"/>
+      <c r="I270" s="77" t="s">
+        <v>518</v>
+      </c>
+      <c r="J270" s="62" t="s">
+        <v>519</v>
       </c>
       <c r="K270" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L270" s="74"/>
-      <c r="M270" s="74"/>
-      <c r="N270" s="75"/>
+      <c r="L270" s="72"/>
+      <c r="M270" s="72"/>
+      <c r="N270" s="73"/>
     </row>
     <row r="271" spans="1:14" ht="141" customHeight="1">
       <c r="A271" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B271" s="73">
+      <c r="B271" s="71">
         <v>46303</v>
       </c>
-      <c r="C271" s="74"/>
-      <c r="D271" s="74"/>
-      <c r="E271" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3+620</t>
-        </is>
-      </c>
-      <c r="F271" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28+300</t>
-        </is>
+      <c r="C271" s="72"/>
+      <c r="D271" s="72"/>
+      <c r="E271" s="57" t="s">
+        <v>520</v>
+      </c>
+      <c r="F271" s="57" t="s">
+        <v>521</v>
       </c>
       <c r="G271" s="57">
         <v>53</v>
       </c>
-      <c r="H271" s="74"/>
-      <c r="I271" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 54 códigos del tramo San Pedro de la Bendita - Velacruz; total micro 54 alcantarillas (1 julio + 53 consolidado). Km nuevos 24.68 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 28.3 km).</t>
-        </is>
-      </c>
-      <c r="J271" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7, 10, 3437, 3447, 3448, 3449, 3450, 3451, 3452, 3453, 3468, 3472, 3474, 3475, 3477, 3483, 3486, 3488, 3505, 3512, 3517, 3526, 3531, 3539, 3541, 3543, 3547, 3549, 3553, 3560, 3565, 3566, 3567, 3579, 3583, 3584, 3590, 3594, 3595, 3597, 3599, 3604, 3605, 3607, 3608, 3612, 3621, 3629, 3638, 3639, 3643, 3647, 3662, 3666</t>
-        </is>
+      <c r="H271" s="72"/>
+      <c r="I271" s="77" t="s">
+        <v>522</v>
+      </c>
+      <c r="J271" s="62" t="s">
+        <v>502</v>
       </c>
       <c r="K271" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L271" s="74"/>
-      <c r="M271" s="74"/>
-      <c r="N271" s="75"/>
+      <c r="L271" s="72"/>
+      <c r="M271" s="72"/>
+      <c r="N271" s="73"/>
     </row>
     <row r="272" spans="1:14" ht="141" customHeight="1">
       <c r="A272" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B272" s="73">
+      <c r="B272" s="71">
         <v>46303</v>
       </c>
-      <c r="C272" s="74"/>
-      <c r="D272" s="74"/>
-      <c r="E272" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10+500</t>
-        </is>
-      </c>
-      <c r="F272" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29+400</t>
-        </is>
-      </c>
-      <c r="G272" s="76">
+      <c r="C272" s="72"/>
+      <c r="D272" s="72"/>
+      <c r="E272" s="57" t="s">
+        <v>486</v>
+      </c>
+      <c r="F272" s="72" t="s">
+        <v>523</v>
+      </c>
+      <c r="G272" s="74">
         <v>5</v>
       </c>
-      <c r="H272" s="74"/>
-      <c r="I272" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 7 códigos del tramo Catamayo - Gonzanamá; total micro 7 alcantarillas (2 julio + 5 consolidado). Km nuevos 18.90 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 29.4 km).</t>
-        </is>
-      </c>
-      <c r="J272" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3656, 3692, 3724, 3764, 3772, 3809, 3850</t>
-        </is>
+      <c r="H272" s="72"/>
+      <c r="I272" s="77" t="s">
+        <v>524</v>
+      </c>
+      <c r="J272" s="62" t="s">
+        <v>503</v>
       </c>
       <c r="K272" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L272" s="74"/>
-      <c r="M272" s="74"/>
-      <c r="N272" s="75"/>
+      <c r="L272" s="72"/>
+      <c r="M272" s="72"/>
+      <c r="N272" s="73"/>
     </row>
     <row r="273" spans="1:14" ht="141" customHeight="1">
       <c r="A273" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B273" s="73">
+      <c r="B273" s="71">
         <v>46303</v>
       </c>
-      <c r="C273" s="74"/>
-      <c r="D273" s="74"/>
+      <c r="C273" s="72"/>
+      <c r="D273" s="72"/>
       <c r="E273" s="57"/>
-      <c r="F273" s="74"/>
+      <c r="F273" s="72"/>
       <c r="G273" s="57">
         <v>104</v>
       </c>
-      <c r="H273" s="74"/>
-      <c r="I273" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 104 códigos del tramo Catacocha - El Empalme; total micro 104 alcantarillas (0 julio + 104 consolidado). Sin km adicionales: las filas de julio ya suman 34.7 km (tramo 32.9 km).</t>
-        </is>
-      </c>
-      <c r="J273" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1746, 1790, 1799, 1810, 1816, 1820, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1906, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2032, 2045, 2054, 2059, 2133, 2166, 2193, 2202, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2359, 2364, 2372, 2382, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2649, 2671, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
-        </is>
+      <c r="H273" s="72"/>
+      <c r="I273" s="77" t="s">
+        <v>525</v>
+      </c>
+      <c r="J273" s="62" t="s">
+        <v>504</v>
       </c>
       <c r="K273" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L273" s="74"/>
-      <c r="M273" s="74"/>
-      <c r="N273" s="75"/>
+      <c r="L273" s="72"/>
+      <c r="M273" s="72"/>
+      <c r="N273" s="73"/>
     </row>
     <row r="274" spans="1:14" ht="141" customHeight="1">
       <c r="A274" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B274" s="73">
+      <c r="B274" s="71">
         <v>46303</v>
       </c>
-      <c r="C274" s="74"/>
-      <c r="D274" s="74">
+      <c r="C274" s="72"/>
+      <c r="D274" s="72">
         <v>214</v>
       </c>
-      <c r="E274" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24+414</t>
-        </is>
-      </c>
-      <c r="F274" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42+000</t>
-        </is>
+      <c r="E274" s="57" t="s">
+        <v>526</v>
+      </c>
+      <c r="F274" s="57" t="s">
+        <v>527</v>
       </c>
       <c r="G274" s="57">
         <v>134</v>
       </c>
-      <c r="H274" s="74"/>
-      <c r="I274" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 138 códigos del tramo San Lucas - Loja; total micro 155 alcantarillas (21 julio + 134 consolidado). Km nuevos 17.59 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 42 km). Se quitaron 17 códigos repetidos con julio.</t>
-        </is>
-      </c>
-      <c r="J274" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3, 15, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3914, 3915, 3917, 3918, 3920, 3923, 3925, 3928, 3929, 3931, 3933, 3934, 3937, 3938, 3939, 3940, 3943, 3944, 3946, 3947, 3951, 3953, 3961, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4029, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4201, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4230, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
-        </is>
+      <c r="H274" s="72"/>
+      <c r="I274" s="77" t="s">
+        <v>528</v>
+      </c>
+      <c r="J274" s="62" t="s">
+        <v>529</v>
       </c>
       <c r="K274" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L274" s="74"/>
-      <c r="M274" s="74"/>
-      <c r="N274" s="75"/>
+      <c r="L274" s="72"/>
+      <c r="M274" s="72"/>
+      <c r="N274" s="73"/>
     </row>
     <row r="275" spans="1:14" ht="141" customHeight="1">
       <c r="A275" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="B275" s="73">
+      <c r="B275" s="71">
         <v>46303</v>
       </c>
-      <c r="C275" s="74"/>
-      <c r="D275" s="74"/>
-      <c r="E275" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0+000</t>
-        </is>
-      </c>
-      <c r="F275" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5+000</t>
-        </is>
+      <c r="C275" s="72"/>
+      <c r="D275" s="72"/>
+      <c r="E275" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="F275" s="57" t="s">
+        <v>183</v>
       </c>
       <c r="G275" s="57">
         <v>20</v>
       </c>
-      <c r="H275" s="74"/>
-      <c r="I275" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 20 códigos del tramo Redondel de Carigán - Capulí; total micro 20 alcantarillas (0 julio + 20 consolidado).</t>
-        </is>
-      </c>
-      <c r="J275" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000, 10002, 10005, 10006, 10007, 10008, 10009, 10010, 10013, 10014, 10015, 10016, 10019, 10021, 10022, 10024, 10026, 10028, 10031, 10032</t>
-        </is>
+      <c r="H275" s="72"/>
+      <c r="I275" s="77" t="s">
+        <v>530</v>
+      </c>
+      <c r="J275" s="62" t="s">
+        <v>505</v>
       </c>
       <c r="K275" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L275" s="74"/>
-      <c r="M275" s="74"/>
-      <c r="N275" s="75"/>
+      <c r="L275" s="72"/>
+      <c r="M275" s="72"/>
+      <c r="N275" s="73"/>
     </row>
     <row r="276" spans="1:14" ht="141" customHeight="1">
       <c r="A276" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B276" s="73">
+      <c r="B276" s="71">
         <v>46303</v>
       </c>
-      <c r="C276" s="74"/>
-      <c r="D276" s="74"/>
-      <c r="E276" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0+000</t>
-        </is>
-      </c>
-      <c r="F276" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19+529</t>
-        </is>
+      <c r="C276" s="72"/>
+      <c r="D276" s="72"/>
+      <c r="E276" s="55" t="s">
+        <v>284</v>
+      </c>
+      <c r="F276" s="72" t="s">
+        <v>531</v>
       </c>
       <c r="G276" s="57">
         <v>76</v>
       </c>
-      <c r="H276" s="74"/>
-      <c r="I276" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 76 códigos del tramo Loja - Vilcabamba; total micro 76 alcantarillas (0 julio + 76 consolidado). Km nuevos 19.53 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39.5 km).</t>
-        </is>
-      </c>
-      <c r="J276" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333, 335, 4238, 4240, 4255, 4269, 4272, 4274, 4276, 4283, 4289, 4290, 4295, 4298, 4302, 4303, 4311, 4312, 4316, 4327, 4330, 4336, 4341, 4345, 4350, 4352, 4353, 4370, 4375, 4387, 4393, 4394, 4395, 4400, 4406, 4421, 4422, 4433, 4435, 4436, 4437, 4440, 4443, 4444, 4449, 4454, 4456, 4458, 4459, 4460, 4461, 4464, 4466, 4467, 4471, 4474, 4478, 4481, 4484, 4487, 4491, 4492, 4498, 4508, 4510, 4522, 4524, 4531, 4533, 4536, 4540, 4544, 4545, 4548, 4549, 4552</t>
-        </is>
+      <c r="H276" s="72"/>
+      <c r="I276" s="77" t="s">
+        <v>532</v>
+      </c>
+      <c r="J276" s="62" t="s">
+        <v>506</v>
       </c>
       <c r="K276" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L276" s="74"/>
-      <c r="M276" s="74"/>
-      <c r="N276" s="75"/>
+      <c r="L276" s="72"/>
+      <c r="M276" s="72"/>
+      <c r="N276" s="73"/>
     </row>
     <row r="277" spans="1:14" ht="141" customHeight="1">
       <c r="A277" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B277" s="73">
+      <c r="B277" s="71">
         <v>46303</v>
       </c>
-      <c r="C277" s="74"/>
-      <c r="D277" s="74"/>
-      <c r="E277" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7+320</t>
-        </is>
-      </c>
-      <c r="F277" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21+400</t>
-        </is>
-      </c>
-      <c r="G277" s="76">
+      <c r="C277" s="72"/>
+      <c r="D277" s="72"/>
+      <c r="E277" s="57" t="s">
+        <v>533</v>
+      </c>
+      <c r="F277" s="72" t="s">
+        <v>534</v>
+      </c>
+      <c r="G277" s="74">
         <v>39</v>
       </c>
-      <c r="H277" s="74"/>
-      <c r="I277" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 39 códigos del tramo Célica - El Empalme; total micro 39 alcantarillas (0 julio + 39 consolidado). Km nuevos 14.08 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 21.4 km). Se agregaron 1660 (del tramo, estaban en julio en otra micro).</t>
-        </is>
-      </c>
-      <c r="J277" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1245, 1262, 1268, 1289, 1290, 1296, 1297, 1304, 1307, 1314, 1325, 1332, 1342, 1377, 1392, 1393, 1397, 1404, 1405, 1407, 1408, 1413, 1416, 1423, 1424, 1427, 1436, 1440, 1456, 1466, 1472, 1496, 1499, 1526, 1532, 1537, 1553, 1632, 1660</t>
-        </is>
+      <c r="H277" s="72"/>
+      <c r="I277" s="77" t="s">
+        <v>535</v>
+      </c>
+      <c r="J277" s="62" t="s">
+        <v>536</v>
       </c>
       <c r="K277" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L277" s="74"/>
-      <c r="M277" s="74"/>
-      <c r="N277" s="75"/>
+      <c r="L277" s="72"/>
+      <c r="M277" s="72"/>
+      <c r="N277" s="73"/>
     </row>
     <row r="278" spans="1:14" ht="141" customHeight="1">
       <c r="A278" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B278" s="73">
+      <c r="B278" s="71">
         <v>46303</v>
       </c>
-      <c r="C278" s="74"/>
-      <c r="D278" s="74"/>
+      <c r="C278" s="72"/>
+      <c r="D278" s="72"/>
       <c r="E278" s="55"/>
-      <c r="F278" s="74"/>
-      <c r="G278" s="76">
+      <c r="F278" s="72"/>
+      <c r="G278" s="74">
         <v>19</v>
       </c>
-      <c r="H278" s="74"/>
-      <c r="I278" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 19 códigos del tramo Cariamanga - Sozoranga; total micro 19 alcantarillas (0 julio + 19 consolidado). Sin km adicionales: las filas de julio ya suman 43.49 km (tramo 46.3 km).</t>
-        </is>
-      </c>
-      <c r="J278" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2186, 2194, 2198, 2212, 2219, 2225, 2241, 2244, 2417, 2450, 2462, 2536, 2758, 2797, 2803, 2813, 2934, 3416, 3428</t>
-        </is>
+      <c r="H278" s="72"/>
+      <c r="I278" s="77" t="s">
+        <v>537</v>
+      </c>
+      <c r="J278" s="62" t="s">
+        <v>507</v>
       </c>
       <c r="K278" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L278" s="74"/>
-      <c r="M278" s="74"/>
-      <c r="N278" s="75"/>
+      <c r="L278" s="72"/>
+      <c r="M278" s="72"/>
+      <c r="N278" s="73"/>
     </row>
     <row r="279" spans="1:14" ht="141" customHeight="1">
       <c r="A279" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B279" s="73">
+      <c r="B279" s="71">
         <v>46303</v>
       </c>
-      <c r="C279" s="74"/>
-      <c r="D279" s="74"/>
-      <c r="E279" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7+000</t>
-        </is>
-      </c>
-      <c r="F279" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21+000</t>
-        </is>
-      </c>
-      <c r="G279" s="76">
+      <c r="C279" s="72"/>
+      <c r="D279" s="72"/>
+      <c r="E279" s="57" t="s">
+        <v>538</v>
+      </c>
+      <c r="F279" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="G279" s="74">
         <v>12</v>
       </c>
-      <c r="H279" s="74"/>
-      <c r="I279" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 18 códigos del tramo El Empalme - Macará; total micro 19 alcantarillas (7 julio + 12 consolidado). Km nuevos 14.00 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39.6 km).</t>
-        </is>
-      </c>
-      <c r="J279" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1271, 1273, 1276, 1279, 1280, 1339, 1362, 1363, 1371, 1420, 1449, 1479, 1560, 1598, 1603, 1606, 1611, 1625</t>
-        </is>
+      <c r="H279" s="72"/>
+      <c r="I279" s="77" t="s">
+        <v>539</v>
+      </c>
+      <c r="J279" s="62" t="s">
+        <v>508</v>
       </c>
       <c r="K279" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L279" s="74"/>
-      <c r="M279" s="74"/>
-      <c r="N279" s="75"/>
+      <c r="L279" s="72"/>
+      <c r="M279" s="72"/>
+      <c r="N279" s="73"/>
     </row>
     <row r="280" spans="1:14" ht="141" customHeight="1">
       <c r="A280" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B280" s="73">
+      <c r="B280" s="71">
         <v>46303</v>
       </c>
-      <c r="C280" s="74"/>
-      <c r="D280" s="74"/>
+      <c r="C280" s="72"/>
+      <c r="D280" s="72"/>
       <c r="E280" s="55"/>
       <c r="F280" s="57"/>
       <c r="G280" s="57">
         <v>58</v>
       </c>
-      <c r="H280" s="74">
-        <v>32.2</v>
-      </c>
-      <c r="I280" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 69 códigos del tramo Río Pindo - Chaguarpamba; total micro 104 alcantarillas (46 julio + 58 consolidado). Sin km adicionales: las filas de julio ya suman 64.05 km (tramo 32.2 km). Se quitaron 35 códigos repetidos con julio.</t>
-        </is>
-      </c>
-      <c r="J280" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288, 2173, 2181, 2206, 2215, 2276, 2281, 2288, 2305, 2317, 2332, 2354, 2355, 2361, 2367, 2368, 2385, 2389, 2395, 2408, 2428, 2440, 2445, 2446, 2452, 2468, 2469, 2475, 2479, 2484, 2495, 2577, 2578, 2605, 2615, 2617, 2628, 2636, 2640, 2647, 2651, 2653, 2654, 2657, 2661, 2665, 2676, 2677, 2692, 2701, 2714, 2745, 2755, 2764, 2772, 2835, 2850, 2870, 2894, 2898, 2941, 3015, 3031, 3064, 3081, 3097, 3104, 3108, 3112</t>
-        </is>
+      <c r="H280" s="72">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="I280" s="77" t="s">
+        <v>540</v>
+      </c>
+      <c r="J280" s="62" t="s">
+        <v>541</v>
       </c>
       <c r="K280" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L280" s="74"/>
-      <c r="M280" s="74"/>
-      <c r="N280" s="75"/>
+      <c r="L280" s="72"/>
+      <c r="M280" s="72"/>
+      <c r="N280" s="73"/>
     </row>
     <row r="281" spans="1:14" ht="141" customHeight="1">
       <c r="A281" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B281" s="73">
+      <c r="B281" s="71">
         <v>46303</v>
       </c>
-      <c r="C281" s="74"/>
-      <c r="D281" s="74"/>
-      <c r="E281" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2+000</t>
-        </is>
-      </c>
-      <c r="F281" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9+000</t>
-        </is>
-      </c>
-      <c r="G281" s="76">
+      <c r="C281" s="72"/>
+      <c r="D281" s="72"/>
+      <c r="E281" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F281" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="G281" s="74">
         <v>10</v>
       </c>
-      <c r="H281" s="74">
-        <v>33.2</v>
-      </c>
-      <c r="I281" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 11 códigos del tramo Sozoranga - Macará; total micro 11 alcantarillas (1 julio + 10 consolidado). Km nuevos 7.00 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 33.2 km).</t>
-        </is>
-      </c>
-      <c r="J281" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1394, 1845, 2042, 2047, 2052, 2060, 2063, 2087, 2112, 2113, 2144</t>
-        </is>
+      <c r="H281" s="72">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="I281" s="77" t="s">
+        <v>542</v>
+      </c>
+      <c r="J281" s="62" t="s">
+        <v>509</v>
       </c>
       <c r="K281" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L281" s="74"/>
-      <c r="M281" s="74"/>
-      <c r="N281" s="75"/>
+      <c r="L281" s="72"/>
+      <c r="M281" s="72"/>
+      <c r="N281" s="73"/>
     </row>
     <row r="282" spans="1:14" ht="141" customHeight="1">
       <c r="A282" s="23" t="s">
-        <v>520</v>
-      </c>
-      <c r="B282" s="73">
+        <v>511</v>
+      </c>
+      <c r="B282" s="71">
         <v>46303</v>
       </c>
-      <c r="C282" s="74"/>
-      <c r="D282" s="74"/>
-      <c r="E282" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0+000</t>
-        </is>
-      </c>
-      <c r="F282" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10+100</t>
-        </is>
-      </c>
-      <c r="G282" s="76"/>
-      <c r="H282" s="74"/>
-      <c r="I282" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: sin códigos de alcantarillas registrados para el tramo; se conservan las abscisas del usuario.</t>
-        </is>
-      </c>
-      <c r="J282" s="63"/>
+      <c r="C282" s="72"/>
+      <c r="D282" s="72"/>
+      <c r="E282" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="F282" s="72" t="s">
+        <v>512</v>
+      </c>
+      <c r="G282" s="74"/>
+      <c r="H282" s="72"/>
+      <c r="I282" s="77" t="s">
+        <v>543</v>
+      </c>
+      <c r="J282" s="62"/>
       <c r="K282" s="18"/>
-      <c r="L282" s="74"/>
-      <c r="M282" s="74"/>
-      <c r="N282" s="75"/>
+      <c r="L282" s="72"/>
+      <c r="M282" s="72"/>
+      <c r="N282" s="73"/>
     </row>
     <row r="283" spans="1:14" ht="141" customHeight="1">
       <c r="A283" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B283" s="73">
+      <c r="B283" s="71">
         <v>46303</v>
       </c>
-      <c r="C283" s="74"/>
-      <c r="D283" s="74"/>
-      <c r="E283" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20+930</t>
-        </is>
-      </c>
-      <c r="F283" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39+000</t>
-        </is>
+      <c r="C283" s="72"/>
+      <c r="D283" s="72"/>
+      <c r="E283" s="57" t="s">
+        <v>544</v>
+      </c>
+      <c r="F283" s="72" t="s">
+        <v>545</v>
       </c>
       <c r="G283" s="57">
         <v>63</v>
       </c>
-      <c r="H283" s="74"/>
-      <c r="I283" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consolidado 08/10: 107 códigos del tramo Y de Alamor - Pindal - Zapotillo; total micro 107 alcantarillas (44 julio + 63 consolidado). Km nuevos 18.07 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39 km).</t>
-        </is>
-      </c>
-      <c r="J283" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80, 105, 522, 569, 571, 575, 577, 578, 579, 580, 581, 583, 584, 586, 590, 593, 595, 596, 600, 601, 602, 603, 604, 605, 606, 610, 614, 615, 616, 617, 618, 623, 625, 628, 632, 633, 634, 636, 639, 640, 642, 643, 644, 645, 646, 647, 648, 649, 650, 653, 654, 656, 660, 661, 664, 666, 670, 671, 673, 675, 677, 680, 682, 683, 686, 687, 690, 696, 705, 707, 711, 721, 729, 730, 731, 732, 745, 755, 758, 760, 761, 770, 772, 777, 779, 782, 784, 791, 803, 807, 813, 816, 821, 824, 837, 839, 861, 863, 864, 867, 868, 879, 882, 903, 943, 944, 949</t>
-        </is>
+      <c r="H283" s="72"/>
+      <c r="I283" s="77" t="s">
+        <v>546</v>
+      </c>
+      <c r="J283" s="62" t="s">
+        <v>510</v>
       </c>
       <c r="K283" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L283" s="74"/>
-      <c r="M283" s="74"/>
-      <c r="N283" s="75"/>
+      <c r="L283" s="72"/>
+      <c r="M283" s="72"/>
+      <c r="N283" s="73"/>
     </row>
     <row r="284" spans="1:14" ht="15" customHeight="1">
-      <c r="A284" s="75"/>
-      <c r="B284" s="75"/>
-      <c r="C284" s="75"/>
-      <c r="D284" s="75"/>
-      <c r="E284" s="75"/>
-      <c r="F284" s="75"/>
-      <c r="G284" s="77"/>
-      <c r="H284" s="75"/>
-      <c r="I284" s="75"/>
-      <c r="J284" s="75"/>
-      <c r="K284" s="75"/>
-      <c r="L284" s="75"/>
-      <c r="M284" s="75"/>
-      <c r="N284" s="75"/>
+      <c r="A284" s="73"/>
+      <c r="B284" s="73"/>
+      <c r="C284" s="73"/>
+      <c r="D284" s="73"/>
+      <c r="E284" s="73"/>
+      <c r="F284" s="73"/>
+      <c r="G284" s="75"/>
+      <c r="H284" s="73"/>
+      <c r="I284" s="88"/>
+      <c r="J284" s="73"/>
+      <c r="K284" s="73"/>
+      <c r="L284" s="73"/>
+      <c r="M284" s="73"/>
+      <c r="N284" s="73"/>
     </row>
     <row r="285" spans="1:14" ht="15" customHeight="1">
-      <c r="A285" s="75"/>
-      <c r="B285" s="75"/>
-      <c r="C285" s="75"/>
-      <c r="D285" s="75"/>
-      <c r="E285" s="75"/>
-      <c r="F285" s="75"/>
-      <c r="G285" s="77"/>
-      <c r="H285" s="75"/>
-      <c r="I285" s="75"/>
-      <c r="J285" s="75"/>
-      <c r="K285" s="75"/>
-      <c r="L285" s="75"/>
-      <c r="M285" s="75"/>
-      <c r="N285" s="75"/>
+      <c r="A285" s="73"/>
+      <c r="B285" s="73"/>
+      <c r="C285" s="73"/>
+      <c r="D285" s="73"/>
+      <c r="E285" s="73"/>
+      <c r="F285" s="73"/>
+      <c r="G285" s="75"/>
+      <c r="H285" s="73"/>
+      <c r="I285" s="88"/>
+      <c r="J285" s="73"/>
+      <c r="K285" s="73"/>
+      <c r="L285" s="73"/>
+      <c r="M285" s="73"/>
+      <c r="N285" s="73"/>
     </row>
     <row r="286" spans="1:14">
-      <c r="G286" s="78"/>
+      <c r="G286" s="76"/>
     </row>
     <row r="287" spans="1:14">
-      <c r="G287" s="78"/>
+      <c r="G287" s="76"/>
     </row>
     <row r="288" spans="1:14">
-      <c r="G288" s="78"/>
+      <c r="G288" s="76"/>
     </row>
     <row r="289" spans="7:7">
-      <c r="G289" s="78"/>
+      <c r="G289" s="76"/>
     </row>
     <row r="290" spans="7:7">
-      <c r="G290" s="78"/>
+      <c r="G290" s="76"/>
     </row>
     <row r="291" spans="7:7">
-      <c r="G291" s="78"/>
+      <c r="G291" s="76"/>
     </row>
     <row r="292" spans="7:7">
-      <c r="G292" s="78"/>
+      <c r="G292" s="76"/>
     </row>
     <row r="293" spans="7:7">
-      <c r="G293" s="78"/>
+      <c r="G293" s="76"/>
     </row>
     <row r="294" spans="7:7">
-      <c r="G294" s="78"/>
+      <c r="G294" s="76"/>
     </row>
     <row r="295" spans="7:7">
-      <c r="G295" s="78"/>
+      <c r="G295" s="76"/>
     </row>
     <row r="296" spans="7:7">
-      <c r="G296" s="78"/>
+      <c r="G296" s="76"/>
     </row>
     <row r="297" spans="7:7">
-      <c r="G297" s="78"/>
+      <c r="G297" s="76"/>
     </row>
     <row r="298" spans="7:7">
-      <c r="G298" s="78"/>
+      <c r="G298" s="76"/>
     </row>
     <row r="299" spans="7:7">
-      <c r="G299" s="78"/>
+      <c r="G299" s="76"/>
     </row>
     <row r="300" spans="7:7">
-      <c r="G300" s="78"/>
+      <c r="G300" s="76"/>
     </row>
     <row r="301" spans="7:7">
-      <c r="G301" s="78"/>
+      <c r="G301" s="76"/>
     </row>
     <row r="302" spans="7:7">
-      <c r="G302" s="78"/>
+      <c r="G302" s="76"/>
     </row>
     <row r="303" spans="7:7">
-      <c r="G303" s="78"/>
+      <c r="G303" s="76"/>
     </row>
     <row r="304" spans="7:7">
-      <c r="G304" s="78"/>
+      <c r="G304" s="76"/>
     </row>
     <row r="305" spans="7:7">
-      <c r="G305" s="78"/>
+      <c r="G305" s="76"/>
     </row>
     <row r="306" spans="7:7">
-      <c r="G306" s="78"/>
+      <c r="G306" s="76"/>
     </row>
     <row r="307" spans="7:7">
-      <c r="G307" s="78"/>
+      <c r="G307" s="76"/>
     </row>
     <row r="308" spans="7:7">
-      <c r="G308" s="78"/>
+      <c r="G308" s="76"/>
     </row>
     <row r="309" spans="7:7">
-      <c r="G309" s="78"/>
+      <c r="G309" s="76"/>
     </row>
     <row r="310" spans="7:7">
-      <c r="G310" s="78"/>
+      <c r="G310" s="76"/>
     </row>
     <row r="311" spans="7:7">
-      <c r="G311" s="78"/>
+      <c r="G311" s="76"/>
     </row>
     <row r="312" spans="7:7">
-      <c r="G312" s="78"/>
+      <c r="G312" s="76"/>
     </row>
     <row r="313" spans="7:7">
-      <c r="G313" s="78"/>
+      <c r="G313" s="76"/>
     </row>
     <row r="314" spans="7:7">
-      <c r="G314" s="78"/>
+      <c r="G314" s="76"/>
     </row>
     <row r="315" spans="7:7">
-      <c r="G315" s="78"/>
+      <c r="G315" s="76"/>
     </row>
     <row r="316" spans="7:7">
-      <c r="G316" s="78"/>
+      <c r="G316" s="76"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11880"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTE DIARIO" sheetId="1" r:id="rId1"/>
@@ -1578,9 +1578,6 @@
     <t>7, 10, 3437, 3447, 3448, 3449, 3450, 3451, 3452, 3453, 3468, 3472, 3474, 3475, 3477, 3483, 3486, 3488, 3505, 3512, 3517, 3526, 3531, 3539, 3541, 3543, 3547, 3549, 3553, 3560, 3565, 3566, 3567, 3579, 3583, 3584, 3590, 3594, 3595, 3597, 3599, 3604, 3605, 3607, 3608, 3612, 3621, 3629, 3638, 3639, 3643, 3647, 3662, 3666</t>
   </si>
   <si>
-    <t>3656, 3692, 3724, 3764, 3772, 3809, 3850</t>
-  </si>
-  <si>
     <t>1746, 1790, 1799, 1810, 1816, 1820, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1906, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2032, 2045, 2054, 2059, 2133, 2166, 2193, 2202, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2359, 2364, 2372, 2382, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2649, 2671, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
   </si>
   <si>
@@ -1590,9 +1587,6 @@
     <t>333, 335, 4238, 4240, 4255, 4269, 4272, 4274, 4276, 4283, 4289, 4290, 4295, 4298, 4302, 4303, 4311, 4312, 4316, 4327, 4330, 4336, 4341, 4345, 4350, 4352, 4353, 4370, 4375, 4387, 4393, 4394, 4395, 4400, 4406, 4421, 4422, 4433, 4435, 4436, 4437, 4440, 4443, 4444, 4449, 4454, 4456, 4458, 4459, 4460, 4461, 4464, 4466, 4467, 4471, 4474, 4478, 4481, 4484, 4487, 4491, 4492, 4498, 4508, 4510, 4522, 4524, 4531, 4533, 4536, 4540, 4544, 4545, 4548, 4549, 4552</t>
   </si>
   <si>
-    <t>2186, 2194, 2198, 2212, 2219, 2225, 2241, 2244, 2417, 2450, 2462, 2536, 2758, 2797, 2803, 2813, 2934, 3416, 3428</t>
-  </si>
-  <si>
     <t>1271, 1273, 1276, 1279, 1280, 1339, 1362, 1363, 1371, 1420, 1449, 1479, 1560, 1598, 1603, 1606, 1611, 1625</t>
   </si>
   <si>
@@ -1708,6 +1702,12 @@
   </si>
   <si>
     <t>Consolidado 08/10: 107 códigos del tramo Y de Alamor - Pindal - Zapotillo; total micro 107 alcantarillas (44 julio + 63 consolidado). Km nuevos 18.07 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 39 km).</t>
+  </si>
+  <si>
+    <t>2186, 2194, 2198, 2212, 2219, 2225, 2241, 2244, 2417, 2450, 2462, 2536, 2758, 2797, 2803, 2813, 2934, 3416, 3428, 2237</t>
+  </si>
+  <si>
+    <t>3656, 3692, 3724, 3764, 3772, 3809, 3850, 3855, 3821, 3831, 3801, 3782, 3784</t>
   </si>
 </sst>
 </file>
@@ -1886,7 +1886,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2122,33 +2122,26 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="710">
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="708">
     <dxf>
       <font>
         <b/>
@@ -10880,13 +10873,13 @@
     </row>
     <row r="15" spans="1:17" s="1" customFormat="1" ht="33" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B15" s="15">
         <v>46210</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D15" s="17">
         <v>205</v>
@@ -17186,10 +17179,10 @@
       </c>
       <c r="H269" s="72"/>
       <c r="I269" s="77" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="J269" s="62" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K269" s="18" t="s">
         <v>302</v>
@@ -17208,20 +17201,20 @@
       <c r="C270" s="72"/>
       <c r="D270" s="72"/>
       <c r="E270" s="57" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F270" s="57" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G270" s="57">
         <v>9</v>
       </c>
       <c r="H270" s="72"/>
       <c r="I270" s="77" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J270" s="62" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="K270" s="18" t="s">
         <v>302</v>
@@ -17240,17 +17233,17 @@
       <c r="C271" s="72"/>
       <c r="D271" s="72"/>
       <c r="E271" s="57" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F271" s="57" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G271" s="57">
         <v>53</v>
       </c>
       <c r="H271" s="72"/>
       <c r="I271" s="77" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J271" s="62" t="s">
         <v>502</v>
@@ -17262,37 +17255,37 @@
       <c r="M271" s="72"/>
       <c r="N271" s="73"/>
     </row>
-    <row r="272" spans="1:14" ht="141" customHeight="1">
+    <row r="272" spans="1:14" s="93" customFormat="1" ht="141" customHeight="1">
       <c r="A272" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B272" s="71">
+      <c r="B272" s="90">
         <v>46303</v>
       </c>
-      <c r="C272" s="72"/>
-      <c r="D272" s="72"/>
+      <c r="C272" s="23"/>
+      <c r="D272" s="23"/>
       <c r="E272" s="57" t="s">
         <v>486</v>
       </c>
-      <c r="F272" s="72" t="s">
-        <v>523</v>
-      </c>
-      <c r="G272" s="74">
-        <v>5</v>
-      </c>
-      <c r="H272" s="72"/>
-      <c r="I272" s="77" t="s">
-        <v>524</v>
+      <c r="F272" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="G272" s="89">
+        <v>11</v>
+      </c>
+      <c r="H272" s="23"/>
+      <c r="I272" s="91" t="s">
+        <v>522</v>
       </c>
       <c r="J272" s="62" t="s">
-        <v>503</v>
+        <v>546</v>
       </c>
       <c r="K272" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="L272" s="72"/>
-      <c r="M272" s="72"/>
-      <c r="N272" s="73"/>
+      <c r="L272" s="23"/>
+      <c r="M272" s="23"/>
+      <c r="N272" s="92"/>
     </row>
     <row r="273" spans="1:14" ht="141" customHeight="1">
       <c r="A273" s="23" t="s">
@@ -17310,10 +17303,10 @@
       </c>
       <c r="H273" s="72"/>
       <c r="I273" s="77" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J273" s="62" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K273" s="18" t="s">
         <v>302</v>
@@ -17334,20 +17327,20 @@
         <v>214</v>
       </c>
       <c r="E274" s="57" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F274" s="57" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G274" s="57">
         <v>134</v>
       </c>
       <c r="H274" s="72"/>
       <c r="I274" s="77" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J274" s="62" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K274" s="18" t="s">
         <v>302</v>
@@ -17376,10 +17369,10 @@
       </c>
       <c r="H275" s="72"/>
       <c r="I275" s="77" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J275" s="62" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K275" s="18" t="s">
         <v>302</v>
@@ -17401,17 +17394,17 @@
         <v>284</v>
       </c>
       <c r="F276" s="72" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G276" s="57">
         <v>76</v>
       </c>
       <c r="H276" s="72"/>
       <c r="I276" s="77" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J276" s="62" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K276" s="18" t="s">
         <v>302</v>
@@ -17430,20 +17423,20 @@
       <c r="C277" s="72"/>
       <c r="D277" s="72"/>
       <c r="E277" s="57" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F277" s="72" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G277" s="74">
         <v>39</v>
       </c>
       <c r="H277" s="72"/>
       <c r="I277" s="77" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="J277" s="62" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K277" s="18" t="s">
         <v>302</v>
@@ -17464,14 +17457,14 @@
       <c r="E278" s="55"/>
       <c r="F278" s="72"/>
       <c r="G278" s="74">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H278" s="72"/>
       <c r="I278" s="77" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="J278" s="62" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="K278" s="18" t="s">
         <v>302</v>
@@ -17490,7 +17483,7 @@
       <c r="C279" s="72"/>
       <c r="D279" s="72"/>
       <c r="E279" s="57" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F279" s="72" t="s">
         <v>119</v>
@@ -17500,10 +17493,10 @@
       </c>
       <c r="H279" s="72"/>
       <c r="I279" s="77" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="J279" s="62" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K279" s="18" t="s">
         <v>302</v>
@@ -17530,10 +17523,10 @@
         <v>32.200000000000003</v>
       </c>
       <c r="I280" s="77" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J280" s="62" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K280" s="18" t="s">
         <v>302</v>
@@ -17564,10 +17557,10 @@
         <v>33.200000000000003</v>
       </c>
       <c r="I281" s="77" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J281" s="62" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K281" s="18" t="s">
         <v>302</v>
@@ -17578,7 +17571,7 @@
     </row>
     <row r="282" spans="1:14" ht="141" customHeight="1">
       <c r="A282" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B282" s="71">
         <v>46303</v>
@@ -17589,12 +17582,12 @@
         <v>284</v>
       </c>
       <c r="F282" s="72" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G282" s="74"/>
       <c r="H282" s="72"/>
       <c r="I282" s="77" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J282" s="62"/>
       <c r="K282" s="18"/>
@@ -17612,20 +17605,20 @@
       <c r="C283" s="72"/>
       <c r="D283" s="72"/>
       <c r="E283" s="57" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F283" s="72" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G283" s="57">
         <v>63</v>
       </c>
       <c r="H283" s="72"/>
       <c r="I283" s="77" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J283" s="62" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K283" s="18" t="s">
         <v>302</v>
@@ -17797,7 +17790,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>M37 J39:M39 K22:M22 J32:M33 A30:A42 L59:M59 L68:M68 A72 L70:M71 A1:A14 E73:F73 A44:A56 A58:A70 L74:M74 L84:M85 L97:M97 J97:J98 M143 M148 J143:K143 C198:D198 H74:J74 H75:M83 H72:M73 H69:M69 H68:J68 H60:M67 H59:J59 H34:M36 H39 H38:M38 H37:K37 H22 H23:J23 H32:H33 H1:M21 G34:G42 C1:G30 G58:G70 A286:M1048576 F198:G198 G44:G56 B4:B14 H24:M30 H40:M58 H70:J71 C32:F72 A86 H84:J85 C74:F86 A100 M98 M88 J93:M94 H97:H98 H93:H94 H88:K88 H89:M92 H95:M96 H86:M87 G72:G98 H99:M101 C88:F100 A114 J113:M113 J112 M112 J111:M111 M102 J107:M108 J103:M103 H103 H107:H108 H102:K102 H104:M106 H109:M110 H114:M114 G101:G112 H111:H113 C102:F114 A128 J127:M127 J126 M126 M116 J117:M117 J115:M115 J121:M125 H117 H116:K116 H118:M120 H128:M128 H115 G115:G126 H121:H127 C116:F128 A142 J141:M141 J140 M140 M130 J131:M131 J129:M129 J135:M139 J134 M134 J130:K130 H132:M133 H142:M142 H129:H131 G129:G140 H134:H141 C130:F142 A156 J154 M154 J145:M145 J149:M153 J148:K148 J155:M156 J147:M147 H146:M146 H143:H145 G143:G154 C144:F156 A170 J168 M168 J159:M159 J163:M167 J169:M170 J161:M161 H160:M160 H147:H159 G157:G168 M162 J157:K157 J162:K162 C158:F170 A184 J182 M182 J173:M173 J177:M181 J176 J183:M184 J175:M175 H174:M174 H161:H173 G171:G182 M176 J171:K171 C172:F184 A198 J196 M196 J187:M187 J191:M195 J190 J197:M198 C186:F192 J189:M189 C193:D193 F193 C194:F197 H188:M188 H175:H187 M190 J185:K185 A212 J210 M210 J201:M201 J205:M209 J204 J211:M212 C200:F205 J203:M203 C208:F209 C210:D210 C206:D207 F207 H202:M202 H189:H201 M204 J199:K199 C211:F211 F212 A226 J224 M224 J215:M215 J219:M223 J218 J225:M226 C214:F219 J217:M217 C222:F223 C224:D224 C220:D221 F221 H216:M216 H203:H215 M218 J213:K213 C225:F225 F226 A240 J238 M238 J233:M237 J232 J239:M240 C228:F234 C236:F237 C235:D235 F235 C238:D238 J229:M231 M232 J227:K227 C239:F239 F240 A254 J252 M252 J247:M251 J253:M254 C242:F247 C250:F251 C252:D252 J243:M245 C248:D249 F249 M246 J241:K241 J246:K246 C253:F253 F254 A268 J261:M264 J267:M267 C256:F262 C265:F265 C266:D266 J257:M259 J265:J266 M265:M266 C263:D264 F263 K268:M268 M260 J255:K255 J260:K260 C267:F267 F268 H217:H268 A283 E269:E277 B16:B86 A16:A28</xm:sqref>
+          <xm:sqref>M37 J39:M39 K22:M22 J32:M33 A30:A42 L59:M59 L68:M68 A72 L70:M71 A1:A14 E73:F73 A44:A56 A58:A70 L74:M74 L84:M85 L97:M97 J97:J98 M143 M148 J143:K143 C198:D198 H74:J74 H75:M83 H72:M73 H69:M69 H68:J68 H60:M67 H59:J59 H34:M36 H39 H38:M38 H37:K37 H22 H23:J23 H32:H33 H1:M21 G34:G42 C1:G30 G58:G70 A286:M1048576 F198:G198 G44:G56 B4:B14 H24:M30 H40:M58 H70:J71 C32:F72 A86 H84:J85 C74:F86 A100 M98 M88 J93:M94 H97:H98 H93:H94 H88:K88 H89:M92 H95:M96 H86:M87 G72:G98 H99:M101 C88:F100 A114 J113:M113 J112 M112 J111:M111 M102 J107:M108 J103:M103 H103 H107:H108 H102:K102 H104:M106 H109:M110 H114:M114 G101:G112 H111:H113 C102:F114 A128 J127:M127 J126 M126 M116 J117:M117 J115:M115 J121:M125 H117 H116:K116 H118:M120 H128:M128 H115 G115:G126 H121:H127 C116:F128 A142 J141:M141 J140 M140 M130 J131:M131 J129:M129 J135:M139 J134 M134 J130:K130 H132:M133 H142:M142 H129:H131 G129:G140 H134:H141 C130:F142 A156 J154 M154 J145:M145 J149:M153 J148:K148 J155:M156 J147:M147 H146:M146 H143:H145 G143:G154 C144:F156 A170 J168 M168 J159:M159 J163:M167 J169:M170 J161:M161 H160:M160 H147:H159 G157:G168 M162 J157:K157 J162:K162 C158:F170 A184 J182 M182 J173:M173 J177:M181 J176 J183:M184 J175:M175 H174:M174 H161:H173 G171:G182 M176 J171:K171 C172:F184 A198 J196 M196 J187:M187 J191:M195 J190 J197:M198 C186:F192 J189:M189 C193:D193 F193 C194:F197 H188:M188 H175:H187 M190 J185:K185 A212 J210 M210 J201:M201 J205:M209 J204 J211:M212 C200:F205 J203:M203 C208:F209 C210:D210 C206:D207 F207 H202:M202 H189:H201 M204 J199:K199 C211:F211 F212 A226 J224 M224 J215:M215 J219:M223 J218 J225:M226 C214:F219 J217:M217 C222:F223 C224:D224 C220:D221 F221 H216:M216 H203:H215 M218 J213:K213 C225:F225 F226 A240 J238 M238 J233:M237 J232 J239:M240 C228:F234 C236:F237 C235:D235 F235 C238:D238 J229:M231 M232 J227:K227 C239:F239 F240 A254 J252 M252 J247:M251 J253:M254 C242:F247 C250:F251 C252:D252 J243:M245 C248:D249 F249 M246 J241:K241 J246:K246 C253:F253 F254 A268 J261:M264 J267:M267 C256:F262 C265:F265 C266:D266 J257:M259 J265:J266 M265:M266 C263:D264 F263 K268:M268 M260 J255:K255 J260:K260 C267:F267 F268 H217:H268 A283 E269:E277 B16:B86 A16:A28 B1:B2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="167" operator="containsText" id="{FB5F056F-904D-4DF3-806D-9ACBFA00947C}">
@@ -27104,39 +27097,6 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>L23:M23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="99" operator="containsText" id="{21EB51EB-E6CA-4413-9111-5608D974C568}">
-            <xm:f>NOT(ISERROR(SEARCH($A$16,B1)))</xm:f>
-            <xm:f>$A$16</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <bgColor theme="9"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="containsText" priority="100" operator="containsText" id="{A6C58089-A3A9-479D-B7C2-94C3BD84DD91}">
-            <xm:f>NOT(ISERROR(SEARCH($A$2,B1)))</xm:f>
-            <xm:f>$A$2</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B1:B2</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="171" operator="containsText" id="{E4A11A34-F29D-4452-BE29-1C0572F0CCDE}">

--- a/Reporte_Diario.xlsx
+++ b/Reporte_Diario.xlsx
@@ -1578,7 +1578,7 @@
     <t>7, 10, 3437, 3447, 3448, 3449, 3450, 3451, 3452, 3453, 3468, 3472, 3474, 3475, 3477, 3483, 3486, 3488, 3505, 3512, 3517, 3526, 3531, 3539, 3541, 3543, 3547, 3549, 3553, 3560, 3565, 3566, 3567, 3579, 3583, 3584, 3590, 3594, 3595, 3597, 3599, 3604, 3605, 3607, 3608, 3612, 3621, 3629, 3638, 3639, 3643, 3647, 3662, 3666</t>
   </si>
   <si>
-    <t>1746, 1790, 1799, 1810, 1816, 1820, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1906, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2032, 2045, 2054, 2059, 2133, 2166, 2193, 2202, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2359, 2364, 2372, 2382, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2649, 2671, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
+    <t>1746, 1790, 1799, 1810, 1816, 1820, 1848, 1857, 1860, 1866, 1873, 1875, 1878, 1881, 1882, 1883, 1896, 1905, 1906, 1908, 1916, 1918, 1935, 1938, 1941, 1951, 1955, 1966, 1982, 2032, 2045, 2054, 2059, 2133, 2166, 2193, 2202, 2217, 2224, 2236, 2246, 2250, 2258, 2280, 2295, 2303, 2313, 2321, 2333, 2348, 2364, 2372, 2386, 2391, 2398, 2402, 2420, 2432, 2443, 2566, 2574, 2580, 2598, 2608, 2614, 2695, 2698, 2741, 2749, 2750, 2762, 2779, 2794, 2801, 2808, 2816, 2822, 2869, 2875, 2879, 2907, 2919, 2929, 2977, 2990, 2992, 2994, 3018, 3024, 3029, 3032, 3042, 3056, 3057, 3060, 3075, 3078, 3082, 3088, 3094</t>
   </si>
   <si>
     <t>1000, 10002, 10005, 10006, 10007, 10008, 10009, 10010, 10013, 10014, 10015, 10016, 10019, 10021, 10022, 10024, 10026, 10028, 10031, 10032</t>
@@ -1593,7 +1593,7 @@
     <t>1394, 1845, 2042, 2047, 2052, 2060, 2063, 2087, 2112, 2113, 2144</t>
   </si>
   <si>
-    <t>80, 105, 522, 569, 571, 575, 577, 578, 579, 580, 581, 583, 584, 586, 590, 593, 595, 596, 600, 601, 602, 603, 604, 605, 606, 610, 614, 615, 616, 617, 618, 623, 625, 628, 632, 633, 634, 636, 639, 640, 642, 643, 644, 645, 646, 647, 648, 649, 650, 653, 654, 656, 660, 661, 664, 666, 670, 671, 673, 675, 677, 680, 682, 683, 686, 687, 690, 696, 705, 707, 711, 721, 729, 730, 731, 732, 745, 755, 758, 760, 761, 770, 772, 777, 779, 782, 784, 791, 803, 807, 813, 816, 821, 824, 837, 839, 861, 863, 864, 867, 868, 879, 882, 903, 943, 944, 949</t>
+    <t>80, 105, 522, 569, 571, 575, 577, 578, 579, 580, 583, 584, 586, 590, 593, 595, 596, 600, 601, 602, 603, 604, 605, 606, 610, 614, 615, 616, 617, 618, 623, 625, 628, 632, 633, 634, 636, 639, 640, 642, 643, 644, 645, 646, 647, 648, 649, 650, 653, 654, 656, 660, 661, 664, 666, 670, 671, 673, 675, 677, 680, 682, 683, 686, 687, 690, 696, 705, 707, 711, 721, 729, 730, 731, 732, 745, 755, 758, 760, 761, 770, 772, 777, 779, 782, 784, 791, 803, 807, 813, 816, 821, 824, 837, 839, 861, 863, 864, 867, 868, 879, 882, 903, 943, 944</t>
   </si>
   <si>
     <t>Estoraques del Suro</t>
@@ -1650,7 +1650,7 @@
     <t>Consolidado 08/10: 138 códigos del tramo San Lucas - Loja; total micro 155 alcantarillas (21 julio + 134 consolidado). Km nuevos 17.59 (chat del grupo + ubicación de las alcantarillas limpiadas, tope 42 km). Se quitaron 17 códigos repetidos con julio.</t>
   </si>
   <si>
-    <t>3, 15, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3914, 3915, 3917, 3918, 3920, 3923, 3925, 3928, 3929, 3931, 3933, 3934, 3937, 3938, 3939, 3940, 3943, 3944, 3946, 3947, 3951, 3953, 3961, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4029, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4201, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4230, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
+    <t>3, 15, 305, 306, 308, 310, 311, 313, 315, 316, 317, 319, 321, 324, 325, 327, 3911, 3914, 3915, 3917, 3918, 3920, 3923, 3925, 3928, 3929, 3931, 3933, 3934, 3937, 3938, 3939, 3940, 3943, 3944, 3946, 3947, 3951, 3953, 3961, 3964, 3966, 3969, 3970, 3971, 3972, 3974, 3975, 3977, 3983, 3988, 3997, 3999, 4001, 4008, 4010, 4029, 4032, 4033, 4035, 4037, 4042, 4064, 4071, 4077, 4082, 4083, 4086, 4089, 4092, 4093, 4096, 4099, 4104, 4112, 4123, 4127, 4130, 4134, 4136, 4138, 4140, 4141, 4149, 4152, 4156, 4159, 4165, 4167, 4168, 4169, 4170, 4171, 4174, 4175, 4177, 4178, 4181, 4183, 4184, 4186, 4187, 4188, 4191, 4193, 4194, 4195, 4197, 4199, 4205, 4207, 4211, 4212, 4213, 4214, 4215, 4216, 4217, 4218, 4219, 4220, 4221, 4223, 4227, 4228, 4230, 4232, 4233, 4246, 4251, 4257, 4268, 4305, 4310, 4314, 4322, 4367</t>
   </si>
   <si>
     <t>Consolidado 08/10: 20 códigos del tramo Redondel de Carigán - Capulí; total micro 20 alcantarillas (0 julio + 20 consolidado).</t>
